--- a/artfynd/A 50492-2025 artfynd.xlsx
+++ b/artfynd/A 50492-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129707216</v>
       </c>
       <c r="B2" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129707403</v>
       </c>
       <c r="B3" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,32 +873,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129694842</v>
+        <v>129707440</v>
       </c>
       <c r="B4" t="n">
-        <v>79694</v>
+        <v>92870</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -908,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>431768</v>
+        <v>431828</v>
       </c>
       <c r="R4" t="n">
-        <v>6795469</v>
+        <v>6795476</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -958,22 +958,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129694957</v>
+        <v>129694842</v>
       </c>
       <c r="B5" t="n">
-        <v>78832</v>
+        <v>79695</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -981,21 +981,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1005,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>431725</v>
+        <v>431768</v>
       </c>
       <c r="R5" t="n">
-        <v>6795459</v>
+        <v>6795469</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,10 +1067,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129694862</v>
+        <v>129694957</v>
       </c>
       <c r="B6" t="n">
-        <v>79694</v>
+        <v>78833</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1078,21 +1078,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>431756</v>
+        <v>431725</v>
       </c>
       <c r="R6" t="n">
-        <v>6795121</v>
+        <v>6795459</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,54 +1164,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129707371</v>
+        <v>129694862</v>
       </c>
       <c r="B7" t="n">
-        <v>8450</v>
+        <v>79695</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>431808</v>
+        <v>431756</v>
       </c>
       <c r="R7" t="n">
-        <v>6795442</v>
+        <v>6795121</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1252,64 +1243,71 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129707440</v>
+        <v>129694935</v>
       </c>
       <c r="B8" t="n">
-        <v>92869</v>
+        <v>57733</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>431828</v>
+        <v>431917</v>
       </c>
       <c r="R8" t="n">
-        <v>6795476</v>
+        <v>6795290</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1356,22 +1354,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129694935</v>
+        <v>129694929</v>
       </c>
       <c r="B9" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1411,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>431917</v>
+        <v>431859</v>
       </c>
       <c r="R9" t="n">
-        <v>6795290</v>
+        <v>6795172</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1473,40 +1471,41 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129694929</v>
+        <v>129707371</v>
       </c>
       <c r="B10" t="n">
-        <v>57732</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1516,10 +1515,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>431859</v>
+        <v>431808</v>
       </c>
       <c r="R10" t="n">
-        <v>6795172</v>
+        <v>6795442</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1560,28 +1559,29 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129707336</v>
+        <v>129707358</v>
       </c>
       <c r="B11" t="n">
-        <v>79694</v>
+        <v>57733</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1589,34 +1589,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>431993</v>
+        <v>431912</v>
       </c>
       <c r="R11" t="n">
-        <v>6795380</v>
+        <v>6795310</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1675,10 +1683,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129707434</v>
+        <v>129694843</v>
       </c>
       <c r="B12" t="n">
-        <v>79075</v>
+        <v>79695</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1686,21 +1694,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1710,10 +1718,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>431894</v>
+        <v>431752</v>
       </c>
       <c r="R12" t="n">
-        <v>6795261</v>
+        <v>6795429</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1760,22 +1768,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129707358</v>
+        <v>129694907</v>
       </c>
       <c r="B13" t="n">
-        <v>57732</v>
+        <v>79695</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1783,42 +1791,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>431912</v>
+        <v>431938</v>
       </c>
       <c r="R13" t="n">
-        <v>6795310</v>
+        <v>6795278</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1865,22 +1865,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129694918</v>
+        <v>129707336</v>
       </c>
       <c r="B14" t="n">
-        <v>91608</v>
+        <v>79695</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1888,41 +1888,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>431722</v>
+        <v>431993</v>
       </c>
       <c r="R14" t="n">
-        <v>6795120</v>
+        <v>6795380</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1963,29 +1956,28 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129694843</v>
+        <v>129707434</v>
       </c>
       <c r="B15" t="n">
-        <v>79694</v>
+        <v>79076</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1993,21 +1985,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2017,10 +2009,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>431752</v>
+        <v>431894</v>
       </c>
       <c r="R15" t="n">
-        <v>6795429</v>
+        <v>6795261</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2067,22 +2059,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129694983</v>
+        <v>129694918</v>
       </c>
       <c r="B16" t="n">
-        <v>79075</v>
+        <v>91609</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2090,34 +2082,41 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>431689</v>
+        <v>431722</v>
       </c>
       <c r="R16" t="n">
-        <v>6795456</v>
+        <v>6795120</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2158,6 +2157,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2176,10 +2176,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129694907</v>
+        <v>129694923</v>
       </c>
       <c r="B17" t="n">
-        <v>79694</v>
+        <v>57733</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2187,34 +2187,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>431938</v>
+        <v>431687</v>
       </c>
       <c r="R17" t="n">
-        <v>6795278</v>
+        <v>6795471</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2273,10 +2281,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129694923</v>
+        <v>129694983</v>
       </c>
       <c r="B18" t="n">
-        <v>57732</v>
+        <v>79076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2284,42 +2292,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>431687</v>
+        <v>431689</v>
       </c>
       <c r="R18" t="n">
-        <v>6795471</v>
+        <v>6795456</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2378,10 +2378,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129694845</v>
+        <v>129707378</v>
       </c>
       <c r="B19" t="n">
-        <v>79694</v>
+        <v>78833</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2389,21 +2389,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>431722</v>
+        <v>431814</v>
       </c>
       <c r="R19" t="n">
-        <v>6795478</v>
+        <v>6795444</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2463,22 +2463,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129707378</v>
+        <v>129707310</v>
       </c>
       <c r="B20" t="n">
-        <v>78832</v>
+        <v>79695</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2486,21 +2486,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2510,10 +2510,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>431814</v>
+        <v>431924</v>
       </c>
       <c r="R20" t="n">
-        <v>6795444</v>
+        <v>6795546</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2572,10 +2572,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129707310</v>
+        <v>129694845</v>
       </c>
       <c r="B21" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2607,10 +2607,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>431924</v>
+        <v>431722</v>
       </c>
       <c r="R21" t="n">
-        <v>6795546</v>
+        <v>6795478</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2657,12 +2657,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2672,7 +2672,7 @@
         <v>129707335</v>
       </c>
       <c r="B22" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>129694913</v>
       </c>
       <c r="B23" t="n">
-        <v>56925</v>
+        <v>56926</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>129694942</v>
       </c>
       <c r="B24" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2969,10 +2969,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129707308</v>
+        <v>129694883</v>
       </c>
       <c r="B25" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>431868</v>
+        <v>431885</v>
       </c>
       <c r="R25" t="n">
-        <v>6795565</v>
+        <v>6795213</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3054,22 +3054,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129707407</v>
+        <v>129694884</v>
       </c>
       <c r="B26" t="n">
-        <v>79075</v>
+        <v>79695</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3077,21 +3077,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>431723</v>
+        <v>431885</v>
       </c>
       <c r="R26" t="n">
-        <v>6795371</v>
+        <v>6795215</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3151,22 +3151,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129707331</v>
+        <v>129694898</v>
       </c>
       <c r="B27" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3192,19 +3192,16 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>431916</v>
+        <v>431907</v>
       </c>
       <c r="R27" t="n">
-        <v>6795392</v>
+        <v>6795285</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3245,29 +3242,28 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129694883</v>
+        <v>129694899</v>
       </c>
       <c r="B28" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3299,10 +3295,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>431885</v>
+        <v>431910</v>
       </c>
       <c r="R28" t="n">
-        <v>6795213</v>
+        <v>6795288</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3361,10 +3357,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129694884</v>
+        <v>129694861</v>
       </c>
       <c r="B29" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3396,10 +3392,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>431885</v>
+        <v>431740</v>
       </c>
       <c r="R29" t="n">
-        <v>6795215</v>
+        <v>6795107</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3458,10 +3454,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129694898</v>
+        <v>129707308</v>
       </c>
       <c r="B30" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3493,10 +3489,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>431907</v>
+        <v>431868</v>
       </c>
       <c r="R30" t="n">
-        <v>6795285</v>
+        <v>6795565</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3543,22 +3539,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129694899</v>
+        <v>129707407</v>
       </c>
       <c r="B31" t="n">
-        <v>79694</v>
+        <v>79076</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3566,21 +3562,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3590,10 +3586,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>431910</v>
+        <v>431723</v>
       </c>
       <c r="R31" t="n">
-        <v>6795288</v>
+        <v>6795371</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3640,22 +3636,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129694861</v>
+        <v>129707331</v>
       </c>
       <c r="B32" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3681,16 +3677,19 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>431740</v>
+        <v>431916</v>
       </c>
       <c r="R32" t="n">
-        <v>6795107</v>
+        <v>6795392</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3731,66 +3730,64 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129707390</v>
+        <v>129695010</v>
       </c>
       <c r="B33" t="n">
-        <v>78832</v>
+        <v>92870</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>431952</v>
+        <v>431880</v>
       </c>
       <c r="R33" t="n">
-        <v>6795410</v>
+        <v>6795546</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3831,29 +3828,28 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129707346</v>
+        <v>129694980</v>
       </c>
       <c r="B34" t="n">
-        <v>57732</v>
+        <v>79076</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3861,42 +3857,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>431819</v>
+        <v>431711</v>
       </c>
       <c r="R34" t="n">
-        <v>6795465</v>
+        <v>6795450</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3943,22 +3931,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129694839</v>
+        <v>129694886</v>
       </c>
       <c r="B35" t="n">
-        <v>91510</v>
+        <v>79695</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3966,37 +3954,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3242</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>431869</v>
+        <v>431873</v>
       </c>
       <c r="R35" t="n">
-        <v>6795181</v>
+        <v>6795241</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4037,7 +4022,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4056,10 +4040,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129694921</v>
+        <v>129694878</v>
       </c>
       <c r="B36" t="n">
-        <v>57732</v>
+        <v>79695</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4067,42 +4051,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>431725</v>
+        <v>431889</v>
       </c>
       <c r="R36" t="n">
-        <v>6795459</v>
+        <v>6795186</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4164,7 +4140,7 @@
         <v>129694917</v>
       </c>
       <c r="B37" t="n">
-        <v>91608</v>
+        <v>91609</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4266,45 +4242,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129695010</v>
+        <v>129707390</v>
       </c>
       <c r="B38" t="n">
-        <v>92869</v>
+        <v>78833</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>431880</v>
+        <v>431952</v>
       </c>
       <c r="R38" t="n">
-        <v>6795546</v>
+        <v>6795410</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4345,28 +4324,29 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129694886</v>
+        <v>129707346</v>
       </c>
       <c r="B39" t="n">
-        <v>79694</v>
+        <v>57733</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4374,34 +4354,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>431873</v>
+        <v>431819</v>
       </c>
       <c r="R39" t="n">
-        <v>6795241</v>
+        <v>6795465</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4448,22 +4436,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129694980</v>
+        <v>129694839</v>
       </c>
       <c r="B40" t="n">
-        <v>79075</v>
+        <v>91511</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4471,34 +4459,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>431711</v>
+        <v>431869</v>
       </c>
       <c r="R40" t="n">
-        <v>6795450</v>
+        <v>6795181</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4539,6 +4530,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4557,10 +4549,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129694878</v>
+        <v>129694921</v>
       </c>
       <c r="B41" t="n">
-        <v>79694</v>
+        <v>57733</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4568,34 +4560,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>431889</v>
+        <v>431725</v>
       </c>
       <c r="R41" t="n">
-        <v>6795186</v>
+        <v>6795459</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4751,10 +4751,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129694926</v>
+        <v>129707320</v>
       </c>
       <c r="B43" t="n">
-        <v>57732</v>
+        <v>79695</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4762,42 +4762,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>431711</v>
+        <v>431717</v>
       </c>
       <c r="R43" t="n">
-        <v>6795100</v>
+        <v>6795380</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4844,22 +4836,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129707320</v>
+        <v>129707316</v>
       </c>
       <c r="B44" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4891,10 +4883,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>431717</v>
+        <v>431812</v>
       </c>
       <c r="R44" t="n">
-        <v>6795380</v>
+        <v>6795349</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4953,10 +4945,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129707316</v>
+        <v>129707333</v>
       </c>
       <c r="B45" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4988,10 +4980,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>431812</v>
+        <v>431935</v>
       </c>
       <c r="R45" t="n">
-        <v>6795349</v>
+        <v>6795415</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5050,10 +5042,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129707333</v>
+        <v>129707338</v>
       </c>
       <c r="B46" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5085,10 +5077,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>431935</v>
+        <v>431932</v>
       </c>
       <c r="R46" t="n">
-        <v>6795415</v>
+        <v>6795406</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5147,10 +5139,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129707338</v>
+        <v>129707375</v>
       </c>
       <c r="B47" t="n">
-        <v>79694</v>
+        <v>78833</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5158,21 +5150,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5182,10 +5174,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>431932</v>
+        <v>431881</v>
       </c>
       <c r="R47" t="n">
-        <v>6795406</v>
+        <v>6795522</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5244,10 +5236,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129707375</v>
+        <v>129707351</v>
       </c>
       <c r="B48" t="n">
-        <v>78832</v>
+        <v>57733</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5255,34 +5247,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>431881</v>
+        <v>431756</v>
       </c>
       <c r="R48" t="n">
-        <v>6795522</v>
+        <v>6795202</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5341,10 +5341,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129707351</v>
+        <v>129694847</v>
       </c>
       <c r="B49" t="n">
-        <v>57732</v>
+        <v>79695</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5352,42 +5352,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>431756</v>
+        <v>431724</v>
       </c>
       <c r="R49" t="n">
-        <v>6795202</v>
+        <v>6795460</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5434,22 +5426,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129694847</v>
+        <v>129694999</v>
       </c>
       <c r="B50" t="n">
-        <v>79694</v>
+        <v>79076</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5457,21 +5449,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5481,10 +5473,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>431724</v>
+        <v>431859</v>
       </c>
       <c r="R50" t="n">
-        <v>6795460</v>
+        <v>6795172</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5543,10 +5535,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129694999</v>
+        <v>129694926</v>
       </c>
       <c r="B51" t="n">
-        <v>79075</v>
+        <v>57733</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5554,34 +5546,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>431859</v>
+        <v>431711</v>
       </c>
       <c r="R51" t="n">
-        <v>6795172</v>
+        <v>6795100</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5640,10 +5640,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129707337</v>
+        <v>129695006</v>
       </c>
       <c r="B52" t="n">
-        <v>79694</v>
+        <v>79076</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5651,21 +5651,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5675,10 +5675,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>431999</v>
+        <v>431962</v>
       </c>
       <c r="R52" t="n">
-        <v>6795416</v>
+        <v>6795319</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5725,22 +5725,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129707426</v>
+        <v>129695003</v>
       </c>
       <c r="B53" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>431767</v>
+        <v>431908</v>
       </c>
       <c r="R53" t="n">
-        <v>6795219</v>
+        <v>6795302</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5822,22 +5822,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129707404</v>
+        <v>129694994</v>
       </c>
       <c r="B54" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5863,19 +5863,16 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>431816</v>
+        <v>431804</v>
       </c>
       <c r="R54" t="n">
-        <v>6795333</v>
+        <v>6795151</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5910,40 +5907,34 @@
           <t>2025-11-14</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129707380</v>
+        <v>129694846</v>
       </c>
       <c r="B55" t="n">
-        <v>78832</v>
+        <v>79695</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5951,21 +5942,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5975,10 +5966,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>431820</v>
+        <v>431725</v>
       </c>
       <c r="R55" t="n">
-        <v>6795330</v>
+        <v>6795467</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6025,12 +6016,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6040,7 +6031,7 @@
         <v>129707347</v>
       </c>
       <c r="B56" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6142,10 +6133,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129694846</v>
+        <v>129707426</v>
       </c>
       <c r="B57" t="n">
-        <v>79694</v>
+        <v>79076</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6153,21 +6144,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6177,10 +6168,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>431725</v>
+        <v>431767</v>
       </c>
       <c r="R57" t="n">
-        <v>6795467</v>
+        <v>6795219</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6227,22 +6218,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129695003</v>
+        <v>129707404</v>
       </c>
       <c r="B58" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6268,16 +6259,19 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>431908</v>
+        <v>431816</v>
       </c>
       <c r="R58" t="n">
-        <v>6795302</v>
+        <v>6795333</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6312,34 +6306,40 @@
           <t>2025-11-14</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129695006</v>
+        <v>129707337</v>
       </c>
       <c r="B59" t="n">
-        <v>79075</v>
+        <v>79695</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6347,21 +6347,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>431962</v>
+        <v>431999</v>
       </c>
       <c r="R59" t="n">
-        <v>6795319</v>
+        <v>6795416</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6421,22 +6421,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129694994</v>
+        <v>129707380</v>
       </c>
       <c r="B60" t="n">
-        <v>79075</v>
+        <v>78833</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6444,21 +6444,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6468,10 +6468,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>431804</v>
+        <v>431820</v>
       </c>
       <c r="R60" t="n">
-        <v>6795151</v>
+        <v>6795330</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6518,12 +6518,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -6533,7 +6533,7 @@
         <v>129707319</v>
       </c>
       <c r="B61" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6627,10 +6627,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129694872</v>
+        <v>129694988</v>
       </c>
       <c r="B62" t="n">
-        <v>79694</v>
+        <v>79076</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6638,21 +6638,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6662,10 +6662,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>431833</v>
+        <v>431718</v>
       </c>
       <c r="R62" t="n">
-        <v>6795171</v>
+        <v>6795068</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6724,10 +6724,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129694856</v>
+        <v>129694872</v>
       </c>
       <c r="B63" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6759,10 +6759,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>431693</v>
+        <v>431833</v>
       </c>
       <c r="R63" t="n">
-        <v>6795052</v>
+        <v>6795171</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6821,10 +6821,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129694961</v>
+        <v>129694856</v>
       </c>
       <c r="B64" t="n">
-        <v>78832</v>
+        <v>79695</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6832,21 +6832,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6856,10 +6856,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>431804</v>
+        <v>431693</v>
       </c>
       <c r="R64" t="n">
-        <v>6795100</v>
+        <v>6795052</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6918,10 +6918,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129694988</v>
+        <v>129694961</v>
       </c>
       <c r="B65" t="n">
-        <v>79075</v>
+        <v>78833</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6929,21 +6929,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6953,10 +6953,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>431718</v>
+        <v>431804</v>
       </c>
       <c r="R65" t="n">
-        <v>6795068</v>
+        <v>6795100</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7018,7 +7018,7 @@
         <v>129694930</v>
       </c>
       <c r="B66" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
         <v>129707382</v>
       </c>
       <c r="B67" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7221,10 +7221,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129707420</v>
+        <v>129694928</v>
       </c>
       <c r="B68" t="n">
-        <v>79075</v>
+        <v>57733</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7232,34 +7232,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>431695</v>
+        <v>431801</v>
       </c>
       <c r="R68" t="n">
-        <v>6795256</v>
+        <v>6795136</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7306,22 +7314,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129694928</v>
+        <v>129707420</v>
       </c>
       <c r="B69" t="n">
-        <v>57732</v>
+        <v>79076</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7329,42 +7337,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>431801</v>
+        <v>431695</v>
       </c>
       <c r="R69" t="n">
-        <v>6795136</v>
+        <v>6795256</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7411,12 +7411,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -7426,7 +7426,7 @@
         <v>129694857</v>
       </c>
       <c r="B70" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>129694908</v>
       </c>
       <c r="B71" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>129694858</v>
       </c>
       <c r="B72" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>129694859</v>
       </c>
       <c r="B73" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>129694879</v>
       </c>
       <c r="B74" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>129707317</v>
       </c>
       <c r="B75" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8008,7 +8008,7 @@
         <v>129707391</v>
       </c>
       <c r="B76" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
         <v>129707389</v>
       </c>
       <c r="B77" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>129707314</v>
       </c>
       <c r="B78" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         <v>129707439</v>
       </c>
       <c r="B79" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>129694985</v>
       </c>
       <c r="B80" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         <v>129707388</v>
       </c>
       <c r="B81" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         <v>129707315</v>
       </c>
       <c r="B82" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8691,7 +8691,7 @@
         <v>129707424</v>
       </c>
       <c r="B83" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8785,10 +8785,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129694863</v>
+        <v>129707345</v>
       </c>
       <c r="B84" t="n">
-        <v>79694</v>
+        <v>57733</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8796,34 +8796,42 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>431785</v>
+        <v>431893</v>
       </c>
       <c r="R84" t="n">
-        <v>6795106</v>
+        <v>6795571</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8870,22 +8878,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129694874</v>
+        <v>129695001</v>
       </c>
       <c r="B85" t="n">
-        <v>79694</v>
+        <v>79076</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8893,21 +8901,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8917,10 +8925,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>431827</v>
+        <v>431876</v>
       </c>
       <c r="R85" t="n">
-        <v>6795171</v>
+        <v>6795202</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8979,10 +8987,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129695001</v>
+        <v>129694991</v>
       </c>
       <c r="B86" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9014,10 +9022,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>431876</v>
+        <v>431760</v>
       </c>
       <c r="R86" t="n">
-        <v>6795202</v>
+        <v>6795115</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9076,10 +9084,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129694991</v>
+        <v>129694863</v>
       </c>
       <c r="B87" t="n">
-        <v>79075</v>
+        <v>79695</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9087,21 +9095,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9111,10 +9119,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>431760</v>
+        <v>431785</v>
       </c>
       <c r="R87" t="n">
-        <v>6795115</v>
+        <v>6795106</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9173,10 +9181,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129694933</v>
+        <v>129694874</v>
       </c>
       <c r="B88" t="n">
-        <v>57732</v>
+        <v>79695</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9184,42 +9192,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>431904</v>
+        <v>431827</v>
       </c>
       <c r="R88" t="n">
-        <v>6795243</v>
+        <v>6795171</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9278,10 +9278,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129694948</v>
+        <v>129694933</v>
       </c>
       <c r="B89" t="n">
-        <v>78833</v>
+        <v>57733</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9289,34 +9289,42 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>431725</v>
+        <v>431904</v>
       </c>
       <c r="R89" t="n">
-        <v>6795459</v>
+        <v>6795243</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9375,10 +9383,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129707345</v>
+        <v>129694948</v>
       </c>
       <c r="B90" t="n">
-        <v>57732</v>
+        <v>78834</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9386,42 +9394,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>431893</v>
+        <v>431725</v>
       </c>
       <c r="R90" t="n">
-        <v>6795571</v>
+        <v>6795459</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9468,22 +9468,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129694939</v>
+        <v>129707405</v>
       </c>
       <c r="B91" t="n">
-        <v>57732</v>
+        <v>79076</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9491,21 +9491,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>431913</v>
+        <v>431775</v>
       </c>
       <c r="R91" t="n">
-        <v>6795284</v>
+        <v>6795343</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9553,11 +9553,6 @@
           <t>2025-11-14</t>
         </is>
       </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
@@ -9570,22 +9565,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129694934</v>
+        <v>129707381</v>
       </c>
       <c r="B92" t="n">
-        <v>57732</v>
+        <v>78833</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9593,42 +9588,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>431916</v>
+        <v>431712</v>
       </c>
       <c r="R92" t="n">
-        <v>6795286</v>
+        <v>6795379</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9675,22 +9662,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129707405</v>
+        <v>129694860</v>
       </c>
       <c r="B93" t="n">
-        <v>79075</v>
+        <v>79695</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9698,21 +9685,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9722,10 +9709,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>431775</v>
+        <v>431746</v>
       </c>
       <c r="R93" t="n">
-        <v>6795343</v>
+        <v>6795081</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9772,22 +9759,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129707381</v>
+        <v>129694965</v>
       </c>
       <c r="B94" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9819,10 +9806,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>431712</v>
+        <v>431885</v>
       </c>
       <c r="R94" t="n">
-        <v>6795379</v>
+        <v>6795240</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9869,22 +9856,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129694860</v>
+        <v>129694934</v>
       </c>
       <c r="B95" t="n">
-        <v>79694</v>
+        <v>57733</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9892,34 +9879,42 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>431746</v>
+        <v>431916</v>
       </c>
       <c r="R95" t="n">
-        <v>6795081</v>
+        <v>6795286</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9978,10 +9973,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129694965</v>
+        <v>129694939</v>
       </c>
       <c r="B96" t="n">
-        <v>78832</v>
+        <v>57733</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9989,21 +9984,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10013,10 +10008,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>431885</v>
+        <v>431913</v>
       </c>
       <c r="R96" t="n">
-        <v>6795240</v>
+        <v>6795284</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10049,6 +10044,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10075,45 +10075,53 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129694941</v>
+        <v>129694977</v>
       </c>
       <c r="B97" t="n">
-        <v>79161</v>
+        <v>57733</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6450</v>
+        <v>100049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>431976</v>
+        <v>431933</v>
       </c>
       <c r="R97" t="n">
-        <v>6795333</v>
+        <v>6795295</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10172,10 +10180,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129694977</v>
+        <v>129694989</v>
       </c>
       <c r="B98" t="n">
-        <v>57732</v>
+        <v>79076</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10183,42 +10191,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>431933</v>
+        <v>431723</v>
       </c>
       <c r="R98" t="n">
-        <v>6795295</v>
+        <v>6795090</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10277,32 +10277,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129694989</v>
+        <v>129694941</v>
       </c>
       <c r="B99" t="n">
-        <v>79075</v>
+        <v>79162</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10312,10 +10312,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>431723</v>
+        <v>431976</v>
       </c>
       <c r="R99" t="n">
-        <v>6795090</v>
+        <v>6795333</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10377,7 +10377,7 @@
         <v>129707312</v>
       </c>
       <c r="B100" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10471,10 +10471,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129707349</v>
+        <v>129707397</v>
       </c>
       <c r="B101" t="n">
-        <v>57732</v>
+        <v>79076</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10482,42 +10482,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>431722</v>
+        <v>431915</v>
       </c>
       <c r="R101" t="n">
-        <v>6795217</v>
+        <v>6795541</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10576,10 +10568,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129694877</v>
+        <v>129707396</v>
       </c>
       <c r="B102" t="n">
-        <v>79694</v>
+        <v>79076</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10587,21 +10579,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10611,10 +10603,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>431887</v>
+        <v>431918</v>
       </c>
       <c r="R102" t="n">
-        <v>6795183</v>
+        <v>6795574</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10661,22 +10653,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129694885</v>
+        <v>129707349</v>
       </c>
       <c r="B103" t="n">
-        <v>79694</v>
+        <v>57733</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10684,34 +10676,42 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>431873</v>
+        <v>431722</v>
       </c>
       <c r="R103" t="n">
-        <v>6795224</v>
+        <v>6795217</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10758,22 +10758,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129694864</v>
+        <v>129695000</v>
       </c>
       <c r="B104" t="n">
-        <v>79694</v>
+        <v>79076</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10781,21 +10781,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10805,10 +10805,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>431786</v>
+        <v>431890</v>
       </c>
       <c r="R104" t="n">
-        <v>6795113</v>
+        <v>6795199</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10867,10 +10867,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129694992</v>
+        <v>129694877</v>
       </c>
       <c r="B105" t="n">
-        <v>79075</v>
+        <v>79695</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10878,21 +10878,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10902,10 +10902,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>431799</v>
+        <v>431887</v>
       </c>
       <c r="R105" t="n">
-        <v>6795129</v>
+        <v>6795183</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10964,10 +10964,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129707397</v>
+        <v>129694885</v>
       </c>
       <c r="B106" t="n">
-        <v>79075</v>
+        <v>79695</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10975,21 +10975,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -10999,10 +10999,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>431915</v>
+        <v>431873</v>
       </c>
       <c r="R106" t="n">
-        <v>6795541</v>
+        <v>6795224</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11049,22 +11049,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129707327</v>
+        <v>129694864</v>
       </c>
       <c r="B107" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11096,10 +11096,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>431893</v>
+        <v>431786</v>
       </c>
       <c r="R107" t="n">
-        <v>6795305</v>
+        <v>6795113</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11146,22 +11146,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129707396</v>
+        <v>129694992</v>
       </c>
       <c r="B108" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11193,10 +11193,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>431918</v>
+        <v>431799</v>
       </c>
       <c r="R108" t="n">
-        <v>6795574</v>
+        <v>6795129</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11243,22 +11243,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129707406</v>
+        <v>129694927</v>
       </c>
       <c r="B109" t="n">
-        <v>79075</v>
+        <v>57733</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11266,34 +11266,42 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>431771</v>
+        <v>431711</v>
       </c>
       <c r="R109" t="n">
-        <v>6795344</v>
+        <v>6795094</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11340,44 +11348,44 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129707332</v>
+        <v>129694944</v>
       </c>
       <c r="B110" t="n">
-        <v>79694</v>
+        <v>5480</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6453</v>
+        <v>101920</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11387,10 +11395,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>431923</v>
+        <v>431741</v>
       </c>
       <c r="R110" t="n">
-        <v>6795402</v>
+        <v>6795079</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11437,22 +11445,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129707425</v>
+        <v>129707327</v>
       </c>
       <c r="B111" t="n">
-        <v>79075</v>
+        <v>79695</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11460,21 +11468,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11484,10 +11492,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>431756</v>
+        <v>431893</v>
       </c>
       <c r="R111" t="n">
-        <v>6795247</v>
+        <v>6795305</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11546,10 +11554,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129695000</v>
+        <v>129707406</v>
       </c>
       <c r="B112" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11581,10 +11589,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>431890</v>
+        <v>431771</v>
       </c>
       <c r="R112" t="n">
-        <v>6795199</v>
+        <v>6795344</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11631,22 +11639,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129694927</v>
+        <v>129707332</v>
       </c>
       <c r="B113" t="n">
-        <v>57732</v>
+        <v>79695</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11654,42 +11662,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>431711</v>
+        <v>431923</v>
       </c>
       <c r="R113" t="n">
-        <v>6795094</v>
+        <v>6795402</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11736,22 +11736,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129694938</v>
+        <v>129707425</v>
       </c>
       <c r="B114" t="n">
-        <v>57732</v>
+        <v>79076</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11759,42 +11759,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>431915</v>
+        <v>431756</v>
       </c>
       <c r="R114" t="n">
-        <v>6795279</v>
+        <v>6795247</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11841,57 +11833,65 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129694944</v>
+        <v>129694938</v>
       </c>
       <c r="B115" t="n">
-        <v>5480</v>
+        <v>57733</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>101920</v>
+        <v>100049</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>431741</v>
+        <v>431915</v>
       </c>
       <c r="R115" t="n">
-        <v>6795079</v>
+        <v>6795279</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11953,7 +11953,7 @@
         <v>129707309</v>
       </c>
       <c r="B116" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
         <v>129707330</v>
       </c>
       <c r="B117" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12147,7 +12147,7 @@
         <v>129707323</v>
       </c>
       <c r="B118" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12244,7 +12244,7 @@
         <v>129707386</v>
       </c>
       <c r="B119" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12341,7 +12341,7 @@
         <v>129707421</v>
       </c>
       <c r="B120" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>129694901</v>
       </c>
       <c r="B121" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12532,10 +12532,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129694990</v>
+        <v>129694844</v>
       </c>
       <c r="B122" t="n">
-        <v>79075</v>
+        <v>79695</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12543,21 +12543,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12567,10 +12567,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>431726</v>
+        <v>431739</v>
       </c>
       <c r="R122" t="n">
-        <v>6795117</v>
+        <v>6795440</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12629,10 +12629,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129694844</v>
+        <v>129694990</v>
       </c>
       <c r="B123" t="n">
-        <v>79694</v>
+        <v>79076</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12640,21 +12640,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12664,10 +12664,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>431739</v>
+        <v>431726</v>
       </c>
       <c r="R123" t="n">
-        <v>6795440</v>
+        <v>6795117</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12729,7 +12729,7 @@
         <v>129695013</v>
       </c>
       <c r="B124" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12823,10 +12823,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129694850</v>
+        <v>129694997</v>
       </c>
       <c r="B125" t="n">
-        <v>79694</v>
+        <v>79076</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12834,21 +12834,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12858,10 +12858,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>431686</v>
+        <v>431848</v>
       </c>
       <c r="R125" t="n">
-        <v>6795471</v>
+        <v>6795172</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12920,10 +12920,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129694881</v>
+        <v>129707368</v>
       </c>
       <c r="B126" t="n">
-        <v>79694</v>
+        <v>78834</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12931,34 +12931,37 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>431875</v>
+        <v>431820</v>
       </c>
       <c r="R126" t="n">
-        <v>6795212</v>
+        <v>6795331</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -12999,28 +13002,29 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129694888</v>
+        <v>129694850</v>
       </c>
       <c r="B127" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13052,10 +13056,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>431889</v>
+        <v>431686</v>
       </c>
       <c r="R127" t="n">
-        <v>6795236</v>
+        <v>6795471</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13114,10 +13118,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129694997</v>
+        <v>129694881</v>
       </c>
       <c r="B128" t="n">
-        <v>79075</v>
+        <v>79695</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13125,21 +13129,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13149,10 +13153,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>431848</v>
+        <v>431875</v>
       </c>
       <c r="R128" t="n">
-        <v>6795172</v>
+        <v>6795212</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13211,10 +13215,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129694925</v>
+        <v>129694888</v>
       </c>
       <c r="B129" t="n">
-        <v>57732</v>
+        <v>79695</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13222,42 +13226,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>431687</v>
+        <v>431889</v>
       </c>
       <c r="R129" t="n">
-        <v>6795051</v>
+        <v>6795236</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13316,10 +13312,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129707368</v>
+        <v>129694925</v>
       </c>
       <c r="B130" t="n">
-        <v>78833</v>
+        <v>57733</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13327,26 +13323,31 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
@@ -13354,10 +13355,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>431820</v>
+        <v>431687</v>
       </c>
       <c r="R130" t="n">
-        <v>6795331</v>
+        <v>6795051</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13398,19 +13399,18 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
@@ -13420,7 +13420,7 @@
         <v>129707311</v>
       </c>
       <c r="B131" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13514,10 +13514,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129707399</v>
+        <v>129694900</v>
       </c>
       <c r="B132" t="n">
-        <v>79075</v>
+        <v>79695</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13525,21 +13525,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13549,10 +13549,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>431819</v>
+        <v>431907</v>
       </c>
       <c r="R132" t="n">
-        <v>6795445</v>
+        <v>6795266</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13599,22 +13599,22 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129707387</v>
+        <v>129694906</v>
       </c>
       <c r="B133" t="n">
-        <v>78832</v>
+        <v>79695</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13622,21 +13622,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13646,10 +13646,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>431936</v>
+        <v>431934</v>
       </c>
       <c r="R133" t="n">
-        <v>6795393</v>
+        <v>6795286</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13696,12 +13696,12 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
@@ -13711,7 +13711,7 @@
         <v>129707438</v>
       </c>
       <c r="B134" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13805,10 +13805,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129707318</v>
+        <v>129707399</v>
       </c>
       <c r="B135" t="n">
-        <v>79694</v>
+        <v>79076</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13816,21 +13816,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13840,10 +13840,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>431769</v>
+        <v>431819</v>
       </c>
       <c r="R135" t="n">
-        <v>6795345</v>
+        <v>6795445</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -13902,10 +13902,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129694906</v>
+        <v>129707387</v>
       </c>
       <c r="B136" t="n">
-        <v>79694</v>
+        <v>78833</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13913,21 +13913,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -13937,10 +13937,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>431934</v>
+        <v>431936</v>
       </c>
       <c r="R136" t="n">
-        <v>6795286</v>
+        <v>6795393</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -13987,22 +13987,22 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129694900</v>
+        <v>129707318</v>
       </c>
       <c r="B137" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14034,10 +14034,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>431907</v>
+        <v>431769</v>
       </c>
       <c r="R137" t="n">
-        <v>6795266</v>
+        <v>6795345</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14084,22 +14084,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129694956</v>
+        <v>129694866</v>
       </c>
       <c r="B138" t="n">
-        <v>92005</v>
+        <v>79695</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14107,33 +14107,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6040162</v>
+        <v>6453</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>431718</v>
+        <v>431797</v>
       </c>
       <c r="R138" t="n">
-        <v>6795082</v>
+        <v>6795173</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14168,18 +14169,12 @@
           <t>2025-11-14</t>
         </is>
       </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>Mjuk och len på undetsidan, sämskskinnslik känsla</t>
-        </is>
-      </c>
       <c r="AD138" t="b">
         <v>0</v>
       </c>
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -14198,10 +14193,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129707370</v>
+        <v>129694865</v>
       </c>
       <c r="B139" t="n">
-        <v>78833</v>
+        <v>79695</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14209,21 +14204,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14233,10 +14228,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>431913</v>
+        <v>431787</v>
       </c>
       <c r="R139" t="n">
-        <v>6795394</v>
+        <v>6795115</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14283,22 +14278,22 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129707334</v>
+        <v>129694896</v>
       </c>
       <c r="B140" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14330,10 +14325,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>431936</v>
+        <v>431900</v>
       </c>
       <c r="R140" t="n">
-        <v>6795411</v>
+        <v>6795265</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14380,22 +14375,22 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129694866</v>
+        <v>129694956</v>
       </c>
       <c r="B141" t="n">
-        <v>79694</v>
+        <v>92006</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14403,34 +14398,33 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>431797</v>
+        <v>431718</v>
       </c>
       <c r="R141" t="n">
-        <v>6795173</v>
+        <v>6795082</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14465,12 +14459,18 @@
           <t>2025-11-14</t>
         </is>
       </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Mjuk och len på undetsidan, sämskskinnslik känsla</t>
+        </is>
+      </c>
       <c r="AD141" t="b">
         <v>0</v>
       </c>
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -14489,10 +14489,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129694865</v>
+        <v>129707334</v>
       </c>
       <c r="B142" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14524,10 +14524,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>431787</v>
+        <v>431936</v>
       </c>
       <c r="R142" t="n">
-        <v>6795115</v>
+        <v>6795411</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14574,22 +14574,22 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129694896</v>
+        <v>129707370</v>
       </c>
       <c r="B143" t="n">
-        <v>79694</v>
+        <v>78834</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14597,21 +14597,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14621,10 +14621,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>431900</v>
+        <v>431913</v>
       </c>
       <c r="R143" t="n">
-        <v>6795265</v>
+        <v>6795394</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14671,22 +14671,22 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129694876</v>
+        <v>129707377</v>
       </c>
       <c r="B144" t="n">
-        <v>79694</v>
+        <v>78833</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14694,21 +14694,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14718,10 +14718,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>431871</v>
+        <v>431843</v>
       </c>
       <c r="R144" t="n">
-        <v>6795171</v>
+        <v>6795474</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14768,22 +14768,22 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129694887</v>
+        <v>129707366</v>
       </c>
       <c r="B145" t="n">
-        <v>79694</v>
+        <v>78834</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14791,21 +14791,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -14815,10 +14815,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>431886</v>
+        <v>431840</v>
       </c>
       <c r="R145" t="n">
-        <v>6795236</v>
+        <v>6795476</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -14865,22 +14865,22 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129694880</v>
+        <v>129694876</v>
       </c>
       <c r="B146" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14915,7 +14915,7 @@
         <v>431871</v>
       </c>
       <c r="R146" t="n">
-        <v>6795205</v>
+        <v>6795171</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -14974,10 +14974,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129694897</v>
+        <v>129694887</v>
       </c>
       <c r="B147" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15009,10 +15009,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>431906</v>
+        <v>431886</v>
       </c>
       <c r="R147" t="n">
-        <v>6795283</v>
+        <v>6795236</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15071,10 +15071,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129707377</v>
+        <v>129694880</v>
       </c>
       <c r="B148" t="n">
-        <v>78832</v>
+        <v>79695</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15082,21 +15082,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15106,10 +15106,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>431843</v>
+        <v>431871</v>
       </c>
       <c r="R148" t="n">
-        <v>6795474</v>
+        <v>6795205</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15156,22 +15156,22 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129707366</v>
+        <v>129694897</v>
       </c>
       <c r="B149" t="n">
-        <v>78833</v>
+        <v>79695</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15179,21 +15179,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15203,10 +15203,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>431840</v>
+        <v>431906</v>
       </c>
       <c r="R149" t="n">
-        <v>6795476</v>
+        <v>6795283</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15253,12 +15253,12 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>

--- a/artfynd/A 50492-2025 artfynd.xlsx
+++ b/artfynd/A 50492-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY149"/>
+  <dimension ref="A1:AY147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4654,32 +4654,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129694945</v>
+        <v>129707320</v>
       </c>
       <c r="B42" t="n">
-        <v>5480</v>
+        <v>79695</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>101920</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>431710</v>
+        <v>431717</v>
       </c>
       <c r="R42" t="n">
-        <v>6795099</v>
+        <v>6795380</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4739,19 +4739,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129707320</v>
+        <v>129707316</v>
       </c>
       <c r="B43" t="n">
         <v>79695</v>
@@ -4786,10 +4786,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>431717</v>
+        <v>431812</v>
       </c>
       <c r="R43" t="n">
-        <v>6795380</v>
+        <v>6795349</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4848,7 +4848,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129707316</v>
+        <v>129707333</v>
       </c>
       <c r="B44" t="n">
         <v>79695</v>
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>431812</v>
+        <v>431935</v>
       </c>
       <c r="R44" t="n">
-        <v>6795349</v>
+        <v>6795415</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4945,7 +4945,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129707333</v>
+        <v>129707338</v>
       </c>
       <c r="B45" t="n">
         <v>79695</v>
@@ -4980,10 +4980,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>431935</v>
+        <v>431932</v>
       </c>
       <c r="R45" t="n">
-        <v>6795415</v>
+        <v>6795406</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5042,10 +5042,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129707338</v>
+        <v>129707375</v>
       </c>
       <c r="B46" t="n">
-        <v>79695</v>
+        <v>78833</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5053,21 +5053,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5077,10 +5077,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>431932</v>
+        <v>431881</v>
       </c>
       <c r="R46" t="n">
-        <v>6795406</v>
+        <v>6795522</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5139,10 +5139,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129707375</v>
+        <v>129707351</v>
       </c>
       <c r="B47" t="n">
-        <v>78833</v>
+        <v>57733</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5150,34 +5150,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>431881</v>
+        <v>431756</v>
       </c>
       <c r="R47" t="n">
-        <v>6795522</v>
+        <v>6795202</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5236,10 +5244,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129707351</v>
+        <v>129694847</v>
       </c>
       <c r="B48" t="n">
-        <v>57733</v>
+        <v>79695</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5247,42 +5255,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>431756</v>
+        <v>431724</v>
       </c>
       <c r="R48" t="n">
-        <v>6795202</v>
+        <v>6795460</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5329,22 +5329,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129694847</v>
+        <v>129694999</v>
       </c>
       <c r="B49" t="n">
-        <v>79695</v>
+        <v>79076</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5352,21 +5352,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5376,10 +5376,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>431724</v>
+        <v>431859</v>
       </c>
       <c r="R49" t="n">
-        <v>6795460</v>
+        <v>6795172</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5438,10 +5438,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129694999</v>
+        <v>129694926</v>
       </c>
       <c r="B50" t="n">
-        <v>79076</v>
+        <v>57733</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5449,34 +5449,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>431859</v>
+        <v>431711</v>
       </c>
       <c r="R50" t="n">
-        <v>6795172</v>
+        <v>6795100</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5535,10 +5543,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129694926</v>
+        <v>129695006</v>
       </c>
       <c r="B51" t="n">
-        <v>57733</v>
+        <v>79076</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5546,42 +5554,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>431711</v>
+        <v>431962</v>
       </c>
       <c r="R51" t="n">
-        <v>6795100</v>
+        <v>6795319</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5640,7 +5640,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129695006</v>
+        <v>129695003</v>
       </c>
       <c r="B52" t="n">
         <v>79076</v>
@@ -5675,10 +5675,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>431962</v>
+        <v>431908</v>
       </c>
       <c r="R52" t="n">
-        <v>6795319</v>
+        <v>6795302</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5737,7 +5737,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129695003</v>
+        <v>129694994</v>
       </c>
       <c r="B53" t="n">
         <v>79076</v>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>431908</v>
+        <v>431804</v>
       </c>
       <c r="R53" t="n">
-        <v>6795302</v>
+        <v>6795151</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5834,10 +5834,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129694994</v>
+        <v>129694846</v>
       </c>
       <c r="B54" t="n">
-        <v>79076</v>
+        <v>79695</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5845,21 +5845,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5869,10 +5869,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>431804</v>
+        <v>431725</v>
       </c>
       <c r="R54" t="n">
-        <v>6795151</v>
+        <v>6795467</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5931,10 +5931,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129694846</v>
+        <v>129707347</v>
       </c>
       <c r="B55" t="n">
-        <v>79695</v>
+        <v>57733</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5942,34 +5942,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>431725</v>
+        <v>431662</v>
       </c>
       <c r="R55" t="n">
-        <v>6795467</v>
+        <v>6795391</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6016,22 +6024,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129707347</v>
+        <v>129707426</v>
       </c>
       <c r="B56" t="n">
-        <v>57733</v>
+        <v>79076</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6039,42 +6047,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>431662</v>
+        <v>431767</v>
       </c>
       <c r="R56" t="n">
-        <v>6795391</v>
+        <v>6795219</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6133,7 +6133,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129707426</v>
+        <v>129707404</v>
       </c>
       <c r="B57" t="n">
         <v>79076</v>
@@ -6162,16 +6162,19 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>431767</v>
+        <v>431816</v>
       </c>
       <c r="R57" t="n">
-        <v>6795219</v>
+        <v>6795333</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6206,12 +6209,18 @@
           <t>2025-11-14</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6230,10 +6239,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129707404</v>
+        <v>129707337</v>
       </c>
       <c r="B58" t="n">
-        <v>79076</v>
+        <v>79695</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6241,37 +6250,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>431816</v>
+        <v>431999</v>
       </c>
       <c r="R58" t="n">
-        <v>6795333</v>
+        <v>6795416</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6306,18 +6312,12 @@
           <t>2025-11-14</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6336,10 +6336,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129707337</v>
+        <v>129707380</v>
       </c>
       <c r="B59" t="n">
-        <v>79695</v>
+        <v>78833</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6347,21 +6347,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>431999</v>
+        <v>431820</v>
       </c>
       <c r="R59" t="n">
-        <v>6795416</v>
+        <v>6795330</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6433,10 +6433,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129707380</v>
+        <v>129707319</v>
       </c>
       <c r="B60" t="n">
-        <v>78833</v>
+        <v>79695</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6444,21 +6444,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6468,10 +6468,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>431820</v>
+        <v>431708</v>
       </c>
       <c r="R60" t="n">
-        <v>6795330</v>
+        <v>6795371</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6530,10 +6530,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129707319</v>
+        <v>129694988</v>
       </c>
       <c r="B61" t="n">
-        <v>79695</v>
+        <v>79076</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6541,21 +6541,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6565,10 +6565,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>431708</v>
+        <v>431718</v>
       </c>
       <c r="R61" t="n">
-        <v>6795371</v>
+        <v>6795068</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6615,22 +6615,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129694988</v>
+        <v>129694872</v>
       </c>
       <c r="B62" t="n">
-        <v>79076</v>
+        <v>79695</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6638,21 +6638,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6662,10 +6662,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>431718</v>
+        <v>431833</v>
       </c>
       <c r="R62" t="n">
-        <v>6795068</v>
+        <v>6795171</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6724,7 +6724,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129694872</v>
+        <v>129694856</v>
       </c>
       <c r="B63" t="n">
         <v>79695</v>
@@ -6759,10 +6759,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>431833</v>
+        <v>431693</v>
       </c>
       <c r="R63" t="n">
-        <v>6795171</v>
+        <v>6795052</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6821,10 +6821,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129694856</v>
+        <v>129694961</v>
       </c>
       <c r="B64" t="n">
-        <v>79695</v>
+        <v>78833</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6832,21 +6832,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6856,10 +6856,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>431693</v>
+        <v>431804</v>
       </c>
       <c r="R64" t="n">
-        <v>6795052</v>
+        <v>6795100</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6918,10 +6918,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129694961</v>
+        <v>129694930</v>
       </c>
       <c r="B65" t="n">
-        <v>78833</v>
+        <v>57733</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6929,34 +6929,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>431804</v>
+        <v>431875</v>
       </c>
       <c r="R65" t="n">
-        <v>6795100</v>
+        <v>6795244</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7015,10 +7023,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129694930</v>
+        <v>129707382</v>
       </c>
       <c r="B66" t="n">
-        <v>57733</v>
+        <v>78833</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7026,31 +7034,26 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7058,10 +7061,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>431875</v>
+        <v>431689</v>
       </c>
       <c r="R66" t="n">
-        <v>6795244</v>
+        <v>6795383</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7102,28 +7105,29 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129707382</v>
+        <v>129694928</v>
       </c>
       <c r="B67" t="n">
-        <v>78833</v>
+        <v>57733</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7131,26 +7135,31 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7158,10 +7167,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>431689</v>
+        <v>431801</v>
       </c>
       <c r="R67" t="n">
-        <v>6795383</v>
+        <v>6795136</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7202,29 +7211,28 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129694928</v>
+        <v>129707420</v>
       </c>
       <c r="B68" t="n">
-        <v>57733</v>
+        <v>79076</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7232,42 +7240,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>431801</v>
+        <v>431695</v>
       </c>
       <c r="R68" t="n">
-        <v>6795136</v>
+        <v>6795256</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7314,22 +7314,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129707420</v>
+        <v>129694857</v>
       </c>
       <c r="B69" t="n">
-        <v>79076</v>
+        <v>79695</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7337,21 +7337,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7361,10 +7361,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>431695</v>
+        <v>431800</v>
       </c>
       <c r="R69" t="n">
-        <v>6795256</v>
+        <v>6795130</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7411,19 +7411,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129694857</v>
+        <v>129694908</v>
       </c>
       <c r="B70" t="n">
         <v>79695</v>
@@ -7458,10 +7458,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>431800</v>
+        <v>431973</v>
       </c>
       <c r="R70" t="n">
-        <v>6795130</v>
+        <v>6795310</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7520,7 +7520,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129694908</v>
+        <v>129694858</v>
       </c>
       <c r="B71" t="n">
         <v>79695</v>
@@ -7555,10 +7555,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>431973</v>
+        <v>431749</v>
       </c>
       <c r="R71" t="n">
-        <v>6795310</v>
+        <v>6795079</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7617,7 +7617,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129694858</v>
+        <v>129694859</v>
       </c>
       <c r="B72" t="n">
         <v>79695</v>
@@ -7652,10 +7652,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>431749</v>
+        <v>431702</v>
       </c>
       <c r="R72" t="n">
-        <v>6795079</v>
+        <v>6795115</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7714,7 +7714,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129694859</v>
+        <v>129694879</v>
       </c>
       <c r="B73" t="n">
         <v>79695</v>
@@ -7749,10 +7749,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>431702</v>
+        <v>431888</v>
       </c>
       <c r="R73" t="n">
-        <v>6795115</v>
+        <v>6795198</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7811,32 +7811,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129694879</v>
+        <v>129707439</v>
       </c>
       <c r="B74" t="n">
-        <v>79695</v>
+        <v>92870</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7846,10 +7846,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>431888</v>
+        <v>431891</v>
       </c>
       <c r="R74" t="n">
-        <v>6795198</v>
+        <v>6795553</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7896,12 +7896,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8300,32 +8300,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129707439</v>
+        <v>129694985</v>
       </c>
       <c r="B79" t="n">
-        <v>92870</v>
+        <v>79076</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8335,10 +8335,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>431891</v>
+        <v>431673</v>
       </c>
       <c r="R79" t="n">
-        <v>6795553</v>
+        <v>6795435</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8385,22 +8385,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129694985</v>
+        <v>129707388</v>
       </c>
       <c r="B80" t="n">
-        <v>79076</v>
+        <v>78833</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8408,21 +8408,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8432,10 +8432,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>431673</v>
+        <v>431915</v>
       </c>
       <c r="R80" t="n">
-        <v>6795435</v>
+        <v>6795392</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8482,22 +8482,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129707388</v>
+        <v>129707315</v>
       </c>
       <c r="B81" t="n">
-        <v>78833</v>
+        <v>79695</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8505,21 +8505,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>431915</v>
+        <v>431820</v>
       </c>
       <c r="R81" t="n">
-        <v>6795392</v>
+        <v>6795329</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8591,10 +8591,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129707315</v>
+        <v>129707424</v>
       </c>
       <c r="B82" t="n">
-        <v>79695</v>
+        <v>79076</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8602,21 +8602,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8626,10 +8626,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>431820</v>
+        <v>431760</v>
       </c>
       <c r="R82" t="n">
-        <v>6795329</v>
+        <v>6795200</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8688,10 +8688,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129707424</v>
+        <v>129707345</v>
       </c>
       <c r="B83" t="n">
-        <v>79076</v>
+        <v>57733</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8699,34 +8699,42 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>431760</v>
+        <v>431893</v>
       </c>
       <c r="R83" t="n">
-        <v>6795200</v>
+        <v>6795571</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8785,10 +8793,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129707345</v>
+        <v>129695001</v>
       </c>
       <c r="B84" t="n">
-        <v>57733</v>
+        <v>79076</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8796,42 +8804,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>431893</v>
+        <v>431876</v>
       </c>
       <c r="R84" t="n">
-        <v>6795571</v>
+        <v>6795202</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8878,19 +8878,19 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129695001</v>
+        <v>129694991</v>
       </c>
       <c r="B85" t="n">
         <v>79076</v>
@@ -8925,10 +8925,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>431876</v>
+        <v>431760</v>
       </c>
       <c r="R85" t="n">
-        <v>6795202</v>
+        <v>6795115</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8987,10 +8987,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129694991</v>
+        <v>129694863</v>
       </c>
       <c r="B86" t="n">
-        <v>79076</v>
+        <v>79695</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8998,21 +8998,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9022,10 +9022,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>431760</v>
+        <v>431785</v>
       </c>
       <c r="R86" t="n">
-        <v>6795115</v>
+        <v>6795106</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9084,7 +9084,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129694863</v>
+        <v>129694874</v>
       </c>
       <c r="B87" t="n">
         <v>79695</v>
@@ -9119,10 +9119,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>431785</v>
+        <v>431827</v>
       </c>
       <c r="R87" t="n">
-        <v>6795106</v>
+        <v>6795171</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9181,10 +9181,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129694874</v>
+        <v>129694933</v>
       </c>
       <c r="B88" t="n">
-        <v>79695</v>
+        <v>57733</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9192,34 +9192,42 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>431827</v>
+        <v>431904</v>
       </c>
       <c r="R88" t="n">
-        <v>6795171</v>
+        <v>6795243</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9278,10 +9286,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129694933</v>
+        <v>129694948</v>
       </c>
       <c r="B89" t="n">
-        <v>57733</v>
+        <v>78834</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9289,42 +9297,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>431904</v>
+        <v>431725</v>
       </c>
       <c r="R89" t="n">
-        <v>6795243</v>
+        <v>6795459</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9383,10 +9383,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129694948</v>
+        <v>129707405</v>
       </c>
       <c r="B90" t="n">
-        <v>78834</v>
+        <v>79076</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9394,21 +9394,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9418,10 +9418,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>431725</v>
+        <v>431775</v>
       </c>
       <c r="R90" t="n">
-        <v>6795459</v>
+        <v>6795343</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9468,22 +9468,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129707405</v>
+        <v>129707381</v>
       </c>
       <c r="B91" t="n">
-        <v>79076</v>
+        <v>78833</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9491,21 +9491,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>431775</v>
+        <v>431712</v>
       </c>
       <c r="R91" t="n">
-        <v>6795343</v>
+        <v>6795379</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9577,10 +9577,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129707381</v>
+        <v>129694860</v>
       </c>
       <c r="B92" t="n">
-        <v>78833</v>
+        <v>79695</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9588,21 +9588,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9612,10 +9612,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>431712</v>
+        <v>431746</v>
       </c>
       <c r="R92" t="n">
-        <v>6795379</v>
+        <v>6795081</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9662,22 +9662,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129694860</v>
+        <v>129694965</v>
       </c>
       <c r="B93" t="n">
-        <v>79695</v>
+        <v>78833</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9685,21 +9685,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9709,10 +9709,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>431746</v>
+        <v>431885</v>
       </c>
       <c r="R93" t="n">
-        <v>6795081</v>
+        <v>6795240</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9771,10 +9771,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129694965</v>
+        <v>129694934</v>
       </c>
       <c r="B94" t="n">
-        <v>78833</v>
+        <v>57733</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9782,34 +9782,42 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>431885</v>
+        <v>431916</v>
       </c>
       <c r="R94" t="n">
-        <v>6795240</v>
+        <v>6795286</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9868,7 +9876,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129694934</v>
+        <v>129694939</v>
       </c>
       <c r="B95" t="n">
         <v>57733</v>
@@ -9897,24 +9905,16 @@
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>431916</v>
+        <v>431913</v>
       </c>
       <c r="R95" t="n">
-        <v>6795286</v>
+        <v>6795284</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9947,6 +9947,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -9973,7 +9978,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129694939</v>
+        <v>129694977</v>
       </c>
       <c r="B96" t="n">
         <v>57733</v>
@@ -10002,16 +10007,24 @@
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>431913</v>
+        <v>431933</v>
       </c>
       <c r="R96" t="n">
-        <v>6795284</v>
+        <v>6795295</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10044,11 +10057,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10075,10 +10083,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129694977</v>
+        <v>129694989</v>
       </c>
       <c r="B97" t="n">
-        <v>57733</v>
+        <v>79076</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10086,42 +10094,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>431933</v>
+        <v>431723</v>
       </c>
       <c r="R97" t="n">
-        <v>6795295</v>
+        <v>6795090</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10180,32 +10180,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129694989</v>
+        <v>129694941</v>
       </c>
       <c r="B98" t="n">
-        <v>79076</v>
+        <v>79162</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10215,10 +10215,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>431723</v>
+        <v>431976</v>
       </c>
       <c r="R98" t="n">
-        <v>6795090</v>
+        <v>6795333</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10277,32 +10277,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129694941</v>
+        <v>129707312</v>
       </c>
       <c r="B99" t="n">
-        <v>79162</v>
+        <v>79695</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6450</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10312,10 +10312,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>431976</v>
+        <v>431920</v>
       </c>
       <c r="R99" t="n">
-        <v>6795333</v>
+        <v>6795611</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10362,19 +10362,19 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129707312</v>
+        <v>129694877</v>
       </c>
       <c r="B100" t="n">
         <v>79695</v>
@@ -10409,10 +10409,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>431920</v>
+        <v>431887</v>
       </c>
       <c r="R100" t="n">
-        <v>6795611</v>
+        <v>6795183</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10459,22 +10459,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129707397</v>
+        <v>129707327</v>
       </c>
       <c r="B101" t="n">
-        <v>79076</v>
+        <v>79695</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10482,21 +10482,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10506,10 +10506,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>431915</v>
+        <v>431893</v>
       </c>
       <c r="R101" t="n">
-        <v>6795541</v>
+        <v>6795305</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10568,7 +10568,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129707396</v>
+        <v>129707406</v>
       </c>
       <c r="B102" t="n">
         <v>79076</v>
@@ -10603,10 +10603,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>431918</v>
+        <v>431771</v>
       </c>
       <c r="R102" t="n">
-        <v>6795574</v>
+        <v>6795344</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10665,10 +10665,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129707349</v>
+        <v>129707332</v>
       </c>
       <c r="B103" t="n">
-        <v>57733</v>
+        <v>79695</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10676,42 +10676,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>431722</v>
+        <v>431923</v>
       </c>
       <c r="R103" t="n">
-        <v>6795217</v>
+        <v>6795402</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10770,7 +10762,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129695000</v>
+        <v>129707425</v>
       </c>
       <c r="B104" t="n">
         <v>79076</v>
@@ -10805,10 +10797,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>431890</v>
+        <v>431756</v>
       </c>
       <c r="R104" t="n">
-        <v>6795199</v>
+        <v>6795247</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10855,22 +10847,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129694877</v>
+        <v>129707349</v>
       </c>
       <c r="B105" t="n">
-        <v>79695</v>
+        <v>57733</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10878,34 +10870,42 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>431887</v>
+        <v>431722</v>
       </c>
       <c r="R105" t="n">
-        <v>6795183</v>
+        <v>6795217</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10952,12 +10952,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -11158,10 +11158,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129694992</v>
+        <v>129694927</v>
       </c>
       <c r="B108" t="n">
-        <v>79076</v>
+        <v>57733</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11169,34 +11169,42 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>431799</v>
+        <v>431711</v>
       </c>
       <c r="R108" t="n">
-        <v>6795129</v>
+        <v>6795094</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11255,10 +11263,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129694927</v>
+        <v>129707397</v>
       </c>
       <c r="B109" t="n">
-        <v>57733</v>
+        <v>79076</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11266,42 +11274,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>431711</v>
+        <v>431915</v>
       </c>
       <c r="R109" t="n">
-        <v>6795094</v>
+        <v>6795541</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11348,44 +11348,44 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129694944</v>
+        <v>129707396</v>
       </c>
       <c r="B110" t="n">
-        <v>5480</v>
+        <v>79076</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>101920</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11395,10 +11395,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>431741</v>
+        <v>431918</v>
       </c>
       <c r="R110" t="n">
-        <v>6795079</v>
+        <v>6795574</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11445,22 +11445,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129707327</v>
+        <v>129695000</v>
       </c>
       <c r="B111" t="n">
-        <v>79695</v>
+        <v>79076</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11468,21 +11468,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11492,10 +11492,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>431893</v>
+        <v>431890</v>
       </c>
       <c r="R111" t="n">
-        <v>6795305</v>
+        <v>6795199</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11542,19 +11542,19 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129707406</v>
+        <v>129694992</v>
       </c>
       <c r="B112" t="n">
         <v>79076</v>
@@ -11589,10 +11589,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>431771</v>
+        <v>431799</v>
       </c>
       <c r="R112" t="n">
-        <v>6795344</v>
+        <v>6795129</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11639,22 +11639,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129707332</v>
+        <v>129694938</v>
       </c>
       <c r="B113" t="n">
-        <v>79695</v>
+        <v>57733</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11662,34 +11662,42 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>431923</v>
+        <v>431915</v>
       </c>
       <c r="R113" t="n">
-        <v>6795402</v>
+        <v>6795279</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11736,19 +11744,19 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129707425</v>
+        <v>129694990</v>
       </c>
       <c r="B114" t="n">
         <v>79076</v>
@@ -11783,10 +11791,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>431756</v>
+        <v>431726</v>
       </c>
       <c r="R114" t="n">
-        <v>6795247</v>
+        <v>6795117</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11833,22 +11841,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129694938</v>
+        <v>129694901</v>
       </c>
       <c r="B115" t="n">
-        <v>57733</v>
+        <v>79695</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11856,42 +11864,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>431915</v>
+        <v>431927</v>
       </c>
       <c r="R115" t="n">
-        <v>6795279</v>
+        <v>6795265</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11950,7 +11950,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129707309</v>
+        <v>129694844</v>
       </c>
       <c r="B116" t="n">
         <v>79695</v>
@@ -11985,10 +11985,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>431869</v>
+        <v>431739</v>
       </c>
       <c r="R116" t="n">
-        <v>6795521</v>
+        <v>6795440</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12035,19 +12035,19 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129707330</v>
+        <v>129707309</v>
       </c>
       <c r="B117" t="n">
         <v>79695</v>
@@ -12082,10 +12082,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>431930</v>
+        <v>431869</v>
       </c>
       <c r="R117" t="n">
-        <v>6795399</v>
+        <v>6795521</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12144,7 +12144,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129707323</v>
+        <v>129707330</v>
       </c>
       <c r="B118" t="n">
         <v>79695</v>
@@ -12179,10 +12179,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>431712</v>
+        <v>431930</v>
       </c>
       <c r="R118" t="n">
-        <v>6795236</v>
+        <v>6795399</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12241,10 +12241,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129707386</v>
+        <v>129707323</v>
       </c>
       <c r="B119" t="n">
-        <v>78833</v>
+        <v>79695</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12252,21 +12252,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12276,10 +12276,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>431897</v>
+        <v>431712</v>
       </c>
       <c r="R119" t="n">
-        <v>6795284</v>
+        <v>6795236</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12338,10 +12338,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129707421</v>
+        <v>129707386</v>
       </c>
       <c r="B120" t="n">
-        <v>79076</v>
+        <v>78833</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12349,21 +12349,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12373,10 +12373,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>431711</v>
+        <v>431897</v>
       </c>
       <c r="R120" t="n">
-        <v>6795239</v>
+        <v>6795284</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12435,10 +12435,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129694901</v>
+        <v>129707421</v>
       </c>
       <c r="B121" t="n">
-        <v>79695</v>
+        <v>79076</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12446,21 +12446,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12470,10 +12470,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>431927</v>
+        <v>431711</v>
       </c>
       <c r="R121" t="n">
-        <v>6795265</v>
+        <v>6795239</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12520,44 +12520,44 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129694844</v>
+        <v>129695013</v>
       </c>
       <c r="B122" t="n">
-        <v>79695</v>
+        <v>92870</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12567,10 +12567,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>431739</v>
+        <v>431869</v>
       </c>
       <c r="R122" t="n">
-        <v>6795440</v>
+        <v>6795173</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12629,7 +12629,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129694990</v>
+        <v>129694997</v>
       </c>
       <c r="B123" t="n">
         <v>79076</v>
@@ -12664,10 +12664,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>431726</v>
+        <v>431848</v>
       </c>
       <c r="R123" t="n">
-        <v>6795117</v>
+        <v>6795172</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12726,45 +12726,48 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129695013</v>
+        <v>129707368</v>
       </c>
       <c r="B124" t="n">
-        <v>92870</v>
+        <v>78834</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>431869</v>
+        <v>431820</v>
       </c>
       <c r="R124" t="n">
-        <v>6795173</v>
+        <v>6795331</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12805,28 +12808,29 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129694997</v>
+        <v>129694925</v>
       </c>
       <c r="B125" t="n">
-        <v>79076</v>
+        <v>57733</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12834,34 +12838,42 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>431848</v>
+        <v>431687</v>
       </c>
       <c r="R125" t="n">
-        <v>6795172</v>
+        <v>6795051</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12920,10 +12932,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129707368</v>
+        <v>129694850</v>
       </c>
       <c r="B126" t="n">
-        <v>78834</v>
+        <v>79695</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12931,37 +12943,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>431820</v>
+        <v>431686</v>
       </c>
       <c r="R126" t="n">
-        <v>6795331</v>
+        <v>6795471</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13002,26 +13011,25 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129694850</v>
+        <v>129694881</v>
       </c>
       <c r="B127" t="n">
         <v>79695</v>
@@ -13056,10 +13064,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>431686</v>
+        <v>431875</v>
       </c>
       <c r="R127" t="n">
-        <v>6795471</v>
+        <v>6795212</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13118,7 +13126,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129694881</v>
+        <v>129694888</v>
       </c>
       <c r="B128" t="n">
         <v>79695</v>
@@ -13153,10 +13161,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>431875</v>
+        <v>431889</v>
       </c>
       <c r="R128" t="n">
-        <v>6795212</v>
+        <v>6795236</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13215,7 +13223,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129694888</v>
+        <v>129707311</v>
       </c>
       <c r="B129" t="n">
         <v>79695</v>
@@ -13250,10 +13258,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>431889</v>
+        <v>431921</v>
       </c>
       <c r="R129" t="n">
-        <v>6795236</v>
+        <v>6795587</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13300,22 +13308,22 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129694925</v>
+        <v>129707438</v>
       </c>
       <c r="B130" t="n">
-        <v>57733</v>
+        <v>79076</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13323,42 +13331,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>431687</v>
+        <v>431965</v>
       </c>
       <c r="R130" t="n">
-        <v>6795051</v>
+        <v>6795405</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13405,22 +13405,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129707311</v>
+        <v>129707399</v>
       </c>
       <c r="B131" t="n">
-        <v>79695</v>
+        <v>79076</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13428,21 +13428,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13452,10 +13452,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>431921</v>
+        <v>431819</v>
       </c>
       <c r="R131" t="n">
-        <v>6795587</v>
+        <v>6795445</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13514,10 +13514,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129694900</v>
+        <v>129707387</v>
       </c>
       <c r="B132" t="n">
-        <v>79695</v>
+        <v>78833</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13525,21 +13525,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13549,10 +13549,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>431907</v>
+        <v>431936</v>
       </c>
       <c r="R132" t="n">
-        <v>6795266</v>
+        <v>6795393</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13599,19 +13599,19 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129694906</v>
+        <v>129707318</v>
       </c>
       <c r="B133" t="n">
         <v>79695</v>
@@ -13646,10 +13646,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>431934</v>
+        <v>431769</v>
       </c>
       <c r="R133" t="n">
-        <v>6795286</v>
+        <v>6795345</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13696,22 +13696,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129707438</v>
+        <v>129694900</v>
       </c>
       <c r="B134" t="n">
-        <v>79076</v>
+        <v>79695</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13719,21 +13719,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13743,10 +13743,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>431965</v>
+        <v>431907</v>
       </c>
       <c r="R134" t="n">
-        <v>6795405</v>
+        <v>6795266</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13793,22 +13793,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129707399</v>
+        <v>129694906</v>
       </c>
       <c r="B135" t="n">
-        <v>79076</v>
+        <v>79695</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13816,21 +13816,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13840,10 +13840,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>431819</v>
+        <v>431934</v>
       </c>
       <c r="R135" t="n">
-        <v>6795445</v>
+        <v>6795286</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -13890,22 +13890,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129707387</v>
+        <v>129694866</v>
       </c>
       <c r="B136" t="n">
-        <v>78833</v>
+        <v>79695</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13913,21 +13913,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -13937,10 +13937,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>431936</v>
+        <v>431797</v>
       </c>
       <c r="R136" t="n">
-        <v>6795393</v>
+        <v>6795173</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -13987,19 +13987,19 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129707318</v>
+        <v>129694865</v>
       </c>
       <c r="B137" t="n">
         <v>79695</v>
@@ -14034,10 +14034,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>431769</v>
+        <v>431787</v>
       </c>
       <c r="R137" t="n">
-        <v>6795345</v>
+        <v>6795115</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14084,19 +14084,19 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129694866</v>
+        <v>129694896</v>
       </c>
       <c r="B138" t="n">
         <v>79695</v>
@@ -14131,10 +14131,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>431797</v>
+        <v>431900</v>
       </c>
       <c r="R138" t="n">
-        <v>6795173</v>
+        <v>6795265</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14193,10 +14193,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129694865</v>
+        <v>129694956</v>
       </c>
       <c r="B139" t="n">
-        <v>79695</v>
+        <v>92006</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14204,34 +14204,33 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>431787</v>
+        <v>431718</v>
       </c>
       <c r="R139" t="n">
-        <v>6795115</v>
+        <v>6795082</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14266,12 +14265,18 @@
           <t>2025-11-14</t>
         </is>
       </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Mjuk och len på undetsidan, sämskskinnslik känsla</t>
+        </is>
+      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -14290,7 +14295,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129694896</v>
+        <v>129707334</v>
       </c>
       <c r="B140" t="n">
         <v>79695</v>
@@ -14325,10 +14330,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>431900</v>
+        <v>431936</v>
       </c>
       <c r="R140" t="n">
-        <v>6795265</v>
+        <v>6795411</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14375,22 +14380,22 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129694956</v>
+        <v>129707370</v>
       </c>
       <c r="B141" t="n">
-        <v>92006</v>
+        <v>78834</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14398,33 +14403,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6040162</v>
+        <v>228912</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>431718</v>
+        <v>431913</v>
       </c>
       <c r="R141" t="n">
-        <v>6795082</v>
+        <v>6795394</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14459,40 +14465,34 @@
           <t>2025-11-14</t>
         </is>
       </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Mjuk och len på undetsidan, sämskskinnslik känsla</t>
-        </is>
-      </c>
       <c r="AD141" t="b">
         <v>0</v>
       </c>
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129707334</v>
+        <v>129707377</v>
       </c>
       <c r="B142" t="n">
-        <v>79695</v>
+        <v>78833</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14500,21 +14500,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14524,10 +14524,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>431936</v>
+        <v>431843</v>
       </c>
       <c r="R142" t="n">
-        <v>6795411</v>
+        <v>6795474</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14586,7 +14586,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129707370</v>
+        <v>129707366</v>
       </c>
       <c r="B143" t="n">
         <v>78834</v>
@@ -14621,10 +14621,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>431913</v>
+        <v>431840</v>
       </c>
       <c r="R143" t="n">
-        <v>6795394</v>
+        <v>6795476</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14683,10 +14683,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129707377</v>
+        <v>129694876</v>
       </c>
       <c r="B144" t="n">
-        <v>78833</v>
+        <v>79695</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14694,21 +14694,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14718,10 +14718,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>431843</v>
+        <v>431871</v>
       </c>
       <c r="R144" t="n">
-        <v>6795474</v>
+        <v>6795171</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14768,22 +14768,22 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129707366</v>
+        <v>129694887</v>
       </c>
       <c r="B145" t="n">
-        <v>78834</v>
+        <v>79695</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14791,21 +14791,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -14815,10 +14815,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>431840</v>
+        <v>431886</v>
       </c>
       <c r="R145" t="n">
-        <v>6795476</v>
+        <v>6795236</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -14865,19 +14865,19 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129694876</v>
+        <v>129694880</v>
       </c>
       <c r="B146" t="n">
         <v>79695</v>
@@ -14915,7 +14915,7 @@
         <v>431871</v>
       </c>
       <c r="R146" t="n">
-        <v>6795171</v>
+        <v>6795205</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -14974,7 +14974,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129694887</v>
+        <v>129694897</v>
       </c>
       <c r="B147" t="n">
         <v>79695</v>
@@ -15009,10 +15009,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>431886</v>
+        <v>431906</v>
       </c>
       <c r="R147" t="n">
-        <v>6795236</v>
+        <v>6795283</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15068,200 +15068,6 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
-    </row>
-    <row r="148">
-      <c r="A148" t="n">
-        <v>129694880</v>
-      </c>
-      <c r="B148" t="n">
-        <v>79695</v>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E148" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr"/>
-      <c r="P148" t="inlineStr">
-        <is>
-          <t>Bredvad, Dlr</t>
-        </is>
-      </c>
-      <c r="Q148" t="n">
-        <v>431871</v>
-      </c>
-      <c r="R148" t="n">
-        <v>6795205</v>
-      </c>
-      <c r="S148" t="n">
-        <v>10</v>
-      </c>
-      <c r="T148" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U148" t="inlineStr">
-        <is>
-          <t>Älvdalen</t>
-        </is>
-      </c>
-      <c r="V148" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W148" t="inlineStr">
-        <is>
-          <t>Älvdalen</t>
-        </is>
-      </c>
-      <c r="Y148" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="AA148" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="AD148" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE148" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG148" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT148" t="inlineStr"/>
-      <c r="AW148" t="inlineStr">
-        <is>
-          <t>Louise Tegnér</t>
-        </is>
-      </c>
-      <c r="AX148" t="inlineStr">
-        <is>
-          <t>Louise Tegnér</t>
-        </is>
-      </c>
-      <c r="AY148" t="inlineStr"/>
-    </row>
-    <row r="149">
-      <c r="A149" t="n">
-        <v>129694897</v>
-      </c>
-      <c r="B149" t="n">
-        <v>79695</v>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E149" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
-      <c r="P149" t="inlineStr">
-        <is>
-          <t>Bredvad, Dlr</t>
-        </is>
-      </c>
-      <c r="Q149" t="n">
-        <v>431906</v>
-      </c>
-      <c r="R149" t="n">
-        <v>6795283</v>
-      </c>
-      <c r="S149" t="n">
-        <v>10</v>
-      </c>
-      <c r="T149" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U149" t="inlineStr">
-        <is>
-          <t>Älvdalen</t>
-        </is>
-      </c>
-      <c r="V149" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W149" t="inlineStr">
-        <is>
-          <t>Älvdalen</t>
-        </is>
-      </c>
-      <c r="Y149" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="AA149" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="AD149" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE149" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG149" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT149" t="inlineStr"/>
-      <c r="AW149" t="inlineStr">
-        <is>
-          <t>Louise Tegnér</t>
-        </is>
-      </c>
-      <c r="AX149" t="inlineStr">
-        <is>
-          <t>Louise Tegnér</t>
-        </is>
-      </c>
-      <c r="AY149" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50492-2025 artfynd.xlsx
+++ b/artfynd/A 50492-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129707216</v>
       </c>
       <c r="B2" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129707403</v>
       </c>
       <c r="B3" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,32 +873,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129707440</v>
+        <v>129694842</v>
       </c>
       <c r="B4" t="n">
-        <v>92870</v>
+        <v>79700</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -908,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>431828</v>
+        <v>431768</v>
       </c>
       <c r="R4" t="n">
-        <v>6795476</v>
+        <v>6795469</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -958,22 +958,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129694842</v>
+        <v>129694957</v>
       </c>
       <c r="B5" t="n">
-        <v>79695</v>
+        <v>78838</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -981,21 +981,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1005,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>431768</v>
+        <v>431725</v>
       </c>
       <c r="R5" t="n">
-        <v>6795469</v>
+        <v>6795459</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,10 +1067,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129694957</v>
+        <v>129694862</v>
       </c>
       <c r="B6" t="n">
-        <v>78833</v>
+        <v>79700</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1078,21 +1078,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>431725</v>
+        <v>431756</v>
       </c>
       <c r="R6" t="n">
-        <v>6795459</v>
+        <v>6795121</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,10 +1164,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129694862</v>
+        <v>129694935</v>
       </c>
       <c r="B7" t="n">
-        <v>79695</v>
+        <v>57733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1175,34 +1175,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>431756</v>
+        <v>431917</v>
       </c>
       <c r="R7" t="n">
-        <v>6795121</v>
+        <v>6795290</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,7 +1269,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129694935</v>
+        <v>129694929</v>
       </c>
       <c r="B8" t="n">
         <v>57733</v>
@@ -1304,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>431917</v>
+        <v>431859</v>
       </c>
       <c r="R8" t="n">
-        <v>6795290</v>
+        <v>6795172</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1366,53 +1374,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129694929</v>
+        <v>129707440</v>
       </c>
       <c r="B9" t="n">
-        <v>57733</v>
+        <v>92875</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>431859</v>
+        <v>431828</v>
       </c>
       <c r="R9" t="n">
-        <v>6795172</v>
+        <v>6795476</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,12 +1459,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1578,10 +1578,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129707358</v>
+        <v>129707336</v>
       </c>
       <c r="B11" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1589,42 +1589,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>431912</v>
+        <v>431993</v>
       </c>
       <c r="R11" t="n">
-        <v>6795310</v>
+        <v>6795380</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1686,7 +1678,7 @@
         <v>129694843</v>
       </c>
       <c r="B12" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1783,7 +1775,7 @@
         <v>129694907</v>
       </c>
       <c r="B13" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1877,10 +1869,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129707336</v>
+        <v>129694918</v>
       </c>
       <c r="B14" t="n">
-        <v>79695</v>
+        <v>91614</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1888,34 +1880,41 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>431993</v>
+        <v>431722</v>
       </c>
       <c r="R14" t="n">
-        <v>6795380</v>
+        <v>6795120</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1956,28 +1955,29 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129707434</v>
+        <v>129694983</v>
       </c>
       <c r="B15" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>431894</v>
+        <v>431689</v>
       </c>
       <c r="R15" t="n">
-        <v>6795261</v>
+        <v>6795456</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2059,22 +2059,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129694918</v>
+        <v>129694923</v>
       </c>
       <c r="B16" t="n">
-        <v>91609</v>
+        <v>57733</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2082,30 +2082,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2113,10 +2114,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>431722</v>
+        <v>431687</v>
       </c>
       <c r="R16" t="n">
-        <v>6795120</v>
+        <v>6795471</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2157,7 +2158,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2176,10 +2176,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129694923</v>
+        <v>129707434</v>
       </c>
       <c r="B17" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2187,42 +2187,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>431687</v>
+        <v>431894</v>
       </c>
       <c r="R17" t="n">
-        <v>6795471</v>
+        <v>6795261</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2269,22 +2261,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129694983</v>
+        <v>129707358</v>
       </c>
       <c r="B18" t="n">
-        <v>79076</v>
+        <v>57733</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2292,34 +2284,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>431689</v>
+        <v>431912</v>
       </c>
       <c r="R18" t="n">
-        <v>6795456</v>
+        <v>6795310</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2366,57 +2366,65 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129707378</v>
+        <v>129694913</v>
       </c>
       <c r="B19" t="n">
-        <v>78833</v>
+        <v>56926</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>431814</v>
+        <v>431728</v>
       </c>
       <c r="R19" t="n">
-        <v>6795444</v>
+        <v>6795109</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2463,12 +2471,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2478,7 +2486,7 @@
         <v>129707310</v>
       </c>
       <c r="B20" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2572,10 +2580,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129694845</v>
+        <v>129707335</v>
       </c>
       <c r="B21" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2607,10 +2615,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>431722</v>
+        <v>431965</v>
       </c>
       <c r="R21" t="n">
-        <v>6795478</v>
+        <v>6795430</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2657,22 +2665,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129707335</v>
+        <v>129694845</v>
       </c>
       <c r="B22" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2704,10 +2712,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>431965</v>
+        <v>431722</v>
       </c>
       <c r="R22" t="n">
-        <v>6795430</v>
+        <v>6795478</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2754,65 +2762,57 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129694913</v>
+        <v>129707378</v>
       </c>
       <c r="B23" t="n">
-        <v>56926</v>
+        <v>78838</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>431728</v>
+        <v>431814</v>
       </c>
       <c r="R23" t="n">
-        <v>6795109</v>
+        <v>6795444</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2859,12 +2859,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -2874,7 +2874,7 @@
         <v>129694942</v>
       </c>
       <c r="B24" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>129694883</v>
       </c>
       <c r="B25" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>129694884</v>
       </c>
       <c r="B26" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>129694898</v>
       </c>
       <c r="B27" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>129694899</v>
       </c>
       <c r="B28" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>129694861</v>
       </c>
       <c r="B29" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>129707308</v>
       </c>
       <c r="B30" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3551,10 +3551,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129707407</v>
+        <v>129707331</v>
       </c>
       <c r="B31" t="n">
-        <v>79076</v>
+        <v>79700</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3562,34 +3562,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>431723</v>
+        <v>431916</v>
       </c>
       <c r="R31" t="n">
-        <v>6795371</v>
+        <v>6795392</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3630,6 +3633,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3648,10 +3652,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129707331</v>
+        <v>129707407</v>
       </c>
       <c r="B32" t="n">
-        <v>79695</v>
+        <v>79081</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3659,37 +3663,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>431916</v>
+        <v>431723</v>
       </c>
       <c r="R32" t="n">
-        <v>6795392</v>
+        <v>6795371</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3730,7 +3731,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3752,7 +3752,7 @@
         <v>129695010</v>
       </c>
       <c r="B33" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3846,10 +3846,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129694980</v>
+        <v>129694839</v>
       </c>
       <c r="B34" t="n">
-        <v>79076</v>
+        <v>91516</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3857,34 +3857,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>431711</v>
+        <v>431869</v>
       </c>
       <c r="R34" t="n">
-        <v>6795450</v>
+        <v>6795181</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3925,6 +3928,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -3943,10 +3947,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129694886</v>
+        <v>129694917</v>
       </c>
       <c r="B35" t="n">
-        <v>79695</v>
+        <v>91614</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3954,34 +3958,41 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>431873</v>
+        <v>431672</v>
       </c>
       <c r="R35" t="n">
-        <v>6795241</v>
+        <v>6795442</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4022,6 +4033,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4040,10 +4052,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129694878</v>
+        <v>129694980</v>
       </c>
       <c r="B36" t="n">
-        <v>79695</v>
+        <v>79081</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4051,21 +4063,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4075,10 +4087,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>431889</v>
+        <v>431711</v>
       </c>
       <c r="R36" t="n">
-        <v>6795186</v>
+        <v>6795450</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4137,10 +4149,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129694917</v>
+        <v>129694921</v>
       </c>
       <c r="B37" t="n">
-        <v>91609</v>
+        <v>57733</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4148,30 +4160,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4179,10 +4192,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>431672</v>
+        <v>431725</v>
       </c>
       <c r="R37" t="n">
-        <v>6795442</v>
+        <v>6795459</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4223,7 +4236,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4242,10 +4254,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129707390</v>
+        <v>129707346</v>
       </c>
       <c r="B38" t="n">
-        <v>78833</v>
+        <v>57733</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4253,26 +4265,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4280,10 +4297,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>431952</v>
+        <v>431819</v>
       </c>
       <c r="R38" t="n">
-        <v>6795410</v>
+        <v>6795465</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4324,7 +4341,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4343,10 +4359,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129707346</v>
+        <v>129694886</v>
       </c>
       <c r="B39" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4354,42 +4370,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>431819</v>
+        <v>431873</v>
       </c>
       <c r="R39" t="n">
-        <v>6795465</v>
+        <v>6795241</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4436,22 +4444,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129694839</v>
+        <v>129694878</v>
       </c>
       <c r="B40" t="n">
-        <v>91511</v>
+        <v>79700</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4459,37 +4467,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3242</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>431869</v>
+        <v>431889</v>
       </c>
       <c r="R40" t="n">
-        <v>6795181</v>
+        <v>6795186</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4530,7 +4535,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4549,10 +4553,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129694921</v>
+        <v>129707390</v>
       </c>
       <c r="B41" t="n">
-        <v>57733</v>
+        <v>78838</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4560,31 +4564,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4592,10 +4591,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>431725</v>
+        <v>431952</v>
       </c>
       <c r="R41" t="n">
-        <v>6795459</v>
+        <v>6795410</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4636,28 +4635,29 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129707320</v>
+        <v>129694999</v>
       </c>
       <c r="B42" t="n">
-        <v>79695</v>
+        <v>79081</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4665,21 +4665,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>431717</v>
+        <v>431859</v>
       </c>
       <c r="R42" t="n">
-        <v>6795380</v>
+        <v>6795172</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4739,22 +4739,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129707316</v>
+        <v>129707320</v>
       </c>
       <c r="B43" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4786,10 +4786,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>431812</v>
+        <v>431717</v>
       </c>
       <c r="R43" t="n">
-        <v>6795349</v>
+        <v>6795380</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4848,10 +4848,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129707333</v>
+        <v>129707316</v>
       </c>
       <c r="B44" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>431935</v>
+        <v>431812</v>
       </c>
       <c r="R44" t="n">
-        <v>6795415</v>
+        <v>6795349</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4945,10 +4945,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129707338</v>
+        <v>129707333</v>
       </c>
       <c r="B45" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4980,10 +4980,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>431932</v>
+        <v>431935</v>
       </c>
       <c r="R45" t="n">
-        <v>6795406</v>
+        <v>6795415</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5042,10 +5042,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129707375</v>
+        <v>129707338</v>
       </c>
       <c r="B46" t="n">
-        <v>78833</v>
+        <v>79700</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5053,21 +5053,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5077,10 +5077,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>431881</v>
+        <v>431932</v>
       </c>
       <c r="R46" t="n">
-        <v>6795522</v>
+        <v>6795406</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5139,10 +5139,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129707351</v>
+        <v>129707375</v>
       </c>
       <c r="B47" t="n">
-        <v>57733</v>
+        <v>78838</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5150,42 +5150,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>431756</v>
+        <v>431881</v>
       </c>
       <c r="R47" t="n">
-        <v>6795202</v>
+        <v>6795522</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5244,10 +5236,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129694847</v>
+        <v>129707351</v>
       </c>
       <c r="B48" t="n">
-        <v>79695</v>
+        <v>57733</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5255,34 +5247,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>431724</v>
+        <v>431756</v>
       </c>
       <c r="R48" t="n">
-        <v>6795460</v>
+        <v>6795202</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5329,22 +5329,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129694999</v>
+        <v>129694847</v>
       </c>
       <c r="B49" t="n">
-        <v>79076</v>
+        <v>79700</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5352,21 +5352,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5376,10 +5376,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>431859</v>
+        <v>431724</v>
       </c>
       <c r="R49" t="n">
-        <v>6795172</v>
+        <v>6795460</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5543,10 +5543,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129695006</v>
+        <v>129707337</v>
       </c>
       <c r="B51" t="n">
-        <v>79076</v>
+        <v>79700</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5554,21 +5554,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5578,10 +5578,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>431962</v>
+        <v>431999</v>
       </c>
       <c r="R51" t="n">
-        <v>6795319</v>
+        <v>6795416</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5628,22 +5628,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129695003</v>
+        <v>129707426</v>
       </c>
       <c r="B52" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5675,10 +5675,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>431908</v>
+        <v>431767</v>
       </c>
       <c r="R52" t="n">
-        <v>6795302</v>
+        <v>6795219</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5725,22 +5725,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129694994</v>
+        <v>129707404</v>
       </c>
       <c r="B53" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5766,16 +5766,19 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>431804</v>
+        <v>431816</v>
       </c>
       <c r="R53" t="n">
-        <v>6795151</v>
+        <v>6795333</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5810,34 +5813,40 @@
           <t>2025-11-14</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129694846</v>
+        <v>129707380</v>
       </c>
       <c r="B54" t="n">
-        <v>79695</v>
+        <v>78838</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5845,21 +5854,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5869,10 +5878,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>431725</v>
+        <v>431820</v>
       </c>
       <c r="R54" t="n">
-        <v>6795467</v>
+        <v>6795330</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5919,22 +5928,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129707347</v>
+        <v>129695006</v>
       </c>
       <c r="B55" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5942,42 +5951,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>431662</v>
+        <v>431962</v>
       </c>
       <c r="R55" t="n">
-        <v>6795391</v>
+        <v>6795319</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6024,22 +6025,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129707426</v>
+        <v>129695003</v>
       </c>
       <c r="B56" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6071,10 +6072,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>431767</v>
+        <v>431908</v>
       </c>
       <c r="R56" t="n">
-        <v>6795219</v>
+        <v>6795302</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6121,22 +6122,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129707404</v>
+        <v>129694994</v>
       </c>
       <c r="B57" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6162,19 +6163,16 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>431816</v>
+        <v>431804</v>
       </c>
       <c r="R57" t="n">
-        <v>6795333</v>
+        <v>6795151</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6209,40 +6207,34 @@
           <t>2025-11-14</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129707337</v>
+        <v>129694846</v>
       </c>
       <c r="B58" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6274,10 +6266,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>431999</v>
+        <v>431725</v>
       </c>
       <c r="R58" t="n">
-        <v>6795416</v>
+        <v>6795467</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6324,22 +6316,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129707380</v>
+        <v>129707347</v>
       </c>
       <c r="B59" t="n">
-        <v>78833</v>
+        <v>57733</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6347,34 +6339,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>431820</v>
+        <v>431662</v>
       </c>
       <c r="R59" t="n">
-        <v>6795330</v>
+        <v>6795391</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6433,10 +6433,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129707319</v>
+        <v>129694930</v>
       </c>
       <c r="B60" t="n">
-        <v>79695</v>
+        <v>57733</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6444,34 +6444,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>431708</v>
+        <v>431875</v>
       </c>
       <c r="R60" t="n">
-        <v>6795371</v>
+        <v>6795244</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6518,12 +6526,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -6533,7 +6541,7 @@
         <v>129694988</v>
       </c>
       <c r="B61" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6630,7 +6638,7 @@
         <v>129694872</v>
       </c>
       <c r="B62" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6727,7 +6735,7 @@
         <v>129694856</v>
       </c>
       <c r="B63" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6824,7 +6832,7 @@
         <v>129694961</v>
       </c>
       <c r="B64" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6918,10 +6926,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129694930</v>
+        <v>129707319</v>
       </c>
       <c r="B65" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6929,42 +6937,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>431875</v>
+        <v>431708</v>
       </c>
       <c r="R65" t="n">
-        <v>6795244</v>
+        <v>6795371</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7011,22 +7011,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129707382</v>
+        <v>129694857</v>
       </c>
       <c r="B66" t="n">
-        <v>78833</v>
+        <v>79700</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7034,37 +7034,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>431689</v>
+        <v>431800</v>
       </c>
       <c r="R66" t="n">
-        <v>6795383</v>
+        <v>6795130</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7105,29 +7102,28 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129694928</v>
+        <v>129694908</v>
       </c>
       <c r="B67" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7135,42 +7131,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>431801</v>
+        <v>431973</v>
       </c>
       <c r="R67" t="n">
-        <v>6795136</v>
+        <v>6795310</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7229,10 +7217,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129707420</v>
+        <v>129694858</v>
       </c>
       <c r="B68" t="n">
-        <v>79076</v>
+        <v>79700</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7240,21 +7228,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7264,10 +7252,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>431695</v>
+        <v>431749</v>
       </c>
       <c r="R68" t="n">
-        <v>6795256</v>
+        <v>6795079</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7314,22 +7302,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129694857</v>
+        <v>129694859</v>
       </c>
       <c r="B69" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7361,10 +7349,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>431800</v>
+        <v>431702</v>
       </c>
       <c r="R69" t="n">
-        <v>6795130</v>
+        <v>6795115</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7423,10 +7411,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129694908</v>
+        <v>129694879</v>
       </c>
       <c r="B70" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7458,10 +7446,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>431973</v>
+        <v>431888</v>
       </c>
       <c r="R70" t="n">
-        <v>6795310</v>
+        <v>6795198</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7520,10 +7508,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129694858</v>
+        <v>129694928</v>
       </c>
       <c r="B71" t="n">
-        <v>79695</v>
+        <v>57733</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7531,34 +7519,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>431749</v>
+        <v>431801</v>
       </c>
       <c r="R71" t="n">
-        <v>6795079</v>
+        <v>6795136</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7617,10 +7613,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129694859</v>
+        <v>129707382</v>
       </c>
       <c r="B72" t="n">
-        <v>79695</v>
+        <v>78838</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7628,34 +7624,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>431702</v>
+        <v>431689</v>
       </c>
       <c r="R72" t="n">
-        <v>6795115</v>
+        <v>6795383</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7696,28 +7695,29 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129694879</v>
+        <v>129707420</v>
       </c>
       <c r="B73" t="n">
-        <v>79695</v>
+        <v>79081</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7725,21 +7725,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7749,10 +7749,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>431888</v>
+        <v>431695</v>
       </c>
       <c r="R73" t="n">
-        <v>6795198</v>
+        <v>6795256</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7799,12 +7799,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -7814,7 +7814,7 @@
         <v>129707439</v>
       </c>
       <c r="B74" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7908,10 +7908,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129707317</v>
+        <v>129694985</v>
       </c>
       <c r="B75" t="n">
-        <v>79695</v>
+        <v>79081</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7919,21 +7919,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7943,10 +7943,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>431780</v>
+        <v>431673</v>
       </c>
       <c r="R75" t="n">
-        <v>6795362</v>
+        <v>6795435</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7993,22 +7993,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129707391</v>
+        <v>129707317</v>
       </c>
       <c r="B76" t="n">
-        <v>78833</v>
+        <v>79700</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8016,21 +8016,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>431724</v>
+        <v>431780</v>
       </c>
       <c r="R76" t="n">
-        <v>6795372</v>
+        <v>6795362</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8102,10 +8102,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129707389</v>
+        <v>129707314</v>
       </c>
       <c r="B77" t="n">
-        <v>78833</v>
+        <v>79700</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8113,37 +8113,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>431922</v>
+        <v>431866</v>
       </c>
       <c r="R77" t="n">
-        <v>6795405</v>
+        <v>6795513</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8184,7 +8181,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8203,10 +8199,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129707314</v>
+        <v>129707391</v>
       </c>
       <c r="B78" t="n">
-        <v>79695</v>
+        <v>78838</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8214,21 +8210,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8238,10 +8234,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>431866</v>
+        <v>431724</v>
       </c>
       <c r="R78" t="n">
-        <v>6795513</v>
+        <v>6795372</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8300,10 +8296,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129694985</v>
+        <v>129707389</v>
       </c>
       <c r="B79" t="n">
-        <v>79076</v>
+        <v>78838</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8311,34 +8307,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>431673</v>
+        <v>431922</v>
       </c>
       <c r="R79" t="n">
-        <v>6795435</v>
+        <v>6795405</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8379,28 +8378,29 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129707388</v>
+        <v>129694863</v>
       </c>
       <c r="B80" t="n">
-        <v>78833</v>
+        <v>79700</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8408,21 +8408,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8432,10 +8432,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>431915</v>
+        <v>431785</v>
       </c>
       <c r="R80" t="n">
-        <v>6795392</v>
+        <v>6795106</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8482,22 +8482,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129707315</v>
+        <v>129694874</v>
       </c>
       <c r="B81" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>431820</v>
+        <v>431827</v>
       </c>
       <c r="R81" t="n">
-        <v>6795329</v>
+        <v>6795171</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8579,22 +8579,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129707424</v>
+        <v>129694948</v>
       </c>
       <c r="B82" t="n">
-        <v>79076</v>
+        <v>78839</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8602,21 +8602,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8626,10 +8626,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>431760</v>
+        <v>431725</v>
       </c>
       <c r="R82" t="n">
-        <v>6795200</v>
+        <v>6795459</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8676,22 +8676,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129707345</v>
+        <v>129707315</v>
       </c>
       <c r="B83" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8699,42 +8699,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>431893</v>
+        <v>431820</v>
       </c>
       <c r="R83" t="n">
-        <v>6795571</v>
+        <v>6795329</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8793,10 +8785,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129695001</v>
+        <v>129707345</v>
       </c>
       <c r="B84" t="n">
-        <v>79076</v>
+        <v>57733</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8804,34 +8796,42 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>431876</v>
+        <v>431893</v>
       </c>
       <c r="R84" t="n">
-        <v>6795202</v>
+        <v>6795571</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8878,22 +8878,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129694991</v>
+        <v>129695001</v>
       </c>
       <c r="B85" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8925,10 +8925,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>431760</v>
+        <v>431876</v>
       </c>
       <c r="R85" t="n">
-        <v>6795115</v>
+        <v>6795202</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8987,10 +8987,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129694863</v>
+        <v>129694991</v>
       </c>
       <c r="B86" t="n">
-        <v>79695</v>
+        <v>79081</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8998,21 +8998,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9022,10 +9022,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>431785</v>
+        <v>431760</v>
       </c>
       <c r="R86" t="n">
-        <v>6795106</v>
+        <v>6795115</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9084,10 +9084,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129694874</v>
+        <v>129694933</v>
       </c>
       <c r="B87" t="n">
-        <v>79695</v>
+        <v>57733</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9095,34 +9095,42 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>431827</v>
+        <v>431904</v>
       </c>
       <c r="R87" t="n">
-        <v>6795171</v>
+        <v>6795243</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9181,10 +9189,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129694933</v>
+        <v>129707388</v>
       </c>
       <c r="B88" t="n">
-        <v>57733</v>
+        <v>78838</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9192,42 +9200,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>431904</v>
+        <v>431915</v>
       </c>
       <c r="R88" t="n">
-        <v>6795243</v>
+        <v>6795392</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9274,22 +9274,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129694948</v>
+        <v>129707424</v>
       </c>
       <c r="B89" t="n">
-        <v>78834</v>
+        <v>79081</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9297,21 +9297,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9321,10 +9321,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>431725</v>
+        <v>431760</v>
       </c>
       <c r="R89" t="n">
-        <v>6795459</v>
+        <v>6795200</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9371,22 +9371,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129707405</v>
+        <v>129694939</v>
       </c>
       <c r="B90" t="n">
-        <v>79076</v>
+        <v>57733</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9394,21 +9394,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9418,10 +9418,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>431775</v>
+        <v>431913</v>
       </c>
       <c r="R90" t="n">
-        <v>6795343</v>
+        <v>6795284</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9456,6 +9456,11 @@
           <t>2025-11-14</t>
         </is>
       </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
@@ -9468,22 +9473,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129707381</v>
+        <v>129694934</v>
       </c>
       <c r="B91" t="n">
-        <v>78833</v>
+        <v>57733</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9491,34 +9496,42 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>431712</v>
+        <v>431916</v>
       </c>
       <c r="R91" t="n">
-        <v>6795379</v>
+        <v>6795286</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9565,22 +9578,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129694860</v>
+        <v>129707405</v>
       </c>
       <c r="B92" t="n">
-        <v>79695</v>
+        <v>79081</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9588,21 +9601,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9612,10 +9625,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>431746</v>
+        <v>431775</v>
       </c>
       <c r="R92" t="n">
-        <v>6795081</v>
+        <v>6795343</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9662,22 +9675,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129694965</v>
+        <v>129694860</v>
       </c>
       <c r="B93" t="n">
-        <v>78833</v>
+        <v>79700</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9685,21 +9698,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9709,10 +9722,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>431885</v>
+        <v>431746</v>
       </c>
       <c r="R93" t="n">
-        <v>6795240</v>
+        <v>6795081</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9771,10 +9784,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129694934</v>
+        <v>129694965</v>
       </c>
       <c r="B94" t="n">
-        <v>57733</v>
+        <v>78838</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9782,42 +9795,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>431916</v>
+        <v>431885</v>
       </c>
       <c r="R94" t="n">
-        <v>6795286</v>
+        <v>6795240</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9876,10 +9881,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129694939</v>
+        <v>129707381</v>
       </c>
       <c r="B95" t="n">
-        <v>57733</v>
+        <v>78838</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9887,21 +9892,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9911,10 +9916,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>431913</v>
+        <v>431712</v>
       </c>
       <c r="R95" t="n">
-        <v>6795284</v>
+        <v>6795379</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9949,11 +9954,6 @@
           <t>2025-11-14</t>
         </is>
       </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
@@ -9966,12 +9966,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -10086,7 +10086,7 @@
         <v>129694989</v>
       </c>
       <c r="B97" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10183,7 +10183,7 @@
         <v>129694941</v>
       </c>
       <c r="B98" t="n">
-        <v>79162</v>
+        <v>79167</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10280,7 +10280,7 @@
         <v>129707312</v>
       </c>
       <c r="B99" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
         <v>129694877</v>
       </c>
       <c r="B100" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10471,10 +10471,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129707327</v>
+        <v>129694885</v>
       </c>
       <c r="B101" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10506,10 +10506,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>431893</v>
+        <v>431873</v>
       </c>
       <c r="R101" t="n">
-        <v>6795305</v>
+        <v>6795224</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10556,22 +10556,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129707406</v>
+        <v>129694864</v>
       </c>
       <c r="B102" t="n">
-        <v>79076</v>
+        <v>79700</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10579,21 +10579,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10603,10 +10603,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>431771</v>
+        <v>431786</v>
       </c>
       <c r="R102" t="n">
-        <v>6795344</v>
+        <v>6795113</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10653,22 +10653,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129707332</v>
+        <v>129707327</v>
       </c>
       <c r="B103" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10700,10 +10700,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>431923</v>
+        <v>431893</v>
       </c>
       <c r="R103" t="n">
-        <v>6795402</v>
+        <v>6795305</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10762,10 +10762,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129707425</v>
+        <v>129707332</v>
       </c>
       <c r="B104" t="n">
-        <v>79076</v>
+        <v>79700</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10773,21 +10773,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10797,10 +10797,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>431756</v>
+        <v>431923</v>
       </c>
       <c r="R104" t="n">
-        <v>6795247</v>
+        <v>6795402</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10859,7 +10859,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129707349</v>
+        <v>129694927</v>
       </c>
       <c r="B105" t="n">
         <v>57733</v>
@@ -10902,10 +10902,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>431722</v>
+        <v>431711</v>
       </c>
       <c r="R105" t="n">
-        <v>6795217</v>
+        <v>6795094</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10952,22 +10952,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129694885</v>
+        <v>129694938</v>
       </c>
       <c r="B106" t="n">
-        <v>79695</v>
+        <v>57733</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10975,34 +10975,42 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>431873</v>
+        <v>431915</v>
       </c>
       <c r="R106" t="n">
-        <v>6795224</v>
+        <v>6795279</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11061,10 +11069,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129694864</v>
+        <v>129695000</v>
       </c>
       <c r="B107" t="n">
-        <v>79695</v>
+        <v>79081</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11072,21 +11080,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11096,10 +11104,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>431786</v>
+        <v>431890</v>
       </c>
       <c r="R107" t="n">
-        <v>6795113</v>
+        <v>6795199</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11158,10 +11166,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129694927</v>
+        <v>129694992</v>
       </c>
       <c r="B108" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11169,42 +11177,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>431711</v>
+        <v>431799</v>
       </c>
       <c r="R108" t="n">
-        <v>6795094</v>
+        <v>6795129</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11266,7 +11266,7 @@
         <v>129707397</v>
       </c>
       <c r="B109" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11363,7 +11363,7 @@
         <v>129707396</v>
       </c>
       <c r="B110" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11457,10 +11457,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129695000</v>
+        <v>129707406</v>
       </c>
       <c r="B111" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11492,10 +11492,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>431890</v>
+        <v>431771</v>
       </c>
       <c r="R111" t="n">
-        <v>6795199</v>
+        <v>6795344</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11542,22 +11542,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129694992</v>
+        <v>129707425</v>
       </c>
       <c r="B112" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11589,10 +11589,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>431799</v>
+        <v>431756</v>
       </c>
       <c r="R112" t="n">
-        <v>6795129</v>
+        <v>6795247</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11639,19 +11639,19 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129694938</v>
+        <v>129707349</v>
       </c>
       <c r="B113" t="n">
         <v>57733</v>
@@ -11694,10 +11694,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>431915</v>
+        <v>431722</v>
       </c>
       <c r="R113" t="n">
-        <v>6795279</v>
+        <v>6795217</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11744,22 +11744,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129694990</v>
+        <v>129707309</v>
       </c>
       <c r="B114" t="n">
-        <v>79076</v>
+        <v>79700</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11767,21 +11767,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11791,10 +11791,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>431726</v>
+        <v>431869</v>
       </c>
       <c r="R114" t="n">
-        <v>6795117</v>
+        <v>6795521</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11841,22 +11841,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129694901</v>
+        <v>129707330</v>
       </c>
       <c r="B115" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11888,10 +11888,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>431927</v>
+        <v>431930</v>
       </c>
       <c r="R115" t="n">
-        <v>6795265</v>
+        <v>6795399</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11938,22 +11938,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129694844</v>
+        <v>129707323</v>
       </c>
       <c r="B116" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11985,10 +11985,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>431739</v>
+        <v>431712</v>
       </c>
       <c r="R116" t="n">
-        <v>6795440</v>
+        <v>6795236</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12035,22 +12035,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129707309</v>
+        <v>129694990</v>
       </c>
       <c r="B117" t="n">
-        <v>79695</v>
+        <v>79081</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12058,21 +12058,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12082,10 +12082,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>431869</v>
+        <v>431726</v>
       </c>
       <c r="R117" t="n">
-        <v>6795521</v>
+        <v>6795117</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12132,22 +12132,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129707330</v>
+        <v>129694901</v>
       </c>
       <c r="B118" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12179,10 +12179,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>431930</v>
+        <v>431927</v>
       </c>
       <c r="R118" t="n">
-        <v>6795399</v>
+        <v>6795265</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12229,22 +12229,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129707323</v>
+        <v>129694844</v>
       </c>
       <c r="B119" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12276,10 +12276,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>431712</v>
+        <v>431739</v>
       </c>
       <c r="R119" t="n">
-        <v>6795236</v>
+        <v>6795440</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12326,12 +12326,12 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
@@ -12341,7 +12341,7 @@
         <v>129707386</v>
       </c>
       <c r="B120" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>129707421</v>
       </c>
       <c r="B121" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12532,32 +12532,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129695013</v>
+        <v>129694850</v>
       </c>
       <c r="B122" t="n">
-        <v>92870</v>
+        <v>79700</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12567,10 +12567,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>431869</v>
+        <v>431686</v>
       </c>
       <c r="R122" t="n">
-        <v>6795173</v>
+        <v>6795471</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12629,10 +12629,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129694997</v>
+        <v>129694881</v>
       </c>
       <c r="B123" t="n">
-        <v>79076</v>
+        <v>79700</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12640,21 +12640,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12664,10 +12664,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>431848</v>
+        <v>431875</v>
       </c>
       <c r="R123" t="n">
-        <v>6795172</v>
+        <v>6795212</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12726,10 +12726,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129707368</v>
+        <v>129694888</v>
       </c>
       <c r="B124" t="n">
-        <v>78834</v>
+        <v>79700</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12737,37 +12737,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>431820</v>
+        <v>431889</v>
       </c>
       <c r="R124" t="n">
-        <v>6795331</v>
+        <v>6795236</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12808,19 +12805,18 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
@@ -12932,32 +12928,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129694850</v>
+        <v>129695013</v>
       </c>
       <c r="B126" t="n">
-        <v>79695</v>
+        <v>92875</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -12967,10 +12963,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>431686</v>
+        <v>431869</v>
       </c>
       <c r="R126" t="n">
-        <v>6795471</v>
+        <v>6795173</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13029,10 +13025,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129694881</v>
+        <v>129694997</v>
       </c>
       <c r="B127" t="n">
-        <v>79695</v>
+        <v>79081</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13040,21 +13036,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13064,10 +13060,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>431875</v>
+        <v>431848</v>
       </c>
       <c r="R127" t="n">
-        <v>6795212</v>
+        <v>6795172</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13126,10 +13122,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129694888</v>
+        <v>129707368</v>
       </c>
       <c r="B128" t="n">
-        <v>79695</v>
+        <v>78839</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13137,34 +13133,37 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>431889</v>
+        <v>431820</v>
       </c>
       <c r="R128" t="n">
-        <v>6795236</v>
+        <v>6795331</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13205,18 +13204,19 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
@@ -13226,7 +13226,7 @@
         <v>129707311</v>
       </c>
       <c r="B129" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13320,10 +13320,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129707438</v>
+        <v>129707318</v>
       </c>
       <c r="B130" t="n">
-        <v>79076</v>
+        <v>79700</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13331,21 +13331,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13355,10 +13355,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>431965</v>
+        <v>431769</v>
       </c>
       <c r="R130" t="n">
-        <v>6795405</v>
+        <v>6795345</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13420,7 +13420,7 @@
         <v>129707399</v>
       </c>
       <c r="B131" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
         <v>129707387</v>
       </c>
       <c r="B132" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13611,10 +13611,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129707318</v>
+        <v>129707438</v>
       </c>
       <c r="B133" t="n">
-        <v>79695</v>
+        <v>79081</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13622,21 +13622,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13646,10 +13646,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>431769</v>
+        <v>431965</v>
       </c>
       <c r="R133" t="n">
-        <v>6795345</v>
+        <v>6795405</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13711,7 +13711,7 @@
         <v>129694900</v>
       </c>
       <c r="B134" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>129694906</v>
       </c>
       <c r="B135" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13902,10 +13902,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129694866</v>
+        <v>129694956</v>
       </c>
       <c r="B136" t="n">
-        <v>79695</v>
+        <v>92011</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13913,34 +13913,33 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>431797</v>
+        <v>431718</v>
       </c>
       <c r="R136" t="n">
-        <v>6795173</v>
+        <v>6795082</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -13975,12 +13974,18 @@
           <t>2025-11-14</t>
         </is>
       </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Mjuk och len på undetsidan, sämskskinnslik känsla</t>
+        </is>
+      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -13999,10 +14004,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129694865</v>
+        <v>129707334</v>
       </c>
       <c r="B137" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14034,10 +14039,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>431787</v>
+        <v>431936</v>
       </c>
       <c r="R137" t="n">
-        <v>6795115</v>
+        <v>6795411</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14084,22 +14089,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129694896</v>
+        <v>129707370</v>
       </c>
       <c r="B138" t="n">
-        <v>79695</v>
+        <v>78839</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14107,21 +14112,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14131,10 +14136,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>431900</v>
+        <v>431913</v>
       </c>
       <c r="R138" t="n">
-        <v>6795265</v>
+        <v>6795394</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14181,22 +14186,22 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129694956</v>
+        <v>129694866</v>
       </c>
       <c r="B139" t="n">
-        <v>92006</v>
+        <v>79700</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14204,33 +14209,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6040162</v>
+        <v>6453</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>431718</v>
+        <v>431797</v>
       </c>
       <c r="R139" t="n">
-        <v>6795082</v>
+        <v>6795173</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14265,18 +14271,12 @@
           <t>2025-11-14</t>
         </is>
       </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>Mjuk och len på undetsidan, sämskskinnslik känsla</t>
-        </is>
-      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -14295,10 +14295,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129707334</v>
+        <v>129694865</v>
       </c>
       <c r="B140" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14330,10 +14330,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>431936</v>
+        <v>431787</v>
       </c>
       <c r="R140" t="n">
-        <v>6795411</v>
+        <v>6795115</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14380,22 +14380,22 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129707370</v>
+        <v>129694896</v>
       </c>
       <c r="B141" t="n">
-        <v>78834</v>
+        <v>79700</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14403,21 +14403,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14427,10 +14427,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>431913</v>
+        <v>431900</v>
       </c>
       <c r="R141" t="n">
-        <v>6795394</v>
+        <v>6795265</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14477,12 +14477,12 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
@@ -14492,7 +14492,7 @@
         <v>129707377</v>
       </c>
       <c r="B142" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14586,10 +14586,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129707366</v>
+        <v>129694876</v>
       </c>
       <c r="B143" t="n">
-        <v>78834</v>
+        <v>79700</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14597,21 +14597,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14621,10 +14621,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>431840</v>
+        <v>431871</v>
       </c>
       <c r="R143" t="n">
-        <v>6795476</v>
+        <v>6795171</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14671,22 +14671,22 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129694876</v>
+        <v>129694887</v>
       </c>
       <c r="B144" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14718,10 +14718,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>431871</v>
+        <v>431886</v>
       </c>
       <c r="R144" t="n">
-        <v>6795171</v>
+        <v>6795236</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14780,10 +14780,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129694887</v>
+        <v>129694880</v>
       </c>
       <c r="B145" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14815,10 +14815,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>431886</v>
+        <v>431871</v>
       </c>
       <c r="R145" t="n">
-        <v>6795236</v>
+        <v>6795205</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -14877,10 +14877,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129694880</v>
+        <v>129694897</v>
       </c>
       <c r="B146" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14912,10 +14912,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>431871</v>
+        <v>431906</v>
       </c>
       <c r="R146" t="n">
-        <v>6795205</v>
+        <v>6795283</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -14974,10 +14974,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129694897</v>
+        <v>129707366</v>
       </c>
       <c r="B147" t="n">
-        <v>79695</v>
+        <v>78839</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14985,21 +14985,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15009,10 +15009,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>431906</v>
+        <v>431840</v>
       </c>
       <c r="R147" t="n">
-        <v>6795283</v>
+        <v>6795476</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15059,12 +15059,12 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>

--- a/artfynd/A 50492-2025 artfynd.xlsx
+++ b/artfynd/A 50492-2025 artfynd.xlsx
@@ -675,48 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129707216</v>
+        <v>129707440</v>
       </c>
       <c r="B2" t="n">
-        <v>79081</v>
+        <v>92875</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>432007</v>
+        <v>431828</v>
       </c>
       <c r="R2" t="n">
-        <v>6795475</v>
+        <v>6795476</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -776,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129707403</v>
+        <v>129707216</v>
       </c>
       <c r="B3" t="n">
         <v>79081</v>
@@ -805,16 +801,19 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>431851</v>
+        <v>432007</v>
       </c>
       <c r="R3" t="n">
-        <v>6795372</v>
+        <v>6795475</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,6 +854,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -873,10 +873,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129694842</v>
+        <v>129707403</v>
       </c>
       <c r="B4" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -884,21 +884,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -908,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>431768</v>
+        <v>431851</v>
       </c>
       <c r="R4" t="n">
-        <v>6795469</v>
+        <v>6795372</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -958,57 +958,66 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129694957</v>
+        <v>129707371</v>
       </c>
       <c r="B5" t="n">
-        <v>78838</v>
+        <v>8450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>431725</v>
+        <v>431808</v>
       </c>
       <c r="R5" t="n">
-        <v>6795459</v>
+        <v>6795442</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1049,25 +1058,26 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129694862</v>
+        <v>129694842</v>
       </c>
       <c r="B6" t="n">
         <v>79700</v>
@@ -1102,10 +1112,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>431756</v>
+        <v>431768</v>
       </c>
       <c r="R6" t="n">
-        <v>6795121</v>
+        <v>6795469</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,10 +1174,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129694935</v>
+        <v>129694957</v>
       </c>
       <c r="B7" t="n">
-        <v>57733</v>
+        <v>78838</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1175,42 +1185,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>431917</v>
+        <v>431725</v>
       </c>
       <c r="R7" t="n">
-        <v>6795290</v>
+        <v>6795459</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1269,10 +1271,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129694929</v>
+        <v>129694862</v>
       </c>
       <c r="B8" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1280,42 +1282,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>431859</v>
+        <v>431756</v>
       </c>
       <c r="R8" t="n">
-        <v>6795172</v>
+        <v>6795121</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,45 +1368,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129707440</v>
+        <v>129694935</v>
       </c>
       <c r="B9" t="n">
-        <v>92875</v>
+        <v>57733</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>431828</v>
+        <v>431917</v>
       </c>
       <c r="R9" t="n">
-        <v>6795476</v>
+        <v>6795290</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,53 +1461,52 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129707371</v>
+        <v>129694929</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1515,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>431808</v>
+        <v>431859</v>
       </c>
       <c r="R10" t="n">
-        <v>6795442</v>
+        <v>6795172</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1559,29 +1560,28 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129707336</v>
+        <v>129694983</v>
       </c>
       <c r="B11" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1589,21 +1589,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>431993</v>
+        <v>431689</v>
       </c>
       <c r="R11" t="n">
-        <v>6795380</v>
+        <v>6795456</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1663,22 +1663,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129694843</v>
+        <v>129694923</v>
       </c>
       <c r="B12" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1686,34 +1686,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>431752</v>
+        <v>431687</v>
       </c>
       <c r="R12" t="n">
-        <v>6795429</v>
+        <v>6795471</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1772,10 +1780,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129694907</v>
+        <v>129694918</v>
       </c>
       <c r="B13" t="n">
-        <v>79700</v>
+        <v>91614</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1783,34 +1791,41 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>431938</v>
+        <v>431722</v>
       </c>
       <c r="R13" t="n">
-        <v>6795278</v>
+        <v>6795120</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1851,6 +1866,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1869,10 +1885,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129694918</v>
+        <v>129694843</v>
       </c>
       <c r="B14" t="n">
-        <v>91614</v>
+        <v>79700</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1880,41 +1896,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>431722</v>
+        <v>431752</v>
       </c>
       <c r="R14" t="n">
-        <v>6795120</v>
+        <v>6795429</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1955,7 +1964,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1974,10 +1982,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129694983</v>
+        <v>129694907</v>
       </c>
       <c r="B15" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1985,21 +1993,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2009,10 +2017,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>431689</v>
+        <v>431938</v>
       </c>
       <c r="R15" t="n">
-        <v>6795456</v>
+        <v>6795278</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2071,7 +2079,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129694923</v>
+        <v>129707358</v>
       </c>
       <c r="B16" t="n">
         <v>57733</v>
@@ -2104,7 +2112,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2114,10 +2122,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>431687</v>
+        <v>431912</v>
       </c>
       <c r="R16" t="n">
-        <v>6795471</v>
+        <v>6795310</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2164,22 +2172,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129707434</v>
+        <v>129707336</v>
       </c>
       <c r="B17" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2187,21 +2195,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2211,10 +2219,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>431894</v>
+        <v>431993</v>
       </c>
       <c r="R17" t="n">
-        <v>6795261</v>
+        <v>6795380</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2273,10 +2281,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129707358</v>
+        <v>129707434</v>
       </c>
       <c r="B18" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2284,42 +2292,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>431912</v>
+        <v>431894</v>
       </c>
       <c r="R18" t="n">
-        <v>6795310</v>
+        <v>6795261</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2378,53 +2378,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129694913</v>
+        <v>129707378</v>
       </c>
       <c r="B19" t="n">
-        <v>56926</v>
+        <v>78838</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>431728</v>
+        <v>431814</v>
       </c>
       <c r="R19" t="n">
-        <v>6795109</v>
+        <v>6795444</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2471,12 +2463,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2580,7 +2572,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129707335</v>
+        <v>129694845</v>
       </c>
       <c r="B21" t="n">
         <v>79700</v>
@@ -2615,10 +2607,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>431965</v>
+        <v>431722</v>
       </c>
       <c r="R21" t="n">
-        <v>6795430</v>
+        <v>6795478</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2665,57 +2657,65 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129694845</v>
+        <v>129694913</v>
       </c>
       <c r="B22" t="n">
-        <v>79700</v>
+        <v>56926</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>431722</v>
+        <v>431728</v>
       </c>
       <c r="R22" t="n">
-        <v>6795478</v>
+        <v>6795109</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2774,10 +2774,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129707378</v>
+        <v>129707335</v>
       </c>
       <c r="B23" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2785,21 +2785,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2809,10 +2809,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>431814</v>
+        <v>431965</v>
       </c>
       <c r="R23" t="n">
-        <v>6795444</v>
+        <v>6795430</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2871,10 +2871,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129694942</v>
+        <v>129694883</v>
       </c>
       <c r="B24" t="n">
-        <v>91891</v>
+        <v>79700</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2882,21 +2882,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2906,10 +2906,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>431803</v>
+        <v>431885</v>
       </c>
       <c r="R24" t="n">
-        <v>6795150</v>
+        <v>6795213</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2950,7 +2950,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2969,7 +2968,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129694883</v>
+        <v>129694884</v>
       </c>
       <c r="B25" t="n">
         <v>79700</v>
@@ -3007,7 +3006,7 @@
         <v>431885</v>
       </c>
       <c r="R25" t="n">
-        <v>6795213</v>
+        <v>6795215</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3066,7 +3065,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129694884</v>
+        <v>129694898</v>
       </c>
       <c r="B26" t="n">
         <v>79700</v>
@@ -3101,10 +3100,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>431885</v>
+        <v>431907</v>
       </c>
       <c r="R26" t="n">
-        <v>6795215</v>
+        <v>6795285</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3163,7 +3162,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129694898</v>
+        <v>129694899</v>
       </c>
       <c r="B27" t="n">
         <v>79700</v>
@@ -3198,10 +3197,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>431907</v>
+        <v>431910</v>
       </c>
       <c r="R27" t="n">
-        <v>6795285</v>
+        <v>6795288</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3260,7 +3259,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129694899</v>
+        <v>129694861</v>
       </c>
       <c r="B28" t="n">
         <v>79700</v>
@@ -3295,10 +3294,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>431910</v>
+        <v>431740</v>
       </c>
       <c r="R28" t="n">
-        <v>6795288</v>
+        <v>6795107</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3357,7 +3356,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129694861</v>
+        <v>129707308</v>
       </c>
       <c r="B29" t="n">
         <v>79700</v>
@@ -3392,10 +3391,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>431740</v>
+        <v>431868</v>
       </c>
       <c r="R29" t="n">
-        <v>6795107</v>
+        <v>6795565</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3442,22 +3441,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129707308</v>
+        <v>129707407</v>
       </c>
       <c r="B30" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3465,21 +3464,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3489,10 +3488,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>431868</v>
+        <v>431723</v>
       </c>
       <c r="R30" t="n">
-        <v>6795565</v>
+        <v>6795371</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3652,10 +3651,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129707407</v>
+        <v>129694942</v>
       </c>
       <c r="B32" t="n">
-        <v>79081</v>
+        <v>91891</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3663,21 +3662,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3687,10 +3686,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>431723</v>
+        <v>431803</v>
       </c>
       <c r="R32" t="n">
-        <v>6795371</v>
+        <v>6795150</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3731,63 +3730,72 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129695010</v>
+        <v>129707346</v>
       </c>
       <c r="B33" t="n">
-        <v>92875</v>
+        <v>57733</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>431880</v>
+        <v>431819</v>
       </c>
       <c r="R33" t="n">
-        <v>6795546</v>
+        <v>6795465</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3834,22 +3842,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129694839</v>
+        <v>129707390</v>
       </c>
       <c r="B34" t="n">
-        <v>91516</v>
+        <v>78838</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3857,21 +3865,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3242</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3884,10 +3892,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>431869</v>
+        <v>431952</v>
       </c>
       <c r="R34" t="n">
-        <v>6795181</v>
+        <v>6795410</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3935,22 +3943,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129694917</v>
+        <v>129694839</v>
       </c>
       <c r="B35" t="n">
-        <v>91614</v>
+        <v>91516</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3958,28 +3966,24 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5442</v>
+        <v>3242</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
@@ -3989,10 +3993,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>431672</v>
+        <v>431869</v>
       </c>
       <c r="R35" t="n">
-        <v>6795442</v>
+        <v>6795181</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4149,10 +4153,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129694921</v>
+        <v>129694886</v>
       </c>
       <c r="B37" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4160,42 +4164,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>431725</v>
+        <v>431873</v>
       </c>
       <c r="R37" t="n">
-        <v>6795459</v>
+        <v>6795241</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4254,10 +4250,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129707346</v>
+        <v>129694878</v>
       </c>
       <c r="B38" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4265,42 +4261,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>431819</v>
+        <v>431889</v>
       </c>
       <c r="R38" t="n">
-        <v>6795465</v>
+        <v>6795186</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4347,44 +4335,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129694886</v>
+        <v>129695010</v>
       </c>
       <c r="B39" t="n">
-        <v>79700</v>
+        <v>92875</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4394,10 +4382,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>431873</v>
+        <v>431880</v>
       </c>
       <c r="R39" t="n">
-        <v>6795241</v>
+        <v>6795546</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4456,10 +4444,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129694878</v>
+        <v>129694917</v>
       </c>
       <c r="B40" t="n">
-        <v>79700</v>
+        <v>91614</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4467,34 +4455,41 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>431889</v>
+        <v>431672</v>
       </c>
       <c r="R40" t="n">
-        <v>6795186</v>
+        <v>6795442</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4535,6 +4530,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4553,10 +4549,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129707390</v>
+        <v>129694921</v>
       </c>
       <c r="B41" t="n">
-        <v>78838</v>
+        <v>57733</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4564,26 +4560,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4591,10 +4592,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>431952</v>
+        <v>431725</v>
       </c>
       <c r="R41" t="n">
-        <v>6795410</v>
+        <v>6795459</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4635,29 +4636,28 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129694999</v>
+        <v>129694847</v>
       </c>
       <c r="B42" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4665,21 +4665,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>431859</v>
+        <v>431724</v>
       </c>
       <c r="R42" t="n">
-        <v>6795172</v>
+        <v>6795460</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4751,10 +4751,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129707320</v>
+        <v>129707351</v>
       </c>
       <c r="B43" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4762,34 +4762,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>431717</v>
+        <v>431756</v>
       </c>
       <c r="R43" t="n">
-        <v>6795380</v>
+        <v>6795202</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4848,7 +4856,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129707316</v>
+        <v>129707333</v>
       </c>
       <c r="B44" t="n">
         <v>79700</v>
@@ -4883,10 +4891,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>431812</v>
+        <v>431935</v>
       </c>
       <c r="R44" t="n">
-        <v>6795349</v>
+        <v>6795415</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4945,7 +4953,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129707333</v>
+        <v>129707338</v>
       </c>
       <c r="B45" t="n">
         <v>79700</v>
@@ -4980,10 +4988,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>431935</v>
+        <v>431932</v>
       </c>
       <c r="R45" t="n">
-        <v>6795415</v>
+        <v>6795406</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5042,10 +5050,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129707338</v>
+        <v>129694999</v>
       </c>
       <c r="B46" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5053,21 +5061,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5077,10 +5085,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>431932</v>
+        <v>431859</v>
       </c>
       <c r="R46" t="n">
-        <v>6795406</v>
+        <v>6795172</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5127,22 +5135,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129707375</v>
+        <v>129694926</v>
       </c>
       <c r="B47" t="n">
-        <v>78838</v>
+        <v>57733</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5150,34 +5158,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>431881</v>
+        <v>431711</v>
       </c>
       <c r="R47" t="n">
-        <v>6795522</v>
+        <v>6795100</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5224,22 +5240,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129707351</v>
+        <v>129707320</v>
       </c>
       <c r="B48" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5247,42 +5263,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>431756</v>
+        <v>431717</v>
       </c>
       <c r="R48" t="n">
-        <v>6795202</v>
+        <v>6795380</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5341,7 +5349,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129694847</v>
+        <v>129707316</v>
       </c>
       <c r="B49" t="n">
         <v>79700</v>
@@ -5376,10 +5384,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>431724</v>
+        <v>431812</v>
       </c>
       <c r="R49" t="n">
-        <v>6795460</v>
+        <v>6795349</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5426,22 +5434,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129694926</v>
+        <v>129707375</v>
       </c>
       <c r="B50" t="n">
-        <v>57733</v>
+        <v>78838</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5449,42 +5457,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>431711</v>
+        <v>431881</v>
       </c>
       <c r="R50" t="n">
-        <v>6795100</v>
+        <v>6795522</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5531,22 +5531,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129707337</v>
+        <v>129695006</v>
       </c>
       <c r="B51" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5554,21 +5554,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5578,10 +5578,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>431999</v>
+        <v>431962</v>
       </c>
       <c r="R51" t="n">
-        <v>6795416</v>
+        <v>6795319</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5628,19 +5628,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129707426</v>
+        <v>129694994</v>
       </c>
       <c r="B52" t="n">
         <v>79081</v>
@@ -5675,10 +5675,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>431767</v>
+        <v>431804</v>
       </c>
       <c r="R52" t="n">
-        <v>6795219</v>
+        <v>6795151</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5725,22 +5725,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129707404</v>
+        <v>129694846</v>
       </c>
       <c r="B53" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5748,37 +5748,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>431816</v>
+        <v>431725</v>
       </c>
       <c r="R53" t="n">
-        <v>6795333</v>
+        <v>6795467</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5813,40 +5810,34 @@
           <t>2025-11-14</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129707380</v>
+        <v>129695003</v>
       </c>
       <c r="B54" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5854,21 +5845,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5878,10 +5869,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>431820</v>
+        <v>431908</v>
       </c>
       <c r="R54" t="n">
-        <v>6795330</v>
+        <v>6795302</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5928,22 +5919,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129695006</v>
+        <v>129707347</v>
       </c>
       <c r="B55" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5951,34 +5942,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>431962</v>
+        <v>431662</v>
       </c>
       <c r="R55" t="n">
-        <v>6795319</v>
+        <v>6795391</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6025,22 +6024,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129695003</v>
+        <v>129707337</v>
       </c>
       <c r="B56" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6048,21 +6047,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6072,10 +6071,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>431908</v>
+        <v>431999</v>
       </c>
       <c r="R56" t="n">
-        <v>6795302</v>
+        <v>6795416</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6122,19 +6121,19 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129694994</v>
+        <v>129707426</v>
       </c>
       <c r="B57" t="n">
         <v>79081</v>
@@ -6169,10 +6168,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>431804</v>
+        <v>431767</v>
       </c>
       <c r="R57" t="n">
-        <v>6795151</v>
+        <v>6795219</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6219,22 +6218,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129694846</v>
+        <v>129707404</v>
       </c>
       <c r="B58" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6242,34 +6241,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>431725</v>
+        <v>431816</v>
       </c>
       <c r="R58" t="n">
-        <v>6795467</v>
+        <v>6795333</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6304,34 +6306,40 @@
           <t>2025-11-14</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129707347</v>
+        <v>129707380</v>
       </c>
       <c r="B59" t="n">
-        <v>57733</v>
+        <v>78838</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6339,42 +6347,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>431662</v>
+        <v>431820</v>
       </c>
       <c r="R59" t="n">
-        <v>6795391</v>
+        <v>6795330</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6433,10 +6433,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129694930</v>
+        <v>129694988</v>
       </c>
       <c r="B60" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6444,42 +6444,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>431875</v>
+        <v>431718</v>
       </c>
       <c r="R60" t="n">
-        <v>6795244</v>
+        <v>6795068</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6538,10 +6530,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129694988</v>
+        <v>129694872</v>
       </c>
       <c r="B61" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6549,21 +6541,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6573,10 +6565,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>431718</v>
+        <v>431833</v>
       </c>
       <c r="R61" t="n">
-        <v>6795068</v>
+        <v>6795171</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6635,7 +6627,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129694872</v>
+        <v>129694856</v>
       </c>
       <c r="B62" t="n">
         <v>79700</v>
@@ -6670,10 +6662,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>431833</v>
+        <v>431693</v>
       </c>
       <c r="R62" t="n">
-        <v>6795171</v>
+        <v>6795052</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6732,10 +6724,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129694856</v>
+        <v>129694961</v>
       </c>
       <c r="B63" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6743,21 +6735,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6767,10 +6759,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>431693</v>
+        <v>431804</v>
       </c>
       <c r="R63" t="n">
-        <v>6795052</v>
+        <v>6795100</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6829,10 +6821,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129694961</v>
+        <v>129707319</v>
       </c>
       <c r="B64" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6840,21 +6832,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6864,10 +6856,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>431804</v>
+        <v>431708</v>
       </c>
       <c r="R64" t="n">
-        <v>6795100</v>
+        <v>6795371</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6914,22 +6906,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129707319</v>
+        <v>129694930</v>
       </c>
       <c r="B65" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6937,34 +6929,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>431708</v>
+        <v>431875</v>
       </c>
       <c r="R65" t="n">
-        <v>6795371</v>
+        <v>6795244</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7011,22 +7011,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129694857</v>
+        <v>129707382</v>
       </c>
       <c r="B66" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7034,34 +7034,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>431800</v>
+        <v>431689</v>
       </c>
       <c r="R66" t="n">
-        <v>6795130</v>
+        <v>6795383</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7102,28 +7105,29 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129694908</v>
+        <v>129707420</v>
       </c>
       <c r="B67" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7131,21 +7135,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7155,10 +7159,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>431973</v>
+        <v>431695</v>
       </c>
       <c r="R67" t="n">
-        <v>6795310</v>
+        <v>6795256</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7205,19 +7209,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129694858</v>
+        <v>129694857</v>
       </c>
       <c r="B68" t="n">
         <v>79700</v>
@@ -7252,10 +7256,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>431749</v>
+        <v>431800</v>
       </c>
       <c r="R68" t="n">
-        <v>6795079</v>
+        <v>6795130</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7314,7 +7318,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129694859</v>
+        <v>129694908</v>
       </c>
       <c r="B69" t="n">
         <v>79700</v>
@@ -7349,10 +7353,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>431702</v>
+        <v>431973</v>
       </c>
       <c r="R69" t="n">
-        <v>6795115</v>
+        <v>6795310</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7411,7 +7415,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129694879</v>
+        <v>129694858</v>
       </c>
       <c r="B70" t="n">
         <v>79700</v>
@@ -7446,10 +7450,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>431888</v>
+        <v>431749</v>
       </c>
       <c r="R70" t="n">
-        <v>6795198</v>
+        <v>6795079</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7508,10 +7512,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129694928</v>
+        <v>129694859</v>
       </c>
       <c r="B71" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7519,42 +7523,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>431801</v>
+        <v>431702</v>
       </c>
       <c r="R71" t="n">
-        <v>6795136</v>
+        <v>6795115</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7613,10 +7609,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129707382</v>
+        <v>129694879</v>
       </c>
       <c r="B72" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7624,37 +7620,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>431689</v>
+        <v>431888</v>
       </c>
       <c r="R72" t="n">
-        <v>6795383</v>
+        <v>6795198</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7695,29 +7688,28 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129707420</v>
+        <v>129694928</v>
       </c>
       <c r="B73" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7725,34 +7717,42 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>431695</v>
+        <v>431801</v>
       </c>
       <c r="R73" t="n">
-        <v>6795256</v>
+        <v>6795136</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7799,44 +7799,44 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129707439</v>
+        <v>129694985</v>
       </c>
       <c r="B74" t="n">
-        <v>92875</v>
+        <v>79081</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7846,10 +7846,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>431891</v>
+        <v>431673</v>
       </c>
       <c r="R74" t="n">
-        <v>6795553</v>
+        <v>6795435</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7896,44 +7896,44 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129694985</v>
+        <v>129707439</v>
       </c>
       <c r="B75" t="n">
-        <v>79081</v>
+        <v>92875</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7943,10 +7943,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>431673</v>
+        <v>431891</v>
       </c>
       <c r="R75" t="n">
-        <v>6795435</v>
+        <v>6795553</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7993,19 +7993,19 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129707317</v>
+        <v>129707314</v>
       </c>
       <c r="B76" t="n">
         <v>79700</v>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>431780</v>
+        <v>431866</v>
       </c>
       <c r="R76" t="n">
-        <v>6795362</v>
+        <v>6795513</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8102,7 +8102,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129707314</v>
+        <v>129707317</v>
       </c>
       <c r="B77" t="n">
         <v>79700</v>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>431866</v>
+        <v>431780</v>
       </c>
       <c r="R77" t="n">
-        <v>6795513</v>
+        <v>6795362</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8397,10 +8397,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129694863</v>
+        <v>129695001</v>
       </c>
       <c r="B80" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8408,21 +8408,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8432,10 +8432,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>431785</v>
+        <v>431876</v>
       </c>
       <c r="R80" t="n">
-        <v>6795106</v>
+        <v>6795202</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8494,10 +8494,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129694874</v>
+        <v>129694948</v>
       </c>
       <c r="B81" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8505,21 +8505,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>431827</v>
+        <v>431725</v>
       </c>
       <c r="R81" t="n">
-        <v>6795171</v>
+        <v>6795459</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8591,10 +8591,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129694948</v>
+        <v>129707345</v>
       </c>
       <c r="B82" t="n">
-        <v>78839</v>
+        <v>57733</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8602,34 +8602,42 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>431725</v>
+        <v>431893</v>
       </c>
       <c r="R82" t="n">
-        <v>6795459</v>
+        <v>6795571</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8676,22 +8684,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129707315</v>
+        <v>129707424</v>
       </c>
       <c r="B83" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8699,21 +8707,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8723,10 +8731,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>431820</v>
+        <v>431760</v>
       </c>
       <c r="R83" t="n">
-        <v>6795329</v>
+        <v>6795200</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8785,10 +8793,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129707345</v>
+        <v>129694991</v>
       </c>
       <c r="B84" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8796,42 +8804,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>431893</v>
+        <v>431760</v>
       </c>
       <c r="R84" t="n">
-        <v>6795571</v>
+        <v>6795115</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8878,22 +8878,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129695001</v>
+        <v>129694863</v>
       </c>
       <c r="B85" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8901,21 +8901,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8925,10 +8925,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>431876</v>
+        <v>431785</v>
       </c>
       <c r="R85" t="n">
-        <v>6795202</v>
+        <v>6795106</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8987,10 +8987,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129694991</v>
+        <v>129694874</v>
       </c>
       <c r="B86" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8998,21 +8998,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9022,10 +9022,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>431760</v>
+        <v>431827</v>
       </c>
       <c r="R86" t="n">
-        <v>6795115</v>
+        <v>6795171</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9286,10 +9286,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129707424</v>
+        <v>129707315</v>
       </c>
       <c r="B89" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9297,21 +9297,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9321,10 +9321,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>431760</v>
+        <v>431820</v>
       </c>
       <c r="R89" t="n">
-        <v>6795200</v>
+        <v>6795329</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9383,10 +9383,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129694939</v>
+        <v>129694860</v>
       </c>
       <c r="B90" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9394,21 +9394,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9418,10 +9418,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>431913</v>
+        <v>431746</v>
       </c>
       <c r="R90" t="n">
-        <v>6795284</v>
+        <v>6795081</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9454,11 +9454,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9485,10 +9480,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129694934</v>
+        <v>129694965</v>
       </c>
       <c r="B91" t="n">
-        <v>57733</v>
+        <v>78838</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9496,42 +9491,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>431916</v>
+        <v>431885</v>
       </c>
       <c r="R91" t="n">
-        <v>6795286</v>
+        <v>6795240</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9590,10 +9577,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129707405</v>
+        <v>129694934</v>
       </c>
       <c r="B92" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9601,34 +9588,42 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>431775</v>
+        <v>431916</v>
       </c>
       <c r="R92" t="n">
-        <v>6795343</v>
+        <v>6795286</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9675,22 +9670,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129694860</v>
+        <v>129694939</v>
       </c>
       <c r="B93" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9698,21 +9693,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9722,10 +9717,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>431746</v>
+        <v>431913</v>
       </c>
       <c r="R93" t="n">
-        <v>6795081</v>
+        <v>6795284</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9758,6 +9753,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9784,10 +9784,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129694965</v>
+        <v>129707405</v>
       </c>
       <c r="B94" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9795,21 +9795,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9819,10 +9819,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>431885</v>
+        <v>431775</v>
       </c>
       <c r="R94" t="n">
-        <v>6795240</v>
+        <v>6795343</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9869,12 +9869,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -9978,10 +9978,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129694977</v>
+        <v>129694989</v>
       </c>
       <c r="B96" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9989,42 +9989,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>431933</v>
+        <v>431723</v>
       </c>
       <c r="R96" t="n">
-        <v>6795295</v>
+        <v>6795090</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10083,32 +10075,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129694989</v>
+        <v>129694941</v>
       </c>
       <c r="B97" t="n">
-        <v>79081</v>
+        <v>79167</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10118,10 +10110,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>431723</v>
+        <v>431976</v>
       </c>
       <c r="R97" t="n">
-        <v>6795090</v>
+        <v>6795333</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10180,32 +10172,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129694941</v>
+        <v>129707312</v>
       </c>
       <c r="B98" t="n">
-        <v>79167</v>
+        <v>79700</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6450</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10215,10 +10207,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>431976</v>
+        <v>431920</v>
       </c>
       <c r="R98" t="n">
-        <v>6795333</v>
+        <v>6795611</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10265,22 +10257,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129707312</v>
+        <v>129694977</v>
       </c>
       <c r="B99" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10288,34 +10280,42 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>431920</v>
+        <v>431933</v>
       </c>
       <c r="R99" t="n">
-        <v>6795611</v>
+        <v>6795295</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10362,22 +10362,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129694877</v>
+        <v>129694927</v>
       </c>
       <c r="B100" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10385,34 +10385,42 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>431887</v>
+        <v>431711</v>
       </c>
       <c r="R100" t="n">
-        <v>6795183</v>
+        <v>6795094</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10471,10 +10479,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129694885</v>
+        <v>129694938</v>
       </c>
       <c r="B101" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10482,34 +10490,42 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>431873</v>
+        <v>431915</v>
       </c>
       <c r="R101" t="n">
-        <v>6795224</v>
+        <v>6795279</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10568,10 +10584,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129694864</v>
+        <v>129695000</v>
       </c>
       <c r="B102" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10579,21 +10595,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10603,10 +10619,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>431786</v>
+        <v>431890</v>
       </c>
       <c r="R102" t="n">
-        <v>6795113</v>
+        <v>6795199</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10665,10 +10681,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129707327</v>
+        <v>129694992</v>
       </c>
       <c r="B103" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10676,21 +10692,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10700,10 +10716,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>431893</v>
+        <v>431799</v>
       </c>
       <c r="R103" t="n">
-        <v>6795305</v>
+        <v>6795129</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10750,19 +10766,19 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129707332</v>
+        <v>129694877</v>
       </c>
       <c r="B104" t="n">
         <v>79700</v>
@@ -10797,10 +10813,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>431923</v>
+        <v>431887</v>
       </c>
       <c r="R104" t="n">
-        <v>6795402</v>
+        <v>6795183</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10847,22 +10863,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129694927</v>
+        <v>129694885</v>
       </c>
       <c r="B105" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10870,42 +10886,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>431711</v>
+        <v>431873</v>
       </c>
       <c r="R105" t="n">
-        <v>6795094</v>
+        <v>6795224</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10964,10 +10972,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129694938</v>
+        <v>129694864</v>
       </c>
       <c r="B106" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10975,42 +10983,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>431915</v>
+        <v>431786</v>
       </c>
       <c r="R106" t="n">
-        <v>6795279</v>
+        <v>6795113</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11069,10 +11069,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129695000</v>
+        <v>129707349</v>
       </c>
       <c r="B107" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11080,34 +11080,42 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>431890</v>
+        <v>431722</v>
       </c>
       <c r="R107" t="n">
-        <v>6795199</v>
+        <v>6795217</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11154,19 +11162,19 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129694992</v>
+        <v>129707397</v>
       </c>
       <c r="B108" t="n">
         <v>79081</v>
@@ -11201,10 +11209,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>431799</v>
+        <v>431915</v>
       </c>
       <c r="R108" t="n">
-        <v>6795129</v>
+        <v>6795541</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11251,22 +11259,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129707397</v>
+        <v>129707327</v>
       </c>
       <c r="B109" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11274,21 +11282,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11298,10 +11306,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>431915</v>
+        <v>431893</v>
       </c>
       <c r="R109" t="n">
-        <v>6795541</v>
+        <v>6795305</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11554,10 +11562,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129707425</v>
+        <v>129707332</v>
       </c>
       <c r="B112" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11565,21 +11573,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11589,10 +11597,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>431756</v>
+        <v>431923</v>
       </c>
       <c r="R112" t="n">
-        <v>6795247</v>
+        <v>6795402</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11651,10 +11659,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129707349</v>
+        <v>129707425</v>
       </c>
       <c r="B113" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11662,42 +11670,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>431722</v>
+        <v>431756</v>
       </c>
       <c r="R113" t="n">
-        <v>6795217</v>
+        <v>6795247</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11756,10 +11756,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129707309</v>
+        <v>129694990</v>
       </c>
       <c r="B114" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11767,21 +11767,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11791,10 +11791,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>431869</v>
+        <v>431726</v>
       </c>
       <c r="R114" t="n">
-        <v>6795521</v>
+        <v>6795117</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11841,19 +11841,19 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129707330</v>
+        <v>129694901</v>
       </c>
       <c r="B115" t="n">
         <v>79700</v>
@@ -11888,10 +11888,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>431930</v>
+        <v>431927</v>
       </c>
       <c r="R115" t="n">
-        <v>6795399</v>
+        <v>6795265</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11938,19 +11938,19 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129707323</v>
+        <v>129694844</v>
       </c>
       <c r="B116" t="n">
         <v>79700</v>
@@ -11985,10 +11985,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>431712</v>
+        <v>431739</v>
       </c>
       <c r="R116" t="n">
-        <v>6795236</v>
+        <v>6795440</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12035,22 +12035,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129694990</v>
+        <v>129707309</v>
       </c>
       <c r="B117" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12058,21 +12058,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12082,10 +12082,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>431726</v>
+        <v>431869</v>
       </c>
       <c r="R117" t="n">
-        <v>6795117</v>
+        <v>6795521</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12132,19 +12132,19 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129694901</v>
+        <v>129707330</v>
       </c>
       <c r="B118" t="n">
         <v>79700</v>
@@ -12179,10 +12179,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>431927</v>
+        <v>431930</v>
       </c>
       <c r="R118" t="n">
-        <v>6795265</v>
+        <v>6795399</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12229,19 +12229,19 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129694844</v>
+        <v>129707323</v>
       </c>
       <c r="B119" t="n">
         <v>79700</v>
@@ -12276,10 +12276,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>431739</v>
+        <v>431712</v>
       </c>
       <c r="R119" t="n">
-        <v>6795440</v>
+        <v>6795236</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12326,12 +12326,12 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
@@ -12532,32 +12532,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129694850</v>
+        <v>129695013</v>
       </c>
       <c r="B122" t="n">
-        <v>79700</v>
+        <v>92875</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12567,10 +12567,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>431686</v>
+        <v>431869</v>
       </c>
       <c r="R122" t="n">
-        <v>6795471</v>
+        <v>6795173</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12629,10 +12629,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129694881</v>
+        <v>129694997</v>
       </c>
       <c r="B123" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12640,21 +12640,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12664,10 +12664,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>431875</v>
+        <v>431848</v>
       </c>
       <c r="R123" t="n">
-        <v>6795212</v>
+        <v>6795172</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12726,7 +12726,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129694888</v>
+        <v>129694850</v>
       </c>
       <c r="B124" t="n">
         <v>79700</v>
@@ -12761,10 +12761,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>431889</v>
+        <v>431686</v>
       </c>
       <c r="R124" t="n">
-        <v>6795236</v>
+        <v>6795471</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12823,10 +12823,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129694925</v>
+        <v>129694881</v>
       </c>
       <c r="B125" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12834,42 +12834,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>431687</v>
+        <v>431875</v>
       </c>
       <c r="R125" t="n">
-        <v>6795051</v>
+        <v>6795212</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12928,32 +12920,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129695013</v>
+        <v>129694888</v>
       </c>
       <c r="B126" t="n">
-        <v>92875</v>
+        <v>79700</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -12963,10 +12955,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>431869</v>
+        <v>431889</v>
       </c>
       <c r="R126" t="n">
-        <v>6795173</v>
+        <v>6795236</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13025,10 +13017,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129694997</v>
+        <v>129707368</v>
       </c>
       <c r="B127" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13036,34 +13028,37 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>431848</v>
+        <v>431820</v>
       </c>
       <c r="R127" t="n">
-        <v>6795172</v>
+        <v>6795331</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13104,28 +13099,29 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129707368</v>
+        <v>129694925</v>
       </c>
       <c r="B128" t="n">
-        <v>78839</v>
+        <v>57733</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13133,26 +13129,31 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
@@ -13160,10 +13161,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>431820</v>
+        <v>431687</v>
       </c>
       <c r="R128" t="n">
-        <v>6795331</v>
+        <v>6795051</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13204,19 +13205,18 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
@@ -13320,7 +13320,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129707318</v>
+        <v>129694900</v>
       </c>
       <c r="B130" t="n">
         <v>79700</v>
@@ -13355,10 +13355,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>431769</v>
+        <v>431907</v>
       </c>
       <c r="R130" t="n">
-        <v>6795345</v>
+        <v>6795266</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13405,22 +13405,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129707399</v>
+        <v>129694906</v>
       </c>
       <c r="B131" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13428,21 +13428,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13452,10 +13452,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>431819</v>
+        <v>431934</v>
       </c>
       <c r="R131" t="n">
-        <v>6795445</v>
+        <v>6795286</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13502,22 +13502,22 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129707387</v>
+        <v>129707399</v>
       </c>
       <c r="B132" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13525,21 +13525,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13549,10 +13549,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>431936</v>
+        <v>431819</v>
       </c>
       <c r="R132" t="n">
-        <v>6795393</v>
+        <v>6795445</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13611,10 +13611,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129707438</v>
+        <v>129707387</v>
       </c>
       <c r="B133" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13622,21 +13622,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13646,10 +13646,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>431965</v>
+        <v>431936</v>
       </c>
       <c r="R133" t="n">
-        <v>6795405</v>
+        <v>6795393</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13708,10 +13708,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129694900</v>
+        <v>129707438</v>
       </c>
       <c r="B134" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13719,21 +13719,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13743,10 +13743,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>431907</v>
+        <v>431965</v>
       </c>
       <c r="R134" t="n">
-        <v>6795266</v>
+        <v>6795405</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13793,19 +13793,19 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129694906</v>
+        <v>129707318</v>
       </c>
       <c r="B135" t="n">
         <v>79700</v>
@@ -13840,10 +13840,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>431934</v>
+        <v>431769</v>
       </c>
       <c r="R135" t="n">
-        <v>6795286</v>
+        <v>6795345</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -13890,22 +13890,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129694956</v>
+        <v>129694866</v>
       </c>
       <c r="B136" t="n">
-        <v>92011</v>
+        <v>79700</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13913,33 +13913,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6040162</v>
+        <v>6453</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>431718</v>
+        <v>431797</v>
       </c>
       <c r="R136" t="n">
-        <v>6795082</v>
+        <v>6795173</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -13974,18 +13975,12 @@
           <t>2025-11-14</t>
         </is>
       </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Mjuk och len på undetsidan, sämskskinnslik känsla</t>
-        </is>
-      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -14004,7 +13999,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129707334</v>
+        <v>129694865</v>
       </c>
       <c r="B137" t="n">
         <v>79700</v>
@@ -14039,10 +14034,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>431936</v>
+        <v>431787</v>
       </c>
       <c r="R137" t="n">
-        <v>6795411</v>
+        <v>6795115</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14089,22 +14084,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129707370</v>
+        <v>129694896</v>
       </c>
       <c r="B138" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14112,21 +14107,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14136,10 +14131,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>431913</v>
+        <v>431900</v>
       </c>
       <c r="R138" t="n">
-        <v>6795394</v>
+        <v>6795265</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14186,22 +14181,22 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129694866</v>
+        <v>129694956</v>
       </c>
       <c r="B139" t="n">
-        <v>79700</v>
+        <v>92011</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14209,34 +14204,33 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>431797</v>
+        <v>431718</v>
       </c>
       <c r="R139" t="n">
-        <v>6795173</v>
+        <v>6795082</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14271,12 +14265,18 @@
           <t>2025-11-14</t>
         </is>
       </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Mjuk och len på undetsidan, sämskskinnslik känsla</t>
+        </is>
+      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -14295,7 +14295,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129694865</v>
+        <v>129707334</v>
       </c>
       <c r="B140" t="n">
         <v>79700</v>
@@ -14330,10 +14330,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>431787</v>
+        <v>431936</v>
       </c>
       <c r="R140" t="n">
-        <v>6795115</v>
+        <v>6795411</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14380,22 +14380,22 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129694896</v>
+        <v>129707370</v>
       </c>
       <c r="B141" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14403,21 +14403,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14427,10 +14427,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>431900</v>
+        <v>431913</v>
       </c>
       <c r="R141" t="n">
-        <v>6795265</v>
+        <v>6795394</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14477,12 +14477,12 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>

--- a/artfynd/A 50492-2025 artfynd.xlsx
+++ b/artfynd/A 50492-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129707440</v>
+        <v>129707371</v>
       </c>
       <c r="B2" t="n">
-        <v>92875</v>
+        <v>8450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,43 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>431828</v>
+        <v>431808</v>
       </c>
       <c r="R2" t="n">
-        <v>6795476</v>
+        <v>6795442</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,6 +763,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -772,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129707216</v>
+        <v>129694929</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,26 +793,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -810,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>432007</v>
+        <v>431859</v>
       </c>
       <c r="R3" t="n">
-        <v>6795475</v>
+        <v>6795172</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,51 +869,50 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129707403</v>
+        <v>129707440</v>
       </c>
       <c r="B4" t="n">
-        <v>79081</v>
+        <v>92875</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -908,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>431851</v>
+        <v>431828</v>
       </c>
       <c r="R4" t="n">
-        <v>6795372</v>
+        <v>6795476</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,54 +984,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129707371</v>
+        <v>129694842</v>
       </c>
       <c r="B5" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>431808</v>
+        <v>431768</v>
       </c>
       <c r="R5" t="n">
-        <v>6795442</v>
+        <v>6795469</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1058,29 +1063,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129694842</v>
+        <v>129694957</v>
       </c>
       <c r="B6" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1088,21 +1092,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1112,10 +1116,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>431768</v>
+        <v>431725</v>
       </c>
       <c r="R6" t="n">
-        <v>6795469</v>
+        <v>6795459</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,10 +1178,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129694957</v>
+        <v>129694862</v>
       </c>
       <c r="B7" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1185,21 +1189,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1209,10 +1213,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>431725</v>
+        <v>431756</v>
       </c>
       <c r="R7" t="n">
-        <v>6795459</v>
+        <v>6795121</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,10 +1275,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129694862</v>
+        <v>129694935</v>
       </c>
       <c r="B8" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1282,34 +1286,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>431756</v>
+        <v>431917</v>
       </c>
       <c r="R8" t="n">
-        <v>6795121</v>
+        <v>6795290</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,10 +1380,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129694935</v>
+        <v>129707216</v>
       </c>
       <c r="B9" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1379,31 +1391,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1411,10 +1418,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>431917</v>
+        <v>432007</v>
       </c>
       <c r="R9" t="n">
-        <v>6795290</v>
+        <v>6795475</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1455,28 +1462,29 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129694929</v>
+        <v>129707403</v>
       </c>
       <c r="B10" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1484,42 +1492,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>431859</v>
+        <v>431851</v>
       </c>
       <c r="R10" t="n">
-        <v>6795172</v>
+        <v>6795372</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,22 +1566,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129694983</v>
+        <v>129694843</v>
       </c>
       <c r="B11" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1589,21 +1589,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>431689</v>
+        <v>431752</v>
       </c>
       <c r="R11" t="n">
-        <v>6795456</v>
+        <v>6795429</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1675,10 +1675,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129694923</v>
+        <v>129694907</v>
       </c>
       <c r="B12" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1686,42 +1686,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>431687</v>
+        <v>431938</v>
       </c>
       <c r="R12" t="n">
-        <v>6795471</v>
+        <v>6795278</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1885,10 +1877,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129694843</v>
+        <v>129694923</v>
       </c>
       <c r="B14" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1896,34 +1888,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>431752</v>
+        <v>431687</v>
       </c>
       <c r="R14" t="n">
-        <v>6795429</v>
+        <v>6795471</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1982,7 +1982,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129694907</v>
+        <v>129707336</v>
       </c>
       <c r="B15" t="n">
         <v>79700</v>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>431938</v>
+        <v>431993</v>
       </c>
       <c r="R15" t="n">
-        <v>6795278</v>
+        <v>6795380</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2067,22 +2067,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129707358</v>
+        <v>129694983</v>
       </c>
       <c r="B16" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2090,42 +2090,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>431912</v>
+        <v>431689</v>
       </c>
       <c r="R16" t="n">
-        <v>6795310</v>
+        <v>6795456</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2172,22 +2164,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129707336</v>
+        <v>129707434</v>
       </c>
       <c r="B17" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2195,21 +2187,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2219,10 +2211,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>431993</v>
+        <v>431894</v>
       </c>
       <c r="R17" t="n">
-        <v>6795380</v>
+        <v>6795261</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2281,10 +2273,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129707434</v>
+        <v>129707358</v>
       </c>
       <c r="B18" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2292,34 +2284,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>431894</v>
+        <v>431912</v>
       </c>
       <c r="R18" t="n">
-        <v>6795261</v>
+        <v>6795310</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2475,7 +2475,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129707310</v>
+        <v>129707335</v>
       </c>
       <c r="B20" t="n">
         <v>79700</v>
@@ -2510,10 +2510,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>431924</v>
+        <v>431965</v>
       </c>
       <c r="R20" t="n">
-        <v>6795546</v>
+        <v>6795430</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2572,7 +2572,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129694845</v>
+        <v>129707310</v>
       </c>
       <c r="B21" t="n">
         <v>79700</v>
@@ -2607,10 +2607,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>431722</v>
+        <v>431924</v>
       </c>
       <c r="R21" t="n">
-        <v>6795478</v>
+        <v>6795546</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2657,65 +2657,57 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129694913</v>
+        <v>129694845</v>
       </c>
       <c r="B22" t="n">
-        <v>56926</v>
+        <v>79700</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>431728</v>
+        <v>431722</v>
       </c>
       <c r="R22" t="n">
-        <v>6795109</v>
+        <v>6795478</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2774,45 +2766,53 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129707335</v>
+        <v>129694913</v>
       </c>
       <c r="B23" t="n">
-        <v>79700</v>
+        <v>56926</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>431965</v>
+        <v>431728</v>
       </c>
       <c r="R23" t="n">
-        <v>6795430</v>
+        <v>6795109</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2859,19 +2859,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129694883</v>
+        <v>129707331</v>
       </c>
       <c r="B24" t="n">
         <v>79700</v>
@@ -2900,16 +2900,19 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>431885</v>
+        <v>431916</v>
       </c>
       <c r="R24" t="n">
-        <v>6795213</v>
+        <v>6795392</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2950,28 +2953,29 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129694884</v>
+        <v>129694942</v>
       </c>
       <c r="B25" t="n">
-        <v>79700</v>
+        <v>91891</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2979,21 +2983,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3003,10 +3007,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>431885</v>
+        <v>431803</v>
       </c>
       <c r="R25" t="n">
-        <v>6795215</v>
+        <v>6795150</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3047,6 +3051,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3065,7 +3070,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129694898</v>
+        <v>129694883</v>
       </c>
       <c r="B26" t="n">
         <v>79700</v>
@@ -3100,10 +3105,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>431907</v>
+        <v>431885</v>
       </c>
       <c r="R26" t="n">
-        <v>6795285</v>
+        <v>6795213</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3162,7 +3167,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129694899</v>
+        <v>129694884</v>
       </c>
       <c r="B27" t="n">
         <v>79700</v>
@@ -3197,10 +3202,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>431910</v>
+        <v>431885</v>
       </c>
       <c r="R27" t="n">
-        <v>6795288</v>
+        <v>6795215</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3259,7 +3264,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129694861</v>
+        <v>129694898</v>
       </c>
       <c r="B28" t="n">
         <v>79700</v>
@@ -3294,10 +3299,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>431740</v>
+        <v>431907</v>
       </c>
       <c r="R28" t="n">
-        <v>6795107</v>
+        <v>6795285</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3356,7 +3361,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129707308</v>
+        <v>129694899</v>
       </c>
       <c r="B29" t="n">
         <v>79700</v>
@@ -3391,10 +3396,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>431868</v>
+        <v>431910</v>
       </c>
       <c r="R29" t="n">
-        <v>6795565</v>
+        <v>6795288</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3441,22 +3446,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129707407</v>
+        <v>129694861</v>
       </c>
       <c r="B30" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3464,21 +3469,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3488,10 +3493,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>431723</v>
+        <v>431740</v>
       </c>
       <c r="R30" t="n">
-        <v>6795371</v>
+        <v>6795107</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3538,22 +3543,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129707331</v>
+        <v>129707407</v>
       </c>
       <c r="B31" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3561,37 +3566,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>431916</v>
+        <v>431723</v>
       </c>
       <c r="R31" t="n">
-        <v>6795392</v>
+        <v>6795371</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3632,7 +3634,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3651,10 +3652,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129694942</v>
+        <v>129707308</v>
       </c>
       <c r="B32" t="n">
-        <v>91891</v>
+        <v>79700</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3662,21 +3663,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3686,10 +3687,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>431803</v>
+        <v>431868</v>
       </c>
       <c r="R32" t="n">
-        <v>6795150</v>
+        <v>6795565</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3730,29 +3731,28 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129707346</v>
+        <v>129694917</v>
       </c>
       <c r="B33" t="n">
-        <v>57733</v>
+        <v>91614</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3760,31 +3760,30 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3792,10 +3791,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>431819</v>
+        <v>431672</v>
       </c>
       <c r="R33" t="n">
-        <v>6795465</v>
+        <v>6795442</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3836,28 +3835,29 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129707390</v>
+        <v>129694980</v>
       </c>
       <c r="B34" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3865,37 +3865,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>431952</v>
+        <v>431711</v>
       </c>
       <c r="R34" t="n">
-        <v>6795410</v>
+        <v>6795450</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3936,19 +3933,18 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4056,10 +4052,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129694980</v>
+        <v>129694921</v>
       </c>
       <c r="B36" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4067,34 +4063,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>431711</v>
+        <v>431725</v>
       </c>
       <c r="R36" t="n">
-        <v>6795450</v>
+        <v>6795459</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4153,10 +4157,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129694886</v>
+        <v>129707390</v>
       </c>
       <c r="B37" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4164,34 +4168,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>431873</v>
+        <v>431952</v>
       </c>
       <c r="R37" t="n">
-        <v>6795241</v>
+        <v>6795410</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4232,50 +4239,51 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129694878</v>
+        <v>129695010</v>
       </c>
       <c r="B38" t="n">
-        <v>79700</v>
+        <v>92875</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4285,10 +4293,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>431889</v>
+        <v>431880</v>
       </c>
       <c r="R38" t="n">
-        <v>6795186</v>
+        <v>6795546</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4347,32 +4355,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129695010</v>
+        <v>129694886</v>
       </c>
       <c r="B39" t="n">
-        <v>92875</v>
+        <v>79700</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4382,10 +4390,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>431880</v>
+        <v>431873</v>
       </c>
       <c r="R39" t="n">
-        <v>6795546</v>
+        <v>6795241</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4444,10 +4452,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129694917</v>
+        <v>129694878</v>
       </c>
       <c r="B40" t="n">
-        <v>91614</v>
+        <v>79700</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4455,41 +4463,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>431672</v>
+        <v>431889</v>
       </c>
       <c r="R40" t="n">
-        <v>6795442</v>
+        <v>6795186</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4530,7 +4531,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4549,7 +4549,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129694921</v>
+        <v>129707346</v>
       </c>
       <c r="B41" t="n">
         <v>57733</v>
@@ -4592,10 +4592,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>431725</v>
+        <v>431819</v>
       </c>
       <c r="R41" t="n">
-        <v>6795459</v>
+        <v>6795465</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4642,22 +4642,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129694847</v>
+        <v>129707351</v>
       </c>
       <c r="B42" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4665,34 +4665,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>431724</v>
+        <v>431756</v>
       </c>
       <c r="R42" t="n">
-        <v>6795460</v>
+        <v>6795202</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4739,22 +4747,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129707351</v>
+        <v>129694847</v>
       </c>
       <c r="B43" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4762,42 +4770,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>431756</v>
+        <v>431724</v>
       </c>
       <c r="R43" t="n">
-        <v>6795202</v>
+        <v>6795460</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4844,22 +4844,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129707333</v>
+        <v>129694999</v>
       </c>
       <c r="B44" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4867,21 +4867,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4891,10 +4891,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>431935</v>
+        <v>431859</v>
       </c>
       <c r="R44" t="n">
-        <v>6795415</v>
+        <v>6795172</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4941,22 +4941,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129707338</v>
+        <v>129694926</v>
       </c>
       <c r="B45" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4964,34 +4964,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>431932</v>
+        <v>431711</v>
       </c>
       <c r="R45" t="n">
-        <v>6795406</v>
+        <v>6795100</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5038,22 +5046,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129694999</v>
+        <v>129707316</v>
       </c>
       <c r="B46" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5061,21 +5069,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5085,10 +5093,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>431859</v>
+        <v>431812</v>
       </c>
       <c r="R46" t="n">
-        <v>6795172</v>
+        <v>6795349</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5135,22 +5143,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129694926</v>
+        <v>129707333</v>
       </c>
       <c r="B47" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5158,42 +5166,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>431711</v>
+        <v>431935</v>
       </c>
       <c r="R47" t="n">
-        <v>6795100</v>
+        <v>6795415</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5240,19 +5240,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129707320</v>
+        <v>129707338</v>
       </c>
       <c r="B48" t="n">
         <v>79700</v>
@@ -5287,10 +5287,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>431717</v>
+        <v>431932</v>
       </c>
       <c r="R48" t="n">
-        <v>6795380</v>
+        <v>6795406</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5349,10 +5349,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129707316</v>
+        <v>129707375</v>
       </c>
       <c r="B49" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5360,21 +5360,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5384,10 +5384,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>431812</v>
+        <v>431881</v>
       </c>
       <c r="R49" t="n">
-        <v>6795349</v>
+        <v>6795522</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5446,10 +5446,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129707375</v>
+        <v>129707320</v>
       </c>
       <c r="B50" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5457,21 +5457,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5481,10 +5481,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>431881</v>
+        <v>431717</v>
       </c>
       <c r="R50" t="n">
-        <v>6795522</v>
+        <v>6795380</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5640,7 +5640,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129694994</v>
+        <v>129695003</v>
       </c>
       <c r="B52" t="n">
         <v>79081</v>
@@ -5675,10 +5675,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>431804</v>
+        <v>431908</v>
       </c>
       <c r="R52" t="n">
-        <v>6795151</v>
+        <v>6795302</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5737,10 +5737,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129694846</v>
+        <v>129694994</v>
       </c>
       <c r="B53" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5748,21 +5748,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>431725</v>
+        <v>431804</v>
       </c>
       <c r="R53" t="n">
-        <v>6795467</v>
+        <v>6795151</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5834,10 +5834,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129695003</v>
+        <v>129707337</v>
       </c>
       <c r="B54" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5845,21 +5845,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5869,10 +5869,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>431908</v>
+        <v>431999</v>
       </c>
       <c r="R54" t="n">
-        <v>6795302</v>
+        <v>6795416</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5919,12 +5919,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6036,7 +6036,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129707337</v>
+        <v>129694846</v>
       </c>
       <c r="B56" t="n">
         <v>79700</v>
@@ -6071,10 +6071,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>431999</v>
+        <v>431725</v>
       </c>
       <c r="R56" t="n">
-        <v>6795416</v>
+        <v>6795467</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6121,22 +6121,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129707426</v>
+        <v>129707380</v>
       </c>
       <c r="B57" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6144,21 +6144,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6168,10 +6168,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>431767</v>
+        <v>431820</v>
       </c>
       <c r="R57" t="n">
-        <v>6795219</v>
+        <v>6795330</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6230,7 +6230,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129707404</v>
+        <v>129707426</v>
       </c>
       <c r="B58" t="n">
         <v>79081</v>
@@ -6259,19 +6259,16 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>431816</v>
+        <v>431767</v>
       </c>
       <c r="R58" t="n">
-        <v>6795333</v>
+        <v>6795219</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6306,18 +6303,12 @@
           <t>2025-11-14</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6336,10 +6327,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129707380</v>
+        <v>129707404</v>
       </c>
       <c r="B59" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6347,34 +6338,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>431820</v>
+        <v>431816</v>
       </c>
       <c r="R59" t="n">
-        <v>6795330</v>
+        <v>6795333</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6409,12 +6403,18 @@
           <t>2025-11-14</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6821,10 +6821,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129707319</v>
+        <v>129694930</v>
       </c>
       <c r="B64" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6832,34 +6832,42 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>431708</v>
+        <v>431875</v>
       </c>
       <c r="R64" t="n">
-        <v>6795371</v>
+        <v>6795244</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6906,22 +6914,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129694930</v>
+        <v>129707319</v>
       </c>
       <c r="B65" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6929,42 +6937,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>431875</v>
+        <v>431708</v>
       </c>
       <c r="R65" t="n">
-        <v>6795244</v>
+        <v>6795371</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7011,22 +7011,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129707382</v>
+        <v>129694857</v>
       </c>
       <c r="B66" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7034,37 +7034,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>431689</v>
+        <v>431800</v>
       </c>
       <c r="R66" t="n">
-        <v>6795383</v>
+        <v>6795130</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7105,29 +7102,28 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129707420</v>
+        <v>129694908</v>
       </c>
       <c r="B67" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7135,21 +7131,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7159,10 +7155,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>431695</v>
+        <v>431973</v>
       </c>
       <c r="R67" t="n">
-        <v>6795256</v>
+        <v>6795310</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7209,19 +7205,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129694857</v>
+        <v>129694858</v>
       </c>
       <c r="B68" t="n">
         <v>79700</v>
@@ -7256,10 +7252,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>431800</v>
+        <v>431749</v>
       </c>
       <c r="R68" t="n">
-        <v>6795130</v>
+        <v>6795079</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7318,7 +7314,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129694908</v>
+        <v>129694859</v>
       </c>
       <c r="B69" t="n">
         <v>79700</v>
@@ -7353,10 +7349,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>431973</v>
+        <v>431702</v>
       </c>
       <c r="R69" t="n">
-        <v>6795310</v>
+        <v>6795115</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7415,7 +7411,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129694858</v>
+        <v>129694879</v>
       </c>
       <c r="B70" t="n">
         <v>79700</v>
@@ -7450,10 +7446,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>431749</v>
+        <v>431888</v>
       </c>
       <c r="R70" t="n">
-        <v>6795079</v>
+        <v>6795198</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7512,10 +7508,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129694859</v>
+        <v>129707382</v>
       </c>
       <c r="B71" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7523,34 +7519,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>431702</v>
+        <v>431689</v>
       </c>
       <c r="R71" t="n">
-        <v>6795115</v>
+        <v>6795383</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7591,28 +7590,29 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129694879</v>
+        <v>129694928</v>
       </c>
       <c r="B72" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7620,34 +7620,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>431888</v>
+        <v>431801</v>
       </c>
       <c r="R72" t="n">
-        <v>6795198</v>
+        <v>6795136</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7706,10 +7714,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129694928</v>
+        <v>129707420</v>
       </c>
       <c r="B73" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7717,42 +7725,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>431801</v>
+        <v>431695</v>
       </c>
       <c r="R73" t="n">
-        <v>6795136</v>
+        <v>6795256</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7799,22 +7799,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129694985</v>
+        <v>129707389</v>
       </c>
       <c r="B74" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7822,34 +7822,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>431673</v>
+        <v>431922</v>
       </c>
       <c r="R74" t="n">
-        <v>6795435</v>
+        <v>6795405</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7890,50 +7893,51 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129707439</v>
+        <v>129707391</v>
       </c>
       <c r="B75" t="n">
-        <v>92875</v>
+        <v>78838</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7943,10 +7947,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>431891</v>
+        <v>431724</v>
       </c>
       <c r="R75" t="n">
-        <v>6795553</v>
+        <v>6795372</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8005,32 +8009,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129707314</v>
+        <v>129707439</v>
       </c>
       <c r="B76" t="n">
-        <v>79700</v>
+        <v>92875</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8040,10 +8044,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>431866</v>
+        <v>431891</v>
       </c>
       <c r="R76" t="n">
-        <v>6795513</v>
+        <v>6795553</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8199,10 +8203,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129707391</v>
+        <v>129707314</v>
       </c>
       <c r="B78" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8210,21 +8214,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8234,10 +8238,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>431724</v>
+        <v>431866</v>
       </c>
       <c r="R78" t="n">
-        <v>6795372</v>
+        <v>6795513</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8296,10 +8300,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129707389</v>
+        <v>129694985</v>
       </c>
       <c r="B79" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8307,37 +8311,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>431922</v>
+        <v>431673</v>
       </c>
       <c r="R79" t="n">
-        <v>6795405</v>
+        <v>6795435</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8378,29 +8379,28 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129695001</v>
+        <v>129694863</v>
       </c>
       <c r="B80" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8408,21 +8408,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8432,10 +8432,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>431876</v>
+        <v>431785</v>
       </c>
       <c r="R80" t="n">
-        <v>6795202</v>
+        <v>6795106</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8494,10 +8494,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129694948</v>
+        <v>129694874</v>
       </c>
       <c r="B81" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8505,21 +8505,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>431725</v>
+        <v>431827</v>
       </c>
       <c r="R81" t="n">
-        <v>6795459</v>
+        <v>6795171</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8591,10 +8591,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129707345</v>
+        <v>129695001</v>
       </c>
       <c r="B82" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8602,42 +8602,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>431893</v>
+        <v>431876</v>
       </c>
       <c r="R82" t="n">
-        <v>6795571</v>
+        <v>6795202</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8684,19 +8676,19 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129707424</v>
+        <v>129694991</v>
       </c>
       <c r="B83" t="n">
         <v>79081</v>
@@ -8734,7 +8726,7 @@
         <v>431760</v>
       </c>
       <c r="R83" t="n">
-        <v>6795200</v>
+        <v>6795115</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8781,22 +8773,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129694991</v>
+        <v>129707388</v>
       </c>
       <c r="B84" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8804,21 +8796,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8828,10 +8820,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>431760</v>
+        <v>431915</v>
       </c>
       <c r="R84" t="n">
-        <v>6795115</v>
+        <v>6795392</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8878,22 +8870,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129694863</v>
+        <v>129694933</v>
       </c>
       <c r="B85" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8901,34 +8893,42 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>431785</v>
+        <v>431904</v>
       </c>
       <c r="R85" t="n">
-        <v>6795106</v>
+        <v>6795243</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8987,10 +8987,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129694874</v>
+        <v>129707424</v>
       </c>
       <c r="B86" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8998,21 +8998,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9022,10 +9022,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>431827</v>
+        <v>431760</v>
       </c>
       <c r="R86" t="n">
-        <v>6795171</v>
+        <v>6795200</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9072,22 +9072,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129694933</v>
+        <v>129707315</v>
       </c>
       <c r="B87" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9095,42 +9095,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>431904</v>
+        <v>431820</v>
       </c>
       <c r="R87" t="n">
-        <v>6795243</v>
+        <v>6795329</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9177,22 +9169,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129707388</v>
+        <v>129707345</v>
       </c>
       <c r="B88" t="n">
-        <v>78838</v>
+        <v>57733</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9200,34 +9192,42 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>431915</v>
+        <v>431893</v>
       </c>
       <c r="R88" t="n">
-        <v>6795392</v>
+        <v>6795571</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9286,10 +9286,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129707315</v>
+        <v>129694948</v>
       </c>
       <c r="B89" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9297,21 +9297,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9321,10 +9321,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>431820</v>
+        <v>431725</v>
       </c>
       <c r="R89" t="n">
-        <v>6795329</v>
+        <v>6795459</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9371,22 +9371,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129694860</v>
+        <v>129694939</v>
       </c>
       <c r="B90" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9394,21 +9394,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9418,10 +9418,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>431746</v>
+        <v>431913</v>
       </c>
       <c r="R90" t="n">
-        <v>6795081</v>
+        <v>6795284</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9454,6 +9454,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9480,10 +9485,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129694965</v>
+        <v>129694934</v>
       </c>
       <c r="B91" t="n">
-        <v>78838</v>
+        <v>57733</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9491,34 +9496,42 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>431885</v>
+        <v>431916</v>
       </c>
       <c r="R91" t="n">
-        <v>6795240</v>
+        <v>6795286</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9577,10 +9590,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129694934</v>
+        <v>129707381</v>
       </c>
       <c r="B92" t="n">
-        <v>57733</v>
+        <v>78838</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9588,42 +9601,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>431916</v>
+        <v>431712</v>
       </c>
       <c r="R92" t="n">
-        <v>6795286</v>
+        <v>6795379</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9670,22 +9675,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129694939</v>
+        <v>129694860</v>
       </c>
       <c r="B93" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9693,21 +9698,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9717,10 +9722,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>431913</v>
+        <v>431746</v>
       </c>
       <c r="R93" t="n">
-        <v>6795284</v>
+        <v>6795081</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9753,11 +9758,6 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9784,10 +9784,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129707405</v>
+        <v>129694965</v>
       </c>
       <c r="B94" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9795,21 +9795,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9819,10 +9819,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>431775</v>
+        <v>431885</v>
       </c>
       <c r="R94" t="n">
-        <v>6795343</v>
+        <v>6795240</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9869,22 +9869,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129707381</v>
+        <v>129707405</v>
       </c>
       <c r="B95" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9892,21 +9892,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9916,10 +9916,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>431712</v>
+        <v>431775</v>
       </c>
       <c r="R95" t="n">
-        <v>6795379</v>
+        <v>6795343</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9978,32 +9978,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129694989</v>
+        <v>129694941</v>
       </c>
       <c r="B96" t="n">
-        <v>79081</v>
+        <v>79167</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10013,10 +10013,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>431723</v>
+        <v>431976</v>
       </c>
       <c r="R96" t="n">
-        <v>6795090</v>
+        <v>6795333</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10075,32 +10075,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129694941</v>
+        <v>129707312</v>
       </c>
       <c r="B97" t="n">
-        <v>79167</v>
+        <v>79700</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6450</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10110,10 +10110,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>431976</v>
+        <v>431920</v>
       </c>
       <c r="R97" t="n">
-        <v>6795333</v>
+        <v>6795611</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10160,22 +10160,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129707312</v>
+        <v>129694989</v>
       </c>
       <c r="B98" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10183,21 +10183,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10207,10 +10207,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>431920</v>
+        <v>431723</v>
       </c>
       <c r="R98" t="n">
-        <v>6795611</v>
+        <v>6795090</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10257,12 +10257,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -10374,10 +10374,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129694927</v>
+        <v>129694877</v>
       </c>
       <c r="B100" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10385,42 +10385,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>431711</v>
+        <v>431887</v>
       </c>
       <c r="R100" t="n">
-        <v>6795094</v>
+        <v>6795183</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10479,10 +10471,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129694938</v>
+        <v>129694885</v>
       </c>
       <c r="B101" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10490,42 +10482,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>431915</v>
+        <v>431873</v>
       </c>
       <c r="R101" t="n">
-        <v>6795279</v>
+        <v>6795224</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10584,10 +10568,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129695000</v>
+        <v>129694864</v>
       </c>
       <c r="B102" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10595,21 +10579,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10619,10 +10603,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>431890</v>
+        <v>431786</v>
       </c>
       <c r="R102" t="n">
-        <v>6795199</v>
+        <v>6795113</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10681,7 +10665,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129694992</v>
+        <v>129695000</v>
       </c>
       <c r="B103" t="n">
         <v>79081</v>
@@ -10716,10 +10700,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>431799</v>
+        <v>431890</v>
       </c>
       <c r="R103" t="n">
-        <v>6795129</v>
+        <v>6795199</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10778,10 +10762,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129694877</v>
+        <v>129694992</v>
       </c>
       <c r="B104" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10789,21 +10773,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10813,10 +10797,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>431887</v>
+        <v>431799</v>
       </c>
       <c r="R104" t="n">
-        <v>6795183</v>
+        <v>6795129</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10875,10 +10859,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129694885</v>
+        <v>129694938</v>
       </c>
       <c r="B105" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10886,34 +10870,42 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>431873</v>
+        <v>431915</v>
       </c>
       <c r="R105" t="n">
-        <v>6795224</v>
+        <v>6795279</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10972,10 +10964,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129694864</v>
+        <v>129707425</v>
       </c>
       <c r="B106" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10983,21 +10975,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11007,10 +10999,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>431786</v>
+        <v>431756</v>
       </c>
       <c r="R106" t="n">
-        <v>6795113</v>
+        <v>6795247</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11057,19 +11049,19 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129707349</v>
+        <v>129694927</v>
       </c>
       <c r="B107" t="n">
         <v>57733</v>
@@ -11112,10 +11104,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>431722</v>
+        <v>431711</v>
       </c>
       <c r="R107" t="n">
-        <v>6795217</v>
+        <v>6795094</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11162,12 +11154,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
@@ -11271,10 +11263,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129707327</v>
+        <v>129707396</v>
       </c>
       <c r="B109" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11282,21 +11274,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11306,10 +11298,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>431893</v>
+        <v>431918</v>
       </c>
       <c r="R109" t="n">
-        <v>6795305</v>
+        <v>6795574</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11368,7 +11360,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129707396</v>
+        <v>129707406</v>
       </c>
       <c r="B110" t="n">
         <v>79081</v>
@@ -11403,10 +11395,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>431918</v>
+        <v>431771</v>
       </c>
       <c r="R110" t="n">
-        <v>6795574</v>
+        <v>6795344</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11465,10 +11457,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129707406</v>
+        <v>129707332</v>
       </c>
       <c r="B111" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11476,21 +11468,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11500,10 +11492,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>431771</v>
+        <v>431923</v>
       </c>
       <c r="R111" t="n">
-        <v>6795344</v>
+        <v>6795402</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11562,7 +11554,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129707332</v>
+        <v>129707327</v>
       </c>
       <c r="B112" t="n">
         <v>79700</v>
@@ -11597,10 +11589,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>431923</v>
+        <v>431893</v>
       </c>
       <c r="R112" t="n">
-        <v>6795402</v>
+        <v>6795305</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11659,10 +11651,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129707425</v>
+        <v>129707349</v>
       </c>
       <c r="B113" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11670,34 +11662,42 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>431756</v>
+        <v>431722</v>
       </c>
       <c r="R113" t="n">
-        <v>6795247</v>
+        <v>6795217</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11756,7 +11756,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129694990</v>
+        <v>129707421</v>
       </c>
       <c r="B114" t="n">
         <v>79081</v>
@@ -11791,10 +11791,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>431726</v>
+        <v>431711</v>
       </c>
       <c r="R114" t="n">
-        <v>6795117</v>
+        <v>6795239</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11841,19 +11841,19 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129694901</v>
+        <v>129707330</v>
       </c>
       <c r="B115" t="n">
         <v>79700</v>
@@ -11888,10 +11888,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>431927</v>
+        <v>431930</v>
       </c>
       <c r="R115" t="n">
-        <v>6795265</v>
+        <v>6795399</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11938,19 +11938,19 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129694844</v>
+        <v>129707309</v>
       </c>
       <c r="B116" t="n">
         <v>79700</v>
@@ -11985,10 +11985,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>431739</v>
+        <v>431869</v>
       </c>
       <c r="R116" t="n">
-        <v>6795440</v>
+        <v>6795521</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12035,19 +12035,19 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129707309</v>
+        <v>129707323</v>
       </c>
       <c r="B117" t="n">
         <v>79700</v>
@@ -12082,10 +12082,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>431869</v>
+        <v>431712</v>
       </c>
       <c r="R117" t="n">
-        <v>6795521</v>
+        <v>6795236</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12144,7 +12144,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129707330</v>
+        <v>129694901</v>
       </c>
       <c r="B118" t="n">
         <v>79700</v>
@@ -12179,10 +12179,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>431930</v>
+        <v>431927</v>
       </c>
       <c r="R118" t="n">
-        <v>6795399</v>
+        <v>6795265</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12229,19 +12229,19 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129707323</v>
+        <v>129694844</v>
       </c>
       <c r="B119" t="n">
         <v>79700</v>
@@ -12276,10 +12276,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>431712</v>
+        <v>431739</v>
       </c>
       <c r="R119" t="n">
-        <v>6795236</v>
+        <v>6795440</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12326,22 +12326,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129707386</v>
+        <v>129694990</v>
       </c>
       <c r="B120" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12349,21 +12349,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12373,10 +12373,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>431897</v>
+        <v>431726</v>
       </c>
       <c r="R120" t="n">
-        <v>6795284</v>
+        <v>6795117</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12423,22 +12423,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129707421</v>
+        <v>129707386</v>
       </c>
       <c r="B121" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12446,21 +12446,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12470,10 +12470,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>431711</v>
+        <v>431897</v>
       </c>
       <c r="R121" t="n">
-        <v>6795239</v>
+        <v>6795284</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13017,10 +13017,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129707368</v>
+        <v>129694925</v>
       </c>
       <c r="B127" t="n">
-        <v>78839</v>
+        <v>57733</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13028,26 +13028,31 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
@@ -13055,10 +13060,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>431820</v>
+        <v>431687</v>
       </c>
       <c r="R127" t="n">
-        <v>6795331</v>
+        <v>6795051</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13099,29 +13104,28 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129694925</v>
+        <v>129707368</v>
       </c>
       <c r="B128" t="n">
-        <v>57733</v>
+        <v>78839</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13129,31 +13133,26 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
@@ -13161,10 +13160,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>431687</v>
+        <v>431820</v>
       </c>
       <c r="R128" t="n">
-        <v>6795051</v>
+        <v>6795331</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13205,18 +13204,19 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
@@ -14193,10 +14193,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129694956</v>
+        <v>129707334</v>
       </c>
       <c r="B139" t="n">
-        <v>92011</v>
+        <v>79700</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14204,33 +14204,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6040162</v>
+        <v>6453</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>431718</v>
+        <v>431936</v>
       </c>
       <c r="R139" t="n">
-        <v>6795082</v>
+        <v>6795411</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14265,40 +14266,34 @@
           <t>2025-11-14</t>
         </is>
       </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>Mjuk och len på undetsidan, sämskskinnslik känsla</t>
-        </is>
-      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129707334</v>
+        <v>129694956</v>
       </c>
       <c r="B140" t="n">
-        <v>79700</v>
+        <v>92011</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14306,34 +14301,33 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>431936</v>
+        <v>431718</v>
       </c>
       <c r="R140" t="n">
-        <v>6795411</v>
+        <v>6795082</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14368,24 +14362,30 @@
           <t>2025-11-14</t>
         </is>
       </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Mjuk och len på undetsidan, sämskskinnslik känsla</t>
+        </is>
+      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
@@ -14489,10 +14489,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129707377</v>
+        <v>129694876</v>
       </c>
       <c r="B142" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14500,21 +14500,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14524,10 +14524,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>431843</v>
+        <v>431871</v>
       </c>
       <c r="R142" t="n">
-        <v>6795474</v>
+        <v>6795171</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14574,19 +14574,19 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129694876</v>
+        <v>129694887</v>
       </c>
       <c r="B143" t="n">
         <v>79700</v>
@@ -14621,10 +14621,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>431871</v>
+        <v>431886</v>
       </c>
       <c r="R143" t="n">
-        <v>6795171</v>
+        <v>6795236</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14683,7 +14683,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129694887</v>
+        <v>129694880</v>
       </c>
       <c r="B144" t="n">
         <v>79700</v>
@@ -14718,10 +14718,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>431886</v>
+        <v>431871</v>
       </c>
       <c r="R144" t="n">
-        <v>6795236</v>
+        <v>6795205</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14780,7 +14780,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129694880</v>
+        <v>129694897</v>
       </c>
       <c r="B145" t="n">
         <v>79700</v>
@@ -14815,10 +14815,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>431871</v>
+        <v>431906</v>
       </c>
       <c r="R145" t="n">
-        <v>6795205</v>
+        <v>6795283</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -14877,10 +14877,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129694897</v>
+        <v>129707377</v>
       </c>
       <c r="B146" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14888,21 +14888,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -14912,10 +14912,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>431906</v>
+        <v>431843</v>
       </c>
       <c r="R146" t="n">
-        <v>6795283</v>
+        <v>6795474</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -14962,12 +14962,12 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>

--- a/artfynd/A 50492-2025 artfynd.xlsx
+++ b/artfynd/A 50492-2025 artfynd.xlsx
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129707371</v>
+        <v>129707403</v>
       </c>
       <c r="B2" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>431808</v>
+        <v>431851</v>
       </c>
       <c r="R2" t="n">
-        <v>6795442</v>
+        <v>6795372</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -763,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129694929</v>
+        <v>129707216</v>
       </c>
       <c r="B3" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,31 +783,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,10 +810,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>431859</v>
+        <v>432007</v>
       </c>
       <c r="R3" t="n">
-        <v>6795172</v>
+        <v>6795475</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,63 +854,72 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129707440</v>
+        <v>129694935</v>
       </c>
       <c r="B4" t="n">
-        <v>92875</v>
+        <v>57733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>431828</v>
+        <v>431917</v>
       </c>
       <c r="R4" t="n">
-        <v>6795476</v>
+        <v>6795290</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,22 +966,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129694842</v>
+        <v>129694929</v>
       </c>
       <c r="B5" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -995,34 +989,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>431768</v>
+        <v>431859</v>
       </c>
       <c r="R5" t="n">
-        <v>6795469</v>
+        <v>6795172</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129694957</v>
+        <v>129694842</v>
       </c>
       <c r="B6" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1092,21 +1094,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1116,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>431725</v>
+        <v>431768</v>
       </c>
       <c r="R6" t="n">
-        <v>6795459</v>
+        <v>6795469</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129694862</v>
+        <v>129694957</v>
       </c>
       <c r="B7" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1189,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1213,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>431756</v>
+        <v>431725</v>
       </c>
       <c r="R7" t="n">
-        <v>6795121</v>
+        <v>6795459</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129694935</v>
+        <v>129694862</v>
       </c>
       <c r="B8" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1286,42 +1288,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>431917</v>
+        <v>431756</v>
       </c>
       <c r="R8" t="n">
-        <v>6795290</v>
+        <v>6795121</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1380,48 +1374,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129707216</v>
+        <v>129707440</v>
       </c>
       <c r="B9" t="n">
-        <v>79081</v>
+        <v>92875</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>432007</v>
+        <v>431828</v>
       </c>
       <c r="R9" t="n">
-        <v>6795475</v>
+        <v>6795476</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1462,7 +1453,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1481,45 +1471,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129707403</v>
+        <v>129707371</v>
       </c>
       <c r="B10" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>431851</v>
+        <v>431808</v>
       </c>
       <c r="R10" t="n">
-        <v>6795372</v>
+        <v>6795442</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1560,6 +1559,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1578,10 +1578,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129694843</v>
+        <v>129694918</v>
       </c>
       <c r="B11" t="n">
-        <v>79700</v>
+        <v>91614</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1589,34 +1589,41 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>431752</v>
+        <v>431722</v>
       </c>
       <c r="R11" t="n">
-        <v>6795429</v>
+        <v>6795120</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1657,6 +1664,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1675,7 +1683,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129694907</v>
+        <v>129694843</v>
       </c>
       <c r="B12" t="n">
         <v>79700</v>
@@ -1710,10 +1718,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>431938</v>
+        <v>431752</v>
       </c>
       <c r="R12" t="n">
-        <v>6795278</v>
+        <v>6795429</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1772,10 +1780,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129694918</v>
+        <v>129694907</v>
       </c>
       <c r="B13" t="n">
-        <v>91614</v>
+        <v>79700</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1783,41 +1791,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>431722</v>
+        <v>431938</v>
       </c>
       <c r="R13" t="n">
-        <v>6795120</v>
+        <v>6795278</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1858,7 +1859,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1982,10 +1982,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129707336</v>
+        <v>129707434</v>
       </c>
       <c r="B15" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1993,21 +1993,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>431993</v>
+        <v>431894</v>
       </c>
       <c r="R15" t="n">
-        <v>6795380</v>
+        <v>6795261</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2176,10 +2176,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129707434</v>
+        <v>129707336</v>
       </c>
       <c r="B17" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2187,21 +2187,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>431894</v>
+        <v>431993</v>
       </c>
       <c r="R17" t="n">
-        <v>6795261</v>
+        <v>6795380</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2378,45 +2378,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129707378</v>
+        <v>129694913</v>
       </c>
       <c r="B19" t="n">
-        <v>78838</v>
+        <v>56926</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>431814</v>
+        <v>431728</v>
       </c>
       <c r="R19" t="n">
-        <v>6795444</v>
+        <v>6795109</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2463,19 +2471,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129707335</v>
+        <v>129694845</v>
       </c>
       <c r="B20" t="n">
         <v>79700</v>
@@ -2510,10 +2518,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>431965</v>
+        <v>431722</v>
       </c>
       <c r="R20" t="n">
-        <v>6795430</v>
+        <v>6795478</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2560,19 +2568,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129707310</v>
+        <v>129707335</v>
       </c>
       <c r="B21" t="n">
         <v>79700</v>
@@ -2607,10 +2615,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>431924</v>
+        <v>431965</v>
       </c>
       <c r="R21" t="n">
-        <v>6795546</v>
+        <v>6795430</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2669,10 +2677,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129694845</v>
+        <v>129707378</v>
       </c>
       <c r="B22" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2680,21 +2688,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2704,10 +2712,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>431722</v>
+        <v>431814</v>
       </c>
       <c r="R22" t="n">
-        <v>6795478</v>
+        <v>6795444</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2754,65 +2762,57 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129694913</v>
+        <v>129707310</v>
       </c>
       <c r="B23" t="n">
-        <v>56926</v>
+        <v>79700</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>431728</v>
+        <v>431924</v>
       </c>
       <c r="R23" t="n">
-        <v>6795109</v>
+        <v>6795546</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2859,22 +2859,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129707331</v>
+        <v>129694942</v>
       </c>
       <c r="B24" t="n">
-        <v>79700</v>
+        <v>91891</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2882,37 +2882,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>431916</v>
+        <v>431803</v>
       </c>
       <c r="R24" t="n">
-        <v>6795392</v>
+        <v>6795150</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2960,22 +2957,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129694942</v>
+        <v>129707407</v>
       </c>
       <c r="B25" t="n">
-        <v>91891</v>
+        <v>79081</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2983,21 +2980,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3007,10 +3004,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>431803</v>
+        <v>431723</v>
       </c>
       <c r="R25" t="n">
-        <v>6795150</v>
+        <v>6795371</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3051,26 +3048,25 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129694883</v>
+        <v>129707331</v>
       </c>
       <c r="B26" t="n">
         <v>79700</v>
@@ -3099,16 +3095,19 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>431885</v>
+        <v>431916</v>
       </c>
       <c r="R26" t="n">
-        <v>6795213</v>
+        <v>6795392</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3149,25 +3148,26 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129694884</v>
+        <v>129707308</v>
       </c>
       <c r="B27" t="n">
         <v>79700</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>431885</v>
+        <v>431868</v>
       </c>
       <c r="R27" t="n">
-        <v>6795215</v>
+        <v>6795565</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3252,19 +3252,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129694898</v>
+        <v>129694883</v>
       </c>
       <c r="B28" t="n">
         <v>79700</v>
@@ -3299,10 +3299,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>431907</v>
+        <v>431885</v>
       </c>
       <c r="R28" t="n">
-        <v>6795285</v>
+        <v>6795213</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3361,7 +3361,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129694899</v>
+        <v>129694884</v>
       </c>
       <c r="B29" t="n">
         <v>79700</v>
@@ -3396,10 +3396,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>431910</v>
+        <v>431885</v>
       </c>
       <c r="R29" t="n">
-        <v>6795288</v>
+        <v>6795215</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3458,7 +3458,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129694861</v>
+        <v>129694898</v>
       </c>
       <c r="B30" t="n">
         <v>79700</v>
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>431740</v>
+        <v>431907</v>
       </c>
       <c r="R30" t="n">
-        <v>6795107</v>
+        <v>6795285</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3555,10 +3555,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129707407</v>
+        <v>129694899</v>
       </c>
       <c r="B31" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3566,21 +3566,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>431723</v>
+        <v>431910</v>
       </c>
       <c r="R31" t="n">
-        <v>6795371</v>
+        <v>6795288</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3640,19 +3640,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129707308</v>
+        <v>129694861</v>
       </c>
       <c r="B32" t="n">
         <v>79700</v>
@@ -3687,10 +3687,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>431868</v>
+        <v>431740</v>
       </c>
       <c r="R32" t="n">
-        <v>6795565</v>
+        <v>6795107</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3737,64 +3737,57 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129694917</v>
+        <v>129695010</v>
       </c>
       <c r="B33" t="n">
-        <v>91614</v>
+        <v>92875</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>431672</v>
+        <v>431880</v>
       </c>
       <c r="R33" t="n">
-        <v>6795442</v>
+        <v>6795546</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3835,7 +3828,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3854,10 +3846,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129694980</v>
+        <v>129694917</v>
       </c>
       <c r="B34" t="n">
-        <v>79081</v>
+        <v>91614</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3865,34 +3857,41 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>431711</v>
+        <v>431672</v>
       </c>
       <c r="R34" t="n">
-        <v>6795450</v>
+        <v>6795442</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3933,6 +3932,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -3951,10 +3951,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129694839</v>
+        <v>129694878</v>
       </c>
       <c r="B35" t="n">
-        <v>91516</v>
+        <v>79700</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3962,37 +3962,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3242</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>431869</v>
+        <v>431889</v>
       </c>
       <c r="R35" t="n">
-        <v>6795181</v>
+        <v>6795186</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4033,7 +4030,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4052,10 +4048,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129694921</v>
+        <v>129694839</v>
       </c>
       <c r="B36" t="n">
-        <v>57733</v>
+        <v>91516</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4063,31 +4059,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>3242</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4095,10 +4086,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>431725</v>
+        <v>431869</v>
       </c>
       <c r="R36" t="n">
-        <v>6795459</v>
+        <v>6795181</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4139,6 +4130,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4157,10 +4149,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129707390</v>
+        <v>129694980</v>
       </c>
       <c r="B37" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4168,37 +4160,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>431952</v>
+        <v>431711</v>
       </c>
       <c r="R37" t="n">
-        <v>6795410</v>
+        <v>6795450</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4239,51 +4228,50 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129695010</v>
+        <v>129694886</v>
       </c>
       <c r="B38" t="n">
-        <v>92875</v>
+        <v>79700</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4293,10 +4281,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>431880</v>
+        <v>431873</v>
       </c>
       <c r="R38" t="n">
-        <v>6795546</v>
+        <v>6795241</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4355,10 +4343,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129694886</v>
+        <v>129694921</v>
       </c>
       <c r="B39" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4366,34 +4354,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>431873</v>
+        <v>431725</v>
       </c>
       <c r="R39" t="n">
-        <v>6795241</v>
+        <v>6795459</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4452,10 +4448,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129694878</v>
+        <v>129707390</v>
       </c>
       <c r="B40" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4463,34 +4459,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>431889</v>
+        <v>431952</v>
       </c>
       <c r="R40" t="n">
-        <v>6795186</v>
+        <v>6795410</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4531,18 +4530,19 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4654,10 +4654,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129707351</v>
+        <v>129694999</v>
       </c>
       <c r="B42" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4665,42 +4665,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>431756</v>
+        <v>431859</v>
       </c>
       <c r="R42" t="n">
-        <v>6795202</v>
+        <v>6795172</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4747,12 +4739,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -4856,10 +4848,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129694999</v>
+        <v>129694926</v>
       </c>
       <c r="B44" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4867,34 +4859,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>431859</v>
+        <v>431711</v>
       </c>
       <c r="R44" t="n">
-        <v>6795172</v>
+        <v>6795100</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4953,10 +4953,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129694926</v>
+        <v>129707316</v>
       </c>
       <c r="B45" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4964,42 +4964,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>431711</v>
+        <v>431812</v>
       </c>
       <c r="R45" t="n">
-        <v>6795100</v>
+        <v>6795349</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5046,22 +5038,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129707316</v>
+        <v>129707375</v>
       </c>
       <c r="B46" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5069,21 +5061,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5093,10 +5085,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>431812</v>
+        <v>431881</v>
       </c>
       <c r="R46" t="n">
-        <v>6795349</v>
+        <v>6795522</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5252,7 +5244,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129707338</v>
+        <v>129707320</v>
       </c>
       <c r="B48" t="n">
         <v>79700</v>
@@ -5287,10 +5279,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>431932</v>
+        <v>431717</v>
       </c>
       <c r="R48" t="n">
-        <v>6795406</v>
+        <v>6795380</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5349,10 +5341,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129707375</v>
+        <v>129707338</v>
       </c>
       <c r="B49" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5360,21 +5352,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5384,10 +5376,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>431881</v>
+        <v>431932</v>
       </c>
       <c r="R49" t="n">
-        <v>6795522</v>
+        <v>6795406</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5446,10 +5438,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129707320</v>
+        <v>129707351</v>
       </c>
       <c r="B50" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5457,34 +5449,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>431717</v>
+        <v>431756</v>
       </c>
       <c r="R50" t="n">
-        <v>6795380</v>
+        <v>6795202</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5834,7 +5834,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129707337</v>
+        <v>129694846</v>
       </c>
       <c r="B54" t="n">
         <v>79700</v>
@@ -5869,10 +5869,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>431999</v>
+        <v>431725</v>
       </c>
       <c r="R54" t="n">
-        <v>6795416</v>
+        <v>6795467</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5919,22 +5919,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129707347</v>
+        <v>129707404</v>
       </c>
       <c r="B55" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5942,31 +5942,26 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -5974,10 +5969,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>431662</v>
+        <v>431816</v>
       </c>
       <c r="R55" t="n">
-        <v>6795391</v>
+        <v>6795333</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6012,12 +6007,18 @@
           <t>2025-11-14</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6036,10 +6037,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129694846</v>
+        <v>129707426</v>
       </c>
       <c r="B56" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6047,21 +6048,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6071,10 +6072,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>431725</v>
+        <v>431767</v>
       </c>
       <c r="R56" t="n">
-        <v>6795467</v>
+        <v>6795219</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6121,12 +6122,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6230,10 +6231,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129707426</v>
+        <v>129707337</v>
       </c>
       <c r="B58" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6241,21 +6242,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6265,10 +6266,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>431767</v>
+        <v>431999</v>
       </c>
       <c r="R58" t="n">
-        <v>6795219</v>
+        <v>6795416</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6327,10 +6328,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129707404</v>
+        <v>129707347</v>
       </c>
       <c r="B59" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6338,26 +6339,31 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6365,10 +6371,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>431816</v>
+        <v>431662</v>
       </c>
       <c r="R59" t="n">
-        <v>6795333</v>
+        <v>6795391</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6403,18 +6409,12 @@
           <t>2025-11-14</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6433,10 +6433,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129694988</v>
+        <v>129694872</v>
       </c>
       <c r="B60" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6444,21 +6444,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6468,10 +6468,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>431718</v>
+        <v>431833</v>
       </c>
       <c r="R60" t="n">
-        <v>6795068</v>
+        <v>6795171</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6530,7 +6530,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129694872</v>
+        <v>129694856</v>
       </c>
       <c r="B61" t="n">
         <v>79700</v>
@@ -6565,10 +6565,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>431833</v>
+        <v>431693</v>
       </c>
       <c r="R61" t="n">
-        <v>6795171</v>
+        <v>6795052</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6627,10 +6627,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129694856</v>
+        <v>129694961</v>
       </c>
       <c r="B62" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6638,21 +6638,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6662,10 +6662,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>431693</v>
+        <v>431804</v>
       </c>
       <c r="R62" t="n">
-        <v>6795052</v>
+        <v>6795100</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6724,10 +6724,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129694961</v>
+        <v>129694988</v>
       </c>
       <c r="B63" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6735,21 +6735,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6759,10 +6759,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>431804</v>
+        <v>431718</v>
       </c>
       <c r="R63" t="n">
-        <v>6795100</v>
+        <v>6795068</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7508,10 +7508,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129707382</v>
+        <v>129694928</v>
       </c>
       <c r="B71" t="n">
-        <v>78838</v>
+        <v>57733</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7519,26 +7519,31 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -7546,10 +7551,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>431689</v>
+        <v>431801</v>
       </c>
       <c r="R71" t="n">
-        <v>6795383</v>
+        <v>6795136</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7590,29 +7595,28 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129694928</v>
+        <v>129707420</v>
       </c>
       <c r="B72" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7620,42 +7624,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>431801</v>
+        <v>431695</v>
       </c>
       <c r="R72" t="n">
-        <v>6795136</v>
+        <v>6795256</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7702,22 +7698,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129707420</v>
+        <v>129707382</v>
       </c>
       <c r="B73" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7725,34 +7721,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>431695</v>
+        <v>431689</v>
       </c>
       <c r="R73" t="n">
-        <v>6795256</v>
+        <v>6795383</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7793,6 +7792,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7912,10 +7912,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129707391</v>
+        <v>129707317</v>
       </c>
       <c r="B75" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7923,21 +7923,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7947,10 +7947,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>431724</v>
+        <v>431780</v>
       </c>
       <c r="R75" t="n">
-        <v>6795372</v>
+        <v>6795362</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8009,32 +8009,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129707439</v>
+        <v>129707391</v>
       </c>
       <c r="B76" t="n">
-        <v>92875</v>
+        <v>78838</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8044,10 +8044,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>431891</v>
+        <v>431724</v>
       </c>
       <c r="R76" t="n">
-        <v>6795553</v>
+        <v>6795372</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8106,7 +8106,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129707317</v>
+        <v>129707314</v>
       </c>
       <c r="B77" t="n">
         <v>79700</v>
@@ -8141,10 +8141,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>431780</v>
+        <v>431866</v>
       </c>
       <c r="R77" t="n">
-        <v>6795362</v>
+        <v>6795513</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8203,10 +8203,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129707314</v>
+        <v>129694985</v>
       </c>
       <c r="B78" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8214,21 +8214,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8238,10 +8238,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>431866</v>
+        <v>431673</v>
       </c>
       <c r="R78" t="n">
-        <v>6795513</v>
+        <v>6795435</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8288,44 +8288,44 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129694985</v>
+        <v>129707439</v>
       </c>
       <c r="B79" t="n">
-        <v>79081</v>
+        <v>92875</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8335,10 +8335,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>431673</v>
+        <v>431891</v>
       </c>
       <c r="R79" t="n">
-        <v>6795435</v>
+        <v>6795553</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8385,12 +8385,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -8494,10 +8494,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129694874</v>
+        <v>129695001</v>
       </c>
       <c r="B81" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8505,21 +8505,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>431827</v>
+        <v>431876</v>
       </c>
       <c r="R81" t="n">
-        <v>6795171</v>
+        <v>6795202</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8591,7 +8591,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129695001</v>
+        <v>129694991</v>
       </c>
       <c r="B82" t="n">
         <v>79081</v>
@@ -8626,10 +8626,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>431876</v>
+        <v>431760</v>
       </c>
       <c r="R82" t="n">
-        <v>6795202</v>
+        <v>6795115</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8688,10 +8688,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129694991</v>
+        <v>129707388</v>
       </c>
       <c r="B83" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8699,21 +8699,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8723,10 +8723,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>431760</v>
+        <v>431915</v>
       </c>
       <c r="R83" t="n">
-        <v>6795115</v>
+        <v>6795392</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8773,22 +8773,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129707388</v>
+        <v>129707315</v>
       </c>
       <c r="B84" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8796,21 +8796,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8820,10 +8820,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>431915</v>
+        <v>431820</v>
       </c>
       <c r="R84" t="n">
-        <v>6795392</v>
+        <v>6795329</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8882,10 +8882,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129694933</v>
+        <v>129694874</v>
       </c>
       <c r="B85" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8893,42 +8893,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>431904</v>
+        <v>431827</v>
       </c>
       <c r="R85" t="n">
-        <v>6795243</v>
+        <v>6795171</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8987,10 +8979,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129707424</v>
+        <v>129694933</v>
       </c>
       <c r="B86" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8998,34 +8990,42 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>431760</v>
+        <v>431904</v>
       </c>
       <c r="R86" t="n">
-        <v>6795200</v>
+        <v>6795243</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9072,22 +9072,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129707315</v>
+        <v>129707424</v>
       </c>
       <c r="B87" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9095,21 +9095,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9119,10 +9119,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>431820</v>
+        <v>431760</v>
       </c>
       <c r="R87" t="n">
-        <v>6795329</v>
+        <v>6795200</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9181,10 +9181,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129707345</v>
+        <v>129694948</v>
       </c>
       <c r="B88" t="n">
-        <v>57733</v>
+        <v>78839</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9192,42 +9192,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>431893</v>
+        <v>431725</v>
       </c>
       <c r="R88" t="n">
-        <v>6795571</v>
+        <v>6795459</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9274,22 +9266,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129694948</v>
+        <v>129707345</v>
       </c>
       <c r="B89" t="n">
-        <v>78839</v>
+        <v>57733</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9297,34 +9289,42 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>431725</v>
+        <v>431893</v>
       </c>
       <c r="R89" t="n">
-        <v>6795459</v>
+        <v>6795571</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9371,22 +9371,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129694939</v>
+        <v>129694860</v>
       </c>
       <c r="B90" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9394,21 +9394,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9418,10 +9418,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>431913</v>
+        <v>431746</v>
       </c>
       <c r="R90" t="n">
-        <v>6795284</v>
+        <v>6795081</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9454,11 +9454,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9485,10 +9480,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129694934</v>
+        <v>129694965</v>
       </c>
       <c r="B91" t="n">
-        <v>57733</v>
+        <v>78838</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9496,42 +9491,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>431916</v>
+        <v>431885</v>
       </c>
       <c r="R91" t="n">
-        <v>6795286</v>
+        <v>6795240</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9590,10 +9577,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129707381</v>
+        <v>129694939</v>
       </c>
       <c r="B92" t="n">
-        <v>78838</v>
+        <v>57733</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9601,21 +9588,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9625,10 +9612,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>431712</v>
+        <v>431913</v>
       </c>
       <c r="R92" t="n">
-        <v>6795379</v>
+        <v>6795284</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9663,6 +9650,11 @@
           <t>2025-11-14</t>
         </is>
       </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
@@ -9675,22 +9667,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129694860</v>
+        <v>129694934</v>
       </c>
       <c r="B93" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9698,34 +9690,42 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>431746</v>
+        <v>431916</v>
       </c>
       <c r="R93" t="n">
-        <v>6795081</v>
+        <v>6795286</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9784,10 +9784,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129694965</v>
+        <v>129707405</v>
       </c>
       <c r="B94" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9795,21 +9795,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9819,10 +9819,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>431885</v>
+        <v>431775</v>
       </c>
       <c r="R94" t="n">
-        <v>6795240</v>
+        <v>6795343</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9869,22 +9869,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129707405</v>
+        <v>129707381</v>
       </c>
       <c r="B95" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9892,21 +9892,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9916,10 +9916,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>431775</v>
+        <v>431712</v>
       </c>
       <c r="R95" t="n">
-        <v>6795343</v>
+        <v>6795379</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10665,7 +10665,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129695000</v>
+        <v>129707396</v>
       </c>
       <c r="B103" t="n">
         <v>79081</v>
@@ -10700,10 +10700,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>431890</v>
+        <v>431918</v>
       </c>
       <c r="R103" t="n">
-        <v>6795199</v>
+        <v>6795574</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10750,19 +10750,19 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129694992</v>
+        <v>129707406</v>
       </c>
       <c r="B104" t="n">
         <v>79081</v>
@@ -10797,10 +10797,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>431799</v>
+        <v>431771</v>
       </c>
       <c r="R104" t="n">
-        <v>6795129</v>
+        <v>6795344</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10847,22 +10847,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129694938</v>
+        <v>129707397</v>
       </c>
       <c r="B105" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10870,32 +10870,24 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
@@ -10905,7 +10897,7 @@
         <v>431915</v>
       </c>
       <c r="R105" t="n">
-        <v>6795279</v>
+        <v>6795541</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10952,22 +10944,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129707425</v>
+        <v>129707332</v>
       </c>
       <c r="B106" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10975,21 +10967,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -10999,10 +10991,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>431756</v>
+        <v>431923</v>
       </c>
       <c r="R106" t="n">
-        <v>6795247</v>
+        <v>6795402</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11061,10 +11053,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129694927</v>
+        <v>129707327</v>
       </c>
       <c r="B107" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11072,42 +11064,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>431711</v>
+        <v>431893</v>
       </c>
       <c r="R107" t="n">
-        <v>6795094</v>
+        <v>6795305</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11154,22 +11138,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129707397</v>
+        <v>129707349</v>
       </c>
       <c r="B108" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11177,34 +11161,42 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>431915</v>
+        <v>431722</v>
       </c>
       <c r="R108" t="n">
-        <v>6795541</v>
+        <v>6795217</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11263,7 +11255,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129707396</v>
+        <v>129695000</v>
       </c>
       <c r="B109" t="n">
         <v>79081</v>
@@ -11298,10 +11290,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>431918</v>
+        <v>431890</v>
       </c>
       <c r="R109" t="n">
-        <v>6795574</v>
+        <v>6795199</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11348,19 +11340,19 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129707406</v>
+        <v>129694992</v>
       </c>
       <c r="B110" t="n">
         <v>79081</v>
@@ -11395,10 +11387,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>431771</v>
+        <v>431799</v>
       </c>
       <c r="R110" t="n">
-        <v>6795344</v>
+        <v>6795129</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11445,22 +11437,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129707332</v>
+        <v>129694927</v>
       </c>
       <c r="B111" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11468,34 +11460,42 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>431923</v>
+        <v>431711</v>
       </c>
       <c r="R111" t="n">
-        <v>6795402</v>
+        <v>6795094</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11542,22 +11542,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129707327</v>
+        <v>129694938</v>
       </c>
       <c r="B112" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11565,34 +11565,42 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>431893</v>
+        <v>431915</v>
       </c>
       <c r="R112" t="n">
-        <v>6795305</v>
+        <v>6795279</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11639,22 +11647,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129707349</v>
+        <v>129707425</v>
       </c>
       <c r="B113" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11662,42 +11670,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>431722</v>
+        <v>431756</v>
       </c>
       <c r="R113" t="n">
-        <v>6795217</v>
+        <v>6795247</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11756,7 +11756,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129707421</v>
+        <v>129694990</v>
       </c>
       <c r="B114" t="n">
         <v>79081</v>
@@ -11791,10 +11791,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>431711</v>
+        <v>431726</v>
       </c>
       <c r="R114" t="n">
-        <v>6795239</v>
+        <v>6795117</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11841,19 +11841,19 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129707330</v>
+        <v>129694901</v>
       </c>
       <c r="B115" t="n">
         <v>79700</v>
@@ -11888,10 +11888,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>431930</v>
+        <v>431927</v>
       </c>
       <c r="R115" t="n">
-        <v>6795399</v>
+        <v>6795265</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11938,19 +11938,19 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129707309</v>
+        <v>129694844</v>
       </c>
       <c r="B116" t="n">
         <v>79700</v>
@@ -11985,10 +11985,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>431869</v>
+        <v>431739</v>
       </c>
       <c r="R116" t="n">
-        <v>6795521</v>
+        <v>6795440</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12035,22 +12035,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129707323</v>
+        <v>129707421</v>
       </c>
       <c r="B117" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12058,21 +12058,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12082,10 +12082,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>431712</v>
+        <v>431711</v>
       </c>
       <c r="R117" t="n">
-        <v>6795236</v>
+        <v>6795239</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12144,7 +12144,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129694901</v>
+        <v>129707330</v>
       </c>
       <c r="B118" t="n">
         <v>79700</v>
@@ -12179,10 +12179,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>431927</v>
+        <v>431930</v>
       </c>
       <c r="R118" t="n">
-        <v>6795265</v>
+        <v>6795399</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12229,19 +12229,19 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129694844</v>
+        <v>129707309</v>
       </c>
       <c r="B119" t="n">
         <v>79700</v>
@@ -12276,10 +12276,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>431739</v>
+        <v>431869</v>
       </c>
       <c r="R119" t="n">
-        <v>6795440</v>
+        <v>6795521</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12326,22 +12326,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129694990</v>
+        <v>129707323</v>
       </c>
       <c r="B120" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12349,21 +12349,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12373,10 +12373,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>431726</v>
+        <v>431712</v>
       </c>
       <c r="R120" t="n">
-        <v>6795117</v>
+        <v>6795236</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12423,12 +12423,12 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
@@ -13320,7 +13320,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129694900</v>
+        <v>129694906</v>
       </c>
       <c r="B130" t="n">
         <v>79700</v>
@@ -13355,10 +13355,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>431907</v>
+        <v>431934</v>
       </c>
       <c r="R130" t="n">
-        <v>6795266</v>
+        <v>6795286</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13417,7 +13417,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129694906</v>
+        <v>129694900</v>
       </c>
       <c r="B131" t="n">
         <v>79700</v>
@@ -13452,10 +13452,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>431934</v>
+        <v>431907</v>
       </c>
       <c r="R131" t="n">
-        <v>6795286</v>
+        <v>6795266</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13514,7 +13514,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129707399</v>
+        <v>129707438</v>
       </c>
       <c r="B132" t="n">
         <v>79081</v>
@@ -13549,10 +13549,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>431819</v>
+        <v>431965</v>
       </c>
       <c r="R132" t="n">
-        <v>6795445</v>
+        <v>6795405</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13611,10 +13611,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129707387</v>
+        <v>129707399</v>
       </c>
       <c r="B133" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13622,21 +13622,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13646,10 +13646,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>431936</v>
+        <v>431819</v>
       </c>
       <c r="R133" t="n">
-        <v>6795393</v>
+        <v>6795445</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13708,10 +13708,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129707438</v>
+        <v>129707318</v>
       </c>
       <c r="B134" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13719,21 +13719,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13743,10 +13743,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>431965</v>
+        <v>431769</v>
       </c>
       <c r="R134" t="n">
-        <v>6795405</v>
+        <v>6795345</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13805,10 +13805,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129707318</v>
+        <v>129707387</v>
       </c>
       <c r="B135" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13816,21 +13816,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13840,10 +13840,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>431769</v>
+        <v>431936</v>
       </c>
       <c r="R135" t="n">
-        <v>6795345</v>
+        <v>6795393</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14193,10 +14193,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129707334</v>
+        <v>129694956</v>
       </c>
       <c r="B139" t="n">
-        <v>79700</v>
+        <v>92011</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14204,34 +14204,33 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>431936</v>
+        <v>431718</v>
       </c>
       <c r="R139" t="n">
-        <v>6795411</v>
+        <v>6795082</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14266,34 +14265,40 @@
           <t>2025-11-14</t>
         </is>
       </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Mjuk och len på undetsidan, sämskskinnslik känsla</t>
+        </is>
+      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129694956</v>
+        <v>129707334</v>
       </c>
       <c r="B140" t="n">
-        <v>92011</v>
+        <v>79700</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14301,33 +14306,34 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6040162</v>
+        <v>6453</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>431718</v>
+        <v>431936</v>
       </c>
       <c r="R140" t="n">
-        <v>6795082</v>
+        <v>6795411</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14362,30 +14368,24 @@
           <t>2025-11-14</t>
         </is>
       </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Mjuk och len på undetsidan, sämskskinnslik känsla</t>
-        </is>
-      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>

--- a/artfynd/A 50492-2025 artfynd.xlsx
+++ b/artfynd/A 50492-2025 artfynd.xlsx
@@ -772,48 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129707216</v>
+        <v>129707440</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>92879</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>432007</v>
+        <v>431828</v>
       </c>
       <c r="R3" t="n">
-        <v>6795475</v>
+        <v>6795476</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,7 +851,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -873,40 +869,41 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129694935</v>
+        <v>129707371</v>
       </c>
       <c r="B4" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -916,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>431917</v>
+        <v>431808</v>
       </c>
       <c r="R4" t="n">
-        <v>6795290</v>
+        <v>6795442</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,28 +957,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129694929</v>
+        <v>129707216</v>
       </c>
       <c r="B5" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,31 +987,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1021,10 +1014,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>431859</v>
+        <v>432007</v>
       </c>
       <c r="R5" t="n">
-        <v>6795172</v>
+        <v>6795475</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1065,28 +1058,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129694842</v>
+        <v>129694935</v>
       </c>
       <c r="B6" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,34 +1088,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>431768</v>
+        <v>431917</v>
       </c>
       <c r="R6" t="n">
-        <v>6795469</v>
+        <v>6795290</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,10 +1182,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129694957</v>
+        <v>129694929</v>
       </c>
       <c r="B7" t="n">
-        <v>78838</v>
+        <v>57733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,34 +1193,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>431725</v>
+        <v>431859</v>
       </c>
       <c r="R7" t="n">
-        <v>6795459</v>
+        <v>6795172</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1277,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129694862</v>
+        <v>129694842</v>
       </c>
       <c r="B8" t="n">
         <v>79700</v>
@@ -1312,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>431756</v>
+        <v>431768</v>
       </c>
       <c r="R8" t="n">
-        <v>6795121</v>
+        <v>6795469</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,32 +1384,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129707440</v>
+        <v>129694957</v>
       </c>
       <c r="B9" t="n">
-        <v>92875</v>
+        <v>78838</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,10 +1419,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>431828</v>
+        <v>431725</v>
       </c>
       <c r="R9" t="n">
-        <v>6795476</v>
+        <v>6795459</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,66 +1469,57 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129707371</v>
+        <v>129694862</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>431808</v>
+        <v>431756</v>
       </c>
       <c r="R10" t="n">
-        <v>6795442</v>
+        <v>6795121</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1559,29 +1560,28 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129694918</v>
+        <v>129694923</v>
       </c>
       <c r="B11" t="n">
-        <v>91614</v>
+        <v>57733</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1589,30 +1589,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1620,10 +1621,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>431722</v>
+        <v>431687</v>
       </c>
       <c r="R11" t="n">
-        <v>6795120</v>
+        <v>6795471</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1664,7 +1665,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1683,10 +1683,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129694843</v>
+        <v>129694918</v>
       </c>
       <c r="B12" t="n">
-        <v>79700</v>
+        <v>91618</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1694,34 +1694,41 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>431752</v>
+        <v>431722</v>
       </c>
       <c r="R12" t="n">
-        <v>6795429</v>
+        <v>6795120</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1762,6 +1769,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1780,7 +1788,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129694907</v>
+        <v>129694843</v>
       </c>
       <c r="B13" t="n">
         <v>79700</v>
@@ -1815,10 +1823,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>431938</v>
+        <v>431752</v>
       </c>
       <c r="R13" t="n">
-        <v>6795278</v>
+        <v>6795429</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1877,10 +1885,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129694923</v>
+        <v>129694983</v>
       </c>
       <c r="B14" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1888,42 +1896,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>431687</v>
+        <v>431689</v>
       </c>
       <c r="R14" t="n">
-        <v>6795471</v>
+        <v>6795456</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1982,10 +1982,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129707434</v>
+        <v>129694907</v>
       </c>
       <c r="B15" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1993,21 +1993,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>431894</v>
+        <v>431938</v>
       </c>
       <c r="R15" t="n">
-        <v>6795261</v>
+        <v>6795278</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2067,19 +2067,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129694983</v>
+        <v>129707434</v>
       </c>
       <c r="B16" t="n">
         <v>79081</v>
@@ -2114,10 +2114,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>431689</v>
+        <v>431894</v>
       </c>
       <c r="R16" t="n">
-        <v>6795456</v>
+        <v>6795261</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2164,12 +2164,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2580,10 +2580,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129707335</v>
+        <v>129707378</v>
       </c>
       <c r="B21" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2591,21 +2591,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2615,10 +2615,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>431965</v>
+        <v>431814</v>
       </c>
       <c r="R21" t="n">
-        <v>6795430</v>
+        <v>6795444</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2677,10 +2677,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129707378</v>
+        <v>129707310</v>
       </c>
       <c r="B22" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2688,21 +2688,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2712,10 +2712,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>431814</v>
+        <v>431924</v>
       </c>
       <c r="R22" t="n">
-        <v>6795444</v>
+        <v>6795546</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2774,7 +2774,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129707310</v>
+        <v>129707335</v>
       </c>
       <c r="B23" t="n">
         <v>79700</v>
@@ -2809,10 +2809,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>431924</v>
+        <v>431965</v>
       </c>
       <c r="R23" t="n">
-        <v>6795546</v>
+        <v>6795430</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2874,7 +2874,7 @@
         <v>129694942</v>
       </c>
       <c r="B24" t="n">
-        <v>91891</v>
+        <v>91895</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2969,10 +2969,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129707407</v>
+        <v>129694883</v>
       </c>
       <c r="B25" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2980,21 +2980,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>431723</v>
+        <v>431885</v>
       </c>
       <c r="R25" t="n">
-        <v>6795371</v>
+        <v>6795213</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3054,19 +3054,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129707331</v>
+        <v>129694884</v>
       </c>
       <c r="B26" t="n">
         <v>79700</v>
@@ -3095,19 +3095,16 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>431916</v>
+        <v>431885</v>
       </c>
       <c r="R26" t="n">
-        <v>6795392</v>
+        <v>6795215</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3148,26 +3145,25 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129707308</v>
+        <v>129694898</v>
       </c>
       <c r="B27" t="n">
         <v>79700</v>
@@ -3202,10 +3198,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>431868</v>
+        <v>431907</v>
       </c>
       <c r="R27" t="n">
-        <v>6795565</v>
+        <v>6795285</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3252,19 +3248,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129694883</v>
+        <v>129694899</v>
       </c>
       <c r="B28" t="n">
         <v>79700</v>
@@ -3299,10 +3295,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>431885</v>
+        <v>431910</v>
       </c>
       <c r="R28" t="n">
-        <v>6795213</v>
+        <v>6795288</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3361,7 +3357,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129694884</v>
+        <v>129694861</v>
       </c>
       <c r="B29" t="n">
         <v>79700</v>
@@ -3396,10 +3392,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>431885</v>
+        <v>431740</v>
       </c>
       <c r="R29" t="n">
-        <v>6795215</v>
+        <v>6795107</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3458,7 +3454,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129694898</v>
+        <v>129707308</v>
       </c>
       <c r="B30" t="n">
         <v>79700</v>
@@ -3493,10 +3489,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>431907</v>
+        <v>431868</v>
       </c>
       <c r="R30" t="n">
-        <v>6795285</v>
+        <v>6795565</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3543,19 +3539,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129694899</v>
+        <v>129707331</v>
       </c>
       <c r="B31" t="n">
         <v>79700</v>
@@ -3584,16 +3580,19 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>431910</v>
+        <v>431916</v>
       </c>
       <c r="R31" t="n">
-        <v>6795288</v>
+        <v>6795392</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3634,28 +3633,29 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129694861</v>
+        <v>129707407</v>
       </c>
       <c r="B32" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3663,21 +3663,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3687,10 +3687,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>431740</v>
+        <v>431723</v>
       </c>
       <c r="R32" t="n">
-        <v>6795107</v>
+        <v>6795371</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3737,57 +3737,60 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129695010</v>
+        <v>129694839</v>
       </c>
       <c r="B33" t="n">
-        <v>92875</v>
+        <v>91520</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>3242</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>431880</v>
+        <v>431869</v>
       </c>
       <c r="R33" t="n">
-        <v>6795546</v>
+        <v>6795181</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3828,6 +3831,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3846,52 +3850,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129694917</v>
+        <v>129695010</v>
       </c>
       <c r="B34" t="n">
-        <v>91614</v>
+        <v>92879</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>431672</v>
+        <v>431880</v>
       </c>
       <c r="R34" t="n">
-        <v>6795442</v>
+        <v>6795546</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3932,7 +3929,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -3951,10 +3947,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129694878</v>
+        <v>129694921</v>
       </c>
       <c r="B35" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3962,34 +3958,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>431889</v>
+        <v>431725</v>
       </c>
       <c r="R35" t="n">
-        <v>6795186</v>
+        <v>6795459</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4048,10 +4052,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129694839</v>
+        <v>129694917</v>
       </c>
       <c r="B36" t="n">
-        <v>91516</v>
+        <v>91618</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4059,24 +4063,28 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3242</v>
+        <v>5442</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
@@ -4086,10 +4094,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>431869</v>
+        <v>431672</v>
       </c>
       <c r="R36" t="n">
-        <v>6795181</v>
+        <v>6795442</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4149,10 +4157,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129694980</v>
+        <v>129694886</v>
       </c>
       <c r="B37" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4160,21 +4168,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4184,10 +4192,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>431711</v>
+        <v>431873</v>
       </c>
       <c r="R37" t="n">
-        <v>6795450</v>
+        <v>6795241</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4246,10 +4254,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129694886</v>
+        <v>129694980</v>
       </c>
       <c r="B38" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4257,21 +4265,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4281,10 +4289,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>431873</v>
+        <v>431711</v>
       </c>
       <c r="R38" t="n">
-        <v>6795241</v>
+        <v>6795450</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4343,10 +4351,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129694921</v>
+        <v>129694878</v>
       </c>
       <c r="B39" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4354,42 +4362,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>431725</v>
+        <v>431889</v>
       </c>
       <c r="R39" t="n">
-        <v>6795459</v>
+        <v>6795186</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4654,10 +4654,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129694999</v>
+        <v>129694926</v>
       </c>
       <c r="B42" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4665,34 +4665,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>431859</v>
+        <v>431711</v>
       </c>
       <c r="R42" t="n">
-        <v>6795172</v>
+        <v>6795100</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4848,10 +4856,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129694926</v>
+        <v>129694999</v>
       </c>
       <c r="B44" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4859,42 +4867,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>431711</v>
+        <v>431859</v>
       </c>
       <c r="R44" t="n">
-        <v>6795100</v>
+        <v>6795172</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4953,7 +4953,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129707316</v>
+        <v>129707320</v>
       </c>
       <c r="B45" t="n">
         <v>79700</v>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>431812</v>
+        <v>431717</v>
       </c>
       <c r="R45" t="n">
-        <v>6795349</v>
+        <v>6795380</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5050,10 +5050,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129707375</v>
+        <v>129707316</v>
       </c>
       <c r="B46" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5061,21 +5061,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5085,10 +5085,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>431881</v>
+        <v>431812</v>
       </c>
       <c r="R46" t="n">
-        <v>6795522</v>
+        <v>6795349</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5244,7 +5244,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129707320</v>
+        <v>129707338</v>
       </c>
       <c r="B48" t="n">
         <v>79700</v>
@@ -5279,10 +5279,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>431717</v>
+        <v>431932</v>
       </c>
       <c r="R48" t="n">
-        <v>6795380</v>
+        <v>6795406</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5341,10 +5341,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129707338</v>
+        <v>129707375</v>
       </c>
       <c r="B49" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5352,21 +5352,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5376,10 +5376,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>431932</v>
+        <v>431881</v>
       </c>
       <c r="R49" t="n">
-        <v>6795406</v>
+        <v>6795522</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5543,10 +5543,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129695006</v>
+        <v>129707347</v>
       </c>
       <c r="B51" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5554,34 +5554,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>431962</v>
+        <v>431662</v>
       </c>
       <c r="R51" t="n">
-        <v>6795319</v>
+        <v>6795391</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5628,22 +5636,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129695003</v>
+        <v>129694846</v>
       </c>
       <c r="B52" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5651,21 +5659,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5675,10 +5683,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>431908</v>
+        <v>431725</v>
       </c>
       <c r="R52" t="n">
-        <v>6795302</v>
+        <v>6795467</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5737,7 +5745,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129694994</v>
+        <v>129695006</v>
       </c>
       <c r="B53" t="n">
         <v>79081</v>
@@ -5772,10 +5780,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>431804</v>
+        <v>431962</v>
       </c>
       <c r="R53" t="n">
-        <v>6795151</v>
+        <v>6795319</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5834,10 +5842,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129694846</v>
+        <v>129695003</v>
       </c>
       <c r="B54" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5845,21 +5853,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5869,10 +5877,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>431725</v>
+        <v>431908</v>
       </c>
       <c r="R54" t="n">
-        <v>6795467</v>
+        <v>6795302</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5931,7 +5939,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129707404</v>
+        <v>129694994</v>
       </c>
       <c r="B55" t="n">
         <v>79081</v>
@@ -5960,19 +5968,16 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>431816</v>
+        <v>431804</v>
       </c>
       <c r="R55" t="n">
-        <v>6795333</v>
+        <v>6795151</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6007,40 +6012,34 @@
           <t>2025-11-14</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129707426</v>
+        <v>129707380</v>
       </c>
       <c r="B56" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6048,21 +6047,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6072,10 +6071,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>431767</v>
+        <v>431820</v>
       </c>
       <c r="R56" t="n">
-        <v>6795219</v>
+        <v>6795330</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6134,10 +6133,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129707380</v>
+        <v>129707426</v>
       </c>
       <c r="B57" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6145,21 +6144,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6169,10 +6168,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>431820</v>
+        <v>431767</v>
       </c>
       <c r="R57" t="n">
-        <v>6795330</v>
+        <v>6795219</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6231,10 +6230,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129707337</v>
+        <v>129707404</v>
       </c>
       <c r="B58" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6242,34 +6241,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>431999</v>
+        <v>431816</v>
       </c>
       <c r="R58" t="n">
-        <v>6795416</v>
+        <v>6795333</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6304,12 +6306,18 @@
           <t>2025-11-14</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6328,10 +6336,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129707347</v>
+        <v>129707337</v>
       </c>
       <c r="B59" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6339,42 +6347,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>431662</v>
+        <v>431999</v>
       </c>
       <c r="R59" t="n">
-        <v>6795391</v>
+        <v>6795416</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6821,10 +6821,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129694930</v>
+        <v>129707319</v>
       </c>
       <c r="B64" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6832,42 +6832,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>431875</v>
+        <v>431708</v>
       </c>
       <c r="R64" t="n">
-        <v>6795244</v>
+        <v>6795371</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6914,22 +6906,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129707319</v>
+        <v>129694930</v>
       </c>
       <c r="B65" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6937,34 +6929,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>431708</v>
+        <v>431875</v>
       </c>
       <c r="R65" t="n">
-        <v>6795371</v>
+        <v>6795244</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7011,22 +7011,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129694857</v>
+        <v>129694928</v>
       </c>
       <c r="B66" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7034,34 +7034,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>431800</v>
+        <v>431801</v>
       </c>
       <c r="R66" t="n">
-        <v>6795130</v>
+        <v>6795136</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7120,7 +7128,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129694908</v>
+        <v>129694857</v>
       </c>
       <c r="B67" t="n">
         <v>79700</v>
@@ -7155,10 +7163,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>431973</v>
+        <v>431800</v>
       </c>
       <c r="R67" t="n">
-        <v>6795310</v>
+        <v>6795130</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7217,7 +7225,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129694858</v>
+        <v>129694908</v>
       </c>
       <c r="B68" t="n">
         <v>79700</v>
@@ -7252,10 +7260,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>431749</v>
+        <v>431973</v>
       </c>
       <c r="R68" t="n">
-        <v>6795079</v>
+        <v>6795310</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7314,7 +7322,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129694859</v>
+        <v>129694858</v>
       </c>
       <c r="B69" t="n">
         <v>79700</v>
@@ -7349,10 +7357,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>431702</v>
+        <v>431749</v>
       </c>
       <c r="R69" t="n">
-        <v>6795115</v>
+        <v>6795079</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7411,7 +7419,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129694879</v>
+        <v>129694859</v>
       </c>
       <c r="B70" t="n">
         <v>79700</v>
@@ -7446,10 +7454,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>431888</v>
+        <v>431702</v>
       </c>
       <c r="R70" t="n">
-        <v>6795198</v>
+        <v>6795115</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7508,10 +7516,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129694928</v>
+        <v>129694879</v>
       </c>
       <c r="B71" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7519,42 +7527,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>431801</v>
+        <v>431888</v>
       </c>
       <c r="R71" t="n">
-        <v>6795136</v>
+        <v>6795198</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7811,10 +7811,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129707389</v>
+        <v>129694985</v>
       </c>
       <c r="B74" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7822,37 +7822,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>431922</v>
+        <v>431673</v>
       </c>
       <c r="R74" t="n">
-        <v>6795405</v>
+        <v>6795435</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7893,29 +7890,28 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129707317</v>
+        <v>129707391</v>
       </c>
       <c r="B75" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7923,21 +7919,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7947,10 +7943,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>431780</v>
+        <v>431724</v>
       </c>
       <c r="R75" t="n">
-        <v>6795362</v>
+        <v>6795372</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8009,7 +8005,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129707391</v>
+        <v>129707389</v>
       </c>
       <c r="B76" t="n">
         <v>78838</v>
@@ -8038,16 +8034,19 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>431724</v>
+        <v>431922</v>
       </c>
       <c r="R76" t="n">
-        <v>6795372</v>
+        <v>6795405</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8088,6 +8087,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8106,32 +8106,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129707314</v>
+        <v>129707439</v>
       </c>
       <c r="B77" t="n">
-        <v>79700</v>
+        <v>92879</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8141,10 +8141,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>431866</v>
+        <v>431891</v>
       </c>
       <c r="R77" t="n">
-        <v>6795513</v>
+        <v>6795553</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8203,10 +8203,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129694985</v>
+        <v>129707317</v>
       </c>
       <c r="B78" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8214,21 +8214,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8238,10 +8238,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>431673</v>
+        <v>431780</v>
       </c>
       <c r="R78" t="n">
-        <v>6795435</v>
+        <v>6795362</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8288,44 +8288,44 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129707439</v>
+        <v>129707314</v>
       </c>
       <c r="B79" t="n">
-        <v>92875</v>
+        <v>79700</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8335,10 +8335,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>431891</v>
+        <v>431866</v>
       </c>
       <c r="R79" t="n">
-        <v>6795553</v>
+        <v>6795513</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8397,10 +8397,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129694863</v>
+        <v>129694948</v>
       </c>
       <c r="B80" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8408,21 +8408,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8432,10 +8432,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>431785</v>
+        <v>431725</v>
       </c>
       <c r="R80" t="n">
-        <v>6795106</v>
+        <v>6795459</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8494,10 +8494,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129695001</v>
+        <v>129707388</v>
       </c>
       <c r="B81" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8505,21 +8505,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>431876</v>
+        <v>431915</v>
       </c>
       <c r="R81" t="n">
-        <v>6795202</v>
+        <v>6795392</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8579,19 +8579,19 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129694991</v>
+        <v>129707424</v>
       </c>
       <c r="B82" t="n">
         <v>79081</v>
@@ -8629,7 +8629,7 @@
         <v>431760</v>
       </c>
       <c r="R82" t="n">
-        <v>6795115</v>
+        <v>6795200</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8676,22 +8676,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129707388</v>
+        <v>129707345</v>
       </c>
       <c r="B83" t="n">
-        <v>78838</v>
+        <v>57733</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8699,34 +8699,42 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>431915</v>
+        <v>431893</v>
       </c>
       <c r="R83" t="n">
-        <v>6795392</v>
+        <v>6795571</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8785,10 +8793,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129707315</v>
+        <v>129694933</v>
       </c>
       <c r="B84" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8796,34 +8804,42 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>431820</v>
+        <v>431904</v>
       </c>
       <c r="R84" t="n">
-        <v>6795329</v>
+        <v>6795243</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8870,19 +8886,19 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129694874</v>
+        <v>129694863</v>
       </c>
       <c r="B85" t="n">
         <v>79700</v>
@@ -8917,10 +8933,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>431827</v>
+        <v>431785</v>
       </c>
       <c r="R85" t="n">
-        <v>6795171</v>
+        <v>6795106</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8979,10 +8995,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129694933</v>
+        <v>129694874</v>
       </c>
       <c r="B86" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8990,42 +9006,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>431904</v>
+        <v>431827</v>
       </c>
       <c r="R86" t="n">
-        <v>6795243</v>
+        <v>6795171</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9084,7 +9092,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129707424</v>
+        <v>129695001</v>
       </c>
       <c r="B87" t="n">
         <v>79081</v>
@@ -9119,10 +9127,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>431760</v>
+        <v>431876</v>
       </c>
       <c r="R87" t="n">
-        <v>6795200</v>
+        <v>6795202</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9169,22 +9177,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129694948</v>
+        <v>129694991</v>
       </c>
       <c r="B88" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9192,21 +9200,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9216,10 +9224,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>431725</v>
+        <v>431760</v>
       </c>
       <c r="R88" t="n">
-        <v>6795459</v>
+        <v>6795115</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9278,10 +9286,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129707345</v>
+        <v>129707315</v>
       </c>
       <c r="B89" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9289,42 +9297,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>431893</v>
+        <v>431820</v>
       </c>
       <c r="R89" t="n">
-        <v>6795571</v>
+        <v>6795329</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9577,10 +9577,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129694939</v>
+        <v>129707381</v>
       </c>
       <c r="B92" t="n">
-        <v>57733</v>
+        <v>78838</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9588,21 +9588,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9612,10 +9612,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>431913</v>
+        <v>431712</v>
       </c>
       <c r="R92" t="n">
-        <v>6795284</v>
+        <v>6795379</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9650,11 +9650,6 @@
           <t>2025-11-14</t>
         </is>
       </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
-        </is>
-      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
@@ -9667,19 +9662,19 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129694934</v>
+        <v>129694939</v>
       </c>
       <c r="B93" t="n">
         <v>57733</v>
@@ -9708,24 +9703,16 @@
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>431916</v>
+        <v>431913</v>
       </c>
       <c r="R93" t="n">
-        <v>6795286</v>
+        <v>6795284</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9758,6 +9745,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9784,10 +9776,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129707405</v>
+        <v>129694934</v>
       </c>
       <c r="B94" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9795,34 +9787,42 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>431775</v>
+        <v>431916</v>
       </c>
       <c r="R94" t="n">
-        <v>6795343</v>
+        <v>6795286</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9869,22 +9869,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129707381</v>
+        <v>129707405</v>
       </c>
       <c r="B95" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9892,21 +9892,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9916,10 +9916,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>431712</v>
+        <v>431775</v>
       </c>
       <c r="R95" t="n">
-        <v>6795379</v>
+        <v>6795343</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9978,32 +9978,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129694941</v>
+        <v>129707312</v>
       </c>
       <c r="B96" t="n">
-        <v>79167</v>
+        <v>79700</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6450</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10013,10 +10013,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>431976</v>
+        <v>431920</v>
       </c>
       <c r="R96" t="n">
-        <v>6795333</v>
+        <v>6795611</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10063,22 +10063,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129707312</v>
+        <v>129694977</v>
       </c>
       <c r="B97" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10086,34 +10086,42 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>431920</v>
+        <v>431933</v>
       </c>
       <c r="R97" t="n">
-        <v>6795611</v>
+        <v>6795295</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10160,12 +10168,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -10269,53 +10277,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129694977</v>
+        <v>129694941</v>
       </c>
       <c r="B99" t="n">
-        <v>57733</v>
+        <v>79167</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100049</v>
+        <v>6450</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>431933</v>
+        <v>431976</v>
       </c>
       <c r="R99" t="n">
-        <v>6795295</v>
+        <v>6795333</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10374,10 +10374,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129694877</v>
+        <v>129707397</v>
       </c>
       <c r="B100" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10385,21 +10385,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10409,10 +10409,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>431887</v>
+        <v>431915</v>
       </c>
       <c r="R100" t="n">
-        <v>6795183</v>
+        <v>6795541</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10459,22 +10459,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129694885</v>
+        <v>129707396</v>
       </c>
       <c r="B101" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10482,21 +10482,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10506,10 +10506,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>431873</v>
+        <v>431918</v>
       </c>
       <c r="R101" t="n">
-        <v>6795224</v>
+        <v>6795574</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10556,22 +10556,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129694864</v>
+        <v>129707406</v>
       </c>
       <c r="B102" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10579,21 +10579,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10603,10 +10603,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>431786</v>
+        <v>431771</v>
       </c>
       <c r="R102" t="n">
-        <v>6795113</v>
+        <v>6795344</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10653,19 +10653,19 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129707396</v>
+        <v>129707425</v>
       </c>
       <c r="B103" t="n">
         <v>79081</v>
@@ -10700,10 +10700,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>431918</v>
+        <v>431756</v>
       </c>
       <c r="R103" t="n">
-        <v>6795574</v>
+        <v>6795247</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10762,10 +10762,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129707406</v>
+        <v>129707327</v>
       </c>
       <c r="B104" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10773,21 +10773,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10797,10 +10797,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>431771</v>
+        <v>431893</v>
       </c>
       <c r="R104" t="n">
-        <v>6795344</v>
+        <v>6795305</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10859,10 +10859,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129707397</v>
+        <v>129707332</v>
       </c>
       <c r="B105" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10870,21 +10870,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10894,10 +10894,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>431915</v>
+        <v>431923</v>
       </c>
       <c r="R105" t="n">
-        <v>6795541</v>
+        <v>6795402</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10956,10 +10956,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129707332</v>
+        <v>129707349</v>
       </c>
       <c r="B106" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10967,34 +10967,42 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>431923</v>
+        <v>431722</v>
       </c>
       <c r="R106" t="n">
-        <v>6795402</v>
+        <v>6795217</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11053,10 +11061,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129707327</v>
+        <v>129694927</v>
       </c>
       <c r="B107" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11064,34 +11072,42 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>431893</v>
+        <v>431711</v>
       </c>
       <c r="R107" t="n">
-        <v>6795305</v>
+        <v>6795094</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11138,19 +11154,19 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129707349</v>
+        <v>129694938</v>
       </c>
       <c r="B108" t="n">
         <v>57733</v>
@@ -11193,10 +11209,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>431722</v>
+        <v>431915</v>
       </c>
       <c r="R108" t="n">
-        <v>6795217</v>
+        <v>6795279</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11243,12 +11259,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -11352,10 +11368,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129694992</v>
+        <v>129694877</v>
       </c>
       <c r="B110" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11363,21 +11379,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11387,10 +11403,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>431799</v>
+        <v>431887</v>
       </c>
       <c r="R110" t="n">
-        <v>6795129</v>
+        <v>6795183</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11449,10 +11465,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129694927</v>
+        <v>129694885</v>
       </c>
       <c r="B111" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11460,42 +11476,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>431711</v>
+        <v>431873</v>
       </c>
       <c r="R111" t="n">
-        <v>6795094</v>
+        <v>6795224</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11554,10 +11562,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129694938</v>
+        <v>129694864</v>
       </c>
       <c r="B112" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11565,42 +11573,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>431915</v>
+        <v>431786</v>
       </c>
       <c r="R112" t="n">
-        <v>6795279</v>
+        <v>6795113</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11659,7 +11659,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129707425</v>
+        <v>129694992</v>
       </c>
       <c r="B113" t="n">
         <v>79081</v>
@@ -11694,10 +11694,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>431756</v>
+        <v>431799</v>
       </c>
       <c r="R113" t="n">
-        <v>6795247</v>
+        <v>6795129</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11744,22 +11744,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129694990</v>
+        <v>129694901</v>
       </c>
       <c r="B114" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11767,21 +11767,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11791,10 +11791,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>431726</v>
+        <v>431927</v>
       </c>
       <c r="R114" t="n">
-        <v>6795117</v>
+        <v>6795265</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11853,10 +11853,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129694901</v>
+        <v>129694990</v>
       </c>
       <c r="B115" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11864,21 +11864,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11888,10 +11888,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>431927</v>
+        <v>431726</v>
       </c>
       <c r="R115" t="n">
-        <v>6795265</v>
+        <v>6795117</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12047,10 +12047,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129707421</v>
+        <v>129707309</v>
       </c>
       <c r="B117" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12058,21 +12058,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12082,10 +12082,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>431711</v>
+        <v>431869</v>
       </c>
       <c r="R117" t="n">
-        <v>6795239</v>
+        <v>6795521</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12241,7 +12241,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129707309</v>
+        <v>129707323</v>
       </c>
       <c r="B119" t="n">
         <v>79700</v>
@@ -12276,10 +12276,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>431869</v>
+        <v>431712</v>
       </c>
       <c r="R119" t="n">
-        <v>6795521</v>
+        <v>6795236</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12338,10 +12338,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129707323</v>
+        <v>129707386</v>
       </c>
       <c r="B120" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12349,21 +12349,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12373,10 +12373,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>431712</v>
+        <v>431897</v>
       </c>
       <c r="R120" t="n">
-        <v>6795236</v>
+        <v>6795284</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12435,10 +12435,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129707386</v>
+        <v>129707421</v>
       </c>
       <c r="B121" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12446,21 +12446,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12470,10 +12470,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>431897</v>
+        <v>431711</v>
       </c>
       <c r="R121" t="n">
-        <v>6795284</v>
+        <v>6795239</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12532,45 +12532,53 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129695013</v>
+        <v>129694925</v>
       </c>
       <c r="B122" t="n">
-        <v>92875</v>
+        <v>57733</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>431869</v>
+        <v>431687</v>
       </c>
       <c r="R122" t="n">
-        <v>6795173</v>
+        <v>6795051</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12629,10 +12637,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129694997</v>
+        <v>129694850</v>
       </c>
       <c r="B123" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12640,21 +12648,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12664,10 +12672,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>431848</v>
+        <v>431686</v>
       </c>
       <c r="R123" t="n">
-        <v>6795172</v>
+        <v>6795471</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12726,7 +12734,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129694850</v>
+        <v>129694881</v>
       </c>
       <c r="B124" t="n">
         <v>79700</v>
@@ -12761,10 +12769,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>431686</v>
+        <v>431875</v>
       </c>
       <c r="R124" t="n">
-        <v>6795471</v>
+        <v>6795212</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12823,7 +12831,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129694881</v>
+        <v>129694888</v>
       </c>
       <c r="B125" t="n">
         <v>79700</v>
@@ -12858,10 +12866,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>431875</v>
+        <v>431889</v>
       </c>
       <c r="R125" t="n">
-        <v>6795212</v>
+        <v>6795236</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12920,10 +12928,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129694888</v>
+        <v>129694997</v>
       </c>
       <c r="B126" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12931,21 +12939,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -12955,10 +12963,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>431889</v>
+        <v>431848</v>
       </c>
       <c r="R126" t="n">
-        <v>6795236</v>
+        <v>6795172</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13017,53 +13025,45 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129694925</v>
+        <v>129695013</v>
       </c>
       <c r="B127" t="n">
-        <v>57733</v>
+        <v>92879</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>431687</v>
+        <v>431869</v>
       </c>
       <c r="R127" t="n">
-        <v>6795051</v>
+        <v>6795173</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13320,7 +13320,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129694906</v>
+        <v>129694900</v>
       </c>
       <c r="B130" t="n">
         <v>79700</v>
@@ -13355,10 +13355,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>431934</v>
+        <v>431907</v>
       </c>
       <c r="R130" t="n">
-        <v>6795286</v>
+        <v>6795266</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13417,7 +13417,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129694900</v>
+        <v>129694906</v>
       </c>
       <c r="B131" t="n">
         <v>79700</v>
@@ -13452,10 +13452,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>431907</v>
+        <v>431934</v>
       </c>
       <c r="R131" t="n">
-        <v>6795266</v>
+        <v>6795286</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13514,7 +13514,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129707438</v>
+        <v>129707399</v>
       </c>
       <c r="B132" t="n">
         <v>79081</v>
@@ -13549,10 +13549,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>431965</v>
+        <v>431819</v>
       </c>
       <c r="R132" t="n">
-        <v>6795405</v>
+        <v>6795445</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13611,10 +13611,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129707399</v>
+        <v>129707387</v>
       </c>
       <c r="B133" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13622,21 +13622,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13646,10 +13646,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>431819</v>
+        <v>431936</v>
       </c>
       <c r="R133" t="n">
-        <v>6795445</v>
+        <v>6795393</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13708,10 +13708,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129707318</v>
+        <v>129707438</v>
       </c>
       <c r="B134" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13719,21 +13719,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13743,10 +13743,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>431769</v>
+        <v>431965</v>
       </c>
       <c r="R134" t="n">
-        <v>6795345</v>
+        <v>6795405</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13805,10 +13805,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129707387</v>
+        <v>129707318</v>
       </c>
       <c r="B135" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13816,21 +13816,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13840,10 +13840,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>431936</v>
+        <v>431769</v>
       </c>
       <c r="R135" t="n">
-        <v>6795393</v>
+        <v>6795345</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -13902,7 +13902,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129694866</v>
+        <v>129694865</v>
       </c>
       <c r="B136" t="n">
         <v>79700</v>
@@ -13937,10 +13937,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>431797</v>
+        <v>431787</v>
       </c>
       <c r="R136" t="n">
-        <v>6795173</v>
+        <v>6795115</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -13999,7 +13999,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129694865</v>
+        <v>129694896</v>
       </c>
       <c r="B137" t="n">
         <v>79700</v>
@@ -14034,10 +14034,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>431787</v>
+        <v>431900</v>
       </c>
       <c r="R137" t="n">
-        <v>6795115</v>
+        <v>6795265</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14096,10 +14096,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129694896</v>
+        <v>129694956</v>
       </c>
       <c r="B138" t="n">
-        <v>79700</v>
+        <v>92015</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14107,34 +14107,33 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>431900</v>
+        <v>431718</v>
       </c>
       <c r="R138" t="n">
-        <v>6795265</v>
+        <v>6795082</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14169,12 +14168,18 @@
           <t>2025-11-14</t>
         </is>
       </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>Mjuk och len på undetsidan, sämskskinnslik känsla</t>
+        </is>
+      </c>
       <c r="AD138" t="b">
         <v>0</v>
       </c>
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -14193,10 +14198,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129694956</v>
+        <v>129707334</v>
       </c>
       <c r="B139" t="n">
-        <v>92011</v>
+        <v>79700</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14204,33 +14209,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6040162</v>
+        <v>6453</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>431718</v>
+        <v>431936</v>
       </c>
       <c r="R139" t="n">
-        <v>6795082</v>
+        <v>6795411</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14265,40 +14271,34 @@
           <t>2025-11-14</t>
         </is>
       </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>Mjuk och len på undetsidan, sämskskinnslik känsla</t>
-        </is>
-      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129707334</v>
+        <v>129707370</v>
       </c>
       <c r="B140" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14306,21 +14306,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14330,10 +14330,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>431936</v>
+        <v>431913</v>
       </c>
       <c r="R140" t="n">
-        <v>6795411</v>
+        <v>6795394</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14392,10 +14392,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129707370</v>
+        <v>129694866</v>
       </c>
       <c r="B141" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14403,21 +14403,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14427,10 +14427,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>431913</v>
+        <v>431797</v>
       </c>
       <c r="R141" t="n">
-        <v>6795394</v>
+        <v>6795173</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14477,22 +14477,22 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129694876</v>
+        <v>129707377</v>
       </c>
       <c r="B142" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14500,21 +14500,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14524,10 +14524,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>431871</v>
+        <v>431843</v>
       </c>
       <c r="R142" t="n">
-        <v>6795171</v>
+        <v>6795474</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14574,22 +14574,22 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129694887</v>
+        <v>129707366</v>
       </c>
       <c r="B143" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14597,21 +14597,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14621,10 +14621,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>431886</v>
+        <v>431840</v>
       </c>
       <c r="R143" t="n">
-        <v>6795236</v>
+        <v>6795476</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14671,19 +14671,19 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129694880</v>
+        <v>129694876</v>
       </c>
       <c r="B144" t="n">
         <v>79700</v>
@@ -14721,7 +14721,7 @@
         <v>431871</v>
       </c>
       <c r="R144" t="n">
-        <v>6795205</v>
+        <v>6795171</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14780,7 +14780,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129694897</v>
+        <v>129694887</v>
       </c>
       <c r="B145" t="n">
         <v>79700</v>
@@ -14815,10 +14815,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>431906</v>
+        <v>431886</v>
       </c>
       <c r="R145" t="n">
-        <v>6795283</v>
+        <v>6795236</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -14877,10 +14877,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129707377</v>
+        <v>129694880</v>
       </c>
       <c r="B146" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14888,21 +14888,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -14912,10 +14912,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>431843</v>
+        <v>431871</v>
       </c>
       <c r="R146" t="n">
-        <v>6795474</v>
+        <v>6795205</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -14962,22 +14962,22 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129707366</v>
+        <v>129694897</v>
       </c>
       <c r="B147" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14985,21 +14985,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15009,10 +15009,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>431840</v>
+        <v>431906</v>
       </c>
       <c r="R147" t="n">
-        <v>6795476</v>
+        <v>6795283</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15059,12 +15059,12 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>

--- a/artfynd/A 50492-2025 artfynd.xlsx
+++ b/artfynd/A 50492-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129707403</v>
+        <v>129694842</v>
       </c>
       <c r="B2" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>431851</v>
+        <v>431768</v>
       </c>
       <c r="R2" t="n">
-        <v>6795372</v>
+        <v>6795469</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,44 +760,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129707440</v>
+        <v>129694957</v>
       </c>
       <c r="B3" t="n">
-        <v>92879</v>
+        <v>78838</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>431828</v>
+        <v>431725</v>
       </c>
       <c r="R3" t="n">
-        <v>6795476</v>
+        <v>6795459</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,66 +857,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129707371</v>
+        <v>129694862</v>
       </c>
       <c r="B4" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>431808</v>
+        <v>431756</v>
       </c>
       <c r="R4" t="n">
-        <v>6795442</v>
+        <v>6795121</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,29 +948,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129707216</v>
+        <v>129694935</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,26 +977,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1014,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>432007</v>
+        <v>431917</v>
       </c>
       <c r="R5" t="n">
-        <v>6795475</v>
+        <v>6795290</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1058,26 +1053,25 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129694935</v>
+        <v>129694929</v>
       </c>
       <c r="B6" t="n">
         <v>57733</v>
@@ -1120,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>431917</v>
+        <v>431859</v>
       </c>
       <c r="R6" t="n">
-        <v>6795290</v>
+        <v>6795172</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,53 +1176,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129694929</v>
+        <v>129707440</v>
       </c>
       <c r="B7" t="n">
-        <v>57733</v>
+        <v>92881</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>431859</v>
+        <v>431828</v>
       </c>
       <c r="R7" t="n">
-        <v>6795172</v>
+        <v>6795476</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,22 +1261,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129694842</v>
+        <v>129707216</v>
       </c>
       <c r="B8" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1298,34 +1284,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>431768</v>
+        <v>432007</v>
       </c>
       <c r="R8" t="n">
-        <v>6795469</v>
+        <v>6795475</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1366,28 +1355,29 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129694957</v>
+        <v>129707403</v>
       </c>
       <c r="B9" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1395,21 +1385,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1419,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>431725</v>
+        <v>431851</v>
       </c>
       <c r="R9" t="n">
-        <v>6795459</v>
+        <v>6795372</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1469,57 +1459,66 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129694862</v>
+        <v>129707371</v>
       </c>
       <c r="B10" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>431756</v>
+        <v>431808</v>
       </c>
       <c r="R10" t="n">
-        <v>6795121</v>
+        <v>6795442</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1560,18 +1559,19 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1683,10 +1683,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129694918</v>
+        <v>129707336</v>
       </c>
       <c r="B12" t="n">
-        <v>91618</v>
+        <v>79700</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1694,41 +1694,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>431722</v>
+        <v>431993</v>
       </c>
       <c r="R12" t="n">
-        <v>6795120</v>
+        <v>6795380</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1769,29 +1762,28 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129694843</v>
+        <v>129707434</v>
       </c>
       <c r="B13" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1799,21 +1791,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1823,10 +1815,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>431752</v>
+        <v>431894</v>
       </c>
       <c r="R13" t="n">
-        <v>6795429</v>
+        <v>6795261</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1873,22 +1865,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129694983</v>
+        <v>129694918</v>
       </c>
       <c r="B14" t="n">
-        <v>79081</v>
+        <v>91620</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1896,34 +1888,41 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>431689</v>
+        <v>431722</v>
       </c>
       <c r="R14" t="n">
-        <v>6795456</v>
+        <v>6795120</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1964,6 +1963,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1982,10 +1982,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129694907</v>
+        <v>129694983</v>
       </c>
       <c r="B15" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1993,21 +1993,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>431938</v>
+        <v>431689</v>
       </c>
       <c r="R15" t="n">
-        <v>6795278</v>
+        <v>6795456</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2079,10 +2079,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129707434</v>
+        <v>129694843</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2090,21 +2090,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2114,10 +2114,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>431894</v>
+        <v>431752</v>
       </c>
       <c r="R16" t="n">
-        <v>6795261</v>
+        <v>6795429</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2164,19 +2164,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129707336</v>
+        <v>129694907</v>
       </c>
       <c r="B17" t="n">
         <v>79700</v>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>431993</v>
+        <v>431938</v>
       </c>
       <c r="R17" t="n">
-        <v>6795380</v>
+        <v>6795278</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2261,12 +2261,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2378,53 +2378,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129694913</v>
+        <v>129694845</v>
       </c>
       <c r="B19" t="n">
-        <v>56926</v>
+        <v>79700</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>431728</v>
+        <v>431722</v>
       </c>
       <c r="R19" t="n">
-        <v>6795109</v>
+        <v>6795478</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2483,45 +2475,53 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129694845</v>
+        <v>129694913</v>
       </c>
       <c r="B20" t="n">
-        <v>79700</v>
+        <v>56926</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>431722</v>
+        <v>431728</v>
       </c>
       <c r="R20" t="n">
-        <v>6795478</v>
+        <v>6795109</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2871,10 +2871,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129694942</v>
+        <v>129694883</v>
       </c>
       <c r="B24" t="n">
-        <v>91895</v>
+        <v>79700</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2882,21 +2882,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2906,10 +2906,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>431803</v>
+        <v>431885</v>
       </c>
       <c r="R24" t="n">
-        <v>6795150</v>
+        <v>6795213</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2950,7 +2950,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2969,7 +2968,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129694883</v>
+        <v>129694884</v>
       </c>
       <c r="B25" t="n">
         <v>79700</v>
@@ -3007,7 +3006,7 @@
         <v>431885</v>
       </c>
       <c r="R25" t="n">
-        <v>6795213</v>
+        <v>6795215</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3066,7 +3065,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129694884</v>
+        <v>129694898</v>
       </c>
       <c r="B26" t="n">
         <v>79700</v>
@@ -3101,10 +3100,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>431885</v>
+        <v>431907</v>
       </c>
       <c r="R26" t="n">
-        <v>6795215</v>
+        <v>6795285</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3163,7 +3162,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129694898</v>
+        <v>129694899</v>
       </c>
       <c r="B27" t="n">
         <v>79700</v>
@@ -3198,10 +3197,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>431907</v>
+        <v>431910</v>
       </c>
       <c r="R27" t="n">
-        <v>6795285</v>
+        <v>6795288</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3260,7 +3259,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129694899</v>
+        <v>129694861</v>
       </c>
       <c r="B28" t="n">
         <v>79700</v>
@@ -3295,10 +3294,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>431910</v>
+        <v>431740</v>
       </c>
       <c r="R28" t="n">
-        <v>6795288</v>
+        <v>6795107</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3357,10 +3356,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129694861</v>
+        <v>129707407</v>
       </c>
       <c r="B29" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3368,21 +3367,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3392,10 +3391,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>431740</v>
+        <v>431723</v>
       </c>
       <c r="R29" t="n">
-        <v>6795107</v>
+        <v>6795371</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3442,12 +3441,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3551,10 +3550,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129707331</v>
+        <v>129694942</v>
       </c>
       <c r="B31" t="n">
-        <v>79700</v>
+        <v>91897</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3562,37 +3561,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>431916</v>
+        <v>431803</v>
       </c>
       <c r="R31" t="n">
-        <v>6795392</v>
+        <v>6795150</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3640,22 +3636,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129707407</v>
+        <v>129707331</v>
       </c>
       <c r="B32" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3663,34 +3659,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>431723</v>
+        <v>431916</v>
       </c>
       <c r="R32" t="n">
-        <v>6795371</v>
+        <v>6795392</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3731,6 +3730,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3749,10 +3749,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129694839</v>
+        <v>129694921</v>
       </c>
       <c r="B33" t="n">
-        <v>91520</v>
+        <v>57733</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3760,26 +3760,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3242</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3787,10 +3792,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>431869</v>
+        <v>431725</v>
       </c>
       <c r="R33" t="n">
-        <v>6795181</v>
+        <v>6795459</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3831,7 +3836,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3850,45 +3854,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129695010</v>
+        <v>129707390</v>
       </c>
       <c r="B34" t="n">
-        <v>92879</v>
+        <v>78838</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>431880</v>
+        <v>431952</v>
       </c>
       <c r="R34" t="n">
-        <v>6795546</v>
+        <v>6795410</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3929,25 +3936,26 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129694921</v>
+        <v>129707346</v>
       </c>
       <c r="B35" t="n">
         <v>57733</v>
@@ -3990,10 +3998,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>431725</v>
+        <v>431819</v>
       </c>
       <c r="R35" t="n">
-        <v>6795459</v>
+        <v>6795465</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4040,64 +4048,57 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129694917</v>
+        <v>129695010</v>
       </c>
       <c r="B36" t="n">
-        <v>91618</v>
+        <v>92881</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>431672</v>
+        <v>431880</v>
       </c>
       <c r="R36" t="n">
-        <v>6795442</v>
+        <v>6795546</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4138,7 +4139,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4157,10 +4157,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129694886</v>
+        <v>129694917</v>
       </c>
       <c r="B37" t="n">
-        <v>79700</v>
+        <v>91620</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4168,34 +4168,41 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>431873</v>
+        <v>431672</v>
       </c>
       <c r="R37" t="n">
-        <v>6795241</v>
+        <v>6795442</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4236,6 +4243,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4351,10 +4359,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129694878</v>
+        <v>129694839</v>
       </c>
       <c r="B39" t="n">
-        <v>79700</v>
+        <v>91522</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4362,34 +4370,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>3242</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>431889</v>
+        <v>431869</v>
       </c>
       <c r="R39" t="n">
-        <v>6795186</v>
+        <v>6795181</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4430,6 +4441,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4448,10 +4460,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129707390</v>
+        <v>129694886</v>
       </c>
       <c r="B40" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4459,37 +4471,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>431952</v>
+        <v>431873</v>
       </c>
       <c r="R40" t="n">
-        <v>6795410</v>
+        <v>6795241</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4530,29 +4539,28 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129707346</v>
+        <v>129694878</v>
       </c>
       <c r="B41" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4560,42 +4568,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>431819</v>
+        <v>431889</v>
       </c>
       <c r="R41" t="n">
-        <v>6795465</v>
+        <v>6795186</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4642,22 +4642,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129694926</v>
+        <v>129694847</v>
       </c>
       <c r="B42" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4665,42 +4665,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>431711</v>
+        <v>431724</v>
       </c>
       <c r="R42" t="n">
-        <v>6795100</v>
+        <v>6795460</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4759,10 +4751,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129694847</v>
+        <v>129694999</v>
       </c>
       <c r="B43" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4770,21 +4762,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4794,10 +4786,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>431724</v>
+        <v>431859</v>
       </c>
       <c r="R43" t="n">
-        <v>6795460</v>
+        <v>6795172</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4856,10 +4848,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129694999</v>
+        <v>129694926</v>
       </c>
       <c r="B44" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4867,34 +4859,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>431859</v>
+        <v>431711</v>
       </c>
       <c r="R44" t="n">
-        <v>6795172</v>
+        <v>6795100</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4953,10 +4953,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129707320</v>
+        <v>129707351</v>
       </c>
       <c r="B45" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4964,34 +4964,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>431717</v>
+        <v>431756</v>
       </c>
       <c r="R45" t="n">
-        <v>6795380</v>
+        <v>6795202</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5050,10 +5058,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129707316</v>
+        <v>129707375</v>
       </c>
       <c r="B46" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5061,21 +5069,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5085,10 +5093,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>431812</v>
+        <v>431881</v>
       </c>
       <c r="R46" t="n">
-        <v>6795349</v>
+        <v>6795522</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5147,7 +5155,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129707333</v>
+        <v>129707320</v>
       </c>
       <c r="B47" t="n">
         <v>79700</v>
@@ -5182,10 +5190,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>431935</v>
+        <v>431717</v>
       </c>
       <c r="R47" t="n">
-        <v>6795415</v>
+        <v>6795380</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5244,7 +5252,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129707338</v>
+        <v>129707316</v>
       </c>
       <c r="B48" t="n">
         <v>79700</v>
@@ -5279,10 +5287,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>431932</v>
+        <v>431812</v>
       </c>
       <c r="R48" t="n">
-        <v>6795406</v>
+        <v>6795349</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5341,10 +5349,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129707375</v>
+        <v>129707333</v>
       </c>
       <c r="B49" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5352,21 +5360,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5376,10 +5384,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>431881</v>
+        <v>431935</v>
       </c>
       <c r="R49" t="n">
-        <v>6795522</v>
+        <v>6795415</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5438,10 +5446,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129707351</v>
+        <v>129707338</v>
       </c>
       <c r="B50" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5449,42 +5457,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>431756</v>
+        <v>431932</v>
       </c>
       <c r="R50" t="n">
-        <v>6795202</v>
+        <v>6795406</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5543,10 +5543,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129707347</v>
+        <v>129694994</v>
       </c>
       <c r="B51" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5554,42 +5554,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>431662</v>
+        <v>431804</v>
       </c>
       <c r="R51" t="n">
-        <v>6795391</v>
+        <v>6795151</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5636,12 +5628,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -5939,10 +5931,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129694994</v>
+        <v>129707347</v>
       </c>
       <c r="B55" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5950,34 +5942,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>431804</v>
+        <v>431662</v>
       </c>
       <c r="R55" t="n">
-        <v>6795151</v>
+        <v>6795391</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6024,22 +6024,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129707380</v>
+        <v>129707426</v>
       </c>
       <c r="B56" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6047,21 +6047,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6071,10 +6071,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>431820</v>
+        <v>431767</v>
       </c>
       <c r="R56" t="n">
-        <v>6795330</v>
+        <v>6795219</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6133,7 +6133,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129707426</v>
+        <v>129707404</v>
       </c>
       <c r="B57" t="n">
         <v>79081</v>
@@ -6162,16 +6162,19 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>431767</v>
+        <v>431816</v>
       </c>
       <c r="R57" t="n">
-        <v>6795219</v>
+        <v>6795333</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6206,12 +6209,18 @@
           <t>2025-11-14</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6230,10 +6239,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129707404</v>
+        <v>129707380</v>
       </c>
       <c r="B58" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6241,37 +6250,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>431816</v>
+        <v>431820</v>
       </c>
       <c r="R58" t="n">
-        <v>6795333</v>
+        <v>6795330</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6306,18 +6312,12 @@
           <t>2025-11-14</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6821,10 +6821,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129707319</v>
+        <v>129694930</v>
       </c>
       <c r="B64" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6832,34 +6832,42 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>431708</v>
+        <v>431875</v>
       </c>
       <c r="R64" t="n">
-        <v>6795371</v>
+        <v>6795244</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6906,22 +6914,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129694930</v>
+        <v>129707319</v>
       </c>
       <c r="B65" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6929,42 +6937,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>431875</v>
+        <v>431708</v>
       </c>
       <c r="R65" t="n">
-        <v>6795244</v>
+        <v>6795371</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7011,12 +7011,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7908,7 +7908,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129707391</v>
+        <v>129707389</v>
       </c>
       <c r="B75" t="n">
         <v>78838</v>
@@ -7937,16 +7937,19 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>431724</v>
+        <v>431922</v>
       </c>
       <c r="R75" t="n">
-        <v>6795372</v>
+        <v>6795405</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7987,6 +7990,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8005,10 +8009,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129707389</v>
+        <v>129707314</v>
       </c>
       <c r="B76" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8016,37 +8020,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>431922</v>
+        <v>431866</v>
       </c>
       <c r="R76" t="n">
-        <v>6795405</v>
+        <v>6795513</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8087,7 +8088,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8106,32 +8106,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129707439</v>
+        <v>129707317</v>
       </c>
       <c r="B77" t="n">
-        <v>92879</v>
+        <v>79700</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8141,10 +8141,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>431891</v>
+        <v>431780</v>
       </c>
       <c r="R77" t="n">
-        <v>6795553</v>
+        <v>6795362</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8203,10 +8203,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129707317</v>
+        <v>129707391</v>
       </c>
       <c r="B78" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8214,21 +8214,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8238,10 +8238,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>431780</v>
+        <v>431724</v>
       </c>
       <c r="R78" t="n">
-        <v>6795362</v>
+        <v>6795372</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8300,32 +8300,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129707314</v>
+        <v>129707439</v>
       </c>
       <c r="B79" t="n">
-        <v>79700</v>
+        <v>92881</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8335,10 +8335,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>431866</v>
+        <v>431891</v>
       </c>
       <c r="R79" t="n">
-        <v>6795513</v>
+        <v>6795553</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8397,10 +8397,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129694948</v>
+        <v>129695001</v>
       </c>
       <c r="B80" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8408,21 +8408,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8432,10 +8432,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>431725</v>
+        <v>431876</v>
       </c>
       <c r="R80" t="n">
-        <v>6795459</v>
+        <v>6795202</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8494,10 +8494,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129707388</v>
+        <v>129694863</v>
       </c>
       <c r="B81" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8505,21 +8505,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>431915</v>
+        <v>431785</v>
       </c>
       <c r="R81" t="n">
-        <v>6795392</v>
+        <v>6795106</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8579,22 +8579,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129707424</v>
+        <v>129694874</v>
       </c>
       <c r="B82" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8602,21 +8602,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8626,10 +8626,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>431760</v>
+        <v>431827</v>
       </c>
       <c r="R82" t="n">
-        <v>6795200</v>
+        <v>6795171</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8676,22 +8676,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129707345</v>
+        <v>129694991</v>
       </c>
       <c r="B83" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8699,42 +8699,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>431893</v>
+        <v>431760</v>
       </c>
       <c r="R83" t="n">
-        <v>6795571</v>
+        <v>6795115</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8781,12 +8773,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -8898,10 +8890,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129694863</v>
+        <v>129707388</v>
       </c>
       <c r="B85" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8909,21 +8901,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8933,10 +8925,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>431785</v>
+        <v>431915</v>
       </c>
       <c r="R85" t="n">
-        <v>6795106</v>
+        <v>6795392</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8983,19 +8975,19 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129694874</v>
+        <v>129707315</v>
       </c>
       <c r="B86" t="n">
         <v>79700</v>
@@ -9030,10 +9022,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>431827</v>
+        <v>431820</v>
       </c>
       <c r="R86" t="n">
-        <v>6795171</v>
+        <v>6795329</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9080,19 +9072,19 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129695001</v>
+        <v>129707424</v>
       </c>
       <c r="B87" t="n">
         <v>79081</v>
@@ -9127,10 +9119,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>431876</v>
+        <v>431760</v>
       </c>
       <c r="R87" t="n">
-        <v>6795202</v>
+        <v>6795200</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9177,22 +9169,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129694991</v>
+        <v>129707345</v>
       </c>
       <c r="B88" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9200,34 +9192,42 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>431760</v>
+        <v>431893</v>
       </c>
       <c r="R88" t="n">
-        <v>6795115</v>
+        <v>6795571</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9274,22 +9274,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129707315</v>
+        <v>129694948</v>
       </c>
       <c r="B89" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9297,21 +9297,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9321,10 +9321,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>431820</v>
+        <v>431725</v>
       </c>
       <c r="R89" t="n">
-        <v>6795329</v>
+        <v>6795459</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9371,22 +9371,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129694860</v>
+        <v>129694939</v>
       </c>
       <c r="B90" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9394,21 +9394,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9418,10 +9418,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>431746</v>
+        <v>431913</v>
       </c>
       <c r="R90" t="n">
-        <v>6795081</v>
+        <v>6795284</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9454,6 +9454,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9480,10 +9485,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129694965</v>
+        <v>129694934</v>
       </c>
       <c r="B91" t="n">
-        <v>78838</v>
+        <v>57733</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9491,34 +9496,42 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>431885</v>
+        <v>431916</v>
       </c>
       <c r="R91" t="n">
-        <v>6795240</v>
+        <v>6795286</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9577,10 +9590,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129707381</v>
+        <v>129694860</v>
       </c>
       <c r="B92" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9588,21 +9601,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9612,10 +9625,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>431712</v>
+        <v>431746</v>
       </c>
       <c r="R92" t="n">
-        <v>6795379</v>
+        <v>6795081</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9662,22 +9675,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129694939</v>
+        <v>129694965</v>
       </c>
       <c r="B93" t="n">
-        <v>57733</v>
+        <v>78838</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9685,21 +9698,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9709,10 +9722,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>431913</v>
+        <v>431885</v>
       </c>
       <c r="R93" t="n">
-        <v>6795284</v>
+        <v>6795240</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9745,11 +9758,6 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9776,10 +9784,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129694934</v>
+        <v>129707405</v>
       </c>
       <c r="B94" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9787,42 +9795,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>431916</v>
+        <v>431775</v>
       </c>
       <c r="R94" t="n">
-        <v>6795286</v>
+        <v>6795343</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9869,22 +9869,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129707405</v>
+        <v>129707381</v>
       </c>
       <c r="B95" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9892,21 +9892,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9916,10 +9916,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>431775</v>
+        <v>431712</v>
       </c>
       <c r="R95" t="n">
-        <v>6795343</v>
+        <v>6795379</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9978,32 +9978,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129707312</v>
+        <v>129694941</v>
       </c>
       <c r="B96" t="n">
-        <v>79700</v>
+        <v>79167</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>6450</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10013,10 +10013,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>431920</v>
+        <v>431976</v>
       </c>
       <c r="R96" t="n">
-        <v>6795611</v>
+        <v>6795333</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10063,22 +10063,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129694977</v>
+        <v>129707312</v>
       </c>
       <c r="B97" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10086,42 +10086,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>431933</v>
+        <v>431920</v>
       </c>
       <c r="R97" t="n">
-        <v>6795295</v>
+        <v>6795611</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10168,12 +10160,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -10277,45 +10269,53 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129694941</v>
+        <v>129694977</v>
       </c>
       <c r="B99" t="n">
-        <v>79167</v>
+        <v>57733</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6450</v>
+        <v>100049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>431976</v>
+        <v>431933</v>
       </c>
       <c r="R99" t="n">
-        <v>6795333</v>
+        <v>6795295</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10374,7 +10374,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129707397</v>
+        <v>129707406</v>
       </c>
       <c r="B100" t="n">
         <v>79081</v>
@@ -10409,10 +10409,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>431915</v>
+        <v>431771</v>
       </c>
       <c r="R100" t="n">
-        <v>6795541</v>
+        <v>6795344</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10471,7 +10471,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129707396</v>
+        <v>129707425</v>
       </c>
       <c r="B101" t="n">
         <v>79081</v>
@@ -10506,10 +10506,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>431918</v>
+        <v>431756</v>
       </c>
       <c r="R101" t="n">
-        <v>6795574</v>
+        <v>6795247</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10568,10 +10568,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129707406</v>
+        <v>129707349</v>
       </c>
       <c r="B102" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10579,34 +10579,42 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>431771</v>
+        <v>431722</v>
       </c>
       <c r="R102" t="n">
-        <v>6795344</v>
+        <v>6795217</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10665,7 +10673,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129707425</v>
+        <v>129695000</v>
       </c>
       <c r="B103" t="n">
         <v>79081</v>
@@ -10700,10 +10708,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>431756</v>
+        <v>431890</v>
       </c>
       <c r="R103" t="n">
-        <v>6795247</v>
+        <v>6795199</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10750,19 +10758,19 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129707327</v>
+        <v>129694877</v>
       </c>
       <c r="B104" t="n">
         <v>79700</v>
@@ -10797,10 +10805,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>431893</v>
+        <v>431887</v>
       </c>
       <c r="R104" t="n">
-        <v>6795305</v>
+        <v>6795183</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10847,19 +10855,19 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129707332</v>
+        <v>129694885</v>
       </c>
       <c r="B105" t="n">
         <v>79700</v>
@@ -10894,10 +10902,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>431923</v>
+        <v>431873</v>
       </c>
       <c r="R105" t="n">
-        <v>6795402</v>
+        <v>6795224</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10944,22 +10952,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129707349</v>
+        <v>129694864</v>
       </c>
       <c r="B106" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10967,42 +10975,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>431722</v>
+        <v>431786</v>
       </c>
       <c r="R106" t="n">
-        <v>6795217</v>
+        <v>6795113</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11049,22 +11049,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129694927</v>
+        <v>129694992</v>
       </c>
       <c r="B107" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11072,42 +11072,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>431711</v>
+        <v>431799</v>
       </c>
       <c r="R107" t="n">
-        <v>6795094</v>
+        <v>6795129</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11166,7 +11158,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129694938</v>
+        <v>129694927</v>
       </c>
       <c r="B108" t="n">
         <v>57733</v>
@@ -11209,10 +11201,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>431915</v>
+        <v>431711</v>
       </c>
       <c r="R108" t="n">
-        <v>6795279</v>
+        <v>6795094</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11271,10 +11263,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129695000</v>
+        <v>129694938</v>
       </c>
       <c r="B109" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11282,34 +11274,42 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>431890</v>
+        <v>431915</v>
       </c>
       <c r="R109" t="n">
-        <v>6795199</v>
+        <v>6795279</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11368,10 +11368,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129694877</v>
+        <v>129707397</v>
       </c>
       <c r="B110" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11379,21 +11379,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11403,10 +11403,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>431887</v>
+        <v>431915</v>
       </c>
       <c r="R110" t="n">
-        <v>6795183</v>
+        <v>6795541</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11453,22 +11453,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129694885</v>
+        <v>129707396</v>
       </c>
       <c r="B111" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11476,21 +11476,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11500,10 +11500,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>431873</v>
+        <v>431918</v>
       </c>
       <c r="R111" t="n">
-        <v>6795224</v>
+        <v>6795574</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11550,19 +11550,19 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129694864</v>
+        <v>129707327</v>
       </c>
       <c r="B112" t="n">
         <v>79700</v>
@@ -11597,10 +11597,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>431786</v>
+        <v>431893</v>
       </c>
       <c r="R112" t="n">
-        <v>6795113</v>
+        <v>6795305</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11647,22 +11647,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129694992</v>
+        <v>129707332</v>
       </c>
       <c r="B113" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11670,21 +11670,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11694,10 +11694,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>431799</v>
+        <v>431923</v>
       </c>
       <c r="R113" t="n">
-        <v>6795129</v>
+        <v>6795402</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11744,12 +11744,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
@@ -12047,7 +12047,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129707309</v>
+        <v>129707330</v>
       </c>
       <c r="B117" t="n">
         <v>79700</v>
@@ -12082,10 +12082,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>431869</v>
+        <v>431930</v>
       </c>
       <c r="R117" t="n">
-        <v>6795521</v>
+        <v>6795399</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12144,10 +12144,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129707330</v>
+        <v>129707386</v>
       </c>
       <c r="B118" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12155,21 +12155,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12179,10 +12179,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>431930</v>
+        <v>431897</v>
       </c>
       <c r="R118" t="n">
-        <v>6795399</v>
+        <v>6795284</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12241,7 +12241,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129707323</v>
+        <v>129707309</v>
       </c>
       <c r="B119" t="n">
         <v>79700</v>
@@ -12276,10 +12276,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>431712</v>
+        <v>431869</v>
       </c>
       <c r="R119" t="n">
-        <v>6795236</v>
+        <v>6795521</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12338,10 +12338,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129707386</v>
+        <v>129707421</v>
       </c>
       <c r="B120" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12349,21 +12349,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12373,10 +12373,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>431897</v>
+        <v>431711</v>
       </c>
       <c r="R120" t="n">
-        <v>6795284</v>
+        <v>6795239</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12435,10 +12435,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129707421</v>
+        <v>129707323</v>
       </c>
       <c r="B121" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12446,21 +12446,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12470,10 +12470,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>431711</v>
+        <v>431712</v>
       </c>
       <c r="R121" t="n">
-        <v>6795239</v>
+        <v>6795236</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12532,53 +12532,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129694925</v>
+        <v>129695013</v>
       </c>
       <c r="B122" t="n">
-        <v>57733</v>
+        <v>92881</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>431687</v>
+        <v>431869</v>
       </c>
       <c r="R122" t="n">
-        <v>6795051</v>
+        <v>6795173</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12637,10 +12629,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129694850</v>
+        <v>129694925</v>
       </c>
       <c r="B123" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12648,34 +12640,42 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>431686</v>
+        <v>431687</v>
       </c>
       <c r="R123" t="n">
-        <v>6795471</v>
+        <v>6795051</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12734,7 +12734,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129694881</v>
+        <v>129694850</v>
       </c>
       <c r="B124" t="n">
         <v>79700</v>
@@ -12769,10 +12769,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>431875</v>
+        <v>431686</v>
       </c>
       <c r="R124" t="n">
-        <v>6795212</v>
+        <v>6795471</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12831,7 +12831,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129694888</v>
+        <v>129694881</v>
       </c>
       <c r="B125" t="n">
         <v>79700</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>431889</v>
+        <v>431875</v>
       </c>
       <c r="R125" t="n">
-        <v>6795236</v>
+        <v>6795212</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12928,10 +12928,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129694997</v>
+        <v>129694888</v>
       </c>
       <c r="B126" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12939,21 +12939,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -12963,10 +12963,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>431848</v>
+        <v>431889</v>
       </c>
       <c r="R126" t="n">
-        <v>6795172</v>
+        <v>6795236</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13025,32 +13025,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129695013</v>
+        <v>129694997</v>
       </c>
       <c r="B127" t="n">
-        <v>92879</v>
+        <v>79081</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13060,10 +13060,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>431869</v>
+        <v>431848</v>
       </c>
       <c r="R127" t="n">
-        <v>6795173</v>
+        <v>6795172</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13320,10 +13320,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129694900</v>
+        <v>129707399</v>
       </c>
       <c r="B130" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13331,21 +13331,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13355,10 +13355,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>431907</v>
+        <v>431819</v>
       </c>
       <c r="R130" t="n">
-        <v>6795266</v>
+        <v>6795445</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13405,22 +13405,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129694906</v>
+        <v>129707387</v>
       </c>
       <c r="B131" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13428,21 +13428,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13452,10 +13452,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>431934</v>
+        <v>431936</v>
       </c>
       <c r="R131" t="n">
-        <v>6795286</v>
+        <v>6795393</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13502,19 +13502,19 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129707399</v>
+        <v>129707438</v>
       </c>
       <c r="B132" t="n">
         <v>79081</v>
@@ -13549,10 +13549,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>431819</v>
+        <v>431965</v>
       </c>
       <c r="R132" t="n">
-        <v>6795445</v>
+        <v>6795405</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13611,10 +13611,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129707387</v>
+        <v>129707318</v>
       </c>
       <c r="B133" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13622,21 +13622,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13646,10 +13646,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>431936</v>
+        <v>431769</v>
       </c>
       <c r="R133" t="n">
-        <v>6795393</v>
+        <v>6795345</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13708,10 +13708,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129707438</v>
+        <v>129694900</v>
       </c>
       <c r="B134" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13719,21 +13719,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13743,10 +13743,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>431965</v>
+        <v>431907</v>
       </c>
       <c r="R134" t="n">
-        <v>6795405</v>
+        <v>6795266</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13793,19 +13793,19 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129707318</v>
+        <v>129694906</v>
       </c>
       <c r="B135" t="n">
         <v>79700</v>
@@ -13840,10 +13840,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>431769</v>
+        <v>431934</v>
       </c>
       <c r="R135" t="n">
-        <v>6795345</v>
+        <v>6795286</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -13890,19 +13890,19 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129694865</v>
+        <v>129694866</v>
       </c>
       <c r="B136" t="n">
         <v>79700</v>
@@ -13937,10 +13937,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>431787</v>
+        <v>431797</v>
       </c>
       <c r="R136" t="n">
-        <v>6795115</v>
+        <v>6795173</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -13999,7 +13999,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129694896</v>
+        <v>129694865</v>
       </c>
       <c r="B137" t="n">
         <v>79700</v>
@@ -14034,10 +14034,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>431900</v>
+        <v>431787</v>
       </c>
       <c r="R137" t="n">
-        <v>6795265</v>
+        <v>6795115</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14096,10 +14096,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129694956</v>
+        <v>129694896</v>
       </c>
       <c r="B138" t="n">
-        <v>92015</v>
+        <v>79700</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14107,33 +14107,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6040162</v>
+        <v>6453</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>431718</v>
+        <v>431900</v>
       </c>
       <c r="R138" t="n">
-        <v>6795082</v>
+        <v>6795265</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14168,18 +14169,12 @@
           <t>2025-11-14</t>
         </is>
       </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>Mjuk och len på undetsidan, sämskskinnslik känsla</t>
-        </is>
-      </c>
       <c r="AD138" t="b">
         <v>0</v>
       </c>
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -14392,10 +14387,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129694866</v>
+        <v>129694956</v>
       </c>
       <c r="B141" t="n">
-        <v>79700</v>
+        <v>92017</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14403,34 +14398,33 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>431797</v>
+        <v>431718</v>
       </c>
       <c r="R141" t="n">
-        <v>6795173</v>
+        <v>6795082</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14465,12 +14459,18 @@
           <t>2025-11-14</t>
         </is>
       </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Mjuk och len på undetsidan, sämskskinnslik känsla</t>
+        </is>
+      </c>
       <c r="AD141" t="b">
         <v>0</v>
       </c>
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -14489,10 +14489,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129707377</v>
+        <v>129694876</v>
       </c>
       <c r="B142" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14500,21 +14500,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14524,10 +14524,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>431843</v>
+        <v>431871</v>
       </c>
       <c r="R142" t="n">
-        <v>6795474</v>
+        <v>6795171</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14574,22 +14574,22 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129707366</v>
+        <v>129694887</v>
       </c>
       <c r="B143" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14597,21 +14597,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14621,10 +14621,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>431840</v>
+        <v>431886</v>
       </c>
       <c r="R143" t="n">
-        <v>6795476</v>
+        <v>6795236</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14671,19 +14671,19 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129694876</v>
+        <v>129694880</v>
       </c>
       <c r="B144" t="n">
         <v>79700</v>
@@ -14721,7 +14721,7 @@
         <v>431871</v>
       </c>
       <c r="R144" t="n">
-        <v>6795171</v>
+        <v>6795205</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14780,7 +14780,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129694887</v>
+        <v>129694897</v>
       </c>
       <c r="B145" t="n">
         <v>79700</v>
@@ -14815,10 +14815,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>431886</v>
+        <v>431906</v>
       </c>
       <c r="R145" t="n">
-        <v>6795236</v>
+        <v>6795283</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -14877,10 +14877,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129694880</v>
+        <v>129707377</v>
       </c>
       <c r="B146" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14888,21 +14888,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -14912,10 +14912,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>431871</v>
+        <v>431843</v>
       </c>
       <c r="R146" t="n">
-        <v>6795205</v>
+        <v>6795474</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -14962,22 +14962,22 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129694897</v>
+        <v>129707366</v>
       </c>
       <c r="B147" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14985,21 +14985,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15009,10 +15009,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>431906</v>
+        <v>431840</v>
       </c>
       <c r="R147" t="n">
-        <v>6795283</v>
+        <v>6795476</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15059,12 +15059,12 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>

--- a/artfynd/A 50492-2025 artfynd.xlsx
+++ b/artfynd/A 50492-2025 artfynd.xlsx
@@ -1780,10 +1780,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129707434</v>
+        <v>129707358</v>
       </c>
       <c r="B13" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1791,34 +1791,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>431894</v>
+        <v>431912</v>
       </c>
       <c r="R13" t="n">
-        <v>6795261</v>
+        <v>6795310</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2273,10 +2281,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129707358</v>
+        <v>129707434</v>
       </c>
       <c r="B18" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2284,42 +2292,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>431912</v>
+        <v>431894</v>
       </c>
       <c r="R18" t="n">
-        <v>6795310</v>
+        <v>6795261</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2378,7 +2378,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129694845</v>
+        <v>129707310</v>
       </c>
       <c r="B19" t="n">
         <v>79700</v>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>431722</v>
+        <v>431924</v>
       </c>
       <c r="R19" t="n">
-        <v>6795478</v>
+        <v>6795546</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2463,65 +2463,57 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129694913</v>
+        <v>129707335</v>
       </c>
       <c r="B20" t="n">
-        <v>56926</v>
+        <v>79700</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>431728</v>
+        <v>431965</v>
       </c>
       <c r="R20" t="n">
-        <v>6795109</v>
+        <v>6795430</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2568,22 +2560,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129707378</v>
+        <v>129694845</v>
       </c>
       <c r="B21" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2591,21 +2583,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2615,10 +2607,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>431814</v>
+        <v>431722</v>
       </c>
       <c r="R21" t="n">
-        <v>6795444</v>
+        <v>6795478</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2665,57 +2657,65 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129707310</v>
+        <v>129694913</v>
       </c>
       <c r="B22" t="n">
-        <v>79700</v>
+        <v>56926</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>431924</v>
+        <v>431728</v>
       </c>
       <c r="R22" t="n">
-        <v>6795546</v>
+        <v>6795109</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2762,22 +2762,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129707335</v>
+        <v>129707378</v>
       </c>
       <c r="B23" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2785,21 +2785,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2809,10 +2809,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>431965</v>
+        <v>431814</v>
       </c>
       <c r="R23" t="n">
-        <v>6795430</v>
+        <v>6795444</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -5931,10 +5931,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129707347</v>
+        <v>129707426</v>
       </c>
       <c r="B55" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5942,42 +5942,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>431662</v>
+        <v>431767</v>
       </c>
       <c r="R55" t="n">
-        <v>6795391</v>
+        <v>6795219</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6036,7 +6028,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129707426</v>
+        <v>129707404</v>
       </c>
       <c r="B56" t="n">
         <v>79081</v>
@@ -6065,16 +6057,19 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>431767</v>
+        <v>431816</v>
       </c>
       <c r="R56" t="n">
-        <v>6795219</v>
+        <v>6795333</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6109,12 +6104,18 @@
           <t>2025-11-14</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6133,10 +6134,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129707404</v>
+        <v>129707380</v>
       </c>
       <c r="B57" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6144,37 +6145,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>431816</v>
+        <v>431820</v>
       </c>
       <c r="R57" t="n">
-        <v>6795333</v>
+        <v>6795330</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6209,18 +6207,12 @@
           <t>2025-11-14</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6239,10 +6231,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129707380</v>
+        <v>129707337</v>
       </c>
       <c r="B58" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6250,21 +6242,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6274,10 +6266,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>431820</v>
+        <v>431999</v>
       </c>
       <c r="R58" t="n">
-        <v>6795330</v>
+        <v>6795416</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6336,10 +6328,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129707337</v>
+        <v>129707347</v>
       </c>
       <c r="B59" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6347,34 +6339,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>431999</v>
+        <v>431662</v>
       </c>
       <c r="R59" t="n">
-        <v>6795416</v>
+        <v>6795391</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6724,10 +6724,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129694988</v>
+        <v>129707319</v>
       </c>
       <c r="B63" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6735,21 +6735,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6759,10 +6759,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>431718</v>
+        <v>431708</v>
       </c>
       <c r="R63" t="n">
-        <v>6795068</v>
+        <v>6795371</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6809,22 +6809,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129694930</v>
+        <v>129694988</v>
       </c>
       <c r="B64" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6832,42 +6832,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>431875</v>
+        <v>431718</v>
       </c>
       <c r="R64" t="n">
-        <v>6795244</v>
+        <v>6795068</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6926,10 +6918,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129707319</v>
+        <v>129694930</v>
       </c>
       <c r="B65" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6937,34 +6929,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>431708</v>
+        <v>431875</v>
       </c>
       <c r="R65" t="n">
-        <v>6795371</v>
+        <v>6795244</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7011,12 +7011,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -8397,10 +8397,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129695001</v>
+        <v>129694948</v>
       </c>
       <c r="B80" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8408,21 +8408,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8432,10 +8432,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>431876</v>
+        <v>431725</v>
       </c>
       <c r="R80" t="n">
-        <v>6795202</v>
+        <v>6795459</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8494,10 +8494,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129694863</v>
+        <v>129707388</v>
       </c>
       <c r="B81" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8505,21 +8505,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>431785</v>
+        <v>431915</v>
       </c>
       <c r="R81" t="n">
-        <v>6795106</v>
+        <v>6795392</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8579,19 +8579,19 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129694874</v>
+        <v>129707315</v>
       </c>
       <c r="B82" t="n">
         <v>79700</v>
@@ -8626,10 +8626,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>431827</v>
+        <v>431820</v>
       </c>
       <c r="R82" t="n">
-        <v>6795171</v>
+        <v>6795329</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8676,22 +8676,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129694991</v>
+        <v>129707345</v>
       </c>
       <c r="B83" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8699,34 +8699,42 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>431760</v>
+        <v>431893</v>
       </c>
       <c r="R83" t="n">
-        <v>6795115</v>
+        <v>6795571</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8773,22 +8781,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129694933</v>
+        <v>129695001</v>
       </c>
       <c r="B84" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8796,42 +8804,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>431904</v>
+        <v>431876</v>
       </c>
       <c r="R84" t="n">
-        <v>6795243</v>
+        <v>6795202</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8890,10 +8890,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129707388</v>
+        <v>129694863</v>
       </c>
       <c r="B85" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8901,21 +8901,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8925,10 +8925,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>431915</v>
+        <v>431785</v>
       </c>
       <c r="R85" t="n">
-        <v>6795392</v>
+        <v>6795106</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8975,19 +8975,19 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129707315</v>
+        <v>129694874</v>
       </c>
       <c r="B86" t="n">
         <v>79700</v>
@@ -9022,10 +9022,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>431820</v>
+        <v>431827</v>
       </c>
       <c r="R86" t="n">
-        <v>6795329</v>
+        <v>6795171</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9072,19 +9072,19 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129707424</v>
+        <v>129694991</v>
       </c>
       <c r="B87" t="n">
         <v>79081</v>
@@ -9122,7 +9122,7 @@
         <v>431760</v>
       </c>
       <c r="R87" t="n">
-        <v>6795200</v>
+        <v>6795115</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9169,19 +9169,19 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129707345</v>
+        <v>129694933</v>
       </c>
       <c r="B88" t="n">
         <v>57733</v>
@@ -9224,10 +9224,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>431893</v>
+        <v>431904</v>
       </c>
       <c r="R88" t="n">
-        <v>6795571</v>
+        <v>6795243</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9274,22 +9274,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129694948</v>
+        <v>129707424</v>
       </c>
       <c r="B89" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9297,21 +9297,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9321,10 +9321,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>431725</v>
+        <v>431760</v>
       </c>
       <c r="R89" t="n">
-        <v>6795459</v>
+        <v>6795200</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9371,22 +9371,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129694939</v>
+        <v>129707405</v>
       </c>
       <c r="B90" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9394,21 +9394,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9418,10 +9418,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>431913</v>
+        <v>431775</v>
       </c>
       <c r="R90" t="n">
-        <v>6795284</v>
+        <v>6795343</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9456,11 +9456,6 @@
           <t>2025-11-14</t>
         </is>
       </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
-        </is>
-      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
@@ -9473,22 +9468,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129694934</v>
+        <v>129707381</v>
       </c>
       <c r="B91" t="n">
-        <v>57733</v>
+        <v>78838</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9496,42 +9491,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>431916</v>
+        <v>431712</v>
       </c>
       <c r="R91" t="n">
-        <v>6795286</v>
+        <v>6795379</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9578,12 +9565,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -9784,10 +9771,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129707405</v>
+        <v>129694939</v>
       </c>
       <c r="B94" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9795,21 +9782,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9819,10 +9806,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>431775</v>
+        <v>431913</v>
       </c>
       <c r="R94" t="n">
-        <v>6795343</v>
+        <v>6795284</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9857,6 +9844,11 @@
           <t>2025-11-14</t>
         </is>
       </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
@@ -9869,22 +9861,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129707381</v>
+        <v>129694934</v>
       </c>
       <c r="B95" t="n">
-        <v>78838</v>
+        <v>57733</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9892,34 +9884,42 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>431712</v>
+        <v>431916</v>
       </c>
       <c r="R95" t="n">
-        <v>6795379</v>
+        <v>6795286</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9966,12 +9966,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -11756,7 +11756,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129694901</v>
+        <v>129707330</v>
       </c>
       <c r="B114" t="n">
         <v>79700</v>
@@ -11791,10 +11791,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>431927</v>
+        <v>431930</v>
       </c>
       <c r="R114" t="n">
-        <v>6795265</v>
+        <v>6795399</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11841,22 +11841,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129694990</v>
+        <v>129707386</v>
       </c>
       <c r="B115" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11864,21 +11864,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11888,10 +11888,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>431726</v>
+        <v>431897</v>
       </c>
       <c r="R115" t="n">
-        <v>6795117</v>
+        <v>6795284</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11938,22 +11938,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129694844</v>
+        <v>129707421</v>
       </c>
       <c r="B116" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11961,21 +11961,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11985,10 +11985,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>431739</v>
+        <v>431711</v>
       </c>
       <c r="R116" t="n">
-        <v>6795440</v>
+        <v>6795239</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12035,19 +12035,19 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129707330</v>
+        <v>129694901</v>
       </c>
       <c r="B117" t="n">
         <v>79700</v>
@@ -12082,10 +12082,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>431930</v>
+        <v>431927</v>
       </c>
       <c r="R117" t="n">
-        <v>6795399</v>
+        <v>6795265</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12132,22 +12132,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129707386</v>
+        <v>129694990</v>
       </c>
       <c r="B118" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12155,21 +12155,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12179,10 +12179,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>431897</v>
+        <v>431726</v>
       </c>
       <c r="R118" t="n">
-        <v>6795284</v>
+        <v>6795117</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12229,19 +12229,19 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129707309</v>
+        <v>129694844</v>
       </c>
       <c r="B119" t="n">
         <v>79700</v>
@@ -12276,10 +12276,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>431869</v>
+        <v>431739</v>
       </c>
       <c r="R119" t="n">
-        <v>6795521</v>
+        <v>6795440</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12326,22 +12326,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129707421</v>
+        <v>129707309</v>
       </c>
       <c r="B120" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12349,21 +12349,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12373,10 +12373,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>431711</v>
+        <v>431869</v>
       </c>
       <c r="R120" t="n">
-        <v>6795239</v>
+        <v>6795521</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12532,32 +12532,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129695013</v>
+        <v>129694850</v>
       </c>
       <c r="B122" t="n">
-        <v>92881</v>
+        <v>79700</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12567,10 +12567,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>431869</v>
+        <v>431686</v>
       </c>
       <c r="R122" t="n">
-        <v>6795173</v>
+        <v>6795471</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12629,10 +12629,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129694925</v>
+        <v>129694881</v>
       </c>
       <c r="B123" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12640,42 +12640,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>431687</v>
+        <v>431875</v>
       </c>
       <c r="R123" t="n">
-        <v>6795051</v>
+        <v>6795212</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12734,7 +12726,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129694850</v>
+        <v>129694888</v>
       </c>
       <c r="B124" t="n">
         <v>79700</v>
@@ -12769,10 +12761,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>431686</v>
+        <v>431889</v>
       </c>
       <c r="R124" t="n">
-        <v>6795471</v>
+        <v>6795236</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12831,10 +12823,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129694881</v>
+        <v>129694997</v>
       </c>
       <c r="B125" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12842,21 +12834,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12866,10 +12858,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>431875</v>
+        <v>431848</v>
       </c>
       <c r="R125" t="n">
-        <v>6795212</v>
+        <v>6795172</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12928,10 +12920,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129694888</v>
+        <v>129694925</v>
       </c>
       <c r="B126" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12939,34 +12931,42 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>431889</v>
+        <v>431687</v>
       </c>
       <c r="R126" t="n">
-        <v>6795236</v>
+        <v>6795051</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13025,10 +13025,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129694997</v>
+        <v>129707368</v>
       </c>
       <c r="B127" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13036,34 +13036,37 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>431848</v>
+        <v>431820</v>
       </c>
       <c r="R127" t="n">
-        <v>6795172</v>
+        <v>6795331</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13104,66 +13107,64 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129707368</v>
+        <v>129695013</v>
       </c>
       <c r="B128" t="n">
-        <v>78839</v>
+        <v>92881</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>431820</v>
+        <v>431869</v>
       </c>
       <c r="R128" t="n">
-        <v>6795331</v>
+        <v>6795173</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13204,19 +13205,18 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
@@ -13320,10 +13320,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129707399</v>
+        <v>129707387</v>
       </c>
       <c r="B130" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13331,21 +13331,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13355,10 +13355,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>431819</v>
+        <v>431936</v>
       </c>
       <c r="R130" t="n">
-        <v>6795445</v>
+        <v>6795393</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13417,10 +13417,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129707387</v>
+        <v>129707438</v>
       </c>
       <c r="B131" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13428,21 +13428,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13452,10 +13452,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>431936</v>
+        <v>431965</v>
       </c>
       <c r="R131" t="n">
-        <v>6795393</v>
+        <v>6795405</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13514,10 +13514,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129707438</v>
+        <v>129707318</v>
       </c>
       <c r="B132" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13525,21 +13525,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13549,10 +13549,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>431965</v>
+        <v>431769</v>
       </c>
       <c r="R132" t="n">
-        <v>6795405</v>
+        <v>6795345</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13611,7 +13611,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129707318</v>
+        <v>129694900</v>
       </c>
       <c r="B133" t="n">
         <v>79700</v>
@@ -13646,10 +13646,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>431769</v>
+        <v>431907</v>
       </c>
       <c r="R133" t="n">
-        <v>6795345</v>
+        <v>6795266</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13696,19 +13696,19 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129694900</v>
+        <v>129694906</v>
       </c>
       <c r="B134" t="n">
         <v>79700</v>
@@ -13743,10 +13743,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>431907</v>
+        <v>431934</v>
       </c>
       <c r="R134" t="n">
-        <v>6795266</v>
+        <v>6795286</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13805,10 +13805,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129694906</v>
+        <v>129707399</v>
       </c>
       <c r="B135" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13816,21 +13816,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13840,10 +13840,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>431934</v>
+        <v>431819</v>
       </c>
       <c r="R135" t="n">
-        <v>6795286</v>
+        <v>6795445</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -13890,12 +13890,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
@@ -14290,10 +14290,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129707370</v>
+        <v>129694956</v>
       </c>
       <c r="B140" t="n">
-        <v>78839</v>
+        <v>92017</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14301,34 +14301,33 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>431913</v>
+        <v>431718</v>
       </c>
       <c r="R140" t="n">
-        <v>6795394</v>
+        <v>6795082</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14363,34 +14362,40 @@
           <t>2025-11-14</t>
         </is>
       </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Mjuk och len på undetsidan, sämskskinnslik känsla</t>
+        </is>
+      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129694956</v>
+        <v>129707370</v>
       </c>
       <c r="B141" t="n">
-        <v>92017</v>
+        <v>78839</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14398,33 +14403,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6040162</v>
+        <v>228912</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>431718</v>
+        <v>431913</v>
       </c>
       <c r="R141" t="n">
-        <v>6795082</v>
+        <v>6795394</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14459,30 +14465,24 @@
           <t>2025-11-14</t>
         </is>
       </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Mjuk och len på undetsidan, sämskskinnslik känsla</t>
-        </is>
-      </c>
       <c r="AD141" t="b">
         <v>0</v>
       </c>
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
@@ -14586,7 +14586,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129694887</v>
+        <v>129694897</v>
       </c>
       <c r="B143" t="n">
         <v>79700</v>
@@ -14621,10 +14621,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>431886</v>
+        <v>431906</v>
       </c>
       <c r="R143" t="n">
-        <v>6795236</v>
+        <v>6795283</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14683,7 +14683,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129694880</v>
+        <v>129694887</v>
       </c>
       <c r="B144" t="n">
         <v>79700</v>
@@ -14718,10 +14718,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>431871</v>
+        <v>431886</v>
       </c>
       <c r="R144" t="n">
-        <v>6795205</v>
+        <v>6795236</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14780,7 +14780,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129694897</v>
+        <v>129694880</v>
       </c>
       <c r="B145" t="n">
         <v>79700</v>
@@ -14815,10 +14815,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>431906</v>
+        <v>431871</v>
       </c>
       <c r="R145" t="n">
-        <v>6795283</v>
+        <v>6795205</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -14877,10 +14877,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129707377</v>
+        <v>129707366</v>
       </c>
       <c r="B146" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14888,21 +14888,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -14912,10 +14912,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>431843</v>
+        <v>431840</v>
       </c>
       <c r="R146" t="n">
-        <v>6795474</v>
+        <v>6795476</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -14974,10 +14974,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129707366</v>
+        <v>129707377</v>
       </c>
       <c r="B147" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14985,21 +14985,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15009,10 +15009,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>431840</v>
+        <v>431843</v>
       </c>
       <c r="R147" t="n">
-        <v>6795476</v>
+        <v>6795474</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>

--- a/artfynd/A 50492-2025 artfynd.xlsx
+++ b/artfynd/A 50492-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129694842</v>
+        <v>129707216</v>
       </c>
       <c r="B2" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>431768</v>
+        <v>432007</v>
       </c>
       <c r="R2" t="n">
-        <v>6795469</v>
+        <v>6795475</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,28 +757,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129694957</v>
+        <v>129707403</v>
       </c>
       <c r="B3" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>431725</v>
+        <v>431851</v>
       </c>
       <c r="R3" t="n">
-        <v>6795459</v>
+        <v>6795372</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,19 +861,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129694862</v>
+        <v>129694842</v>
       </c>
       <c r="B4" t="n">
         <v>79700</v>
@@ -904,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>431756</v>
+        <v>431768</v>
       </c>
       <c r="R4" t="n">
-        <v>6795121</v>
+        <v>6795469</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +970,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129694935</v>
+        <v>129694957</v>
       </c>
       <c r="B5" t="n">
-        <v>57733</v>
+        <v>78838</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,42 +981,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>431917</v>
+        <v>431725</v>
       </c>
       <c r="R5" t="n">
-        <v>6795290</v>
+        <v>6795459</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,10 +1067,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129694929</v>
+        <v>129694862</v>
       </c>
       <c r="B6" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1082,42 +1078,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>431859</v>
+        <v>431756</v>
       </c>
       <c r="R6" t="n">
-        <v>6795172</v>
+        <v>6795121</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,45 +1164,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129707440</v>
+        <v>129694935</v>
       </c>
       <c r="B7" t="n">
-        <v>92881</v>
+        <v>57733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>431828</v>
+        <v>431917</v>
       </c>
       <c r="R7" t="n">
-        <v>6795476</v>
+        <v>6795290</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,22 +1257,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129707216</v>
+        <v>129694929</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1284,26 +1280,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1311,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>432007</v>
+        <v>431859</v>
       </c>
       <c r="R8" t="n">
-        <v>6795475</v>
+        <v>6795172</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1355,64 +1356,72 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129707403</v>
+        <v>129707371</v>
       </c>
       <c r="B9" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>431851</v>
+        <v>431808</v>
       </c>
       <c r="R9" t="n">
-        <v>6795372</v>
+        <v>6795442</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1453,6 +1462,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1471,10 +1481,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129707371</v>
+        <v>129707440</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>92881</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,43 +1492,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>431808</v>
+        <v>431828</v>
       </c>
       <c r="R10" t="n">
-        <v>6795442</v>
+        <v>6795476</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1559,7 +1560,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -5931,10 +5931,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129707426</v>
+        <v>129707347</v>
       </c>
       <c r="B55" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5942,34 +5942,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>431767</v>
+        <v>431662</v>
       </c>
       <c r="R55" t="n">
-        <v>6795219</v>
+        <v>6795391</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6028,7 +6036,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129707404</v>
+        <v>129707426</v>
       </c>
       <c r="B56" t="n">
         <v>79081</v>
@@ -6057,19 +6065,16 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>431816</v>
+        <v>431767</v>
       </c>
       <c r="R56" t="n">
-        <v>6795333</v>
+        <v>6795219</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6104,18 +6109,12 @@
           <t>2025-11-14</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6134,10 +6133,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129707380</v>
+        <v>129707404</v>
       </c>
       <c r="B57" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6145,34 +6144,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>431820</v>
+        <v>431816</v>
       </c>
       <c r="R57" t="n">
-        <v>6795330</v>
+        <v>6795333</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6207,12 +6209,18 @@
           <t>2025-11-14</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6231,10 +6239,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129707337</v>
+        <v>129707380</v>
       </c>
       <c r="B58" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6242,21 +6250,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6266,10 +6274,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>431999</v>
+        <v>431820</v>
       </c>
       <c r="R58" t="n">
-        <v>6795416</v>
+        <v>6795330</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6328,10 +6336,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129707347</v>
+        <v>129707337</v>
       </c>
       <c r="B59" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6339,42 +6347,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>431662</v>
+        <v>431999</v>
       </c>
       <c r="R59" t="n">
-        <v>6795391</v>
+        <v>6795416</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7023,10 +7023,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129694928</v>
+        <v>129694857</v>
       </c>
       <c r="B66" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7034,42 +7034,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>431801</v>
+        <v>431800</v>
       </c>
       <c r="R66" t="n">
-        <v>6795136</v>
+        <v>6795130</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7128,7 +7120,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129694857</v>
+        <v>129694908</v>
       </c>
       <c r="B67" t="n">
         <v>79700</v>
@@ -7163,10 +7155,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>431800</v>
+        <v>431973</v>
       </c>
       <c r="R67" t="n">
-        <v>6795130</v>
+        <v>6795310</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7225,7 +7217,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129694908</v>
+        <v>129694858</v>
       </c>
       <c r="B68" t="n">
         <v>79700</v>
@@ -7260,10 +7252,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>431973</v>
+        <v>431749</v>
       </c>
       <c r="R68" t="n">
-        <v>6795310</v>
+        <v>6795079</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7322,7 +7314,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129694858</v>
+        <v>129694859</v>
       </c>
       <c r="B69" t="n">
         <v>79700</v>
@@ -7357,10 +7349,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>431749</v>
+        <v>431702</v>
       </c>
       <c r="R69" t="n">
-        <v>6795079</v>
+        <v>6795115</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7419,7 +7411,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129694859</v>
+        <v>129694879</v>
       </c>
       <c r="B70" t="n">
         <v>79700</v>
@@ -7454,10 +7446,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>431702</v>
+        <v>431888</v>
       </c>
       <c r="R70" t="n">
-        <v>6795115</v>
+        <v>6795198</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7516,10 +7508,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129694879</v>
+        <v>129694928</v>
       </c>
       <c r="B71" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7527,34 +7519,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>431888</v>
+        <v>431801</v>
       </c>
       <c r="R71" t="n">
-        <v>6795198</v>
+        <v>6795136</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7613,10 +7613,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129707420</v>
+        <v>129707382</v>
       </c>
       <c r="B72" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7624,34 +7624,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>431695</v>
+        <v>431689</v>
       </c>
       <c r="R72" t="n">
-        <v>6795256</v>
+        <v>6795383</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7692,6 +7695,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7710,10 +7714,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129707382</v>
+        <v>129707420</v>
       </c>
       <c r="B73" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7721,37 +7725,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>431689</v>
+        <v>431695</v>
       </c>
       <c r="R73" t="n">
-        <v>6795383</v>
+        <v>6795256</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7792,7 +7793,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8397,10 +8397,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129694948</v>
+        <v>129695001</v>
       </c>
       <c r="B80" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8408,21 +8408,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8432,10 +8432,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>431725</v>
+        <v>431876</v>
       </c>
       <c r="R80" t="n">
-        <v>6795459</v>
+        <v>6795202</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8494,10 +8494,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129707388</v>
+        <v>129694863</v>
       </c>
       <c r="B81" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8505,21 +8505,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>431915</v>
+        <v>431785</v>
       </c>
       <c r="R81" t="n">
-        <v>6795392</v>
+        <v>6795106</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8579,19 +8579,19 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129707315</v>
+        <v>129694874</v>
       </c>
       <c r="B82" t="n">
         <v>79700</v>
@@ -8626,10 +8626,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>431820</v>
+        <v>431827</v>
       </c>
       <c r="R82" t="n">
-        <v>6795329</v>
+        <v>6795171</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8676,22 +8676,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129707345</v>
+        <v>129694991</v>
       </c>
       <c r="B83" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8699,42 +8699,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>431893</v>
+        <v>431760</v>
       </c>
       <c r="R83" t="n">
-        <v>6795571</v>
+        <v>6795115</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8781,22 +8773,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129695001</v>
+        <v>129694933</v>
       </c>
       <c r="B84" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8804,34 +8796,42 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>431876</v>
+        <v>431904</v>
       </c>
       <c r="R84" t="n">
-        <v>6795202</v>
+        <v>6795243</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8890,10 +8890,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129694863</v>
+        <v>129707388</v>
       </c>
       <c r="B85" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8901,21 +8901,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8925,10 +8925,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>431785</v>
+        <v>431915</v>
       </c>
       <c r="R85" t="n">
-        <v>6795106</v>
+        <v>6795392</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8975,19 +8975,19 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129694874</v>
+        <v>129707315</v>
       </c>
       <c r="B86" t="n">
         <v>79700</v>
@@ -9022,10 +9022,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>431827</v>
+        <v>431820</v>
       </c>
       <c r="R86" t="n">
-        <v>6795171</v>
+        <v>6795329</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9072,19 +9072,19 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129694991</v>
+        <v>129707424</v>
       </c>
       <c r="B87" t="n">
         <v>79081</v>
@@ -9122,7 +9122,7 @@
         <v>431760</v>
       </c>
       <c r="R87" t="n">
-        <v>6795115</v>
+        <v>6795200</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9169,19 +9169,19 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129694933</v>
+        <v>129707345</v>
       </c>
       <c r="B88" t="n">
         <v>57733</v>
@@ -9224,10 +9224,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>431904</v>
+        <v>431893</v>
       </c>
       <c r="R88" t="n">
-        <v>6795243</v>
+        <v>6795571</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9274,22 +9274,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129707424</v>
+        <v>129694948</v>
       </c>
       <c r="B89" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9297,21 +9297,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9321,10 +9321,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>431760</v>
+        <v>431725</v>
       </c>
       <c r="R89" t="n">
-        <v>6795200</v>
+        <v>6795459</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9371,12 +9371,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -11756,7 +11756,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129707330</v>
+        <v>129694901</v>
       </c>
       <c r="B114" t="n">
         <v>79700</v>
@@ -11791,10 +11791,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>431930</v>
+        <v>431927</v>
       </c>
       <c r="R114" t="n">
-        <v>6795399</v>
+        <v>6795265</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11841,22 +11841,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129707386</v>
+        <v>129694990</v>
       </c>
       <c r="B115" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11864,21 +11864,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11888,10 +11888,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>431897</v>
+        <v>431726</v>
       </c>
       <c r="R115" t="n">
-        <v>6795284</v>
+        <v>6795117</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11938,22 +11938,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129707421</v>
+        <v>129694844</v>
       </c>
       <c r="B116" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11961,21 +11961,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11985,10 +11985,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>431711</v>
+        <v>431739</v>
       </c>
       <c r="R116" t="n">
-        <v>6795239</v>
+        <v>6795440</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12035,19 +12035,19 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129694901</v>
+        <v>129707330</v>
       </c>
       <c r="B117" t="n">
         <v>79700</v>
@@ -12082,10 +12082,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>431927</v>
+        <v>431930</v>
       </c>
       <c r="R117" t="n">
-        <v>6795265</v>
+        <v>6795399</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12132,22 +12132,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129694990</v>
+        <v>129707386</v>
       </c>
       <c r="B118" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12155,21 +12155,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12179,10 +12179,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>431726</v>
+        <v>431897</v>
       </c>
       <c r="R118" t="n">
-        <v>6795117</v>
+        <v>6795284</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12229,19 +12229,19 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129694844</v>
+        <v>129707309</v>
       </c>
       <c r="B119" t="n">
         <v>79700</v>
@@ -12276,10 +12276,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>431739</v>
+        <v>431869</v>
       </c>
       <c r="R119" t="n">
-        <v>6795440</v>
+        <v>6795521</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12326,22 +12326,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129707309</v>
+        <v>129707421</v>
       </c>
       <c r="B120" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12349,21 +12349,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12373,10 +12373,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>431869</v>
+        <v>431711</v>
       </c>
       <c r="R120" t="n">
-        <v>6795521</v>
+        <v>6795239</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13320,10 +13320,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129707387</v>
+        <v>129694900</v>
       </c>
       <c r="B130" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13331,21 +13331,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13355,10 +13355,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>431936</v>
+        <v>431907</v>
       </c>
       <c r="R130" t="n">
-        <v>6795393</v>
+        <v>6795266</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13405,22 +13405,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129707438</v>
+        <v>129694906</v>
       </c>
       <c r="B131" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13428,21 +13428,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13452,10 +13452,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>431965</v>
+        <v>431934</v>
       </c>
       <c r="R131" t="n">
-        <v>6795405</v>
+        <v>6795286</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13502,22 +13502,22 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129707318</v>
+        <v>129707387</v>
       </c>
       <c r="B132" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13525,21 +13525,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13549,10 +13549,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>431769</v>
+        <v>431936</v>
       </c>
       <c r="R132" t="n">
-        <v>6795345</v>
+        <v>6795393</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13611,10 +13611,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129694900</v>
+        <v>129707438</v>
       </c>
       <c r="B133" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13622,21 +13622,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13646,10 +13646,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>431907</v>
+        <v>431965</v>
       </c>
       <c r="R133" t="n">
-        <v>6795266</v>
+        <v>6795405</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13696,19 +13696,19 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129694906</v>
+        <v>129707318</v>
       </c>
       <c r="B134" t="n">
         <v>79700</v>
@@ -13743,10 +13743,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>431934</v>
+        <v>431769</v>
       </c>
       <c r="R134" t="n">
-        <v>6795286</v>
+        <v>6795345</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13793,12 +13793,12 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
@@ -14586,7 +14586,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129694897</v>
+        <v>129694887</v>
       </c>
       <c r="B143" t="n">
         <v>79700</v>
@@ -14621,10 +14621,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>431906</v>
+        <v>431886</v>
       </c>
       <c r="R143" t="n">
-        <v>6795283</v>
+        <v>6795236</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14683,7 +14683,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129694887</v>
+        <v>129694880</v>
       </c>
       <c r="B144" t="n">
         <v>79700</v>
@@ -14718,10 +14718,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>431886</v>
+        <v>431871</v>
       </c>
       <c r="R144" t="n">
-        <v>6795236</v>
+        <v>6795205</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14780,7 +14780,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129694880</v>
+        <v>129694897</v>
       </c>
       <c r="B145" t="n">
         <v>79700</v>
@@ -14815,10 +14815,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>431871</v>
+        <v>431906</v>
       </c>
       <c r="R145" t="n">
-        <v>6795205</v>
+        <v>6795283</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -14877,10 +14877,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129707366</v>
+        <v>129707377</v>
       </c>
       <c r="B146" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14888,21 +14888,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -14912,10 +14912,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>431840</v>
+        <v>431843</v>
       </c>
       <c r="R146" t="n">
-        <v>6795476</v>
+        <v>6795474</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -14974,10 +14974,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129707377</v>
+        <v>129707366</v>
       </c>
       <c r="B147" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14985,21 +14985,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15009,10 +15009,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>431843</v>
+        <v>431840</v>
       </c>
       <c r="R147" t="n">
-        <v>6795474</v>
+        <v>6795476</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>

--- a/artfynd/A 50492-2025 artfynd.xlsx
+++ b/artfynd/A 50492-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129707216</v>
+        <v>129694842</v>
       </c>
       <c r="B2" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>432007</v>
+        <v>431768</v>
       </c>
       <c r="R2" t="n">
-        <v>6795475</v>
+        <v>6795469</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,29 +754,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129707403</v>
+        <v>129694862</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>431851</v>
+        <v>431756</v>
       </c>
       <c r="R3" t="n">
-        <v>6795372</v>
+        <v>6795121</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129694842</v>
+        <v>129694957</v>
       </c>
       <c r="B4" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -884,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -908,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>431768</v>
+        <v>431725</v>
       </c>
       <c r="R4" t="n">
-        <v>6795469</v>
+        <v>6795459</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129694957</v>
+        <v>129707440</v>
       </c>
       <c r="B5" t="n">
-        <v>78838</v>
+        <v>92881</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1005,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>431725</v>
+        <v>431828</v>
       </c>
       <c r="R5" t="n">
-        <v>6795459</v>
+        <v>6795476</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1055,22 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129694862</v>
+        <v>129694935</v>
       </c>
       <c r="B6" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1078,34 +1074,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>431756</v>
+        <v>431917</v>
       </c>
       <c r="R6" t="n">
-        <v>6795121</v>
+        <v>6795290</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,7 +1168,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129694935</v>
+        <v>129694929</v>
       </c>
       <c r="B7" t="n">
         <v>57733</v>
@@ -1207,10 +1211,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>431917</v>
+        <v>431859</v>
       </c>
       <c r="R7" t="n">
-        <v>6795290</v>
+        <v>6795172</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1269,10 +1273,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129694929</v>
+        <v>129707216</v>
       </c>
       <c r="B8" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1280,31 +1284,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1312,10 +1311,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>431859</v>
+        <v>432007</v>
       </c>
       <c r="R8" t="n">
-        <v>6795172</v>
+        <v>6795475</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1356,72 +1355,64 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129707371</v>
+        <v>129707403</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>431808</v>
+        <v>431851</v>
       </c>
       <c r="R9" t="n">
-        <v>6795442</v>
+        <v>6795372</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1462,7 +1453,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1481,10 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129707440</v>
+        <v>129707371</v>
       </c>
       <c r="B10" t="n">
-        <v>92881</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1492,34 +1482,43 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>431828</v>
+        <v>431808</v>
       </c>
       <c r="R10" t="n">
-        <v>6795476</v>
+        <v>6795442</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1560,6 +1559,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1780,10 +1780,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129707358</v>
+        <v>129707434</v>
       </c>
       <c r="B13" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1791,42 +1791,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>431912</v>
+        <v>431894</v>
       </c>
       <c r="R13" t="n">
-        <v>6795310</v>
+        <v>6795261</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1885,10 +1877,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129694918</v>
+        <v>129707358</v>
       </c>
       <c r="B14" t="n">
-        <v>91620</v>
+        <v>57733</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1896,30 +1888,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1927,10 +1920,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>431722</v>
+        <v>431912</v>
       </c>
       <c r="R14" t="n">
-        <v>6795120</v>
+        <v>6795310</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1971,19 +1964,18 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2087,10 +2079,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129694843</v>
+        <v>129694918</v>
       </c>
       <c r="B16" t="n">
-        <v>79700</v>
+        <v>91620</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2098,34 +2090,41 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>431752</v>
+        <v>431722</v>
       </c>
       <c r="R16" t="n">
-        <v>6795429</v>
+        <v>6795120</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2166,6 +2165,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2184,7 +2184,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129694907</v>
+        <v>129694843</v>
       </c>
       <c r="B17" t="n">
         <v>79700</v>
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>431938</v>
+        <v>431752</v>
       </c>
       <c r="R17" t="n">
-        <v>6795278</v>
+        <v>6795429</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2281,10 +2281,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129707434</v>
+        <v>129694907</v>
       </c>
       <c r="B18" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2292,21 +2292,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2316,10 +2316,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>431894</v>
+        <v>431938</v>
       </c>
       <c r="R18" t="n">
-        <v>6795261</v>
+        <v>6795278</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2366,19 +2366,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129707310</v>
+        <v>129694845</v>
       </c>
       <c r="B19" t="n">
         <v>79700</v>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>431924</v>
+        <v>431722</v>
       </c>
       <c r="R19" t="n">
-        <v>6795546</v>
+        <v>6795478</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2463,22 +2463,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129707335</v>
+        <v>129707378</v>
       </c>
       <c r="B20" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2486,21 +2486,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2510,10 +2510,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>431965</v>
+        <v>431814</v>
       </c>
       <c r="R20" t="n">
-        <v>6795430</v>
+        <v>6795444</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2572,7 +2572,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129694845</v>
+        <v>129707310</v>
       </c>
       <c r="B21" t="n">
         <v>79700</v>
@@ -2607,10 +2607,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>431722</v>
+        <v>431924</v>
       </c>
       <c r="R21" t="n">
-        <v>6795478</v>
+        <v>6795546</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2657,65 +2657,57 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129694913</v>
+        <v>129707335</v>
       </c>
       <c r="B22" t="n">
-        <v>56926</v>
+        <v>79700</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>431728</v>
+        <v>431965</v>
       </c>
       <c r="R22" t="n">
-        <v>6795109</v>
+        <v>6795430</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2762,57 +2754,65 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129707378</v>
+        <v>129694913</v>
       </c>
       <c r="B23" t="n">
-        <v>78838</v>
+        <v>56926</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>431814</v>
+        <v>431728</v>
       </c>
       <c r="R23" t="n">
-        <v>6795444</v>
+        <v>6795109</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2859,19 +2859,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129694883</v>
+        <v>129707331</v>
       </c>
       <c r="B24" t="n">
         <v>79700</v>
@@ -2900,16 +2900,19 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>431885</v>
+        <v>431916</v>
       </c>
       <c r="R24" t="n">
-        <v>6795213</v>
+        <v>6795392</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2950,28 +2953,29 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129694884</v>
+        <v>129694942</v>
       </c>
       <c r="B25" t="n">
-        <v>79700</v>
+        <v>91897</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2979,21 +2983,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3003,10 +3007,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>431885</v>
+        <v>431803</v>
       </c>
       <c r="R25" t="n">
-        <v>6795215</v>
+        <v>6795150</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3047,6 +3051,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3065,7 +3070,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129694898</v>
+        <v>129694883</v>
       </c>
       <c r="B26" t="n">
         <v>79700</v>
@@ -3100,10 +3105,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>431907</v>
+        <v>431885</v>
       </c>
       <c r="R26" t="n">
-        <v>6795285</v>
+        <v>6795213</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3162,7 +3167,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129694899</v>
+        <v>129694884</v>
       </c>
       <c r="B27" t="n">
         <v>79700</v>
@@ -3197,10 +3202,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>431910</v>
+        <v>431885</v>
       </c>
       <c r="R27" t="n">
-        <v>6795288</v>
+        <v>6795215</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3259,7 +3264,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129694861</v>
+        <v>129694898</v>
       </c>
       <c r="B28" t="n">
         <v>79700</v>
@@ -3294,10 +3299,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>431740</v>
+        <v>431907</v>
       </c>
       <c r="R28" t="n">
-        <v>6795107</v>
+        <v>6795285</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3356,10 +3361,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129707407</v>
+        <v>129694899</v>
       </c>
       <c r="B29" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3367,21 +3372,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3391,10 +3396,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>431723</v>
+        <v>431910</v>
       </c>
       <c r="R29" t="n">
-        <v>6795371</v>
+        <v>6795288</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3441,19 +3446,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129707308</v>
+        <v>129694861</v>
       </c>
       <c r="B30" t="n">
         <v>79700</v>
@@ -3488,10 +3493,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>431868</v>
+        <v>431740</v>
       </c>
       <c r="R30" t="n">
-        <v>6795565</v>
+        <v>6795107</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3538,22 +3543,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129694942</v>
+        <v>129707308</v>
       </c>
       <c r="B31" t="n">
-        <v>91897</v>
+        <v>79700</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3561,21 +3566,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3585,10 +3590,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>431803</v>
+        <v>431868</v>
       </c>
       <c r="R31" t="n">
-        <v>6795150</v>
+        <v>6795565</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3629,29 +3634,28 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129707331</v>
+        <v>129707407</v>
       </c>
       <c r="B32" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3659,37 +3663,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>431916</v>
+        <v>431723</v>
       </c>
       <c r="R32" t="n">
-        <v>6795392</v>
+        <v>6795371</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3730,7 +3731,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3749,53 +3749,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129694921</v>
+        <v>129695010</v>
       </c>
       <c r="B33" t="n">
-        <v>57733</v>
+        <v>92881</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>431725</v>
+        <v>431880</v>
       </c>
       <c r="R33" t="n">
-        <v>6795459</v>
+        <v>6795546</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3854,10 +3846,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129707390</v>
+        <v>129694839</v>
       </c>
       <c r="B34" t="n">
-        <v>78838</v>
+        <v>91522</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3865,21 +3857,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>3242</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3892,10 +3884,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>431952</v>
+        <v>431869</v>
       </c>
       <c r="R34" t="n">
-        <v>6795410</v>
+        <v>6795181</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3943,22 +3935,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129707346</v>
+        <v>129694980</v>
       </c>
       <c r="B35" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3966,42 +3958,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>431819</v>
+        <v>431711</v>
       </c>
       <c r="R35" t="n">
-        <v>6795465</v>
+        <v>6795450</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4048,57 +4032,64 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129695010</v>
+        <v>129694917</v>
       </c>
       <c r="B36" t="n">
-        <v>92881</v>
+        <v>91620</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>431880</v>
+        <v>431672</v>
       </c>
       <c r="R36" t="n">
-        <v>6795546</v>
+        <v>6795442</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4139,6 +4130,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4157,10 +4149,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129694917</v>
+        <v>129694886</v>
       </c>
       <c r="B37" t="n">
-        <v>91620</v>
+        <v>79700</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4168,41 +4160,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>431672</v>
+        <v>431873</v>
       </c>
       <c r="R37" t="n">
-        <v>6795442</v>
+        <v>6795241</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4243,7 +4228,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4262,10 +4246,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129694980</v>
+        <v>129694878</v>
       </c>
       <c r="B38" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4273,21 +4257,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4297,10 +4281,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>431711</v>
+        <v>431889</v>
       </c>
       <c r="R38" t="n">
-        <v>6795450</v>
+        <v>6795186</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4359,10 +4343,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129694839</v>
+        <v>129694921</v>
       </c>
       <c r="B39" t="n">
-        <v>91522</v>
+        <v>57733</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4370,26 +4354,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3242</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4397,10 +4386,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>431869</v>
+        <v>431725</v>
       </c>
       <c r="R39" t="n">
-        <v>6795181</v>
+        <v>6795459</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4441,7 +4430,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4460,10 +4448,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129694886</v>
+        <v>129707390</v>
       </c>
       <c r="B40" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4471,34 +4459,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>431873</v>
+        <v>431952</v>
       </c>
       <c r="R40" t="n">
-        <v>6795241</v>
+        <v>6795410</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4539,28 +4530,29 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129694878</v>
+        <v>129707346</v>
       </c>
       <c r="B41" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4568,34 +4560,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>431889</v>
+        <v>431819</v>
       </c>
       <c r="R41" t="n">
-        <v>6795186</v>
+        <v>6795465</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4642,22 +4642,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129694847</v>
+        <v>129694999</v>
       </c>
       <c r="B42" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4665,21 +4665,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>431724</v>
+        <v>431859</v>
       </c>
       <c r="R42" t="n">
-        <v>6795460</v>
+        <v>6795172</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4751,10 +4751,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129694999</v>
+        <v>129694847</v>
       </c>
       <c r="B43" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4762,21 +4762,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4786,10 +4786,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>431859</v>
+        <v>431724</v>
       </c>
       <c r="R43" t="n">
-        <v>6795172</v>
+        <v>6795460</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4953,10 +4953,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129707351</v>
+        <v>129707320</v>
       </c>
       <c r="B45" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4964,42 +4964,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>431756</v>
+        <v>431717</v>
       </c>
       <c r="R45" t="n">
-        <v>6795202</v>
+        <v>6795380</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5058,10 +5050,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129707375</v>
+        <v>129707316</v>
       </c>
       <c r="B46" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5069,21 +5061,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5093,10 +5085,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>431881</v>
+        <v>431812</v>
       </c>
       <c r="R46" t="n">
-        <v>6795522</v>
+        <v>6795349</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5155,7 +5147,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129707320</v>
+        <v>129707333</v>
       </c>
       <c r="B47" t="n">
         <v>79700</v>
@@ -5190,10 +5182,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>431717</v>
+        <v>431935</v>
       </c>
       <c r="R47" t="n">
-        <v>6795380</v>
+        <v>6795415</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5252,7 +5244,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129707316</v>
+        <v>129707338</v>
       </c>
       <c r="B48" t="n">
         <v>79700</v>
@@ -5287,10 +5279,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>431812</v>
+        <v>431932</v>
       </c>
       <c r="R48" t="n">
-        <v>6795349</v>
+        <v>6795406</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5349,10 +5341,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129707333</v>
+        <v>129707375</v>
       </c>
       <c r="B49" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5360,21 +5352,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5384,10 +5376,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>431935</v>
+        <v>431881</v>
       </c>
       <c r="R49" t="n">
-        <v>6795415</v>
+        <v>6795522</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5446,10 +5438,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129707338</v>
+        <v>129707351</v>
       </c>
       <c r="B50" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5457,34 +5449,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>431932</v>
+        <v>431756</v>
       </c>
       <c r="R50" t="n">
-        <v>6795406</v>
+        <v>6795202</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5543,10 +5543,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129694994</v>
+        <v>129694846</v>
       </c>
       <c r="B51" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5554,21 +5554,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5578,10 +5578,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>431804</v>
+        <v>431725</v>
       </c>
       <c r="R51" t="n">
-        <v>6795151</v>
+        <v>6795467</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5640,10 +5640,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129694846</v>
+        <v>129707347</v>
       </c>
       <c r="B52" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5651,34 +5651,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>431725</v>
+        <v>431662</v>
       </c>
       <c r="R52" t="n">
-        <v>6795467</v>
+        <v>6795391</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5725,19 +5733,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129695006</v>
+        <v>129694994</v>
       </c>
       <c r="B53" t="n">
         <v>79081</v>
@@ -5772,10 +5780,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>431962</v>
+        <v>431804</v>
       </c>
       <c r="R53" t="n">
-        <v>6795319</v>
+        <v>6795151</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5834,7 +5842,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129695003</v>
+        <v>129695006</v>
       </c>
       <c r="B54" t="n">
         <v>79081</v>
@@ -5869,10 +5877,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>431908</v>
+        <v>431962</v>
       </c>
       <c r="R54" t="n">
-        <v>6795302</v>
+        <v>6795319</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5931,10 +5939,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129707347</v>
+        <v>129695003</v>
       </c>
       <c r="B55" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5942,42 +5950,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>431662</v>
+        <v>431908</v>
       </c>
       <c r="R55" t="n">
-        <v>6795391</v>
+        <v>6795302</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6024,22 +6024,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129707426</v>
+        <v>129707337</v>
       </c>
       <c r="B56" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6047,21 +6047,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6071,10 +6071,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>431767</v>
+        <v>431999</v>
       </c>
       <c r="R56" t="n">
-        <v>6795219</v>
+        <v>6795416</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6133,7 +6133,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129707404</v>
+        <v>129707426</v>
       </c>
       <c r="B57" t="n">
         <v>79081</v>
@@ -6162,19 +6162,16 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>431816</v>
+        <v>431767</v>
       </c>
       <c r="R57" t="n">
-        <v>6795333</v>
+        <v>6795219</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6209,18 +6206,12 @@
           <t>2025-11-14</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6239,10 +6230,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129707380</v>
+        <v>129707404</v>
       </c>
       <c r="B58" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6250,34 +6241,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>431820</v>
+        <v>431816</v>
       </c>
       <c r="R58" t="n">
-        <v>6795330</v>
+        <v>6795333</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6312,12 +6306,18 @@
           <t>2025-11-14</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6336,10 +6336,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129707337</v>
+        <v>129707380</v>
       </c>
       <c r="B59" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6347,21 +6347,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>431999</v>
+        <v>431820</v>
       </c>
       <c r="R59" t="n">
-        <v>6795416</v>
+        <v>6795330</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6433,10 +6433,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129694872</v>
+        <v>129694988</v>
       </c>
       <c r="B60" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6444,21 +6444,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6468,10 +6468,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>431833</v>
+        <v>431718</v>
       </c>
       <c r="R60" t="n">
-        <v>6795171</v>
+        <v>6795068</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6530,10 +6530,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129694856</v>
+        <v>129694961</v>
       </c>
       <c r="B61" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6541,21 +6541,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6565,10 +6565,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>431693</v>
+        <v>431804</v>
       </c>
       <c r="R61" t="n">
-        <v>6795052</v>
+        <v>6795100</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6627,10 +6627,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129694961</v>
+        <v>129707319</v>
       </c>
       <c r="B62" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6638,21 +6638,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6662,10 +6662,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>431804</v>
+        <v>431708</v>
       </c>
       <c r="R62" t="n">
-        <v>6795100</v>
+        <v>6795371</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6712,19 +6712,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129707319</v>
+        <v>129694872</v>
       </c>
       <c r="B63" t="n">
         <v>79700</v>
@@ -6759,10 +6759,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>431708</v>
+        <v>431833</v>
       </c>
       <c r="R63" t="n">
-        <v>6795371</v>
+        <v>6795171</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6809,22 +6809,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129694988</v>
+        <v>129694856</v>
       </c>
       <c r="B64" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6832,21 +6832,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6856,10 +6856,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>431718</v>
+        <v>431693</v>
       </c>
       <c r="R64" t="n">
-        <v>6795068</v>
+        <v>6795052</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7811,10 +7811,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129694985</v>
+        <v>129707317</v>
       </c>
       <c r="B74" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7822,21 +7822,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7846,10 +7846,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>431673</v>
+        <v>431780</v>
       </c>
       <c r="R74" t="n">
-        <v>6795435</v>
+        <v>6795362</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7896,19 +7896,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129707389</v>
+        <v>129707391</v>
       </c>
       <c r="B75" t="n">
         <v>78838</v>
@@ -7937,19 +7937,16 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>431922</v>
+        <v>431724</v>
       </c>
       <c r="R75" t="n">
-        <v>6795405</v>
+        <v>6795372</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7990,7 +7987,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8009,10 +8005,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129707314</v>
+        <v>129707389</v>
       </c>
       <c r="B76" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8020,34 +8016,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>431866</v>
+        <v>431922</v>
       </c>
       <c r="R76" t="n">
-        <v>6795513</v>
+        <v>6795405</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8088,6 +8087,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8106,7 +8106,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129707317</v>
+        <v>129707314</v>
       </c>
       <c r="B77" t="n">
         <v>79700</v>
@@ -8141,10 +8141,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>431780</v>
+        <v>431866</v>
       </c>
       <c r="R77" t="n">
-        <v>6795362</v>
+        <v>6795513</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8203,10 +8203,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129707391</v>
+        <v>129694985</v>
       </c>
       <c r="B78" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8214,21 +8214,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8238,10 +8238,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>431724</v>
+        <v>431673</v>
       </c>
       <c r="R78" t="n">
-        <v>6795372</v>
+        <v>6795435</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8288,12 +8288,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -8397,10 +8397,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129695001</v>
+        <v>129694863</v>
       </c>
       <c r="B80" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8408,21 +8408,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8432,10 +8432,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>431876</v>
+        <v>431785</v>
       </c>
       <c r="R80" t="n">
-        <v>6795202</v>
+        <v>6795106</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8494,7 +8494,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129694863</v>
+        <v>129694874</v>
       </c>
       <c r="B81" t="n">
         <v>79700</v>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>431785</v>
+        <v>431827</v>
       </c>
       <c r="R81" t="n">
-        <v>6795106</v>
+        <v>6795171</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8591,10 +8591,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129694874</v>
+        <v>129694948</v>
       </c>
       <c r="B82" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8602,21 +8602,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8626,10 +8626,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>431827</v>
+        <v>431725</v>
       </c>
       <c r="R82" t="n">
-        <v>6795171</v>
+        <v>6795459</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8890,10 +8890,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129707388</v>
+        <v>129695001</v>
       </c>
       <c r="B85" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8901,21 +8901,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8925,10 +8925,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>431915</v>
+        <v>431876</v>
       </c>
       <c r="R85" t="n">
-        <v>6795392</v>
+        <v>6795202</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8975,22 +8975,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129707315</v>
+        <v>129707345</v>
       </c>
       <c r="B86" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8998,34 +8998,42 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>431820</v>
+        <v>431893</v>
       </c>
       <c r="R86" t="n">
-        <v>6795329</v>
+        <v>6795571</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9084,10 +9092,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129707424</v>
+        <v>129707388</v>
       </c>
       <c r="B87" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9095,21 +9103,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9119,10 +9127,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>431760</v>
+        <v>431915</v>
       </c>
       <c r="R87" t="n">
-        <v>6795200</v>
+        <v>6795392</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9181,10 +9189,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129707345</v>
+        <v>129707315</v>
       </c>
       <c r="B88" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9192,42 +9200,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>431893</v>
+        <v>431820</v>
       </c>
       <c r="R88" t="n">
-        <v>6795571</v>
+        <v>6795329</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9286,10 +9286,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129694948</v>
+        <v>129707424</v>
       </c>
       <c r="B89" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9297,21 +9297,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9321,10 +9321,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>431725</v>
+        <v>431760</v>
       </c>
       <c r="R89" t="n">
-        <v>6795459</v>
+        <v>6795200</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9371,22 +9371,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129707405</v>
+        <v>129694934</v>
       </c>
       <c r="B90" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9394,34 +9394,42 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>431775</v>
+        <v>431916</v>
       </c>
       <c r="R90" t="n">
-        <v>6795343</v>
+        <v>6795286</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9468,22 +9476,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129707381</v>
+        <v>129707405</v>
       </c>
       <c r="B91" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9491,21 +9499,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9515,10 +9523,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>431712</v>
+        <v>431775</v>
       </c>
       <c r="R91" t="n">
-        <v>6795379</v>
+        <v>6795343</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9577,10 +9585,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129694860</v>
+        <v>129707381</v>
       </c>
       <c r="B92" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9588,21 +9596,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9612,10 +9620,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>431746</v>
+        <v>431712</v>
       </c>
       <c r="R92" t="n">
-        <v>6795081</v>
+        <v>6795379</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9662,22 +9670,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129694965</v>
+        <v>129694860</v>
       </c>
       <c r="B93" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9685,21 +9693,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9709,10 +9717,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>431885</v>
+        <v>431746</v>
       </c>
       <c r="R93" t="n">
-        <v>6795240</v>
+        <v>6795081</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9873,10 +9881,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129694934</v>
+        <v>129694965</v>
       </c>
       <c r="B95" t="n">
-        <v>57733</v>
+        <v>78838</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9884,42 +9892,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>431916</v>
+        <v>431885</v>
       </c>
       <c r="R95" t="n">
-        <v>6795286</v>
+        <v>6795240</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10075,10 +10075,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129707312</v>
+        <v>129694977</v>
       </c>
       <c r="B97" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10086,34 +10086,42 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>431920</v>
+        <v>431933</v>
       </c>
       <c r="R97" t="n">
-        <v>6795611</v>
+        <v>6795295</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10160,12 +10168,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -10269,10 +10277,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129694977</v>
+        <v>129707312</v>
       </c>
       <c r="B99" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10280,42 +10288,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>431933</v>
+        <v>431920</v>
       </c>
       <c r="R99" t="n">
-        <v>6795295</v>
+        <v>6795611</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10362,22 +10362,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129707406</v>
+        <v>129694877</v>
       </c>
       <c r="B100" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10385,21 +10385,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10409,10 +10409,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>431771</v>
+        <v>431887</v>
       </c>
       <c r="R100" t="n">
-        <v>6795344</v>
+        <v>6795183</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10459,22 +10459,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129707425</v>
+        <v>129694885</v>
       </c>
       <c r="B101" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10482,21 +10482,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10506,10 +10506,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>431756</v>
+        <v>431873</v>
       </c>
       <c r="R101" t="n">
-        <v>6795247</v>
+        <v>6795224</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10556,22 +10556,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129707349</v>
+        <v>129694864</v>
       </c>
       <c r="B102" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10579,42 +10579,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>431722</v>
+        <v>431786</v>
       </c>
       <c r="R102" t="n">
-        <v>6795217</v>
+        <v>6795113</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10661,22 +10653,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129695000</v>
+        <v>129694927</v>
       </c>
       <c r="B103" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10684,34 +10676,42 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>431890</v>
+        <v>431711</v>
       </c>
       <c r="R103" t="n">
-        <v>6795199</v>
+        <v>6795094</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10770,10 +10770,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129694877</v>
+        <v>129694938</v>
       </c>
       <c r="B104" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10781,34 +10781,42 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>431887</v>
+        <v>431915</v>
       </c>
       <c r="R104" t="n">
-        <v>6795183</v>
+        <v>6795279</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10867,10 +10875,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129694885</v>
+        <v>129695000</v>
       </c>
       <c r="B105" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10878,21 +10886,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10902,10 +10910,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>431873</v>
+        <v>431890</v>
       </c>
       <c r="R105" t="n">
-        <v>6795224</v>
+        <v>6795199</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10964,10 +10972,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129694864</v>
+        <v>129694992</v>
       </c>
       <c r="B106" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10975,21 +10983,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -10999,10 +11007,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>431786</v>
+        <v>431799</v>
       </c>
       <c r="R106" t="n">
-        <v>6795113</v>
+        <v>6795129</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11061,7 +11069,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129694992</v>
+        <v>129707397</v>
       </c>
       <c r="B107" t="n">
         <v>79081</v>
@@ -11096,10 +11104,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>431799</v>
+        <v>431915</v>
       </c>
       <c r="R107" t="n">
-        <v>6795129</v>
+        <v>6795541</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11146,22 +11154,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129694927</v>
+        <v>129707327</v>
       </c>
       <c r="B108" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11169,42 +11177,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>431711</v>
+        <v>431893</v>
       </c>
       <c r="R108" t="n">
-        <v>6795094</v>
+        <v>6795305</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11251,22 +11251,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129694938</v>
+        <v>129707396</v>
       </c>
       <c r="B109" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11274,42 +11274,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>431915</v>
+        <v>431918</v>
       </c>
       <c r="R109" t="n">
-        <v>6795279</v>
+        <v>6795574</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11356,19 +11348,19 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129707397</v>
+        <v>129707406</v>
       </c>
       <c r="B110" t="n">
         <v>79081</v>
@@ -11403,10 +11395,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>431915</v>
+        <v>431771</v>
       </c>
       <c r="R110" t="n">
-        <v>6795541</v>
+        <v>6795344</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11465,10 +11457,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129707396</v>
+        <v>129707332</v>
       </c>
       <c r="B111" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11476,21 +11468,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11500,10 +11492,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>431918</v>
+        <v>431923</v>
       </c>
       <c r="R111" t="n">
-        <v>6795574</v>
+        <v>6795402</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11562,10 +11554,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129707327</v>
+        <v>129707425</v>
       </c>
       <c r="B112" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11573,21 +11565,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11597,10 +11589,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>431893</v>
+        <v>431756</v>
       </c>
       <c r="R112" t="n">
-        <v>6795305</v>
+        <v>6795247</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11659,10 +11651,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129707332</v>
+        <v>129707349</v>
       </c>
       <c r="B113" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11670,34 +11662,42 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>431923</v>
+        <v>431722</v>
       </c>
       <c r="R113" t="n">
-        <v>6795402</v>
+        <v>6795217</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11756,10 +11756,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129694901</v>
+        <v>129694990</v>
       </c>
       <c r="B114" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11767,21 +11767,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11791,10 +11791,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>431927</v>
+        <v>431726</v>
       </c>
       <c r="R114" t="n">
-        <v>6795265</v>
+        <v>6795117</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11853,10 +11853,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129694990</v>
+        <v>129694901</v>
       </c>
       <c r="B115" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11864,21 +11864,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11888,10 +11888,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>431726</v>
+        <v>431927</v>
       </c>
       <c r="R115" t="n">
-        <v>6795117</v>
+        <v>6795265</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12047,7 +12047,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129707330</v>
+        <v>129707309</v>
       </c>
       <c r="B117" t="n">
         <v>79700</v>
@@ -12082,10 +12082,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>431930</v>
+        <v>431869</v>
       </c>
       <c r="R117" t="n">
-        <v>6795399</v>
+        <v>6795521</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12144,10 +12144,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129707386</v>
+        <v>129707330</v>
       </c>
       <c r="B118" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12155,21 +12155,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12179,10 +12179,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>431897</v>
+        <v>431930</v>
       </c>
       <c r="R118" t="n">
-        <v>6795284</v>
+        <v>6795399</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12241,7 +12241,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129707309</v>
+        <v>129707323</v>
       </c>
       <c r="B119" t="n">
         <v>79700</v>
@@ -12276,10 +12276,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>431869</v>
+        <v>431712</v>
       </c>
       <c r="R119" t="n">
-        <v>6795521</v>
+        <v>6795236</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12338,10 +12338,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129707421</v>
+        <v>129707386</v>
       </c>
       <c r="B120" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12349,21 +12349,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12373,10 +12373,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>431711</v>
+        <v>431897</v>
       </c>
       <c r="R120" t="n">
-        <v>6795239</v>
+        <v>6795284</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12435,10 +12435,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129707323</v>
+        <v>129707421</v>
       </c>
       <c r="B121" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12446,21 +12446,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12470,10 +12470,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>431712</v>
+        <v>431711</v>
       </c>
       <c r="R121" t="n">
-        <v>6795236</v>
+        <v>6795239</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12532,32 +12532,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129694850</v>
+        <v>129695013</v>
       </c>
       <c r="B122" t="n">
-        <v>79700</v>
+        <v>92881</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12567,10 +12567,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>431686</v>
+        <v>431869</v>
       </c>
       <c r="R122" t="n">
-        <v>6795471</v>
+        <v>6795173</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12629,7 +12629,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129694881</v>
+        <v>129694850</v>
       </c>
       <c r="B123" t="n">
         <v>79700</v>
@@ -12664,10 +12664,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>431875</v>
+        <v>431686</v>
       </c>
       <c r="R123" t="n">
-        <v>6795212</v>
+        <v>6795471</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12726,7 +12726,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129694888</v>
+        <v>129694881</v>
       </c>
       <c r="B124" t="n">
         <v>79700</v>
@@ -12761,10 +12761,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>431889</v>
+        <v>431875</v>
       </c>
       <c r="R124" t="n">
-        <v>6795236</v>
+        <v>6795212</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12823,10 +12823,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129694997</v>
+        <v>129694888</v>
       </c>
       <c r="B125" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12834,21 +12834,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12858,10 +12858,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>431848</v>
+        <v>431889</v>
       </c>
       <c r="R125" t="n">
-        <v>6795172</v>
+        <v>6795236</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13025,10 +13025,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129707368</v>
+        <v>129694997</v>
       </c>
       <c r="B127" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13036,37 +13036,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>431820</v>
+        <v>431848</v>
       </c>
       <c r="R127" t="n">
-        <v>6795331</v>
+        <v>6795172</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13107,64 +13104,66 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129695013</v>
+        <v>129707368</v>
       </c>
       <c r="B128" t="n">
-        <v>92881</v>
+        <v>78839</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>431869</v>
+        <v>431820</v>
       </c>
       <c r="R128" t="n">
-        <v>6795173</v>
+        <v>6795331</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13205,18 +13204,19 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
@@ -13514,10 +13514,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129707387</v>
+        <v>129707399</v>
       </c>
       <c r="B132" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13525,21 +13525,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13549,10 +13549,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>431936</v>
+        <v>431819</v>
       </c>
       <c r="R132" t="n">
-        <v>6795393</v>
+        <v>6795445</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13611,10 +13611,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129707438</v>
+        <v>129707387</v>
       </c>
       <c r="B133" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13622,21 +13622,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13646,10 +13646,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>431965</v>
+        <v>431936</v>
       </c>
       <c r="R133" t="n">
-        <v>6795405</v>
+        <v>6795393</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13708,10 +13708,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129707318</v>
+        <v>129707438</v>
       </c>
       <c r="B134" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13719,21 +13719,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13743,10 +13743,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>431769</v>
+        <v>431965</v>
       </c>
       <c r="R134" t="n">
-        <v>6795345</v>
+        <v>6795405</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13805,10 +13805,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129707399</v>
+        <v>129707318</v>
       </c>
       <c r="B135" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13816,21 +13816,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13840,10 +13840,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>431819</v>
+        <v>431769</v>
       </c>
       <c r="R135" t="n">
-        <v>6795445</v>
+        <v>6795345</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -13902,10 +13902,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129694866</v>
+        <v>129694956</v>
       </c>
       <c r="B136" t="n">
-        <v>79700</v>
+        <v>92017</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13913,34 +13913,33 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>431797</v>
+        <v>431718</v>
       </c>
       <c r="R136" t="n">
-        <v>6795173</v>
+        <v>6795082</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -13975,12 +13974,18 @@
           <t>2025-11-14</t>
         </is>
       </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Mjuk och len på undetsidan, sämskskinnslik känsla</t>
+        </is>
+      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -13999,7 +14004,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129694865</v>
+        <v>129707334</v>
       </c>
       <c r="B137" t="n">
         <v>79700</v>
@@ -14034,10 +14039,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>431787</v>
+        <v>431936</v>
       </c>
       <c r="R137" t="n">
-        <v>6795115</v>
+        <v>6795411</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14084,22 +14089,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129694896</v>
+        <v>129707370</v>
       </c>
       <c r="B138" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14107,21 +14112,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14131,10 +14136,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>431900</v>
+        <v>431913</v>
       </c>
       <c r="R138" t="n">
-        <v>6795265</v>
+        <v>6795394</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14181,19 +14186,19 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129707334</v>
+        <v>129694866</v>
       </c>
       <c r="B139" t="n">
         <v>79700</v>
@@ -14228,10 +14233,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>431936</v>
+        <v>431797</v>
       </c>
       <c r="R139" t="n">
-        <v>6795411</v>
+        <v>6795173</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14278,22 +14283,22 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129694956</v>
+        <v>129694865</v>
       </c>
       <c r="B140" t="n">
-        <v>92017</v>
+        <v>79700</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14301,33 +14306,34 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6040162</v>
+        <v>6453</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>431718</v>
+        <v>431787</v>
       </c>
       <c r="R140" t="n">
-        <v>6795082</v>
+        <v>6795115</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14362,18 +14368,12 @@
           <t>2025-11-14</t>
         </is>
       </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Mjuk och len på undetsidan, sämskskinnslik känsla</t>
-        </is>
-      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -14392,10 +14392,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129707370</v>
+        <v>129694896</v>
       </c>
       <c r="B141" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14403,21 +14403,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14427,10 +14427,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>431913</v>
+        <v>431900</v>
       </c>
       <c r="R141" t="n">
-        <v>6795394</v>
+        <v>6795265</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14477,22 +14477,22 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129694876</v>
+        <v>129707377</v>
       </c>
       <c r="B142" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14500,21 +14500,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14524,10 +14524,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>431871</v>
+        <v>431843</v>
       </c>
       <c r="R142" t="n">
-        <v>6795171</v>
+        <v>6795474</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14574,22 +14574,22 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129694887</v>
+        <v>129707366</v>
       </c>
       <c r="B143" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14597,21 +14597,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14621,10 +14621,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>431886</v>
+        <v>431840</v>
       </c>
       <c r="R143" t="n">
-        <v>6795236</v>
+        <v>6795476</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14671,19 +14671,19 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129694880</v>
+        <v>129694876</v>
       </c>
       <c r="B144" t="n">
         <v>79700</v>
@@ -14721,7 +14721,7 @@
         <v>431871</v>
       </c>
       <c r="R144" t="n">
-        <v>6795205</v>
+        <v>6795171</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14780,7 +14780,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129694897</v>
+        <v>129694887</v>
       </c>
       <c r="B145" t="n">
         <v>79700</v>
@@ -14815,10 +14815,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>431906</v>
+        <v>431886</v>
       </c>
       <c r="R145" t="n">
-        <v>6795283</v>
+        <v>6795236</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -14877,10 +14877,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129707377</v>
+        <v>129694880</v>
       </c>
       <c r="B146" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14888,21 +14888,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -14912,10 +14912,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>431843</v>
+        <v>431871</v>
       </c>
       <c r="R146" t="n">
-        <v>6795474</v>
+        <v>6795205</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -14962,22 +14962,22 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129707366</v>
+        <v>129694897</v>
       </c>
       <c r="B147" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14985,21 +14985,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15009,10 +15009,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>431840</v>
+        <v>431906</v>
       </c>
       <c r="R147" t="n">
-        <v>6795476</v>
+        <v>6795283</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15059,12 +15059,12 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>

--- a/artfynd/A 50492-2025 artfynd.xlsx
+++ b/artfynd/A 50492-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129694957</v>
+        <v>129694935</v>
       </c>
       <c r="B4" t="n">
-        <v>78838</v>
+        <v>57733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,34 +880,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>431725</v>
+        <v>431917</v>
       </c>
       <c r="R4" t="n">
-        <v>6795459</v>
+        <v>6795290</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,45 +974,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129707440</v>
+        <v>129694929</v>
       </c>
       <c r="B5" t="n">
-        <v>92881</v>
+        <v>57733</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>431828</v>
+        <v>431859</v>
       </c>
       <c r="R5" t="n">
-        <v>6795476</v>
+        <v>6795172</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,22 +1067,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129694935</v>
+        <v>129694957</v>
       </c>
       <c r="B6" t="n">
-        <v>57733</v>
+        <v>78838</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,42 +1090,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>431917</v>
+        <v>431725</v>
       </c>
       <c r="R6" t="n">
-        <v>6795290</v>
+        <v>6795459</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,53 +1176,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129694929</v>
+        <v>129707440</v>
       </c>
       <c r="B7" t="n">
-        <v>57733</v>
+        <v>92881</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>431859</v>
+        <v>431828</v>
       </c>
       <c r="R7" t="n">
-        <v>6795172</v>
+        <v>6795476</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,12 +1261,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -2378,45 +2378,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129694845</v>
+        <v>129694913</v>
       </c>
       <c r="B19" t="n">
-        <v>79700</v>
+        <v>56926</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>431722</v>
+        <v>431728</v>
       </c>
       <c r="R19" t="n">
-        <v>6795478</v>
+        <v>6795109</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2766,53 +2774,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129694913</v>
+        <v>129694845</v>
       </c>
       <c r="B23" t="n">
-        <v>56926</v>
+        <v>79700</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>431728</v>
+        <v>431722</v>
       </c>
       <c r="R23" t="n">
-        <v>6795109</v>
+        <v>6795478</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3749,45 +3749,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129695010</v>
+        <v>129707390</v>
       </c>
       <c r="B33" t="n">
-        <v>92881</v>
+        <v>78838</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>431880</v>
+        <v>431952</v>
       </c>
       <c r="R33" t="n">
-        <v>6795546</v>
+        <v>6795410</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3828,28 +3831,29 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129694839</v>
+        <v>129707346</v>
       </c>
       <c r="B34" t="n">
-        <v>91522</v>
+        <v>57733</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3857,26 +3861,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3242</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -3884,10 +3893,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>431869</v>
+        <v>431819</v>
       </c>
       <c r="R34" t="n">
-        <v>6795181</v>
+        <v>6795465</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3928,51 +3937,50 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129694980</v>
+        <v>129695010</v>
       </c>
       <c r="B35" t="n">
-        <v>79081</v>
+        <v>92881</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3982,10 +3990,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>431711</v>
+        <v>431880</v>
       </c>
       <c r="R35" t="n">
-        <v>6795450</v>
+        <v>6795546</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4149,10 +4157,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129694886</v>
+        <v>129694839</v>
       </c>
       <c r="B37" t="n">
-        <v>79700</v>
+        <v>91522</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4160,34 +4168,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>3242</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>431873</v>
+        <v>431869</v>
       </c>
       <c r="R37" t="n">
-        <v>6795241</v>
+        <v>6795181</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4228,6 +4239,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4246,10 +4258,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129694878</v>
+        <v>129694980</v>
       </c>
       <c r="B38" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4257,21 +4269,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4281,10 +4293,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>431889</v>
+        <v>431711</v>
       </c>
       <c r="R38" t="n">
-        <v>6795186</v>
+        <v>6795450</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4343,10 +4355,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129694921</v>
+        <v>129694886</v>
       </c>
       <c r="B39" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4354,42 +4366,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>431725</v>
+        <v>431873</v>
       </c>
       <c r="R39" t="n">
-        <v>6795459</v>
+        <v>6795241</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4448,10 +4452,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129707390</v>
+        <v>129694878</v>
       </c>
       <c r="B40" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4459,37 +4463,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>431952</v>
+        <v>431889</v>
       </c>
       <c r="R40" t="n">
-        <v>6795410</v>
+        <v>6795186</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4530,26 +4531,25 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129707346</v>
+        <v>129694921</v>
       </c>
       <c r="B41" t="n">
         <v>57733</v>
@@ -4592,10 +4592,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>431819</v>
+        <v>431725</v>
       </c>
       <c r="R41" t="n">
-        <v>6795465</v>
+        <v>6795459</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4642,22 +4642,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129694999</v>
+        <v>129694847</v>
       </c>
       <c r="B42" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4665,21 +4665,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>431859</v>
+        <v>431724</v>
       </c>
       <c r="R42" t="n">
-        <v>6795172</v>
+        <v>6795460</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4751,7 +4751,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129694847</v>
+        <v>129707320</v>
       </c>
       <c r="B43" t="n">
         <v>79700</v>
@@ -4786,10 +4786,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>431724</v>
+        <v>431717</v>
       </c>
       <c r="R43" t="n">
-        <v>6795460</v>
+        <v>6795380</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4836,22 +4836,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129694926</v>
+        <v>129707316</v>
       </c>
       <c r="B44" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4859,42 +4859,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>431711</v>
+        <v>431812</v>
       </c>
       <c r="R44" t="n">
-        <v>6795100</v>
+        <v>6795349</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4941,19 +4933,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129707320</v>
+        <v>129707333</v>
       </c>
       <c r="B45" t="n">
         <v>79700</v>
@@ -4988,10 +4980,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>431717</v>
+        <v>431935</v>
       </c>
       <c r="R45" t="n">
-        <v>6795380</v>
+        <v>6795415</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5050,7 +5042,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129707316</v>
+        <v>129707338</v>
       </c>
       <c r="B46" t="n">
         <v>79700</v>
@@ -5085,10 +5077,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>431812</v>
+        <v>431932</v>
       </c>
       <c r="R46" t="n">
-        <v>6795349</v>
+        <v>6795406</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5147,10 +5139,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129707333</v>
+        <v>129707375</v>
       </c>
       <c r="B47" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5158,21 +5150,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5182,10 +5174,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>431935</v>
+        <v>431881</v>
       </c>
       <c r="R47" t="n">
-        <v>6795415</v>
+        <v>6795522</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5244,10 +5236,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129707338</v>
+        <v>129694999</v>
       </c>
       <c r="B48" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5255,21 +5247,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5279,10 +5271,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>431932</v>
+        <v>431859</v>
       </c>
       <c r="R48" t="n">
-        <v>6795406</v>
+        <v>6795172</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5329,22 +5321,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129707375</v>
+        <v>129694926</v>
       </c>
       <c r="B49" t="n">
-        <v>78838</v>
+        <v>57733</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5352,34 +5344,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>431881</v>
+        <v>431711</v>
       </c>
       <c r="R49" t="n">
-        <v>6795522</v>
+        <v>6795100</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5426,12 +5426,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -7811,10 +7811,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129707317</v>
+        <v>129694985</v>
       </c>
       <c r="B74" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7822,21 +7822,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7846,10 +7846,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>431780</v>
+        <v>431673</v>
       </c>
       <c r="R74" t="n">
-        <v>6795362</v>
+        <v>6795435</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7896,44 +7896,44 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129707391</v>
+        <v>129707439</v>
       </c>
       <c r="B75" t="n">
-        <v>78838</v>
+        <v>92881</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7943,10 +7943,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>431724</v>
+        <v>431891</v>
       </c>
       <c r="R75" t="n">
-        <v>6795372</v>
+        <v>6795553</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8005,10 +8005,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129707389</v>
+        <v>129707317</v>
       </c>
       <c r="B76" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8016,37 +8016,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>431922</v>
+        <v>431780</v>
       </c>
       <c r="R76" t="n">
-        <v>6795405</v>
+        <v>6795362</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8087,7 +8084,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8106,10 +8102,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129707314</v>
+        <v>129707391</v>
       </c>
       <c r="B77" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8117,21 +8113,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8141,10 +8137,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>431866</v>
+        <v>431724</v>
       </c>
       <c r="R77" t="n">
-        <v>6795513</v>
+        <v>6795372</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8203,10 +8199,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129694985</v>
+        <v>129707389</v>
       </c>
       <c r="B78" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8214,34 +8210,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>431673</v>
+        <v>431922</v>
       </c>
       <c r="R78" t="n">
-        <v>6795435</v>
+        <v>6795405</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8282,50 +8281,51 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129707439</v>
+        <v>129707314</v>
       </c>
       <c r="B79" t="n">
-        <v>92881</v>
+        <v>79700</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8335,10 +8335,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>431891</v>
+        <v>431866</v>
       </c>
       <c r="R79" t="n">
-        <v>6795553</v>
+        <v>6795513</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10374,10 +10374,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129694877</v>
+        <v>129694992</v>
       </c>
       <c r="B100" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10385,21 +10385,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10409,10 +10409,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>431887</v>
+        <v>431799</v>
       </c>
       <c r="R100" t="n">
-        <v>6795183</v>
+        <v>6795129</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10471,7 +10471,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129694885</v>
+        <v>129694877</v>
       </c>
       <c r="B101" t="n">
         <v>79700</v>
@@ -10506,10 +10506,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>431873</v>
+        <v>431887</v>
       </c>
       <c r="R101" t="n">
-        <v>6795224</v>
+        <v>6795183</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10568,7 +10568,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129694864</v>
+        <v>129694885</v>
       </c>
       <c r="B102" t="n">
         <v>79700</v>
@@ -10603,10 +10603,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>431786</v>
+        <v>431873</v>
       </c>
       <c r="R102" t="n">
-        <v>6795113</v>
+        <v>6795224</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10665,10 +10665,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129694927</v>
+        <v>129694864</v>
       </c>
       <c r="B103" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10676,42 +10676,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>431711</v>
+        <v>431786</v>
       </c>
       <c r="R103" t="n">
-        <v>6795094</v>
+        <v>6795113</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10770,10 +10762,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129694938</v>
+        <v>129695000</v>
       </c>
       <c r="B104" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10781,42 +10773,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>431915</v>
+        <v>431890</v>
       </c>
       <c r="R104" t="n">
-        <v>6795279</v>
+        <v>6795199</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10875,10 +10859,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129695000</v>
+        <v>129694927</v>
       </c>
       <c r="B105" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10886,34 +10870,42 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>431890</v>
+        <v>431711</v>
       </c>
       <c r="R105" t="n">
-        <v>6795199</v>
+        <v>6795094</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10972,10 +10964,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129694992</v>
+        <v>129694938</v>
       </c>
       <c r="B106" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10983,34 +10975,42 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>431799</v>
+        <v>431915</v>
       </c>
       <c r="R106" t="n">
-        <v>6795129</v>
+        <v>6795279</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11069,10 +11069,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129707397</v>
+        <v>129707349</v>
       </c>
       <c r="B107" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11080,34 +11080,42 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>431915</v>
+        <v>431722</v>
       </c>
       <c r="R107" t="n">
-        <v>6795541</v>
+        <v>6795217</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11166,10 +11174,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129707327</v>
+        <v>129707397</v>
       </c>
       <c r="B108" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11177,21 +11185,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11201,10 +11209,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>431893</v>
+        <v>431915</v>
       </c>
       <c r="R108" t="n">
-        <v>6795305</v>
+        <v>6795541</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11263,10 +11271,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129707396</v>
+        <v>129707327</v>
       </c>
       <c r="B109" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11274,21 +11282,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11298,10 +11306,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>431918</v>
+        <v>431893</v>
       </c>
       <c r="R109" t="n">
-        <v>6795574</v>
+        <v>6795305</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11360,7 +11368,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129707406</v>
+        <v>129707396</v>
       </c>
       <c r="B110" t="n">
         <v>79081</v>
@@ -11395,10 +11403,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>431771</v>
+        <v>431918</v>
       </c>
       <c r="R110" t="n">
-        <v>6795344</v>
+        <v>6795574</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11457,10 +11465,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129707332</v>
+        <v>129707406</v>
       </c>
       <c r="B111" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11468,21 +11476,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11492,10 +11500,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>431923</v>
+        <v>431771</v>
       </c>
       <c r="R111" t="n">
-        <v>6795402</v>
+        <v>6795344</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11554,10 +11562,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129707425</v>
+        <v>129707332</v>
       </c>
       <c r="B112" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11565,21 +11573,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11589,10 +11597,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>431756</v>
+        <v>431923</v>
       </c>
       <c r="R112" t="n">
-        <v>6795247</v>
+        <v>6795402</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11651,10 +11659,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129707349</v>
+        <v>129707425</v>
       </c>
       <c r="B113" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11662,42 +11670,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>431722</v>
+        <v>431756</v>
       </c>
       <c r="R113" t="n">
-        <v>6795217</v>
+        <v>6795247</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>

--- a/artfynd/A 50492-2025 artfynd.xlsx
+++ b/artfynd/A 50492-2025 artfynd.xlsx
@@ -2378,53 +2378,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129694913</v>
+        <v>129694845</v>
       </c>
       <c r="B19" t="n">
-        <v>56926</v>
+        <v>79700</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>431728</v>
+        <v>431722</v>
       </c>
       <c r="R19" t="n">
-        <v>6795109</v>
+        <v>6795478</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2774,45 +2766,53 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129694845</v>
+        <v>129694913</v>
       </c>
       <c r="B23" t="n">
-        <v>79700</v>
+        <v>56926</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>431722</v>
+        <v>431728</v>
       </c>
       <c r="R23" t="n">
-        <v>6795478</v>
+        <v>6795109</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3749,10 +3749,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129707390</v>
+        <v>129707346</v>
       </c>
       <c r="B33" t="n">
-        <v>78838</v>
+        <v>57733</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3760,26 +3760,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3787,10 +3792,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>431952</v>
+        <v>431819</v>
       </c>
       <c r="R33" t="n">
-        <v>6795410</v>
+        <v>6795465</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3831,7 +3836,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3850,10 +3854,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129707346</v>
+        <v>129707390</v>
       </c>
       <c r="B34" t="n">
-        <v>57733</v>
+        <v>78838</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3861,31 +3865,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -3893,10 +3892,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>431819</v>
+        <v>431952</v>
       </c>
       <c r="R34" t="n">
-        <v>6795465</v>
+        <v>6795410</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3937,6 +3936,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4052,10 +4052,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129694917</v>
+        <v>129694839</v>
       </c>
       <c r="B36" t="n">
-        <v>91620</v>
+        <v>91522</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4063,28 +4063,24 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5442</v>
+        <v>3242</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
@@ -4094,10 +4090,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>431672</v>
+        <v>431869</v>
       </c>
       <c r="R36" t="n">
-        <v>6795442</v>
+        <v>6795181</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4157,10 +4153,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129694839</v>
+        <v>129694980</v>
       </c>
       <c r="B37" t="n">
-        <v>91522</v>
+        <v>79081</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4168,37 +4164,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3242</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>431869</v>
+        <v>431711</v>
       </c>
       <c r="R37" t="n">
-        <v>6795181</v>
+        <v>6795450</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4239,7 +4232,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4258,10 +4250,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129694980</v>
+        <v>129694917</v>
       </c>
       <c r="B38" t="n">
-        <v>79081</v>
+        <v>91620</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4269,34 +4261,41 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>431711</v>
+        <v>431672</v>
       </c>
       <c r="R38" t="n">
-        <v>6795450</v>
+        <v>6795442</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4337,6 +4336,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4654,10 +4654,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129694847</v>
+        <v>129694999</v>
       </c>
       <c r="B42" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4665,21 +4665,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>431724</v>
+        <v>431859</v>
       </c>
       <c r="R42" t="n">
-        <v>6795460</v>
+        <v>6795172</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4751,7 +4751,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129707320</v>
+        <v>129694847</v>
       </c>
       <c r="B43" t="n">
         <v>79700</v>
@@ -4786,10 +4786,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>431717</v>
+        <v>431724</v>
       </c>
       <c r="R43" t="n">
-        <v>6795380</v>
+        <v>6795460</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4836,22 +4836,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129707316</v>
+        <v>129694926</v>
       </c>
       <c r="B44" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4859,34 +4859,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>431812</v>
+        <v>431711</v>
       </c>
       <c r="R44" t="n">
-        <v>6795349</v>
+        <v>6795100</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4933,19 +4941,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129707333</v>
+        <v>129707320</v>
       </c>
       <c r="B45" t="n">
         <v>79700</v>
@@ -4980,10 +4988,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>431935</v>
+        <v>431717</v>
       </c>
       <c r="R45" t="n">
-        <v>6795415</v>
+        <v>6795380</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5042,7 +5050,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129707338</v>
+        <v>129707316</v>
       </c>
       <c r="B46" t="n">
         <v>79700</v>
@@ -5077,10 +5085,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>431932</v>
+        <v>431812</v>
       </c>
       <c r="R46" t="n">
-        <v>6795406</v>
+        <v>6795349</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5139,10 +5147,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129707375</v>
+        <v>129707333</v>
       </c>
       <c r="B47" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5150,21 +5158,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5174,10 +5182,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>431881</v>
+        <v>431935</v>
       </c>
       <c r="R47" t="n">
-        <v>6795522</v>
+        <v>6795415</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5236,10 +5244,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129694999</v>
+        <v>129707338</v>
       </c>
       <c r="B48" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5247,21 +5255,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5271,10 +5279,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>431859</v>
+        <v>431932</v>
       </c>
       <c r="R48" t="n">
-        <v>6795172</v>
+        <v>6795406</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5321,22 +5329,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129694926</v>
+        <v>129707375</v>
       </c>
       <c r="B49" t="n">
-        <v>57733</v>
+        <v>78838</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5344,42 +5352,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>431711</v>
+        <v>431881</v>
       </c>
       <c r="R49" t="n">
-        <v>6795100</v>
+        <v>6795522</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5426,12 +5426,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5543,10 +5543,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129694846</v>
+        <v>129695006</v>
       </c>
       <c r="B51" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5554,21 +5554,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5578,10 +5578,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>431725</v>
+        <v>431962</v>
       </c>
       <c r="R51" t="n">
-        <v>6795467</v>
+        <v>6795319</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5640,10 +5640,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129707347</v>
+        <v>129695003</v>
       </c>
       <c r="B52" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5651,42 +5651,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>431662</v>
+        <v>431908</v>
       </c>
       <c r="R52" t="n">
-        <v>6795391</v>
+        <v>6795302</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5733,22 +5725,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129694994</v>
+        <v>129707337</v>
       </c>
       <c r="B53" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5756,21 +5748,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5780,10 +5772,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>431804</v>
+        <v>431999</v>
       </c>
       <c r="R53" t="n">
-        <v>6795151</v>
+        <v>6795416</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5830,19 +5822,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129695006</v>
+        <v>129707426</v>
       </c>
       <c r="B54" t="n">
         <v>79081</v>
@@ -5877,10 +5869,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>431962</v>
+        <v>431767</v>
       </c>
       <c r="R54" t="n">
-        <v>6795319</v>
+        <v>6795219</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5927,19 +5919,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129695003</v>
+        <v>129707404</v>
       </c>
       <c r="B55" t="n">
         <v>79081</v>
@@ -5968,16 +5960,19 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>431908</v>
+        <v>431816</v>
       </c>
       <c r="R55" t="n">
-        <v>6795302</v>
+        <v>6795333</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6012,34 +6007,40 @@
           <t>2025-11-14</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129707337</v>
+        <v>129707380</v>
       </c>
       <c r="B56" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6047,21 +6048,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6071,10 +6072,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>431999</v>
+        <v>431820</v>
       </c>
       <c r="R56" t="n">
-        <v>6795416</v>
+        <v>6795330</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6133,10 +6134,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129707426</v>
+        <v>129707347</v>
       </c>
       <c r="B57" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6144,34 +6145,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>431767</v>
+        <v>431662</v>
       </c>
       <c r="R57" t="n">
-        <v>6795219</v>
+        <v>6795391</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6230,10 +6239,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129707404</v>
+        <v>129694846</v>
       </c>
       <c r="B58" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6241,37 +6250,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>431816</v>
+        <v>431725</v>
       </c>
       <c r="R58" t="n">
-        <v>6795333</v>
+        <v>6795467</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6306,40 +6312,34 @@
           <t>2025-11-14</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129707380</v>
+        <v>129694994</v>
       </c>
       <c r="B59" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6347,21 +6347,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>431820</v>
+        <v>431804</v>
       </c>
       <c r="R59" t="n">
-        <v>6795330</v>
+        <v>6795151</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6421,22 +6421,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129694988</v>
+        <v>129694872</v>
       </c>
       <c r="B60" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6444,21 +6444,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6468,10 +6468,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>431718</v>
+        <v>431833</v>
       </c>
       <c r="R60" t="n">
-        <v>6795068</v>
+        <v>6795171</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6530,10 +6530,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129694961</v>
+        <v>129694856</v>
       </c>
       <c r="B61" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6541,21 +6541,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6565,10 +6565,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>431804</v>
+        <v>431693</v>
       </c>
       <c r="R61" t="n">
-        <v>6795100</v>
+        <v>6795052</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6627,10 +6627,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129707319</v>
+        <v>129694988</v>
       </c>
       <c r="B62" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6638,21 +6638,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6662,10 +6662,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>431708</v>
+        <v>431718</v>
       </c>
       <c r="R62" t="n">
-        <v>6795371</v>
+        <v>6795068</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6712,22 +6712,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129694872</v>
+        <v>129694930</v>
       </c>
       <c r="B63" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6735,34 +6735,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>431833</v>
+        <v>431875</v>
       </c>
       <c r="R63" t="n">
-        <v>6795171</v>
+        <v>6795244</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6821,10 +6829,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129694856</v>
+        <v>129694961</v>
       </c>
       <c r="B64" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6832,21 +6840,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6856,10 +6864,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>431693</v>
+        <v>431804</v>
       </c>
       <c r="R64" t="n">
-        <v>6795052</v>
+        <v>6795100</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6918,10 +6926,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129694930</v>
+        <v>129707319</v>
       </c>
       <c r="B65" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6929,42 +6937,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>431875</v>
+        <v>431708</v>
       </c>
       <c r="R65" t="n">
-        <v>6795244</v>
+        <v>6795371</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7011,12 +7011,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7811,10 +7811,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129694985</v>
+        <v>129707317</v>
       </c>
       <c r="B74" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7822,21 +7822,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7846,10 +7846,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>431673</v>
+        <v>431780</v>
       </c>
       <c r="R74" t="n">
-        <v>6795435</v>
+        <v>6795362</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7896,44 +7896,44 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129707439</v>
+        <v>129707391</v>
       </c>
       <c r="B75" t="n">
-        <v>92881</v>
+        <v>78838</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7943,10 +7943,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>431891</v>
+        <v>431724</v>
       </c>
       <c r="R75" t="n">
-        <v>6795553</v>
+        <v>6795372</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8005,10 +8005,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129707317</v>
+        <v>129707389</v>
       </c>
       <c r="B76" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8016,34 +8016,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>431780</v>
+        <v>431922</v>
       </c>
       <c r="R76" t="n">
-        <v>6795362</v>
+        <v>6795405</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8084,6 +8087,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8102,10 +8106,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129707391</v>
+        <v>129707314</v>
       </c>
       <c r="B77" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8113,21 +8117,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8137,10 +8141,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>431724</v>
+        <v>431866</v>
       </c>
       <c r="R77" t="n">
-        <v>6795372</v>
+        <v>6795513</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8199,10 +8203,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129707389</v>
+        <v>129694985</v>
       </c>
       <c r="B78" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8210,37 +8214,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>431922</v>
+        <v>431673</v>
       </c>
       <c r="R78" t="n">
-        <v>6795405</v>
+        <v>6795435</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8281,51 +8282,50 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129707314</v>
+        <v>129707439</v>
       </c>
       <c r="B79" t="n">
-        <v>79700</v>
+        <v>92881</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8335,10 +8335,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>431866</v>
+        <v>431891</v>
       </c>
       <c r="R79" t="n">
-        <v>6795513</v>
+        <v>6795553</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9383,10 +9383,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129694934</v>
+        <v>129694860</v>
       </c>
       <c r="B90" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9394,42 +9394,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>431916</v>
+        <v>431746</v>
       </c>
       <c r="R90" t="n">
-        <v>6795286</v>
+        <v>6795081</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9488,10 +9480,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129707405</v>
+        <v>129694939</v>
       </c>
       <c r="B91" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9499,21 +9491,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9523,10 +9515,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>431775</v>
+        <v>431913</v>
       </c>
       <c r="R91" t="n">
-        <v>6795343</v>
+        <v>6795284</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9561,6 +9553,11 @@
           <t>2025-11-14</t>
         </is>
       </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
@@ -9573,19 +9570,19 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129707381</v>
+        <v>129694965</v>
       </c>
       <c r="B92" t="n">
         <v>78838</v>
@@ -9620,10 +9617,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>431712</v>
+        <v>431885</v>
       </c>
       <c r="R92" t="n">
-        <v>6795379</v>
+        <v>6795240</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9670,22 +9667,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129694860</v>
+        <v>129694934</v>
       </c>
       <c r="B93" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9693,34 +9690,42 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>431746</v>
+        <v>431916</v>
       </c>
       <c r="R93" t="n">
-        <v>6795081</v>
+        <v>6795286</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9779,10 +9784,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129694939</v>
+        <v>129707405</v>
       </c>
       <c r="B94" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9790,21 +9795,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9814,10 +9819,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>431913</v>
+        <v>431775</v>
       </c>
       <c r="R94" t="n">
-        <v>6795284</v>
+        <v>6795343</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9852,11 +9857,6 @@
           <t>2025-11-14</t>
         </is>
       </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
-        </is>
-      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
@@ -9869,19 +9869,19 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129694965</v>
+        <v>129707381</v>
       </c>
       <c r="B95" t="n">
         <v>78838</v>
@@ -9916,10 +9916,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>431885</v>
+        <v>431712</v>
       </c>
       <c r="R95" t="n">
-        <v>6795240</v>
+        <v>6795379</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9966,44 +9966,44 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129694941</v>
+        <v>129707312</v>
       </c>
       <c r="B96" t="n">
-        <v>79167</v>
+        <v>79700</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6450</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10013,10 +10013,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>431976</v>
+        <v>431920</v>
       </c>
       <c r="R96" t="n">
-        <v>6795333</v>
+        <v>6795611</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10063,65 +10063,57 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129694977</v>
+        <v>129694941</v>
       </c>
       <c r="B97" t="n">
-        <v>57733</v>
+        <v>79167</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100049</v>
+        <v>6450</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>431933</v>
+        <v>431976</v>
       </c>
       <c r="R97" t="n">
-        <v>6795295</v>
+        <v>6795333</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10277,10 +10269,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129707312</v>
+        <v>129694977</v>
       </c>
       <c r="B99" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10288,34 +10280,42 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>431920</v>
+        <v>431933</v>
       </c>
       <c r="R99" t="n">
-        <v>6795611</v>
+        <v>6795295</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10362,12 +10362,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
@@ -13902,10 +13902,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129694956</v>
+        <v>129694866</v>
       </c>
       <c r="B136" t="n">
-        <v>92017</v>
+        <v>79700</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13913,33 +13913,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6040162</v>
+        <v>6453</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>431718</v>
+        <v>431797</v>
       </c>
       <c r="R136" t="n">
-        <v>6795082</v>
+        <v>6795173</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -13974,18 +13975,12 @@
           <t>2025-11-14</t>
         </is>
       </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Mjuk och len på undetsidan, sämskskinnslik känsla</t>
-        </is>
-      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -14004,7 +13999,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129707334</v>
+        <v>129694865</v>
       </c>
       <c r="B137" t="n">
         <v>79700</v>
@@ -14039,10 +14034,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>431936</v>
+        <v>431787</v>
       </c>
       <c r="R137" t="n">
-        <v>6795411</v>
+        <v>6795115</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14089,22 +14084,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129707370</v>
+        <v>129694896</v>
       </c>
       <c r="B138" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14112,21 +14107,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14136,10 +14131,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>431913</v>
+        <v>431900</v>
       </c>
       <c r="R138" t="n">
-        <v>6795394</v>
+        <v>6795265</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14186,22 +14181,22 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129694866</v>
+        <v>129694956</v>
       </c>
       <c r="B139" t="n">
-        <v>79700</v>
+        <v>92017</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14209,34 +14204,33 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>431797</v>
+        <v>431718</v>
       </c>
       <c r="R139" t="n">
-        <v>6795173</v>
+        <v>6795082</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14271,12 +14265,18 @@
           <t>2025-11-14</t>
         </is>
       </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Mjuk och len på undetsidan, sämskskinnslik känsla</t>
+        </is>
+      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -14295,7 +14295,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129694865</v>
+        <v>129707334</v>
       </c>
       <c r="B140" t="n">
         <v>79700</v>
@@ -14330,10 +14330,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>431787</v>
+        <v>431936</v>
       </c>
       <c r="R140" t="n">
-        <v>6795115</v>
+        <v>6795411</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14380,22 +14380,22 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129694896</v>
+        <v>129707370</v>
       </c>
       <c r="B141" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14403,21 +14403,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14427,10 +14427,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>431900</v>
+        <v>431913</v>
       </c>
       <c r="R141" t="n">
-        <v>6795265</v>
+        <v>6795394</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14477,12 +14477,12 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>

--- a/artfynd/A 50492-2025 artfynd.xlsx
+++ b/artfynd/A 50492-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129694842</v>
+        <v>129694935</v>
       </c>
       <c r="B2" t="n">
-        <v>79700</v>
+        <v>57734</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>431768</v>
+        <v>431917</v>
       </c>
       <c r="R2" t="n">
-        <v>6795469</v>
+        <v>6795290</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129694862</v>
+        <v>129694929</v>
       </c>
       <c r="B3" t="n">
-        <v>79700</v>
+        <v>57734</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +791,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>431756</v>
+        <v>431859</v>
       </c>
       <c r="R3" t="n">
-        <v>6795121</v>
+        <v>6795172</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129694935</v>
+        <v>129694842</v>
       </c>
       <c r="B4" t="n">
-        <v>57733</v>
+        <v>79703</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,42 +896,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>431917</v>
+        <v>431768</v>
       </c>
       <c r="R4" t="n">
-        <v>6795290</v>
+        <v>6795469</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,10 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129694929</v>
+        <v>129694957</v>
       </c>
       <c r="B5" t="n">
-        <v>57733</v>
+        <v>78841</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,42 +993,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>431859</v>
+        <v>431725</v>
       </c>
       <c r="R5" t="n">
-        <v>6795172</v>
+        <v>6795459</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129694957</v>
+        <v>129694862</v>
       </c>
       <c r="B6" t="n">
-        <v>78838</v>
+        <v>79703</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>431725</v>
+        <v>431756</v>
       </c>
       <c r="R6" t="n">
-        <v>6795459</v>
+        <v>6795121</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,45 +1176,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129707440</v>
+        <v>129707216</v>
       </c>
       <c r="B7" t="n">
-        <v>92881</v>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>431828</v>
+        <v>432007</v>
       </c>
       <c r="R7" t="n">
-        <v>6795476</v>
+        <v>6795475</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,6 +1258,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1273,48 +1277,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129707216</v>
+        <v>129707440</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>92884</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>432007</v>
+        <v>431828</v>
       </c>
       <c r="R8" t="n">
-        <v>6795475</v>
+        <v>6795476</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1355,7 +1356,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1377,7 +1377,7 @@
         <v>129707403</v>
       </c>
       <c r="B9" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,10 +1578,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129694923</v>
+        <v>129694918</v>
       </c>
       <c r="B11" t="n">
-        <v>57733</v>
+        <v>91623</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1589,31 +1589,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1621,10 +1620,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>431687</v>
+        <v>431722</v>
       </c>
       <c r="R11" t="n">
-        <v>6795471</v>
+        <v>6795120</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1665,6 +1664,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1683,10 +1683,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129707336</v>
+        <v>129694923</v>
       </c>
       <c r="B12" t="n">
-        <v>79700</v>
+        <v>57734</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1694,34 +1694,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>431993</v>
+        <v>431687</v>
       </c>
       <c r="R12" t="n">
-        <v>6795380</v>
+        <v>6795471</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1768,22 +1776,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129707434</v>
+        <v>129694843</v>
       </c>
       <c r="B13" t="n">
-        <v>79081</v>
+        <v>79703</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1791,21 +1799,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1815,10 +1823,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>431894</v>
+        <v>431752</v>
       </c>
       <c r="R13" t="n">
-        <v>6795261</v>
+        <v>6795429</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1865,22 +1873,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129707358</v>
+        <v>129694983</v>
       </c>
       <c r="B14" t="n">
-        <v>57733</v>
+        <v>79084</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1888,42 +1896,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>431912</v>
+        <v>431689</v>
       </c>
       <c r="R14" t="n">
-        <v>6795310</v>
+        <v>6795456</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1970,22 +1970,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129694983</v>
+        <v>129694907</v>
       </c>
       <c r="B15" t="n">
-        <v>79081</v>
+        <v>79703</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1993,21 +1993,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>431689</v>
+        <v>431938</v>
       </c>
       <c r="R15" t="n">
-        <v>6795456</v>
+        <v>6795278</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2079,10 +2079,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129694918</v>
+        <v>129707434</v>
       </c>
       <c r="B16" t="n">
-        <v>91620</v>
+        <v>79084</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2090,41 +2090,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>431722</v>
+        <v>431894</v>
       </c>
       <c r="R16" t="n">
-        <v>6795120</v>
+        <v>6795261</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2165,29 +2158,28 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129694843</v>
+        <v>129707336</v>
       </c>
       <c r="B17" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2219,10 +2211,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>431752</v>
+        <v>431993</v>
       </c>
       <c r="R17" t="n">
-        <v>6795429</v>
+        <v>6795380</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2269,22 +2261,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129694907</v>
+        <v>129707358</v>
       </c>
       <c r="B18" t="n">
-        <v>79700</v>
+        <v>57734</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2292,34 +2284,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>431938</v>
+        <v>431912</v>
       </c>
       <c r="R18" t="n">
-        <v>6795278</v>
+        <v>6795310</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2366,57 +2366,65 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129694845</v>
+        <v>129694913</v>
       </c>
       <c r="B19" t="n">
-        <v>79700</v>
+        <v>56927</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>431722</v>
+        <v>431728</v>
       </c>
       <c r="R19" t="n">
-        <v>6795478</v>
+        <v>6795109</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2478,7 +2486,7 @@
         <v>129707378</v>
       </c>
       <c r="B20" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2575,7 +2583,7 @@
         <v>129707310</v>
       </c>
       <c r="B21" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2672,7 +2680,7 @@
         <v>129707335</v>
       </c>
       <c r="B22" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2766,53 +2774,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129694913</v>
+        <v>129694845</v>
       </c>
       <c r="B23" t="n">
-        <v>56926</v>
+        <v>79703</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>431728</v>
+        <v>431722</v>
       </c>
       <c r="R23" t="n">
-        <v>6795109</v>
+        <v>6795478</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2871,10 +2871,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129707331</v>
+        <v>129694883</v>
       </c>
       <c r="B24" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2900,19 +2900,16 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>431916</v>
+        <v>431885</v>
       </c>
       <c r="R24" t="n">
-        <v>6795392</v>
+        <v>6795213</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2953,29 +2950,28 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129694942</v>
+        <v>129694884</v>
       </c>
       <c r="B25" t="n">
-        <v>91897</v>
+        <v>79703</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2983,21 +2979,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3007,10 +3003,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>431803</v>
+        <v>431885</v>
       </c>
       <c r="R25" t="n">
-        <v>6795150</v>
+        <v>6795215</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3051,7 +3047,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3070,10 +3065,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129694883</v>
+        <v>129694898</v>
       </c>
       <c r="B26" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3105,10 +3100,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>431885</v>
+        <v>431907</v>
       </c>
       <c r="R26" t="n">
-        <v>6795213</v>
+        <v>6795285</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3167,10 +3162,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129694884</v>
+        <v>129694899</v>
       </c>
       <c r="B27" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3202,10 +3197,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>431885</v>
+        <v>431910</v>
       </c>
       <c r="R27" t="n">
-        <v>6795215</v>
+        <v>6795288</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3264,10 +3259,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129694898</v>
+        <v>129694861</v>
       </c>
       <c r="B28" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3299,10 +3294,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>431907</v>
+        <v>431740</v>
       </c>
       <c r="R28" t="n">
-        <v>6795285</v>
+        <v>6795107</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3361,10 +3356,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129694899</v>
+        <v>129694942</v>
       </c>
       <c r="B29" t="n">
-        <v>79700</v>
+        <v>91900</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3372,21 +3367,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3396,10 +3391,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>431910</v>
+        <v>431803</v>
       </c>
       <c r="R29" t="n">
-        <v>6795288</v>
+        <v>6795150</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3440,6 +3435,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3458,10 +3454,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129694861</v>
+        <v>129707308</v>
       </c>
       <c r="B30" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3493,10 +3489,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>431740</v>
+        <v>431868</v>
       </c>
       <c r="R30" t="n">
-        <v>6795107</v>
+        <v>6795565</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3543,22 +3539,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129707308</v>
+        <v>129707407</v>
       </c>
       <c r="B31" t="n">
-        <v>79700</v>
+        <v>79084</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3566,21 +3562,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3590,10 +3586,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>431868</v>
+        <v>431723</v>
       </c>
       <c r="R31" t="n">
-        <v>6795565</v>
+        <v>6795371</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3652,10 +3648,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129707407</v>
+        <v>129707331</v>
       </c>
       <c r="B32" t="n">
-        <v>79081</v>
+        <v>79703</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3663,34 +3659,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>431723</v>
+        <v>431916</v>
       </c>
       <c r="R32" t="n">
-        <v>6795371</v>
+        <v>6795392</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3731,6 +3730,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3749,10 +3749,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129707346</v>
+        <v>129694839</v>
       </c>
       <c r="B33" t="n">
-        <v>57733</v>
+        <v>91525</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3760,31 +3760,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>3242</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3792,10 +3787,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>431819</v>
+        <v>431869</v>
       </c>
       <c r="R33" t="n">
-        <v>6795465</v>
+        <v>6795181</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3836,28 +3831,29 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129707390</v>
+        <v>129694921</v>
       </c>
       <c r="B34" t="n">
-        <v>78838</v>
+        <v>57734</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3865,26 +3861,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -3892,10 +3893,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>431952</v>
+        <v>431725</v>
       </c>
       <c r="R34" t="n">
-        <v>6795410</v>
+        <v>6795459</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3936,51 +3937,50 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129695010</v>
+        <v>129694886</v>
       </c>
       <c r="B35" t="n">
-        <v>92881</v>
+        <v>79703</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3990,10 +3990,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>431880</v>
+        <v>431873</v>
       </c>
       <c r="R35" t="n">
-        <v>6795546</v>
+        <v>6795241</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4052,10 +4052,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129694839</v>
+        <v>129694980</v>
       </c>
       <c r="B36" t="n">
-        <v>91522</v>
+        <v>79084</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4063,37 +4063,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3242</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>431869</v>
+        <v>431711</v>
       </c>
       <c r="R36" t="n">
-        <v>6795181</v>
+        <v>6795450</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4134,7 +4131,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4153,10 +4149,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129694980</v>
+        <v>129694878</v>
       </c>
       <c r="B37" t="n">
-        <v>79081</v>
+        <v>79703</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4164,21 +4160,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4188,10 +4184,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>431711</v>
+        <v>431889</v>
       </c>
       <c r="R37" t="n">
-        <v>6795450</v>
+        <v>6795186</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4253,7 +4249,7 @@
         <v>129694917</v>
       </c>
       <c r="B38" t="n">
-        <v>91620</v>
+        <v>91623</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4355,32 +4351,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129694886</v>
+        <v>129695010</v>
       </c>
       <c r="B39" t="n">
-        <v>79700</v>
+        <v>92884</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4390,10 +4386,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>431873</v>
+        <v>431880</v>
       </c>
       <c r="R39" t="n">
-        <v>6795241</v>
+        <v>6795546</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4452,10 +4448,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129694878</v>
+        <v>129707390</v>
       </c>
       <c r="B40" t="n">
-        <v>79700</v>
+        <v>78841</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4463,34 +4459,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>431889</v>
+        <v>431952</v>
       </c>
       <c r="R40" t="n">
-        <v>6795186</v>
+        <v>6795410</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4531,28 +4530,29 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129694921</v>
+        <v>129707346</v>
       </c>
       <c r="B41" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4592,10 +4592,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>431725</v>
+        <v>431819</v>
       </c>
       <c r="R41" t="n">
-        <v>6795459</v>
+        <v>6795465</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4642,22 +4642,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129694999</v>
+        <v>129694926</v>
       </c>
       <c r="B42" t="n">
-        <v>79081</v>
+        <v>57734</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4665,34 +4665,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>431859</v>
+        <v>431711</v>
       </c>
       <c r="R42" t="n">
-        <v>6795172</v>
+        <v>6795100</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4754,7 +4762,7 @@
         <v>129694847</v>
       </c>
       <c r="B43" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4848,10 +4856,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129694926</v>
+        <v>129694999</v>
       </c>
       <c r="B44" t="n">
-        <v>57733</v>
+        <v>79084</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4859,42 +4867,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>431711</v>
+        <v>431859</v>
       </c>
       <c r="R44" t="n">
-        <v>6795100</v>
+        <v>6795172</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4956,7 +4956,7 @@
         <v>129707320</v>
       </c>
       <c r="B45" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>129707316</v>
       </c>
       <c r="B46" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         <v>129707333</v>
       </c>
       <c r="B47" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>129707338</v>
       </c>
       <c r="B48" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>129707375</v>
       </c>
       <c r="B49" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>129707351</v>
       </c>
       <c r="B50" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5543,10 +5543,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129695006</v>
+        <v>129694846</v>
       </c>
       <c r="B51" t="n">
-        <v>79081</v>
+        <v>79703</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5554,21 +5554,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5578,10 +5578,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>431962</v>
+        <v>431725</v>
       </c>
       <c r="R51" t="n">
-        <v>6795319</v>
+        <v>6795467</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5640,10 +5640,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129695003</v>
+        <v>129695006</v>
       </c>
       <c r="B52" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5675,10 +5675,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>431908</v>
+        <v>431962</v>
       </c>
       <c r="R52" t="n">
-        <v>6795302</v>
+        <v>6795319</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5737,10 +5737,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129707337</v>
+        <v>129695003</v>
       </c>
       <c r="B53" t="n">
-        <v>79700</v>
+        <v>79084</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5748,21 +5748,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>431999</v>
+        <v>431908</v>
       </c>
       <c r="R53" t="n">
-        <v>6795416</v>
+        <v>6795302</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5822,22 +5822,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129707426</v>
+        <v>129694994</v>
       </c>
       <c r="B54" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5869,10 +5869,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>431767</v>
+        <v>431804</v>
       </c>
       <c r="R54" t="n">
-        <v>6795219</v>
+        <v>6795151</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5919,12 +5919,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -5934,7 +5934,7 @@
         <v>129707404</v>
       </c>
       <c r="B55" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6037,10 +6037,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129707380</v>
+        <v>129707337</v>
       </c>
       <c r="B56" t="n">
-        <v>78838</v>
+        <v>79703</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6048,21 +6048,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6072,10 +6072,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>431820</v>
+        <v>431999</v>
       </c>
       <c r="R56" t="n">
-        <v>6795330</v>
+        <v>6795416</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6134,10 +6134,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129707347</v>
+        <v>129707426</v>
       </c>
       <c r="B57" t="n">
-        <v>57733</v>
+        <v>79084</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6145,42 +6145,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>431662</v>
+        <v>431767</v>
       </c>
       <c r="R57" t="n">
-        <v>6795391</v>
+        <v>6795219</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6239,10 +6231,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129694846</v>
+        <v>129707380</v>
       </c>
       <c r="B58" t="n">
-        <v>79700</v>
+        <v>78841</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6250,21 +6242,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6274,10 +6266,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>431725</v>
+        <v>431820</v>
       </c>
       <c r="R58" t="n">
-        <v>6795467</v>
+        <v>6795330</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6324,22 +6316,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129694994</v>
+        <v>129707347</v>
       </c>
       <c r="B59" t="n">
-        <v>79081</v>
+        <v>57734</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6347,34 +6339,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>431804</v>
+        <v>431662</v>
       </c>
       <c r="R59" t="n">
-        <v>6795151</v>
+        <v>6795391</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6421,22 +6421,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129694872</v>
+        <v>129707319</v>
       </c>
       <c r="B60" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6468,10 +6468,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>431833</v>
+        <v>431708</v>
       </c>
       <c r="R60" t="n">
-        <v>6795171</v>
+        <v>6795371</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6518,22 +6518,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129694856</v>
+        <v>129694930</v>
       </c>
       <c r="B61" t="n">
-        <v>79700</v>
+        <v>57734</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6541,34 +6541,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>431693</v>
+        <v>431875</v>
       </c>
       <c r="R61" t="n">
-        <v>6795052</v>
+        <v>6795244</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6627,10 +6635,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129694988</v>
+        <v>129694872</v>
       </c>
       <c r="B62" t="n">
-        <v>79081</v>
+        <v>79703</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6638,21 +6646,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6662,10 +6670,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>431718</v>
+        <v>431833</v>
       </c>
       <c r="R62" t="n">
-        <v>6795068</v>
+        <v>6795171</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6724,10 +6732,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129694930</v>
+        <v>129694856</v>
       </c>
       <c r="B63" t="n">
-        <v>57733</v>
+        <v>79703</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6735,42 +6743,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>431875</v>
+        <v>431693</v>
       </c>
       <c r="R63" t="n">
-        <v>6795244</v>
+        <v>6795052</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6832,7 +6832,7 @@
         <v>129694961</v>
       </c>
       <c r="B64" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6926,10 +6926,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129707319</v>
+        <v>129694988</v>
       </c>
       <c r="B65" t="n">
-        <v>79700</v>
+        <v>79084</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6937,21 +6937,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6961,10 +6961,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>431708</v>
+        <v>431718</v>
       </c>
       <c r="R65" t="n">
-        <v>6795371</v>
+        <v>6795068</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7011,22 +7011,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129694857</v>
+        <v>129694928</v>
       </c>
       <c r="B66" t="n">
-        <v>79700</v>
+        <v>57734</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7034,34 +7034,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>431800</v>
+        <v>431801</v>
       </c>
       <c r="R66" t="n">
-        <v>6795130</v>
+        <v>6795136</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7120,10 +7128,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129694908</v>
+        <v>129694857</v>
       </c>
       <c r="B67" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7155,10 +7163,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>431973</v>
+        <v>431800</v>
       </c>
       <c r="R67" t="n">
-        <v>6795310</v>
+        <v>6795130</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7217,10 +7225,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129694858</v>
+        <v>129694908</v>
       </c>
       <c r="B68" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7252,10 +7260,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>431749</v>
+        <v>431973</v>
       </c>
       <c r="R68" t="n">
-        <v>6795079</v>
+        <v>6795310</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7314,10 +7322,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129694859</v>
+        <v>129694858</v>
       </c>
       <c r="B69" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7349,10 +7357,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>431702</v>
+        <v>431749</v>
       </c>
       <c r="R69" t="n">
-        <v>6795115</v>
+        <v>6795079</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7411,10 +7419,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129694879</v>
+        <v>129694859</v>
       </c>
       <c r="B70" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7446,10 +7454,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>431888</v>
+        <v>431702</v>
       </c>
       <c r="R70" t="n">
-        <v>6795198</v>
+        <v>6795115</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7508,10 +7516,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129694928</v>
+        <v>129694879</v>
       </c>
       <c r="B71" t="n">
-        <v>57733</v>
+        <v>79703</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7519,42 +7527,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>431801</v>
+        <v>431888</v>
       </c>
       <c r="R71" t="n">
-        <v>6795136</v>
+        <v>6795198</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7613,10 +7613,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129707382</v>
+        <v>129707420</v>
       </c>
       <c r="B72" t="n">
-        <v>78838</v>
+        <v>79084</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7624,37 +7624,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>431689</v>
+        <v>431695</v>
       </c>
       <c r="R72" t="n">
-        <v>6795383</v>
+        <v>6795256</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7695,7 +7692,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7714,10 +7710,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129707420</v>
+        <v>129707382</v>
       </c>
       <c r="B73" t="n">
-        <v>79081</v>
+        <v>78841</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7725,34 +7721,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>431695</v>
+        <v>431689</v>
       </c>
       <c r="R73" t="n">
-        <v>6795256</v>
+        <v>6795383</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7793,6 +7792,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7811,10 +7811,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129707317</v>
+        <v>129694985</v>
       </c>
       <c r="B74" t="n">
-        <v>79700</v>
+        <v>79084</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7822,21 +7822,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7846,10 +7846,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>431780</v>
+        <v>431673</v>
       </c>
       <c r="R74" t="n">
-        <v>6795362</v>
+        <v>6795435</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7896,22 +7896,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129707391</v>
+        <v>129707317</v>
       </c>
       <c r="B75" t="n">
-        <v>78838</v>
+        <v>79703</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7919,21 +7919,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7943,10 +7943,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>431724</v>
+        <v>431780</v>
       </c>
       <c r="R75" t="n">
-        <v>6795372</v>
+        <v>6795362</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8005,10 +8005,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129707389</v>
+        <v>129707391</v>
       </c>
       <c r="B76" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8034,19 +8034,16 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>431922</v>
+        <v>431724</v>
       </c>
       <c r="R76" t="n">
-        <v>6795405</v>
+        <v>6795372</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8087,7 +8084,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8106,10 +8102,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129707314</v>
+        <v>129707389</v>
       </c>
       <c r="B77" t="n">
-        <v>79700</v>
+        <v>78841</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8117,34 +8113,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>431866</v>
+        <v>431922</v>
       </c>
       <c r="R77" t="n">
-        <v>6795513</v>
+        <v>6795405</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8185,6 +8184,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8203,10 +8203,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129694985</v>
+        <v>129707314</v>
       </c>
       <c r="B78" t="n">
-        <v>79081</v>
+        <v>79703</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8214,21 +8214,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8238,10 +8238,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>431673</v>
+        <v>431866</v>
       </c>
       <c r="R78" t="n">
-        <v>6795435</v>
+        <v>6795513</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8288,12 +8288,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -8303,7 +8303,7 @@
         <v>129707439</v>
       </c>
       <c r="B79" t="n">
-        <v>92881</v>
+        <v>92884</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8397,10 +8397,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129694863</v>
+        <v>129694933</v>
       </c>
       <c r="B80" t="n">
-        <v>79700</v>
+        <v>57734</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8408,34 +8408,42 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>431785</v>
+        <v>431904</v>
       </c>
       <c r="R80" t="n">
-        <v>6795106</v>
+        <v>6795243</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8494,10 +8502,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129694874</v>
+        <v>129694863</v>
       </c>
       <c r="B81" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8529,10 +8537,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>431827</v>
+        <v>431785</v>
       </c>
       <c r="R81" t="n">
-        <v>6795171</v>
+        <v>6795106</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8591,10 +8599,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129694948</v>
+        <v>129694874</v>
       </c>
       <c r="B82" t="n">
-        <v>78839</v>
+        <v>79703</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8602,21 +8610,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8626,10 +8634,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>431725</v>
+        <v>431827</v>
       </c>
       <c r="R82" t="n">
-        <v>6795459</v>
+        <v>6795171</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8688,10 +8696,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129694991</v>
+        <v>129695001</v>
       </c>
       <c r="B83" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8723,10 +8731,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>431760</v>
+        <v>431876</v>
       </c>
       <c r="R83" t="n">
-        <v>6795115</v>
+        <v>6795202</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8785,10 +8793,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129694933</v>
+        <v>129694991</v>
       </c>
       <c r="B84" t="n">
-        <v>57733</v>
+        <v>79084</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8796,42 +8804,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>431904</v>
+        <v>431760</v>
       </c>
       <c r="R84" t="n">
-        <v>6795243</v>
+        <v>6795115</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8890,10 +8890,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129695001</v>
+        <v>129694948</v>
       </c>
       <c r="B85" t="n">
-        <v>79081</v>
+        <v>78842</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8901,21 +8901,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8925,10 +8925,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>431876</v>
+        <v>431725</v>
       </c>
       <c r="R85" t="n">
-        <v>6795202</v>
+        <v>6795459</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8987,10 +8987,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129707345</v>
+        <v>129707388</v>
       </c>
       <c r="B86" t="n">
-        <v>57733</v>
+        <v>78841</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8998,42 +8998,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>431893</v>
+        <v>431915</v>
       </c>
       <c r="R86" t="n">
-        <v>6795571</v>
+        <v>6795392</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9092,10 +9084,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129707388</v>
+        <v>129707315</v>
       </c>
       <c r="B87" t="n">
-        <v>78838</v>
+        <v>79703</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9103,21 +9095,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9127,10 +9119,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>431915</v>
+        <v>431820</v>
       </c>
       <c r="R87" t="n">
-        <v>6795392</v>
+        <v>6795329</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9189,10 +9181,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129707315</v>
+        <v>129707424</v>
       </c>
       <c r="B88" t="n">
-        <v>79700</v>
+        <v>79084</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9200,21 +9192,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9224,10 +9216,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>431820</v>
+        <v>431760</v>
       </c>
       <c r="R88" t="n">
-        <v>6795329</v>
+        <v>6795200</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9286,10 +9278,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129707424</v>
+        <v>129707345</v>
       </c>
       <c r="B89" t="n">
-        <v>79081</v>
+        <v>57734</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9297,34 +9289,42 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>431760</v>
+        <v>431893</v>
       </c>
       <c r="R89" t="n">
-        <v>6795200</v>
+        <v>6795571</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9383,10 +9383,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129694860</v>
+        <v>129694939</v>
       </c>
       <c r="B90" t="n">
-        <v>79700</v>
+        <v>57734</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9394,21 +9394,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9418,10 +9418,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>431746</v>
+        <v>431913</v>
       </c>
       <c r="R90" t="n">
-        <v>6795081</v>
+        <v>6795284</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9454,6 +9454,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9480,10 +9485,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129694939</v>
+        <v>129694934</v>
       </c>
       <c r="B91" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9509,16 +9514,24 @@
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>431913</v>
+        <v>431916</v>
       </c>
       <c r="R91" t="n">
-        <v>6795284</v>
+        <v>6795286</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9551,11 +9564,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9582,10 +9590,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129694965</v>
+        <v>129694860</v>
       </c>
       <c r="B92" t="n">
-        <v>78838</v>
+        <v>79703</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9593,21 +9601,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9617,10 +9625,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>431885</v>
+        <v>431746</v>
       </c>
       <c r="R92" t="n">
-        <v>6795240</v>
+        <v>6795081</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9679,10 +9687,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129694934</v>
+        <v>129694965</v>
       </c>
       <c r="B93" t="n">
-        <v>57733</v>
+        <v>78841</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9690,42 +9698,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>431916</v>
+        <v>431885</v>
       </c>
       <c r="R93" t="n">
-        <v>6795286</v>
+        <v>6795240</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9787,7 +9787,7 @@
         <v>129707405</v>
       </c>
       <c r="B94" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>129707381</v>
       </c>
       <c r="B95" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9978,10 +9978,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129707312</v>
+        <v>129694977</v>
       </c>
       <c r="B96" t="n">
-        <v>79700</v>
+        <v>57734</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9989,34 +9989,42 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>431920</v>
+        <v>431933</v>
       </c>
       <c r="R96" t="n">
-        <v>6795611</v>
+        <v>6795295</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10063,44 +10071,44 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129694941</v>
+        <v>129694989</v>
       </c>
       <c r="B97" t="n">
-        <v>79167</v>
+        <v>79084</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10110,10 +10118,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>431976</v>
+        <v>431723</v>
       </c>
       <c r="R97" t="n">
-        <v>6795333</v>
+        <v>6795090</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10172,32 +10180,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129694989</v>
+        <v>129694941</v>
       </c>
       <c r="B98" t="n">
-        <v>79081</v>
+        <v>79170</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10207,10 +10215,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>431723</v>
+        <v>431976</v>
       </c>
       <c r="R98" t="n">
-        <v>6795090</v>
+        <v>6795333</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10269,10 +10277,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129694977</v>
+        <v>129707312</v>
       </c>
       <c r="B99" t="n">
-        <v>57733</v>
+        <v>79703</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10280,42 +10288,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>431933</v>
+        <v>431920</v>
       </c>
       <c r="R99" t="n">
-        <v>6795295</v>
+        <v>6795611</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10362,22 +10362,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129694992</v>
+        <v>129707397</v>
       </c>
       <c r="B100" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10409,10 +10409,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>431799</v>
+        <v>431915</v>
       </c>
       <c r="R100" t="n">
-        <v>6795129</v>
+        <v>6795541</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10459,22 +10459,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129694877</v>
+        <v>129707327</v>
       </c>
       <c r="B101" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10506,10 +10506,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>431887</v>
+        <v>431893</v>
       </c>
       <c r="R101" t="n">
-        <v>6795183</v>
+        <v>6795305</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10556,22 +10556,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129694885</v>
+        <v>129707396</v>
       </c>
       <c r="B102" t="n">
-        <v>79700</v>
+        <v>79084</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10579,21 +10579,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10603,10 +10603,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>431873</v>
+        <v>431918</v>
       </c>
       <c r="R102" t="n">
-        <v>6795224</v>
+        <v>6795574</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10653,22 +10653,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129694864</v>
+        <v>129707406</v>
       </c>
       <c r="B103" t="n">
-        <v>79700</v>
+        <v>79084</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10676,21 +10676,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10700,10 +10700,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>431786</v>
+        <v>431771</v>
       </c>
       <c r="R103" t="n">
-        <v>6795113</v>
+        <v>6795344</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10750,22 +10750,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129695000</v>
+        <v>129707332</v>
       </c>
       <c r="B104" t="n">
-        <v>79081</v>
+        <v>79703</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10773,21 +10773,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10797,10 +10797,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>431890</v>
+        <v>431923</v>
       </c>
       <c r="R104" t="n">
-        <v>6795199</v>
+        <v>6795402</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10847,22 +10847,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129694927</v>
+        <v>129707425</v>
       </c>
       <c r="B105" t="n">
-        <v>57733</v>
+        <v>79084</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10870,42 +10870,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>431711</v>
+        <v>431756</v>
       </c>
       <c r="R105" t="n">
-        <v>6795094</v>
+        <v>6795247</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10952,22 +10944,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129694938</v>
+        <v>129694927</v>
       </c>
       <c r="B106" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11007,10 +10999,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>431915</v>
+        <v>431711</v>
       </c>
       <c r="R106" t="n">
-        <v>6795279</v>
+        <v>6795094</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11069,10 +11061,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129707349</v>
+        <v>129694938</v>
       </c>
       <c r="B107" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11112,10 +11104,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>431722</v>
+        <v>431915</v>
       </c>
       <c r="R107" t="n">
-        <v>6795217</v>
+        <v>6795279</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11162,22 +11154,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129707397</v>
+        <v>129695000</v>
       </c>
       <c r="B108" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11209,10 +11201,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>431915</v>
+        <v>431890</v>
       </c>
       <c r="R108" t="n">
-        <v>6795541</v>
+        <v>6795199</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11259,22 +11251,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129707327</v>
+        <v>129694877</v>
       </c>
       <c r="B109" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11306,10 +11298,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>431893</v>
+        <v>431887</v>
       </c>
       <c r="R109" t="n">
-        <v>6795305</v>
+        <v>6795183</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11356,22 +11348,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129707396</v>
+        <v>129694885</v>
       </c>
       <c r="B110" t="n">
-        <v>79081</v>
+        <v>79703</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11379,21 +11371,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11403,10 +11395,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>431918</v>
+        <v>431873</v>
       </c>
       <c r="R110" t="n">
-        <v>6795574</v>
+        <v>6795224</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11453,22 +11445,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129707406</v>
+        <v>129694864</v>
       </c>
       <c r="B111" t="n">
-        <v>79081</v>
+        <v>79703</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11476,21 +11468,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11500,10 +11492,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>431771</v>
+        <v>431786</v>
       </c>
       <c r="R111" t="n">
-        <v>6795344</v>
+        <v>6795113</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11550,22 +11542,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129707332</v>
+        <v>129694992</v>
       </c>
       <c r="B112" t="n">
-        <v>79700</v>
+        <v>79084</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11573,21 +11565,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11597,10 +11589,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>431923</v>
+        <v>431799</v>
       </c>
       <c r="R112" t="n">
-        <v>6795402</v>
+        <v>6795129</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11647,22 +11639,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129707425</v>
+        <v>129707349</v>
       </c>
       <c r="B113" t="n">
-        <v>79081</v>
+        <v>57734</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11670,34 +11662,42 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>431756</v>
+        <v>431722</v>
       </c>
       <c r="R113" t="n">
-        <v>6795247</v>
+        <v>6795217</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11756,10 +11756,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129694990</v>
+        <v>129694901</v>
       </c>
       <c r="B114" t="n">
-        <v>79081</v>
+        <v>79703</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11767,21 +11767,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11791,10 +11791,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>431726</v>
+        <v>431927</v>
       </c>
       <c r="R114" t="n">
-        <v>6795117</v>
+        <v>6795265</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11853,10 +11853,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129694901</v>
+        <v>129694990</v>
       </c>
       <c r="B115" t="n">
-        <v>79700</v>
+        <v>79084</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11864,21 +11864,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11888,10 +11888,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>431927</v>
+        <v>431726</v>
       </c>
       <c r="R115" t="n">
-        <v>6795265</v>
+        <v>6795117</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11953,7 +11953,7 @@
         <v>129694844</v>
       </c>
       <c r="B116" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
         <v>129707309</v>
       </c>
       <c r="B117" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12147,7 +12147,7 @@
         <v>129707330</v>
       </c>
       <c r="B118" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12244,7 +12244,7 @@
         <v>129707323</v>
       </c>
       <c r="B119" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12341,7 +12341,7 @@
         <v>129707386</v>
       </c>
       <c r="B120" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>129707421</v>
       </c>
       <c r="B121" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12532,45 +12532,53 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129695013</v>
+        <v>129694925</v>
       </c>
       <c r="B122" t="n">
-        <v>92881</v>
+        <v>57734</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>431869</v>
+        <v>431687</v>
       </c>
       <c r="R122" t="n">
-        <v>6795173</v>
+        <v>6795051</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12632,7 +12640,7 @@
         <v>129694850</v>
       </c>
       <c r="B123" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12729,7 +12737,7 @@
         <v>129694881</v>
       </c>
       <c r="B124" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12826,7 +12834,7 @@
         <v>129694888</v>
       </c>
       <c r="B125" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12920,10 +12928,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129694925</v>
+        <v>129694997</v>
       </c>
       <c r="B126" t="n">
-        <v>57733</v>
+        <v>79084</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12931,42 +12939,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>431687</v>
+        <v>431848</v>
       </c>
       <c r="R126" t="n">
-        <v>6795051</v>
+        <v>6795172</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13025,10 +13025,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129694997</v>
+        <v>129707368</v>
       </c>
       <c r="B127" t="n">
-        <v>79081</v>
+        <v>78842</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13036,34 +13036,37 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>431848</v>
+        <v>431820</v>
       </c>
       <c r="R127" t="n">
-        <v>6795172</v>
+        <v>6795331</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13104,66 +13107,64 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129707368</v>
+        <v>129695013</v>
       </c>
       <c r="B128" t="n">
-        <v>78839</v>
+        <v>92884</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>431820</v>
+        <v>431869</v>
       </c>
       <c r="R128" t="n">
-        <v>6795331</v>
+        <v>6795173</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13204,19 +13205,18 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
@@ -13226,7 +13226,7 @@
         <v>129707311</v>
       </c>
       <c r="B129" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13323,7 +13323,7 @@
         <v>129694900</v>
       </c>
       <c r="B130" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13420,7 +13420,7 @@
         <v>129694906</v>
       </c>
       <c r="B131" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
         <v>129707399</v>
       </c>
       <c r="B132" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         <v>129707387</v>
       </c>
       <c r="B133" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13711,7 +13711,7 @@
         <v>129707438</v>
       </c>
       <c r="B134" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>129707318</v>
       </c>
       <c r="B135" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13905,7 +13905,7 @@
         <v>129694866</v>
       </c>
       <c r="B136" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>129694865</v>
       </c>
       <c r="B137" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14099,7 +14099,7 @@
         <v>129694896</v>
       </c>
       <c r="B138" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14196,7 +14196,7 @@
         <v>129694956</v>
       </c>
       <c r="B139" t="n">
-        <v>92017</v>
+        <v>92020</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14205,6 +14205,11 @@
       </c>
       <c r="E139" t="n">
         <v>6040162</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -14298,7 +14303,7 @@
         <v>129707334</v>
       </c>
       <c r="B140" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14395,7 +14400,7 @@
         <v>129707370</v>
       </c>
       <c r="B141" t="n">
-        <v>78839</v>
+        <v>78842</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14489,10 +14494,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129707377</v>
+        <v>129707366</v>
       </c>
       <c r="B142" t="n">
-        <v>78838</v>
+        <v>78842</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14500,21 +14505,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14524,10 +14529,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>431843</v>
+        <v>431840</v>
       </c>
       <c r="R142" t="n">
-        <v>6795474</v>
+        <v>6795476</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14586,10 +14591,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129707366</v>
+        <v>129707377</v>
       </c>
       <c r="B143" t="n">
-        <v>78839</v>
+        <v>78841</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14597,21 +14602,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14621,10 +14626,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>431840</v>
+        <v>431843</v>
       </c>
       <c r="R143" t="n">
-        <v>6795476</v>
+        <v>6795474</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14686,7 +14691,7 @@
         <v>129694876</v>
       </c>
       <c r="B144" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14783,7 +14788,7 @@
         <v>129694887</v>
       </c>
       <c r="B145" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14880,7 +14885,7 @@
         <v>129694880</v>
       </c>
       <c r="B146" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14977,7 +14982,7 @@
         <v>129694897</v>
       </c>
       <c r="B147" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>

--- a/artfynd/A 50492-2025 artfynd.xlsx
+++ b/artfynd/A 50492-2025 artfynd.xlsx
@@ -2378,53 +2378,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129694913</v>
+        <v>129694845</v>
       </c>
       <c r="B19" t="n">
-        <v>56927</v>
+        <v>79703</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>431728</v>
+        <v>431722</v>
       </c>
       <c r="R19" t="n">
-        <v>6795109</v>
+        <v>6795478</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2483,45 +2475,53 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129707378</v>
+        <v>129694913</v>
       </c>
       <c r="B20" t="n">
-        <v>78841</v>
+        <v>56927</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>431814</v>
+        <v>431728</v>
       </c>
       <c r="R20" t="n">
-        <v>6795444</v>
+        <v>6795109</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2568,22 +2568,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129707310</v>
+        <v>129707378</v>
       </c>
       <c r="B21" t="n">
-        <v>79703</v>
+        <v>78841</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2591,21 +2591,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2615,10 +2615,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>431924</v>
+        <v>431814</v>
       </c>
       <c r="R21" t="n">
-        <v>6795546</v>
+        <v>6795444</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2677,7 +2677,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129707335</v>
+        <v>129707310</v>
       </c>
       <c r="B22" t="n">
         <v>79703</v>
@@ -2712,10 +2712,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>431965</v>
+        <v>431924</v>
       </c>
       <c r="R22" t="n">
-        <v>6795430</v>
+        <v>6795546</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2774,7 +2774,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129694845</v>
+        <v>129707335</v>
       </c>
       <c r="B23" t="n">
         <v>79703</v>
@@ -2809,10 +2809,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>431722</v>
+        <v>431965</v>
       </c>
       <c r="R23" t="n">
-        <v>6795478</v>
+        <v>6795430</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2859,12 +2859,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -7811,10 +7811,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129694985</v>
+        <v>129707317</v>
       </c>
       <c r="B74" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7822,21 +7822,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7846,10 +7846,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>431673</v>
+        <v>431780</v>
       </c>
       <c r="R74" t="n">
-        <v>6795435</v>
+        <v>6795362</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7896,22 +7896,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129707317</v>
+        <v>129707391</v>
       </c>
       <c r="B75" t="n">
-        <v>79703</v>
+        <v>78841</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7919,21 +7919,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7943,10 +7943,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>431780</v>
+        <v>431724</v>
       </c>
       <c r="R75" t="n">
-        <v>6795362</v>
+        <v>6795372</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8005,7 +8005,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129707391</v>
+        <v>129707389</v>
       </c>
       <c r="B76" t="n">
         <v>78841</v>
@@ -8034,16 +8034,19 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>431724</v>
+        <v>431922</v>
       </c>
       <c r="R76" t="n">
-        <v>6795372</v>
+        <v>6795405</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8084,6 +8087,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8102,10 +8106,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129707389</v>
+        <v>129707314</v>
       </c>
       <c r="B77" t="n">
-        <v>78841</v>
+        <v>79703</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8113,37 +8117,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>431922</v>
+        <v>431866</v>
       </c>
       <c r="R77" t="n">
-        <v>6795405</v>
+        <v>6795513</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8184,7 +8185,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8203,10 +8203,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129707314</v>
+        <v>129694985</v>
       </c>
       <c r="B78" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8214,21 +8214,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8238,10 +8238,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>431866</v>
+        <v>431673</v>
       </c>
       <c r="R78" t="n">
-        <v>6795513</v>
+        <v>6795435</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8288,12 +8288,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -10374,10 +10374,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129707397</v>
+        <v>129707349</v>
       </c>
       <c r="B100" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10385,34 +10385,42 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>431915</v>
+        <v>431722</v>
       </c>
       <c r="R100" t="n">
-        <v>6795541</v>
+        <v>6795217</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10471,10 +10479,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129707327</v>
+        <v>129694927</v>
       </c>
       <c r="B101" t="n">
-        <v>79703</v>
+        <v>57734</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10482,34 +10490,42 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>431893</v>
+        <v>431711</v>
       </c>
       <c r="R101" t="n">
-        <v>6795305</v>
+        <v>6795094</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10556,22 +10572,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129707396</v>
+        <v>129694938</v>
       </c>
       <c r="B102" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10579,34 +10595,42 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>431918</v>
+        <v>431915</v>
       </c>
       <c r="R102" t="n">
-        <v>6795574</v>
+        <v>6795279</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10653,19 +10677,19 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129707406</v>
+        <v>129695000</v>
       </c>
       <c r="B103" t="n">
         <v>79084</v>
@@ -10700,10 +10724,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>431771</v>
+        <v>431890</v>
       </c>
       <c r="R103" t="n">
-        <v>6795344</v>
+        <v>6795199</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10750,19 +10774,19 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129707332</v>
+        <v>129694877</v>
       </c>
       <c r="B104" t="n">
         <v>79703</v>
@@ -10797,10 +10821,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>431923</v>
+        <v>431887</v>
       </c>
       <c r="R104" t="n">
-        <v>6795402</v>
+        <v>6795183</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10847,22 +10871,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129707425</v>
+        <v>129694885</v>
       </c>
       <c r="B105" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10870,21 +10894,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10894,10 +10918,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>431756</v>
+        <v>431873</v>
       </c>
       <c r="R105" t="n">
-        <v>6795247</v>
+        <v>6795224</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10944,22 +10968,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129694927</v>
+        <v>129694864</v>
       </c>
       <c r="B106" t="n">
-        <v>57734</v>
+        <v>79703</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10967,42 +10991,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>431711</v>
+        <v>431786</v>
       </c>
       <c r="R106" t="n">
-        <v>6795094</v>
+        <v>6795113</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11061,10 +11077,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129694938</v>
+        <v>129694992</v>
       </c>
       <c r="B107" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11072,42 +11088,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>431915</v>
+        <v>431799</v>
       </c>
       <c r="R107" t="n">
-        <v>6795279</v>
+        <v>6795129</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11166,7 +11174,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129695000</v>
+        <v>129707397</v>
       </c>
       <c r="B108" t="n">
         <v>79084</v>
@@ -11201,10 +11209,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>431890</v>
+        <v>431915</v>
       </c>
       <c r="R108" t="n">
-        <v>6795199</v>
+        <v>6795541</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11251,19 +11259,19 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129694877</v>
+        <v>129707327</v>
       </c>
       <c r="B109" t="n">
         <v>79703</v>
@@ -11298,10 +11306,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>431887</v>
+        <v>431893</v>
       </c>
       <c r="R109" t="n">
-        <v>6795183</v>
+        <v>6795305</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11348,22 +11356,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129694885</v>
+        <v>129707396</v>
       </c>
       <c r="B110" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11371,21 +11379,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11395,10 +11403,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>431873</v>
+        <v>431918</v>
       </c>
       <c r="R110" t="n">
-        <v>6795224</v>
+        <v>6795574</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11445,22 +11453,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129694864</v>
+        <v>129707406</v>
       </c>
       <c r="B111" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11468,21 +11476,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11492,10 +11500,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>431786</v>
+        <v>431771</v>
       </c>
       <c r="R111" t="n">
-        <v>6795113</v>
+        <v>6795344</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11542,22 +11550,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129694992</v>
+        <v>129707332</v>
       </c>
       <c r="B112" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11565,21 +11573,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11589,10 +11597,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>431799</v>
+        <v>431923</v>
       </c>
       <c r="R112" t="n">
-        <v>6795129</v>
+        <v>6795402</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11639,22 +11647,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129707349</v>
+        <v>129707425</v>
       </c>
       <c r="B113" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11662,42 +11670,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>431722</v>
+        <v>431756</v>
       </c>
       <c r="R113" t="n">
-        <v>6795217</v>
+        <v>6795247</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -14494,10 +14494,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129707366</v>
+        <v>129694876</v>
       </c>
       <c r="B142" t="n">
-        <v>78842</v>
+        <v>79703</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14505,21 +14505,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14529,10 +14529,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>431840</v>
+        <v>431871</v>
       </c>
       <c r="R142" t="n">
-        <v>6795476</v>
+        <v>6795171</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14579,22 +14579,22 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129707377</v>
+        <v>129694887</v>
       </c>
       <c r="B143" t="n">
-        <v>78841</v>
+        <v>79703</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14602,21 +14602,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14626,10 +14626,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>431843</v>
+        <v>431886</v>
       </c>
       <c r="R143" t="n">
-        <v>6795474</v>
+        <v>6795236</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14676,19 +14676,19 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129694876</v>
+        <v>129694880</v>
       </c>
       <c r="B144" t="n">
         <v>79703</v>
@@ -14726,7 +14726,7 @@
         <v>431871</v>
       </c>
       <c r="R144" t="n">
-        <v>6795171</v>
+        <v>6795205</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14785,7 +14785,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129694887</v>
+        <v>129694897</v>
       </c>
       <c r="B145" t="n">
         <v>79703</v>
@@ -14820,10 +14820,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>431886</v>
+        <v>431906</v>
       </c>
       <c r="R145" t="n">
-        <v>6795236</v>
+        <v>6795283</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -14882,10 +14882,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129694880</v>
+        <v>129707377</v>
       </c>
       <c r="B146" t="n">
-        <v>79703</v>
+        <v>78841</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14893,21 +14893,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -14917,10 +14917,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>431871</v>
+        <v>431843</v>
       </c>
       <c r="R146" t="n">
-        <v>6795205</v>
+        <v>6795474</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -14967,22 +14967,22 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129694897</v>
+        <v>129707366</v>
       </c>
       <c r="B147" t="n">
-        <v>79703</v>
+        <v>78842</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14990,21 +14990,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15014,10 +15014,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>431906</v>
+        <v>431840</v>
       </c>
       <c r="R147" t="n">
-        <v>6795283</v>
+        <v>6795476</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15064,12 +15064,12 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>

--- a/artfynd/A 50492-2025 artfynd.xlsx
+++ b/artfynd/A 50492-2025 artfynd.xlsx
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129694935</v>
+        <v>129707440</v>
       </c>
       <c r="B2" t="n">
-        <v>57734</v>
+        <v>92887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>431917</v>
+        <v>431828</v>
       </c>
       <c r="R2" t="n">
-        <v>6795290</v>
+        <v>6795476</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -768,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129694929</v>
+        <v>129707216</v>
       </c>
       <c r="B3" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,31 +783,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -823,10 +810,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>431859</v>
+        <v>432007</v>
       </c>
       <c r="R3" t="n">
-        <v>6795172</v>
+        <v>6795475</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,28 +854,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129694842</v>
+        <v>129707403</v>
       </c>
       <c r="B4" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,21 +884,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -920,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>431768</v>
+        <v>431851</v>
       </c>
       <c r="R4" t="n">
-        <v>6795469</v>
+        <v>6795372</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,12 +958,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -985,7 +973,7 @@
         <v>129694957</v>
       </c>
       <c r="B5" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,10 +1067,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129694862</v>
+        <v>129694842</v>
       </c>
       <c r="B6" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,10 +1102,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>431756</v>
+        <v>431768</v>
       </c>
       <c r="R6" t="n">
-        <v>6795121</v>
+        <v>6795469</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,10 +1164,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129707216</v>
+        <v>129694862</v>
       </c>
       <c r="B7" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1187,37 +1175,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>432007</v>
+        <v>431756</v>
       </c>
       <c r="R7" t="n">
-        <v>6795475</v>
+        <v>6795121</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,64 +1243,71 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129707440</v>
+        <v>129694935</v>
       </c>
       <c r="B8" t="n">
-        <v>92884</v>
+        <v>57737</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>431828</v>
+        <v>431917</v>
       </c>
       <c r="R8" t="n">
-        <v>6795476</v>
+        <v>6795290</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,22 +1354,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129707403</v>
+        <v>129694929</v>
       </c>
       <c r="B9" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,34 +1377,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>431851</v>
+        <v>431859</v>
       </c>
       <c r="R9" t="n">
-        <v>6795372</v>
+        <v>6795172</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,12 +1459,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1474,7 +1474,7 @@
         <v>129707371</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1578,10 +1578,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129694918</v>
+        <v>129707434</v>
       </c>
       <c r="B11" t="n">
-        <v>91623</v>
+        <v>79087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1589,41 +1589,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>431722</v>
+        <v>431894</v>
       </c>
       <c r="R11" t="n">
-        <v>6795120</v>
+        <v>6795261</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1664,29 +1657,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129694923</v>
+        <v>129707336</v>
       </c>
       <c r="B12" t="n">
-        <v>57734</v>
+        <v>79706</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1694,42 +1686,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>431687</v>
+        <v>431993</v>
       </c>
       <c r="R12" t="n">
-        <v>6795471</v>
+        <v>6795380</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1776,12 +1760,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1791,7 +1775,7 @@
         <v>129694843</v>
       </c>
       <c r="B13" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1885,10 +1869,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129694983</v>
+        <v>129694907</v>
       </c>
       <c r="B14" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1896,21 +1880,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1920,10 +1904,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>431689</v>
+        <v>431938</v>
       </c>
       <c r="R14" t="n">
-        <v>6795456</v>
+        <v>6795278</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1982,10 +1966,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129694907</v>
+        <v>129694923</v>
       </c>
       <c r="B15" t="n">
-        <v>79703</v>
+        <v>57737</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1993,34 +1977,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>431938</v>
+        <v>431687</v>
       </c>
       <c r="R15" t="n">
-        <v>6795278</v>
+        <v>6795471</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2079,10 +2071,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129707434</v>
+        <v>129694918</v>
       </c>
       <c r="B16" t="n">
-        <v>79084</v>
+        <v>91626</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2090,34 +2082,41 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>431894</v>
+        <v>431722</v>
       </c>
       <c r="R16" t="n">
-        <v>6795261</v>
+        <v>6795120</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2158,28 +2157,29 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129707336</v>
+        <v>129694983</v>
       </c>
       <c r="B17" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2187,21 +2187,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>431993</v>
+        <v>431689</v>
       </c>
       <c r="R17" t="n">
-        <v>6795380</v>
+        <v>6795456</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2261,12 +2261,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2276,7 +2276,7 @@
         <v>129707358</v>
       </c>
       <c r="B18" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2378,45 +2378,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129694845</v>
+        <v>129694913</v>
       </c>
       <c r="B19" t="n">
-        <v>79703</v>
+        <v>56930</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>431722</v>
+        <v>431728</v>
       </c>
       <c r="R19" t="n">
-        <v>6795478</v>
+        <v>6795109</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2475,53 +2483,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129694913</v>
+        <v>129707378</v>
       </c>
       <c r="B20" t="n">
-        <v>56927</v>
+        <v>78844</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>431728</v>
+        <v>431814</v>
       </c>
       <c r="R20" t="n">
-        <v>6795109</v>
+        <v>6795444</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2568,22 +2568,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129707378</v>
+        <v>129707310</v>
       </c>
       <c r="B21" t="n">
-        <v>78841</v>
+        <v>79706</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2591,21 +2591,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2615,10 +2615,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>431814</v>
+        <v>431924</v>
       </c>
       <c r="R21" t="n">
-        <v>6795444</v>
+        <v>6795546</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2677,10 +2677,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129707310</v>
+        <v>129707335</v>
       </c>
       <c r="B22" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2712,10 +2712,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>431924</v>
+        <v>431965</v>
       </c>
       <c r="R22" t="n">
-        <v>6795546</v>
+        <v>6795430</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2774,10 +2774,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129707335</v>
+        <v>129694845</v>
       </c>
       <c r="B23" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2809,10 +2809,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>431965</v>
+        <v>431722</v>
       </c>
       <c r="R23" t="n">
-        <v>6795430</v>
+        <v>6795478</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2859,22 +2859,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129694883</v>
+        <v>129694942</v>
       </c>
       <c r="B24" t="n">
-        <v>79703</v>
+        <v>91903</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2882,21 +2882,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2906,10 +2906,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>431885</v>
+        <v>431803</v>
       </c>
       <c r="R24" t="n">
-        <v>6795213</v>
+        <v>6795150</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2950,6 +2950,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2968,10 +2969,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129694884</v>
+        <v>129707407</v>
       </c>
       <c r="B25" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2979,21 +2980,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3003,10 +3004,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>431885</v>
+        <v>431723</v>
       </c>
       <c r="R25" t="n">
-        <v>6795215</v>
+        <v>6795371</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3053,22 +3054,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129694898</v>
+        <v>129707308</v>
       </c>
       <c r="B26" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3100,10 +3101,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>431907</v>
+        <v>431868</v>
       </c>
       <c r="R26" t="n">
-        <v>6795285</v>
+        <v>6795565</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3150,22 +3151,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129694899</v>
+        <v>129707331</v>
       </c>
       <c r="B27" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3191,16 +3192,19 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>431910</v>
+        <v>431916</v>
       </c>
       <c r="R27" t="n">
-        <v>6795288</v>
+        <v>6795392</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3241,28 +3245,29 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129694861</v>
+        <v>129694883</v>
       </c>
       <c r="B28" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3294,10 +3299,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>431740</v>
+        <v>431885</v>
       </c>
       <c r="R28" t="n">
-        <v>6795107</v>
+        <v>6795213</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3356,10 +3361,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129694942</v>
+        <v>129694884</v>
       </c>
       <c r="B29" t="n">
-        <v>91900</v>
+        <v>79706</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3367,21 +3372,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3391,10 +3396,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>431803</v>
+        <v>431885</v>
       </c>
       <c r="R29" t="n">
-        <v>6795150</v>
+        <v>6795215</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3435,7 +3440,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3454,10 +3458,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129707308</v>
+        <v>129694898</v>
       </c>
       <c r="B30" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3489,10 +3493,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>431868</v>
+        <v>431907</v>
       </c>
       <c r="R30" t="n">
-        <v>6795565</v>
+        <v>6795285</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3539,22 +3543,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129707407</v>
+        <v>129694899</v>
       </c>
       <c r="B31" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3562,21 +3566,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3586,10 +3590,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>431723</v>
+        <v>431910</v>
       </c>
       <c r="R31" t="n">
-        <v>6795371</v>
+        <v>6795288</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3636,22 +3640,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129707331</v>
+        <v>129694861</v>
       </c>
       <c r="B32" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3677,19 +3681,16 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>431916</v>
+        <v>431740</v>
       </c>
       <c r="R32" t="n">
-        <v>6795392</v>
+        <v>6795107</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3730,19 +3731,18 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -3752,7 +3752,7 @@
         <v>129694839</v>
       </c>
       <c r="B33" t="n">
-        <v>91525</v>
+        <v>91528</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3850,53 +3850,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129694921</v>
+        <v>129695010</v>
       </c>
       <c r="B34" t="n">
-        <v>57734</v>
+        <v>92887</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>431725</v>
+        <v>431880</v>
       </c>
       <c r="R34" t="n">
-        <v>6795459</v>
+        <v>6795546</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3955,10 +3947,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129694886</v>
+        <v>129694917</v>
       </c>
       <c r="B35" t="n">
-        <v>79703</v>
+        <v>91626</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3966,34 +3958,41 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>431873</v>
+        <v>431672</v>
       </c>
       <c r="R35" t="n">
-        <v>6795241</v>
+        <v>6795442</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4034,6 +4033,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4052,10 +4052,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129694980</v>
+        <v>129694886</v>
       </c>
       <c r="B36" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4063,21 +4063,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4087,10 +4087,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>431711</v>
+        <v>431873</v>
       </c>
       <c r="R36" t="n">
-        <v>6795450</v>
+        <v>6795241</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4152,7 +4152,7 @@
         <v>129694878</v>
       </c>
       <c r="B37" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4246,10 +4246,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129694917</v>
+        <v>129707390</v>
       </c>
       <c r="B38" t="n">
-        <v>91623</v>
+        <v>78844</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4257,28 +4257,24 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -4288,10 +4284,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>431672</v>
+        <v>431952</v>
       </c>
       <c r="R38" t="n">
-        <v>6795442</v>
+        <v>6795410</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4339,44 +4335,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129695010</v>
+        <v>129694980</v>
       </c>
       <c r="B39" t="n">
-        <v>92884</v>
+        <v>79087</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4386,10 +4382,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>431880</v>
+        <v>431711</v>
       </c>
       <c r="R39" t="n">
-        <v>6795546</v>
+        <v>6795450</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4448,10 +4444,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129707390</v>
+        <v>129707346</v>
       </c>
       <c r="B40" t="n">
-        <v>78841</v>
+        <v>57737</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4459,26 +4455,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4486,10 +4487,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>431952</v>
+        <v>431819</v>
       </c>
       <c r="R40" t="n">
-        <v>6795410</v>
+        <v>6795465</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4530,7 +4531,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4549,10 +4549,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129707346</v>
+        <v>129694921</v>
       </c>
       <c r="B41" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4592,10 +4592,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>431819</v>
+        <v>431725</v>
       </c>
       <c r="R41" t="n">
-        <v>6795465</v>
+        <v>6795459</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4642,22 +4642,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129694926</v>
+        <v>129694999</v>
       </c>
       <c r="B42" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4665,42 +4665,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>431711</v>
+        <v>431859</v>
       </c>
       <c r="R42" t="n">
-        <v>6795100</v>
+        <v>6795172</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4759,10 +4751,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129694847</v>
+        <v>129707320</v>
       </c>
       <c r="B43" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4794,10 +4786,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>431724</v>
+        <v>431717</v>
       </c>
       <c r="R43" t="n">
-        <v>6795460</v>
+        <v>6795380</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4844,22 +4836,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129694999</v>
+        <v>129707316</v>
       </c>
       <c r="B44" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4867,21 +4859,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4891,10 +4883,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>431859</v>
+        <v>431812</v>
       </c>
       <c r="R44" t="n">
-        <v>6795172</v>
+        <v>6795349</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4941,22 +4933,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129707320</v>
+        <v>129707333</v>
       </c>
       <c r="B45" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4988,10 +4980,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>431717</v>
+        <v>431935</v>
       </c>
       <c r="R45" t="n">
-        <v>6795380</v>
+        <v>6795415</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5050,10 +5042,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129707316</v>
+        <v>129707338</v>
       </c>
       <c r="B46" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5085,10 +5077,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>431812</v>
+        <v>431932</v>
       </c>
       <c r="R46" t="n">
-        <v>6795349</v>
+        <v>6795406</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5147,10 +5139,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129707333</v>
+        <v>129707375</v>
       </c>
       <c r="B47" t="n">
-        <v>79703</v>
+        <v>78844</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5158,21 +5150,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5182,10 +5174,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>431935</v>
+        <v>431881</v>
       </c>
       <c r="R47" t="n">
-        <v>6795415</v>
+        <v>6795522</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5244,10 +5236,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129707338</v>
+        <v>129694847</v>
       </c>
       <c r="B48" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5279,10 +5271,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>431932</v>
+        <v>431724</v>
       </c>
       <c r="R48" t="n">
-        <v>6795406</v>
+        <v>6795460</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5329,22 +5321,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129707375</v>
+        <v>129707351</v>
       </c>
       <c r="B49" t="n">
-        <v>78841</v>
+        <v>57737</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5352,34 +5344,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>431881</v>
+        <v>431756</v>
       </c>
       <c r="R49" t="n">
-        <v>6795522</v>
+        <v>6795202</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5438,10 +5438,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129707351</v>
+        <v>129694926</v>
       </c>
       <c r="B50" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -5481,10 +5481,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>431756</v>
+        <v>431711</v>
       </c>
       <c r="R50" t="n">
-        <v>6795202</v>
+        <v>6795100</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5531,22 +5531,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129694846</v>
+        <v>129707337</v>
       </c>
       <c r="B51" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5578,10 +5578,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>431725</v>
+        <v>431999</v>
       </c>
       <c r="R51" t="n">
-        <v>6795467</v>
+        <v>6795416</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5628,22 +5628,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129695006</v>
+        <v>129707380</v>
       </c>
       <c r="B52" t="n">
-        <v>79084</v>
+        <v>78844</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5651,21 +5651,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5675,10 +5675,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>431962</v>
+        <v>431820</v>
       </c>
       <c r="R52" t="n">
-        <v>6795319</v>
+        <v>6795330</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5725,22 +5725,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129695003</v>
+        <v>129694846</v>
       </c>
       <c r="B53" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5748,21 +5748,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>431908</v>
+        <v>431725</v>
       </c>
       <c r="R53" t="n">
-        <v>6795302</v>
+        <v>6795467</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5834,10 +5834,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129694994</v>
+        <v>129707347</v>
       </c>
       <c r="B54" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5845,34 +5845,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>431804</v>
+        <v>431662</v>
       </c>
       <c r="R54" t="n">
-        <v>6795151</v>
+        <v>6795391</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5919,22 +5927,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129707404</v>
+        <v>129695006</v>
       </c>
       <c r="B55" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5960,19 +5968,16 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>431816</v>
+        <v>431962</v>
       </c>
       <c r="R55" t="n">
-        <v>6795333</v>
+        <v>6795319</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6007,40 +6012,34 @@
           <t>2025-11-14</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129707337</v>
+        <v>129695003</v>
       </c>
       <c r="B56" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6048,21 +6047,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6072,10 +6071,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>431999</v>
+        <v>431908</v>
       </c>
       <c r="R56" t="n">
-        <v>6795416</v>
+        <v>6795302</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6122,22 +6121,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129707426</v>
+        <v>129694994</v>
       </c>
       <c r="B57" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6169,10 +6168,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>431767</v>
+        <v>431804</v>
       </c>
       <c r="R57" t="n">
-        <v>6795219</v>
+        <v>6795151</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6219,22 +6218,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129707380</v>
+        <v>129707426</v>
       </c>
       <c r="B58" t="n">
-        <v>78841</v>
+        <v>79087</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6242,21 +6241,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6266,10 +6265,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>431820</v>
+        <v>431767</v>
       </c>
       <c r="R58" t="n">
-        <v>6795330</v>
+        <v>6795219</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6328,10 +6327,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129707347</v>
+        <v>129707404</v>
       </c>
       <c r="B59" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6339,31 +6338,26 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6371,10 +6365,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>431662</v>
+        <v>431816</v>
       </c>
       <c r="R59" t="n">
-        <v>6795391</v>
+        <v>6795333</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6409,12 +6403,18 @@
           <t>2025-11-14</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6433,10 +6433,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129707319</v>
+        <v>129694988</v>
       </c>
       <c r="B60" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6444,21 +6444,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6468,10 +6468,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>431708</v>
+        <v>431718</v>
       </c>
       <c r="R60" t="n">
-        <v>6795371</v>
+        <v>6795068</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6518,22 +6518,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129694930</v>
+        <v>129707319</v>
       </c>
       <c r="B61" t="n">
-        <v>57734</v>
+        <v>79706</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6541,42 +6541,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>431875</v>
+        <v>431708</v>
       </c>
       <c r="R61" t="n">
-        <v>6795244</v>
+        <v>6795371</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6623,22 +6615,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129694872</v>
+        <v>129694961</v>
       </c>
       <c r="B62" t="n">
-        <v>79703</v>
+        <v>78844</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6646,21 +6638,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6670,10 +6662,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>431833</v>
+        <v>431804</v>
       </c>
       <c r="R62" t="n">
-        <v>6795171</v>
+        <v>6795100</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6732,10 +6724,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129694856</v>
+        <v>129694872</v>
       </c>
       <c r="B63" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6767,10 +6759,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>431693</v>
+        <v>431833</v>
       </c>
       <c r="R63" t="n">
-        <v>6795052</v>
+        <v>6795171</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6829,10 +6821,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129694961</v>
+        <v>129694856</v>
       </c>
       <c r="B64" t="n">
-        <v>78841</v>
+        <v>79706</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6840,21 +6832,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6864,10 +6856,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>431804</v>
+        <v>431693</v>
       </c>
       <c r="R64" t="n">
-        <v>6795100</v>
+        <v>6795052</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6926,10 +6918,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129694988</v>
+        <v>129694930</v>
       </c>
       <c r="B65" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6937,34 +6929,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>431718</v>
+        <v>431875</v>
       </c>
       <c r="R65" t="n">
-        <v>6795068</v>
+        <v>6795244</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7023,10 +7023,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129694928</v>
+        <v>129694857</v>
       </c>
       <c r="B66" t="n">
-        <v>57734</v>
+        <v>79706</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7034,42 +7034,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>431801</v>
+        <v>431800</v>
       </c>
       <c r="R66" t="n">
-        <v>6795136</v>
+        <v>6795130</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7128,10 +7120,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129694857</v>
+        <v>129694908</v>
       </c>
       <c r="B67" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7163,10 +7155,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>431800</v>
+        <v>431973</v>
       </c>
       <c r="R67" t="n">
-        <v>6795130</v>
+        <v>6795310</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7225,10 +7217,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129694908</v>
+        <v>129694858</v>
       </c>
       <c r="B68" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7260,10 +7252,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>431973</v>
+        <v>431749</v>
       </c>
       <c r="R68" t="n">
-        <v>6795310</v>
+        <v>6795079</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7322,10 +7314,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129694858</v>
+        <v>129694859</v>
       </c>
       <c r="B69" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7357,10 +7349,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>431749</v>
+        <v>431702</v>
       </c>
       <c r="R69" t="n">
-        <v>6795079</v>
+        <v>6795115</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7419,10 +7411,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129694859</v>
+        <v>129694879</v>
       </c>
       <c r="B70" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7454,10 +7446,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>431702</v>
+        <v>431888</v>
       </c>
       <c r="R70" t="n">
-        <v>6795115</v>
+        <v>6795198</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7516,10 +7508,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129694879</v>
+        <v>129694928</v>
       </c>
       <c r="B71" t="n">
-        <v>79703</v>
+        <v>57737</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7527,34 +7519,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>431888</v>
+        <v>431801</v>
       </c>
       <c r="R71" t="n">
-        <v>6795198</v>
+        <v>6795136</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7613,10 +7613,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129707420</v>
+        <v>129707382</v>
       </c>
       <c r="B72" t="n">
-        <v>79084</v>
+        <v>78844</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7624,34 +7624,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>431695</v>
+        <v>431689</v>
       </c>
       <c r="R72" t="n">
-        <v>6795256</v>
+        <v>6795383</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7692,6 +7695,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7710,10 +7714,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129707382</v>
+        <v>129707420</v>
       </c>
       <c r="B73" t="n">
-        <v>78841</v>
+        <v>79087</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7721,37 +7725,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>431689</v>
+        <v>431695</v>
       </c>
       <c r="R73" t="n">
-        <v>6795383</v>
+        <v>6795256</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7792,7 +7793,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7811,32 +7811,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129707317</v>
+        <v>129707439</v>
       </c>
       <c r="B74" t="n">
-        <v>79703</v>
+        <v>92887</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7846,10 +7846,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>431780</v>
+        <v>431891</v>
       </c>
       <c r="R74" t="n">
-        <v>6795362</v>
+        <v>6795553</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7908,10 +7908,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129707391</v>
+        <v>129694985</v>
       </c>
       <c r="B75" t="n">
-        <v>78841</v>
+        <v>79087</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7919,21 +7919,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7943,10 +7943,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>431724</v>
+        <v>431673</v>
       </c>
       <c r="R75" t="n">
-        <v>6795372</v>
+        <v>6795435</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7993,22 +7993,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129707389</v>
+        <v>129707391</v>
       </c>
       <c r="B76" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8034,19 +8034,16 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>431922</v>
+        <v>431724</v>
       </c>
       <c r="R76" t="n">
-        <v>6795405</v>
+        <v>6795372</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8087,7 +8084,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8106,10 +8102,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129707314</v>
+        <v>129707389</v>
       </c>
       <c r="B77" t="n">
-        <v>79703</v>
+        <v>78844</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8117,34 +8113,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>431866</v>
+        <v>431922</v>
       </c>
       <c r="R77" t="n">
-        <v>6795513</v>
+        <v>6795405</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8185,6 +8184,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8203,10 +8203,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129694985</v>
+        <v>129707317</v>
       </c>
       <c r="B78" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8214,21 +8214,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8238,10 +8238,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>431673</v>
+        <v>431780</v>
       </c>
       <c r="R78" t="n">
-        <v>6795435</v>
+        <v>6795362</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8288,44 +8288,44 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129707439</v>
+        <v>129707314</v>
       </c>
       <c r="B79" t="n">
-        <v>92884</v>
+        <v>79706</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8335,10 +8335,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>431891</v>
+        <v>431866</v>
       </c>
       <c r="R79" t="n">
-        <v>6795553</v>
+        <v>6795513</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8397,10 +8397,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129694933</v>
+        <v>129695001</v>
       </c>
       <c r="B80" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8408,42 +8408,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>431904</v>
+        <v>431876</v>
       </c>
       <c r="R80" t="n">
-        <v>6795243</v>
+        <v>6795202</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8502,10 +8494,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129694863</v>
+        <v>129694991</v>
       </c>
       <c r="B81" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8513,21 +8505,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8537,10 +8529,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>431785</v>
+        <v>431760</v>
       </c>
       <c r="R81" t="n">
-        <v>6795106</v>
+        <v>6795115</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8599,10 +8591,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129694874</v>
+        <v>129707388</v>
       </c>
       <c r="B82" t="n">
-        <v>79703</v>
+        <v>78844</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8610,21 +8602,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8634,10 +8626,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>431827</v>
+        <v>431915</v>
       </c>
       <c r="R82" t="n">
-        <v>6795171</v>
+        <v>6795392</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8684,22 +8676,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129695001</v>
+        <v>129707424</v>
       </c>
       <c r="B83" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8731,10 +8723,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>431876</v>
+        <v>431760</v>
       </c>
       <c r="R83" t="n">
-        <v>6795202</v>
+        <v>6795200</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8781,22 +8773,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129694991</v>
+        <v>129707315</v>
       </c>
       <c r="B84" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8804,21 +8796,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8828,10 +8820,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>431760</v>
+        <v>431820</v>
       </c>
       <c r="R84" t="n">
-        <v>6795115</v>
+        <v>6795329</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8878,22 +8870,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129694948</v>
+        <v>129694863</v>
       </c>
       <c r="B85" t="n">
-        <v>78842</v>
+        <v>79706</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8901,21 +8893,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8925,10 +8917,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>431725</v>
+        <v>431785</v>
       </c>
       <c r="R85" t="n">
-        <v>6795459</v>
+        <v>6795106</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8987,10 +8979,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129707388</v>
+        <v>129694874</v>
       </c>
       <c r="B86" t="n">
-        <v>78841</v>
+        <v>79706</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8998,21 +8990,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9022,10 +9014,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>431915</v>
+        <v>431827</v>
       </c>
       <c r="R86" t="n">
-        <v>6795392</v>
+        <v>6795171</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9072,22 +9064,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129707315</v>
+        <v>129707345</v>
       </c>
       <c r="B87" t="n">
-        <v>79703</v>
+        <v>57737</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9095,34 +9087,42 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>431820</v>
+        <v>431893</v>
       </c>
       <c r="R87" t="n">
-        <v>6795329</v>
+        <v>6795571</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9181,10 +9181,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129707424</v>
+        <v>129694933</v>
       </c>
       <c r="B88" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9192,34 +9192,42 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>431760</v>
+        <v>431904</v>
       </c>
       <c r="R88" t="n">
-        <v>6795200</v>
+        <v>6795243</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9266,22 +9274,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129707345</v>
+        <v>129694948</v>
       </c>
       <c r="B89" t="n">
-        <v>57734</v>
+        <v>78845</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9289,42 +9297,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>431893</v>
+        <v>431725</v>
       </c>
       <c r="R89" t="n">
-        <v>6795571</v>
+        <v>6795459</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9371,22 +9371,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129694939</v>
+        <v>129707405</v>
       </c>
       <c r="B90" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9394,21 +9394,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9418,10 +9418,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>431913</v>
+        <v>431775</v>
       </c>
       <c r="R90" t="n">
-        <v>6795284</v>
+        <v>6795343</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9456,11 +9456,6 @@
           <t>2025-11-14</t>
         </is>
       </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
-        </is>
-      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
@@ -9473,22 +9468,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129694934</v>
+        <v>129707381</v>
       </c>
       <c r="B91" t="n">
-        <v>57734</v>
+        <v>78844</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9496,42 +9491,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>431916</v>
+        <v>431712</v>
       </c>
       <c r="R91" t="n">
-        <v>6795286</v>
+        <v>6795379</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9578,22 +9565,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129694860</v>
+        <v>129694965</v>
       </c>
       <c r="B92" t="n">
-        <v>79703</v>
+        <v>78844</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9601,21 +9588,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9625,10 +9612,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>431746</v>
+        <v>431885</v>
       </c>
       <c r="R92" t="n">
-        <v>6795081</v>
+        <v>6795240</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9687,10 +9674,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129694965</v>
+        <v>129694860</v>
       </c>
       <c r="B93" t="n">
-        <v>78841</v>
+        <v>79706</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9698,21 +9685,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9722,10 +9709,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>431885</v>
+        <v>431746</v>
       </c>
       <c r="R93" t="n">
-        <v>6795240</v>
+        <v>6795081</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9784,10 +9771,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129707405</v>
+        <v>129694939</v>
       </c>
       <c r="B94" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9795,21 +9782,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9819,10 +9806,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>431775</v>
+        <v>431913</v>
       </c>
       <c r="R94" t="n">
-        <v>6795343</v>
+        <v>6795284</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9857,6 +9844,11 @@
           <t>2025-11-14</t>
         </is>
       </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
@@ -9869,22 +9861,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129707381</v>
+        <v>129694934</v>
       </c>
       <c r="B95" t="n">
-        <v>78841</v>
+        <v>57737</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9892,34 +9884,42 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>431712</v>
+        <v>431916</v>
       </c>
       <c r="R95" t="n">
-        <v>6795379</v>
+        <v>6795286</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9966,22 +9966,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129694977</v>
+        <v>129694989</v>
       </c>
       <c r="B96" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9989,42 +9989,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>431933</v>
+        <v>431723</v>
       </c>
       <c r="R96" t="n">
-        <v>6795295</v>
+        <v>6795090</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10083,10 +10075,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129694989</v>
+        <v>129707312</v>
       </c>
       <c r="B97" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10094,21 +10086,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10118,10 +10110,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>431723</v>
+        <v>431920</v>
       </c>
       <c r="R97" t="n">
-        <v>6795090</v>
+        <v>6795611</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10168,12 +10160,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -10183,7 +10175,7 @@
         <v>129694941</v>
       </c>
       <c r="B98" t="n">
-        <v>79170</v>
+        <v>79173</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10277,10 +10269,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129707312</v>
+        <v>129694977</v>
       </c>
       <c r="B99" t="n">
-        <v>79703</v>
+        <v>57737</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10288,34 +10280,42 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>431920</v>
+        <v>431933</v>
       </c>
       <c r="R99" t="n">
-        <v>6795611</v>
+        <v>6795295</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10362,22 +10362,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129707349</v>
+        <v>129695000</v>
       </c>
       <c r="B100" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10385,42 +10385,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>431722</v>
+        <v>431890</v>
       </c>
       <c r="R100" t="n">
-        <v>6795217</v>
+        <v>6795199</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10467,22 +10459,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129694927</v>
+        <v>129694992</v>
       </c>
       <c r="B101" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10490,42 +10482,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>431711</v>
+        <v>431799</v>
       </c>
       <c r="R101" t="n">
-        <v>6795094</v>
+        <v>6795129</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10584,10 +10568,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129694938</v>
+        <v>129707397</v>
       </c>
       <c r="B102" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10595,32 +10579,24 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
@@ -10630,7 +10606,7 @@
         <v>431915</v>
       </c>
       <c r="R102" t="n">
-        <v>6795279</v>
+        <v>6795541</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10677,22 +10653,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129695000</v>
+        <v>129707396</v>
       </c>
       <c r="B103" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10724,10 +10700,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>431890</v>
+        <v>431918</v>
       </c>
       <c r="R103" t="n">
-        <v>6795199</v>
+        <v>6795574</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10774,22 +10750,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129694877</v>
+        <v>129707406</v>
       </c>
       <c r="B104" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10797,21 +10773,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10821,10 +10797,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>431887</v>
+        <v>431771</v>
       </c>
       <c r="R104" t="n">
-        <v>6795183</v>
+        <v>6795344</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10871,22 +10847,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129694885</v>
+        <v>129707425</v>
       </c>
       <c r="B105" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10894,21 +10870,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10918,10 +10894,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>431873</v>
+        <v>431756</v>
       </c>
       <c r="R105" t="n">
-        <v>6795224</v>
+        <v>6795247</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10968,22 +10944,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129694864</v>
+        <v>129694877</v>
       </c>
       <c r="B106" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11015,10 +10991,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>431786</v>
+        <v>431887</v>
       </c>
       <c r="R106" t="n">
-        <v>6795113</v>
+        <v>6795183</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11077,10 +11053,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129694992</v>
+        <v>129694885</v>
       </c>
       <c r="B107" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11088,21 +11064,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11112,10 +11088,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>431799</v>
+        <v>431873</v>
       </c>
       <c r="R107" t="n">
-        <v>6795129</v>
+        <v>6795224</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11174,10 +11150,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129707397</v>
+        <v>129694864</v>
       </c>
       <c r="B108" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11185,21 +11161,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11209,10 +11185,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>431915</v>
+        <v>431786</v>
       </c>
       <c r="R108" t="n">
-        <v>6795541</v>
+        <v>6795113</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11259,22 +11235,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129707327</v>
+        <v>129707349</v>
       </c>
       <c r="B109" t="n">
-        <v>79703</v>
+        <v>57737</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11282,34 +11258,42 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>431893</v>
+        <v>431722</v>
       </c>
       <c r="R109" t="n">
-        <v>6795305</v>
+        <v>6795217</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11368,10 +11352,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129707396</v>
+        <v>129694927</v>
       </c>
       <c r="B110" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11379,34 +11363,42 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>431918</v>
+        <v>431711</v>
       </c>
       <c r="R110" t="n">
-        <v>6795574</v>
+        <v>6795094</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11453,22 +11445,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129707406</v>
+        <v>129694938</v>
       </c>
       <c r="B111" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11476,34 +11468,42 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>431771</v>
+        <v>431915</v>
       </c>
       <c r="R111" t="n">
-        <v>6795344</v>
+        <v>6795279</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11550,22 +11550,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129707332</v>
+        <v>129707327</v>
       </c>
       <c r="B112" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11597,10 +11597,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>431923</v>
+        <v>431893</v>
       </c>
       <c r="R112" t="n">
-        <v>6795402</v>
+        <v>6795305</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11659,10 +11659,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129707425</v>
+        <v>129707332</v>
       </c>
       <c r="B113" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11670,21 +11670,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11694,10 +11694,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>431756</v>
+        <v>431923</v>
       </c>
       <c r="R113" t="n">
-        <v>6795247</v>
+        <v>6795402</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11756,10 +11756,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129694901</v>
+        <v>129694990</v>
       </c>
       <c r="B114" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11767,21 +11767,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11791,10 +11791,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>431927</v>
+        <v>431726</v>
       </c>
       <c r="R114" t="n">
-        <v>6795265</v>
+        <v>6795117</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11853,10 +11853,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129694990</v>
+        <v>129707386</v>
       </c>
       <c r="B115" t="n">
-        <v>79084</v>
+        <v>78844</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11864,21 +11864,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11888,10 +11888,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>431726</v>
+        <v>431897</v>
       </c>
       <c r="R115" t="n">
-        <v>6795117</v>
+        <v>6795284</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11938,22 +11938,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129694844</v>
+        <v>129707421</v>
       </c>
       <c r="B116" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11961,21 +11961,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11985,10 +11985,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>431739</v>
+        <v>431711</v>
       </c>
       <c r="R116" t="n">
-        <v>6795440</v>
+        <v>6795239</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12035,12 +12035,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
@@ -12050,7 +12050,7 @@
         <v>129707309</v>
       </c>
       <c r="B117" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12147,7 +12147,7 @@
         <v>129707330</v>
       </c>
       <c r="B118" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12244,7 +12244,7 @@
         <v>129707323</v>
       </c>
       <c r="B119" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12338,10 +12338,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129707386</v>
+        <v>129694901</v>
       </c>
       <c r="B120" t="n">
-        <v>78841</v>
+        <v>79706</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12349,21 +12349,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12373,10 +12373,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>431897</v>
+        <v>431927</v>
       </c>
       <c r="R120" t="n">
-        <v>6795284</v>
+        <v>6795265</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12423,22 +12423,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129707421</v>
+        <v>129694844</v>
       </c>
       <c r="B121" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12446,21 +12446,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12470,10 +12470,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>431711</v>
+        <v>431739</v>
       </c>
       <c r="R121" t="n">
-        <v>6795239</v>
+        <v>6795440</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12520,65 +12520,57 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129694925</v>
+        <v>129695013</v>
       </c>
       <c r="B122" t="n">
-        <v>57734</v>
+        <v>92887</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>431687</v>
+        <v>431869</v>
       </c>
       <c r="R122" t="n">
-        <v>6795051</v>
+        <v>6795173</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12637,10 +12629,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129694850</v>
+        <v>129694997</v>
       </c>
       <c r="B123" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12648,21 +12640,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12672,10 +12664,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>431686</v>
+        <v>431848</v>
       </c>
       <c r="R123" t="n">
-        <v>6795471</v>
+        <v>6795172</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12734,10 +12726,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129694881</v>
+        <v>129694850</v>
       </c>
       <c r="B124" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12769,10 +12761,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>431875</v>
+        <v>431686</v>
       </c>
       <c r="R124" t="n">
-        <v>6795212</v>
+        <v>6795471</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12831,10 +12823,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129694888</v>
+        <v>129694881</v>
       </c>
       <c r="B125" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12866,10 +12858,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>431889</v>
+        <v>431875</v>
       </c>
       <c r="R125" t="n">
-        <v>6795236</v>
+        <v>6795212</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12928,10 +12920,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129694997</v>
+        <v>129694888</v>
       </c>
       <c r="B126" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12939,21 +12931,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -12963,10 +12955,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>431848</v>
+        <v>431889</v>
       </c>
       <c r="R126" t="n">
-        <v>6795172</v>
+        <v>6795236</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13025,10 +13017,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129707368</v>
+        <v>129694925</v>
       </c>
       <c r="B127" t="n">
-        <v>78842</v>
+        <v>57737</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13036,26 +13028,31 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
@@ -13063,10 +13060,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>431820</v>
+        <v>431687</v>
       </c>
       <c r="R127" t="n">
-        <v>6795331</v>
+        <v>6795051</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13107,64 +13104,66 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129695013</v>
+        <v>129707368</v>
       </c>
       <c r="B128" t="n">
-        <v>92884</v>
+        <v>78845</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>431869</v>
+        <v>431820</v>
       </c>
       <c r="R128" t="n">
-        <v>6795173</v>
+        <v>6795331</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13205,18 +13204,19 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
@@ -13226,7 +13226,7 @@
         <v>129707311</v>
       </c>
       <c r="B129" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13320,10 +13320,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129694900</v>
+        <v>129707399</v>
       </c>
       <c r="B130" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13331,21 +13331,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13355,10 +13355,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>431907</v>
+        <v>431819</v>
       </c>
       <c r="R130" t="n">
-        <v>6795266</v>
+        <v>6795445</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13405,22 +13405,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129694906</v>
+        <v>129707387</v>
       </c>
       <c r="B131" t="n">
-        <v>79703</v>
+        <v>78844</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13428,21 +13428,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13452,10 +13452,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>431934</v>
+        <v>431936</v>
       </c>
       <c r="R131" t="n">
-        <v>6795286</v>
+        <v>6795393</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13502,22 +13502,22 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129707399</v>
+        <v>129707438</v>
       </c>
       <c r="B132" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13549,10 +13549,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>431819</v>
+        <v>431965</v>
       </c>
       <c r="R132" t="n">
-        <v>6795445</v>
+        <v>6795405</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13611,10 +13611,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129707387</v>
+        <v>129707318</v>
       </c>
       <c r="B133" t="n">
-        <v>78841</v>
+        <v>79706</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13622,21 +13622,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13646,10 +13646,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>431936</v>
+        <v>431769</v>
       </c>
       <c r="R133" t="n">
-        <v>6795393</v>
+        <v>6795345</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13708,10 +13708,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129707438</v>
+        <v>129694900</v>
       </c>
       <c r="B134" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13719,21 +13719,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13743,10 +13743,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>431965</v>
+        <v>431907</v>
       </c>
       <c r="R134" t="n">
-        <v>6795405</v>
+        <v>6795266</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13793,22 +13793,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129707318</v>
+        <v>129694906</v>
       </c>
       <c r="B135" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13840,10 +13840,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>431769</v>
+        <v>431934</v>
       </c>
       <c r="R135" t="n">
-        <v>6795345</v>
+        <v>6795286</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -13890,22 +13890,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129694866</v>
+        <v>129694956</v>
       </c>
       <c r="B136" t="n">
-        <v>79703</v>
+        <v>92023</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13913,34 +13913,38 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6453</v>
+        <v>6040162</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallkötticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>431797</v>
+        <v>431718</v>
       </c>
       <c r="R136" t="n">
-        <v>6795173</v>
+        <v>6795082</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -13975,12 +13979,18 @@
           <t>2025-11-14</t>
         </is>
       </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Mjuk och len på undetsidan, sämskskinnslik känsla</t>
+        </is>
+      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -13999,10 +14009,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129694865</v>
+        <v>129707370</v>
       </c>
       <c r="B137" t="n">
-        <v>79703</v>
+        <v>78845</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14010,21 +14020,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14034,10 +14044,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>431787</v>
+        <v>431913</v>
       </c>
       <c r="R137" t="n">
-        <v>6795115</v>
+        <v>6795394</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14084,22 +14094,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129694896</v>
+        <v>129707334</v>
       </c>
       <c r="B138" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14131,10 +14141,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>431900</v>
+        <v>431936</v>
       </c>
       <c r="R138" t="n">
-        <v>6795265</v>
+        <v>6795411</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14181,22 +14191,22 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129694956</v>
+        <v>129694866</v>
       </c>
       <c r="B139" t="n">
-        <v>92020</v>
+        <v>79706</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14204,38 +14214,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6040162</v>
+        <v>6453</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tallkötticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>431718</v>
+        <v>431797</v>
       </c>
       <c r="R139" t="n">
-        <v>6795082</v>
+        <v>6795173</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14270,18 +14276,12 @@
           <t>2025-11-14</t>
         </is>
       </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>Mjuk och len på undetsidan, sämskskinnslik känsla</t>
-        </is>
-      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -14300,10 +14300,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129707334</v>
+        <v>129694865</v>
       </c>
       <c r="B140" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14335,10 +14335,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>431936</v>
+        <v>431787</v>
       </c>
       <c r="R140" t="n">
-        <v>6795411</v>
+        <v>6795115</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14385,22 +14385,22 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129707370</v>
+        <v>129694896</v>
       </c>
       <c r="B141" t="n">
-        <v>78842</v>
+        <v>79706</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14408,21 +14408,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14432,10 +14432,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>431913</v>
+        <v>431900</v>
       </c>
       <c r="R141" t="n">
-        <v>6795394</v>
+        <v>6795265</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14482,12 +14482,12 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
@@ -14497,7 +14497,7 @@
         <v>129694876</v>
       </c>
       <c r="B142" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14594,7 +14594,7 @@
         <v>129694887</v>
       </c>
       <c r="B143" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14691,7 +14691,7 @@
         <v>129694880</v>
       </c>
       <c r="B144" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14788,7 +14788,7 @@
         <v>129694897</v>
       </c>
       <c r="B145" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14885,7 +14885,7 @@
         <v>129707377</v>
       </c>
       <c r="B146" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
         <v>129707366</v>
       </c>
       <c r="B147" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>

--- a/artfynd/A 50492-2025 artfynd.xlsx
+++ b/artfynd/A 50492-2025 artfynd.xlsx
@@ -1578,10 +1578,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129707434</v>
+        <v>129694918</v>
       </c>
       <c r="B11" t="n">
-        <v>79087</v>
+        <v>91626</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1589,34 +1589,41 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>431894</v>
+        <v>431722</v>
       </c>
       <c r="R11" t="n">
-        <v>6795261</v>
+        <v>6795120</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1657,28 +1664,29 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129707336</v>
+        <v>129694983</v>
       </c>
       <c r="B12" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1686,21 +1694,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1710,10 +1718,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>431993</v>
+        <v>431689</v>
       </c>
       <c r="R12" t="n">
-        <v>6795380</v>
+        <v>6795456</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1760,12 +1768,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1966,10 +1974,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129694923</v>
+        <v>129707434</v>
       </c>
       <c r="B15" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1977,42 +1985,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>431687</v>
+        <v>431894</v>
       </c>
       <c r="R15" t="n">
-        <v>6795471</v>
+        <v>6795261</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2059,22 +2059,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129694918</v>
+        <v>129707336</v>
       </c>
       <c r="B16" t="n">
-        <v>91626</v>
+        <v>79706</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2082,41 +2082,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>431722</v>
+        <v>431993</v>
       </c>
       <c r="R16" t="n">
-        <v>6795120</v>
+        <v>6795380</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2157,29 +2150,28 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129694983</v>
+        <v>129707358</v>
       </c>
       <c r="B17" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2187,34 +2179,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>431689</v>
+        <v>431912</v>
       </c>
       <c r="R17" t="n">
-        <v>6795456</v>
+        <v>6795310</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2261,19 +2261,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129707358</v>
+        <v>129694923</v>
       </c>
       <c r="B18" t="n">
         <v>57737</v>
@@ -2306,7 +2306,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2316,10 +2316,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>431912</v>
+        <v>431687</v>
       </c>
       <c r="R18" t="n">
-        <v>6795310</v>
+        <v>6795471</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2366,65 +2366,57 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129694913</v>
+        <v>129707378</v>
       </c>
       <c r="B19" t="n">
-        <v>56930</v>
+        <v>78844</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>431728</v>
+        <v>431814</v>
       </c>
       <c r="R19" t="n">
-        <v>6795109</v>
+        <v>6795444</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2471,22 +2463,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129707378</v>
+        <v>129707310</v>
       </c>
       <c r="B20" t="n">
-        <v>78844</v>
+        <v>79706</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2494,21 +2486,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2518,10 +2510,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>431814</v>
+        <v>431924</v>
       </c>
       <c r="R20" t="n">
-        <v>6795444</v>
+        <v>6795546</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2580,7 +2572,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129707310</v>
+        <v>129707335</v>
       </c>
       <c r="B21" t="n">
         <v>79706</v>
@@ -2615,10 +2607,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>431924</v>
+        <v>431965</v>
       </c>
       <c r="R21" t="n">
-        <v>6795546</v>
+        <v>6795430</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2677,7 +2669,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129707335</v>
+        <v>129694845</v>
       </c>
       <c r="B22" t="n">
         <v>79706</v>
@@ -2712,10 +2704,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>431965</v>
+        <v>431722</v>
       </c>
       <c r="R22" t="n">
-        <v>6795430</v>
+        <v>6795478</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2762,57 +2754,65 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129694845</v>
+        <v>129694913</v>
       </c>
       <c r="B23" t="n">
-        <v>79706</v>
+        <v>56930</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>431722</v>
+        <v>431728</v>
       </c>
       <c r="R23" t="n">
-        <v>6795478</v>
+        <v>6795109</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2871,10 +2871,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129694942</v>
+        <v>129707407</v>
       </c>
       <c r="B24" t="n">
-        <v>91903</v>
+        <v>79087</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2882,21 +2882,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2906,10 +2906,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>431803</v>
+        <v>431723</v>
       </c>
       <c r="R24" t="n">
-        <v>6795150</v>
+        <v>6795371</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2950,29 +2950,28 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129707407</v>
+        <v>129707308</v>
       </c>
       <c r="B25" t="n">
-        <v>79087</v>
+        <v>79706</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2980,21 +2979,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3004,10 +3003,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>431723</v>
+        <v>431868</v>
       </c>
       <c r="R25" t="n">
-        <v>6795371</v>
+        <v>6795565</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3066,7 +3065,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129707308</v>
+        <v>129707331</v>
       </c>
       <c r="B26" t="n">
         <v>79706</v>
@@ -3095,16 +3094,19 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>431868</v>
+        <v>431916</v>
       </c>
       <c r="R26" t="n">
-        <v>6795565</v>
+        <v>6795392</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3145,6 +3147,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3163,10 +3166,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129707331</v>
+        <v>129694942</v>
       </c>
       <c r="B27" t="n">
-        <v>79706</v>
+        <v>91903</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3174,37 +3177,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>431916</v>
+        <v>431803</v>
       </c>
       <c r="R27" t="n">
-        <v>6795392</v>
+        <v>6795150</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3252,12 +3252,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -9383,10 +9383,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129707405</v>
+        <v>129694860</v>
       </c>
       <c r="B90" t="n">
-        <v>79087</v>
+        <v>79706</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9394,21 +9394,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9418,10 +9418,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>431775</v>
+        <v>431746</v>
       </c>
       <c r="R90" t="n">
-        <v>6795343</v>
+        <v>6795081</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9468,22 +9468,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129707381</v>
+        <v>129694939</v>
       </c>
       <c r="B91" t="n">
-        <v>78844</v>
+        <v>57737</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9491,21 +9491,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>431712</v>
+        <v>431913</v>
       </c>
       <c r="R91" t="n">
-        <v>6795379</v>
+        <v>6795284</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9553,6 +9553,11 @@
           <t>2025-11-14</t>
         </is>
       </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
@@ -9565,22 +9570,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129694965</v>
+        <v>129694934</v>
       </c>
       <c r="B92" t="n">
-        <v>78844</v>
+        <v>57737</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9588,34 +9593,42 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>431885</v>
+        <v>431916</v>
       </c>
       <c r="R92" t="n">
-        <v>6795240</v>
+        <v>6795286</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9674,10 +9687,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129694860</v>
+        <v>129707405</v>
       </c>
       <c r="B93" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9685,21 +9698,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9709,10 +9722,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>431746</v>
+        <v>431775</v>
       </c>
       <c r="R93" t="n">
-        <v>6795081</v>
+        <v>6795343</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9759,22 +9772,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129694939</v>
+        <v>129707381</v>
       </c>
       <c r="B94" t="n">
-        <v>57737</v>
+        <v>78844</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9782,21 +9795,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9806,10 +9819,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>431913</v>
+        <v>431712</v>
       </c>
       <c r="R94" t="n">
-        <v>6795284</v>
+        <v>6795379</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9844,11 +9857,6 @@
           <t>2025-11-14</t>
         </is>
       </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
-        </is>
-      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
@@ -9861,22 +9869,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129694934</v>
+        <v>129694965</v>
       </c>
       <c r="B95" t="n">
-        <v>57737</v>
+        <v>78844</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9884,42 +9892,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>431916</v>
+        <v>431885</v>
       </c>
       <c r="R95" t="n">
-        <v>6795286</v>
+        <v>6795240</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12532,32 +12532,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129695013</v>
+        <v>129694850</v>
       </c>
       <c r="B122" t="n">
-        <v>92887</v>
+        <v>79706</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12567,10 +12567,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>431869</v>
+        <v>431686</v>
       </c>
       <c r="R122" t="n">
-        <v>6795173</v>
+        <v>6795471</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12629,10 +12629,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129694997</v>
+        <v>129694881</v>
       </c>
       <c r="B123" t="n">
-        <v>79087</v>
+        <v>79706</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12640,21 +12640,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12664,10 +12664,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>431848</v>
+        <v>431875</v>
       </c>
       <c r="R123" t="n">
-        <v>6795172</v>
+        <v>6795212</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12726,7 +12726,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129694850</v>
+        <v>129694888</v>
       </c>
       <c r="B124" t="n">
         <v>79706</v>
@@ -12761,10 +12761,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>431686</v>
+        <v>431889</v>
       </c>
       <c r="R124" t="n">
-        <v>6795471</v>
+        <v>6795236</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12823,10 +12823,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129694881</v>
+        <v>129707368</v>
       </c>
       <c r="B125" t="n">
-        <v>79706</v>
+        <v>78845</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12834,34 +12834,37 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>431875</v>
+        <v>431820</v>
       </c>
       <c r="R125" t="n">
-        <v>6795212</v>
+        <v>6795331</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12902,50 +12905,51 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129694888</v>
+        <v>129695013</v>
       </c>
       <c r="B126" t="n">
-        <v>79706</v>
+        <v>92887</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -12955,10 +12959,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>431889</v>
+        <v>431869</v>
       </c>
       <c r="R126" t="n">
-        <v>6795236</v>
+        <v>6795173</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13017,10 +13021,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129694925</v>
+        <v>129694997</v>
       </c>
       <c r="B127" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13028,42 +13032,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>431687</v>
+        <v>431848</v>
       </c>
       <c r="R127" t="n">
-        <v>6795051</v>
+        <v>6795172</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13122,10 +13118,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129707368</v>
+        <v>129694925</v>
       </c>
       <c r="B128" t="n">
-        <v>78845</v>
+        <v>57737</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13133,26 +13129,31 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
@@ -13160,10 +13161,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>431820</v>
+        <v>431687</v>
       </c>
       <c r="R128" t="n">
-        <v>6795331</v>
+        <v>6795051</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13204,19 +13205,18 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>

--- a/artfynd/A 50492-2025 artfynd.xlsx
+++ b/artfynd/A 50492-2025 artfynd.xlsx
@@ -2378,45 +2378,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129707378</v>
+        <v>129694913</v>
       </c>
       <c r="B19" t="n">
-        <v>78844</v>
+        <v>56930</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>431814</v>
+        <v>431728</v>
       </c>
       <c r="R19" t="n">
-        <v>6795444</v>
+        <v>6795109</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2463,22 +2471,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129707310</v>
+        <v>129707378</v>
       </c>
       <c r="B20" t="n">
-        <v>79706</v>
+        <v>78844</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2486,21 +2494,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2510,10 +2518,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>431924</v>
+        <v>431814</v>
       </c>
       <c r="R20" t="n">
-        <v>6795546</v>
+        <v>6795444</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2572,7 +2580,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129707335</v>
+        <v>129707310</v>
       </c>
       <c r="B21" t="n">
         <v>79706</v>
@@ -2607,10 +2615,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>431965</v>
+        <v>431924</v>
       </c>
       <c r="R21" t="n">
-        <v>6795430</v>
+        <v>6795546</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2669,7 +2677,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129694845</v>
+        <v>129707335</v>
       </c>
       <c r="B22" t="n">
         <v>79706</v>
@@ -2704,10 +2712,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>431722</v>
+        <v>431965</v>
       </c>
       <c r="R22" t="n">
-        <v>6795478</v>
+        <v>6795430</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2754,65 +2762,57 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129694913</v>
+        <v>129694845</v>
       </c>
       <c r="B23" t="n">
-        <v>56930</v>
+        <v>79706</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>431728</v>
+        <v>431722</v>
       </c>
       <c r="R23" t="n">
-        <v>6795109</v>
+        <v>6795478</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3749,48 +3749,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129694839</v>
+        <v>129695010</v>
       </c>
       <c r="B33" t="n">
-        <v>91528</v>
+        <v>92887</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3242</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>431869</v>
+        <v>431880</v>
       </c>
       <c r="R33" t="n">
-        <v>6795181</v>
+        <v>6795546</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3831,7 +3828,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3850,45 +3846,53 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129695010</v>
+        <v>129707346</v>
       </c>
       <c r="B34" t="n">
-        <v>92887</v>
+        <v>57737</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>431880</v>
+        <v>431819</v>
       </c>
       <c r="R34" t="n">
-        <v>6795546</v>
+        <v>6795465</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3935,22 +3939,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129694917</v>
+        <v>129694921</v>
       </c>
       <c r="B35" t="n">
-        <v>91626</v>
+        <v>57737</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3958,30 +3962,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -3989,10 +3994,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>431672</v>
+        <v>431725</v>
       </c>
       <c r="R35" t="n">
-        <v>6795442</v>
+        <v>6795459</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4033,7 +4038,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4246,10 +4250,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129707390</v>
+        <v>129694839</v>
       </c>
       <c r="B38" t="n">
-        <v>78844</v>
+        <v>91528</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4257,21 +4261,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>3242</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4284,10 +4288,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>431952</v>
+        <v>431869</v>
       </c>
       <c r="R38" t="n">
-        <v>6795410</v>
+        <v>6795181</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4335,22 +4339,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129694980</v>
+        <v>129694917</v>
       </c>
       <c r="B39" t="n">
-        <v>79087</v>
+        <v>91626</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4358,34 +4362,41 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>431711</v>
+        <v>431672</v>
       </c>
       <c r="R39" t="n">
-        <v>6795450</v>
+        <v>6795442</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4426,6 +4437,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4444,10 +4456,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129707346</v>
+        <v>129707390</v>
       </c>
       <c r="B40" t="n">
-        <v>57737</v>
+        <v>78844</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4455,31 +4467,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4487,10 +4494,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>431819</v>
+        <v>431952</v>
       </c>
       <c r="R40" t="n">
-        <v>6795465</v>
+        <v>6795410</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4531,6 +4538,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4549,10 +4557,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129694921</v>
+        <v>129694980</v>
       </c>
       <c r="B41" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4560,42 +4568,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>431725</v>
+        <v>431711</v>
       </c>
       <c r="R41" t="n">
-        <v>6795459</v>
+        <v>6795450</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4654,10 +4654,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129694999</v>
+        <v>129694926</v>
       </c>
       <c r="B42" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4665,34 +4665,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>431859</v>
+        <v>431711</v>
       </c>
       <c r="R42" t="n">
-        <v>6795172</v>
+        <v>6795100</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4751,10 +4759,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129707320</v>
+        <v>129694999</v>
       </c>
       <c r="B43" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4762,21 +4770,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4786,10 +4794,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>431717</v>
+        <v>431859</v>
       </c>
       <c r="R43" t="n">
-        <v>6795380</v>
+        <v>6795172</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4836,19 +4844,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129707316</v>
+        <v>129707320</v>
       </c>
       <c r="B44" t="n">
         <v>79706</v>
@@ -4883,10 +4891,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>431812</v>
+        <v>431717</v>
       </c>
       <c r="R44" t="n">
-        <v>6795349</v>
+        <v>6795380</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4945,7 +4953,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129707333</v>
+        <v>129707316</v>
       </c>
       <c r="B45" t="n">
         <v>79706</v>
@@ -4980,10 +4988,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>431935</v>
+        <v>431812</v>
       </c>
       <c r="R45" t="n">
-        <v>6795415</v>
+        <v>6795349</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5042,7 +5050,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129707338</v>
+        <v>129707333</v>
       </c>
       <c r="B46" t="n">
         <v>79706</v>
@@ -5077,10 +5085,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>431932</v>
+        <v>431935</v>
       </c>
       <c r="R46" t="n">
-        <v>6795406</v>
+        <v>6795415</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5139,10 +5147,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129707375</v>
+        <v>129707338</v>
       </c>
       <c r="B47" t="n">
-        <v>78844</v>
+        <v>79706</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5150,21 +5158,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5174,10 +5182,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>431881</v>
+        <v>431932</v>
       </c>
       <c r="R47" t="n">
-        <v>6795522</v>
+        <v>6795406</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5236,10 +5244,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129694847</v>
+        <v>129707375</v>
       </c>
       <c r="B48" t="n">
-        <v>79706</v>
+        <v>78844</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5247,21 +5255,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5271,10 +5279,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>431724</v>
+        <v>431881</v>
       </c>
       <c r="R48" t="n">
-        <v>6795460</v>
+        <v>6795522</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5321,22 +5329,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129707351</v>
+        <v>129694847</v>
       </c>
       <c r="B49" t="n">
-        <v>57737</v>
+        <v>79706</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5344,42 +5352,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>431756</v>
+        <v>431724</v>
       </c>
       <c r="R49" t="n">
-        <v>6795202</v>
+        <v>6795460</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5426,19 +5426,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129694926</v>
+        <v>129707351</v>
       </c>
       <c r="B50" t="n">
         <v>57737</v>
@@ -5471,7 +5471,7 @@
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -5481,10 +5481,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>431711</v>
+        <v>431756</v>
       </c>
       <c r="R50" t="n">
-        <v>6795100</v>
+        <v>6795202</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5531,12 +5531,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6433,10 +6433,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129694988</v>
+        <v>129707319</v>
       </c>
       <c r="B60" t="n">
-        <v>79087</v>
+        <v>79706</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6444,21 +6444,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6468,10 +6468,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>431718</v>
+        <v>431708</v>
       </c>
       <c r="R60" t="n">
-        <v>6795068</v>
+        <v>6795371</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6518,22 +6518,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129707319</v>
+        <v>129694961</v>
       </c>
       <c r="B61" t="n">
-        <v>79706</v>
+        <v>78844</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6541,21 +6541,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6565,10 +6565,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>431708</v>
+        <v>431804</v>
       </c>
       <c r="R61" t="n">
-        <v>6795371</v>
+        <v>6795100</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6615,22 +6615,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129694961</v>
+        <v>129694872</v>
       </c>
       <c r="B62" t="n">
-        <v>78844</v>
+        <v>79706</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6638,21 +6638,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6662,10 +6662,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>431804</v>
+        <v>431833</v>
       </c>
       <c r="R62" t="n">
-        <v>6795100</v>
+        <v>6795171</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6724,7 +6724,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129694872</v>
+        <v>129694856</v>
       </c>
       <c r="B63" t="n">
         <v>79706</v>
@@ -6759,10 +6759,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>431833</v>
+        <v>431693</v>
       </c>
       <c r="R63" t="n">
-        <v>6795171</v>
+        <v>6795052</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6821,10 +6821,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129694856</v>
+        <v>129694988</v>
       </c>
       <c r="B64" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6832,21 +6832,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6856,10 +6856,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>431693</v>
+        <v>431718</v>
       </c>
       <c r="R64" t="n">
-        <v>6795052</v>
+        <v>6795068</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -9383,10 +9383,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129694860</v>
+        <v>129707405</v>
       </c>
       <c r="B90" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9394,21 +9394,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9418,10 +9418,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>431746</v>
+        <v>431775</v>
       </c>
       <c r="R90" t="n">
-        <v>6795081</v>
+        <v>6795343</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9468,22 +9468,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129694939</v>
+        <v>129707381</v>
       </c>
       <c r="B91" t="n">
-        <v>57737</v>
+        <v>78844</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9491,21 +9491,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>431913</v>
+        <v>431712</v>
       </c>
       <c r="R91" t="n">
-        <v>6795284</v>
+        <v>6795379</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9553,11 +9553,6 @@
           <t>2025-11-14</t>
         </is>
       </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
@@ -9570,22 +9565,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129694934</v>
+        <v>129694965</v>
       </c>
       <c r="B92" t="n">
-        <v>57737</v>
+        <v>78844</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9593,42 +9588,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>431916</v>
+        <v>431885</v>
       </c>
       <c r="R92" t="n">
-        <v>6795286</v>
+        <v>6795240</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9687,10 +9674,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129707405</v>
+        <v>129694860</v>
       </c>
       <c r="B93" t="n">
-        <v>79087</v>
+        <v>79706</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9698,21 +9685,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9722,10 +9709,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>431775</v>
+        <v>431746</v>
       </c>
       <c r="R93" t="n">
-        <v>6795343</v>
+        <v>6795081</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9772,22 +9759,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129707381</v>
+        <v>129694939</v>
       </c>
       <c r="B94" t="n">
-        <v>78844</v>
+        <v>57737</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9795,21 +9782,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9819,10 +9806,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>431712</v>
+        <v>431913</v>
       </c>
       <c r="R94" t="n">
-        <v>6795379</v>
+        <v>6795284</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9857,6 +9844,11 @@
           <t>2025-11-14</t>
         </is>
       </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
@@ -9869,22 +9861,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129694965</v>
+        <v>129694934</v>
       </c>
       <c r="B95" t="n">
-        <v>78844</v>
+        <v>57737</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9892,34 +9884,42 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>431885</v>
+        <v>431916</v>
       </c>
       <c r="R95" t="n">
-        <v>6795240</v>
+        <v>6795286</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9978,10 +9978,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129694989</v>
+        <v>129694977</v>
       </c>
       <c r="B96" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9989,34 +9989,42 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>431723</v>
+        <v>431933</v>
       </c>
       <c r="R96" t="n">
-        <v>6795090</v>
+        <v>6795295</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10075,10 +10083,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129707312</v>
+        <v>129694989</v>
       </c>
       <c r="B97" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10086,21 +10094,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10110,10 +10118,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>431920</v>
+        <v>431723</v>
       </c>
       <c r="R97" t="n">
-        <v>6795611</v>
+        <v>6795090</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10160,44 +10168,44 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129694941</v>
+        <v>129707312</v>
       </c>
       <c r="B98" t="n">
-        <v>79173</v>
+        <v>79706</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6450</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10207,10 +10215,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>431976</v>
+        <v>431920</v>
       </c>
       <c r="R98" t="n">
-        <v>6795333</v>
+        <v>6795611</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10257,65 +10265,57 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129694977</v>
+        <v>129694941</v>
       </c>
       <c r="B99" t="n">
-        <v>57737</v>
+        <v>79173</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100049</v>
+        <v>6450</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>431933</v>
+        <v>431976</v>
       </c>
       <c r="R99" t="n">
-        <v>6795295</v>
+        <v>6795333</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12532,10 +12532,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129694850</v>
+        <v>129707368</v>
       </c>
       <c r="B122" t="n">
-        <v>79706</v>
+        <v>78845</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12543,34 +12543,37 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>431686</v>
+        <v>431820</v>
       </c>
       <c r="R122" t="n">
-        <v>6795471</v>
+        <v>6795331</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12611,50 +12614,51 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129694881</v>
+        <v>129695013</v>
       </c>
       <c r="B123" t="n">
-        <v>79706</v>
+        <v>92887</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12664,10 +12668,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>431875</v>
+        <v>431869</v>
       </c>
       <c r="R123" t="n">
-        <v>6795212</v>
+        <v>6795173</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12726,10 +12730,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129694888</v>
+        <v>129694997</v>
       </c>
       <c r="B124" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12737,21 +12741,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12761,10 +12765,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>431889</v>
+        <v>431848</v>
       </c>
       <c r="R124" t="n">
-        <v>6795236</v>
+        <v>6795172</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12823,10 +12827,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129707368</v>
+        <v>129694850</v>
       </c>
       <c r="B125" t="n">
-        <v>78845</v>
+        <v>79706</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12834,37 +12838,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Bredvad, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>431820</v>
+        <v>431686</v>
       </c>
       <c r="R125" t="n">
-        <v>6795331</v>
+        <v>6795471</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12905,51 +12906,50 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129695013</v>
+        <v>129694881</v>
       </c>
       <c r="B126" t="n">
-        <v>92887</v>
+        <v>79706</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -12959,10 +12959,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>431869</v>
+        <v>431875</v>
       </c>
       <c r="R126" t="n">
-        <v>6795173</v>
+        <v>6795212</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13021,10 +13021,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129694997</v>
+        <v>129694888</v>
       </c>
       <c r="B127" t="n">
-        <v>79087</v>
+        <v>79706</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13032,21 +13032,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13056,10 +13056,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>431848</v>
+        <v>431889</v>
       </c>
       <c r="R127" t="n">
-        <v>6795172</v>
+        <v>6795236</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14494,10 +14494,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129694876</v>
+        <v>129707366</v>
       </c>
       <c r="B142" t="n">
-        <v>79706</v>
+        <v>78845</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14505,21 +14505,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14529,10 +14529,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>431871</v>
+        <v>431840</v>
       </c>
       <c r="R142" t="n">
-        <v>6795171</v>
+        <v>6795476</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14579,22 +14579,22 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129694887</v>
+        <v>129707377</v>
       </c>
       <c r="B143" t="n">
-        <v>79706</v>
+        <v>78844</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14602,21 +14602,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14626,10 +14626,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>431886</v>
+        <v>431843</v>
       </c>
       <c r="R143" t="n">
-        <v>6795236</v>
+        <v>6795474</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14676,19 +14676,19 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129694880</v>
+        <v>129694876</v>
       </c>
       <c r="B144" t="n">
         <v>79706</v>
@@ -14726,7 +14726,7 @@
         <v>431871</v>
       </c>
       <c r="R144" t="n">
-        <v>6795205</v>
+        <v>6795171</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14785,7 +14785,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129694897</v>
+        <v>129694887</v>
       </c>
       <c r="B145" t="n">
         <v>79706</v>
@@ -14820,10 +14820,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>431906</v>
+        <v>431886</v>
       </c>
       <c r="R145" t="n">
-        <v>6795283</v>
+        <v>6795236</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -14882,10 +14882,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129707377</v>
+        <v>129694880</v>
       </c>
       <c r="B146" t="n">
-        <v>78844</v>
+        <v>79706</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14893,21 +14893,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -14917,10 +14917,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>431843</v>
+        <v>431871</v>
       </c>
       <c r="R146" t="n">
-        <v>6795474</v>
+        <v>6795205</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -14967,22 +14967,22 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129707366</v>
+        <v>